--- a/reports/Passed_Test_Cases.xlsx
+++ b/reports/Passed_Test_Cases.xlsx
@@ -466,7 +466,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>TC-SEL-001</t>
+          <t>TC_WEB_AUTH_001</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -507,7 +507,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>TC-SEL-002</t>
+          <t>TC_WEB_AUTH_002</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -527,7 +527,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0.87</v>
+        <v>0.7</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -548,7 +548,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>TC-SEL-003</t>
+          <t>TC_WEB_AUTH_003</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -568,7 +568,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -577,7 +577,7 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0.93</v>
+        <v>0.82</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -589,7 +589,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>TC-SEL-004</t>
+          <t>TC_WEB_AUTH_004</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -609,7 +609,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -618,7 +618,7 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -630,7 +630,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>TC-SEL-005</t>
+          <t>TC_WEB_AUTH_005</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -650,7 +650,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>0.74</v>
+        <v>0.58</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -671,7 +671,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>TC-SEL-006</t>
+          <t>TC_WEB_AUTH_006</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -691,7 +691,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -700,7 +700,7 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>0.91</v>
+        <v>0.88</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -712,7 +712,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>TC-SEL-007</t>
+          <t>TC_WEB_AUTH_007</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -741,7 +741,7 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>0.96</v>
+        <v>0.61</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -753,7 +753,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>TC-SEL-008</t>
+          <t>TC_WEB_AUTH_008</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -773,7 +773,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -782,7 +782,7 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>0.88</v>
+        <v>0.57</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>TC-SEL-009</t>
+          <t>TC_WEB_AUTH_009</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -814,7 +814,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -823,7 +823,7 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>0.45</v>
+        <v>0.75</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -835,7 +835,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>TC-SEL-010</t>
+          <t>TC_WEB_AUTH_010</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -864,7 +864,7 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>1.09</v>
+        <v>0.46</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -876,7 +876,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>TC-SEL-011</t>
+          <t>TC_WEB_AUTH_011</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -905,7 +905,7 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>0.96</v>
+        <v>0.74</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -917,7 +917,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>TC-SEL-012</t>
+          <t>TC_WEB_AUTH_012</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -937,7 +937,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -946,7 +946,7 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>0.43</v>
+        <v>0.71</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -958,7 +958,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>TC-SEL-013</t>
+          <t>TC_WEB_AUTH_013</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -987,7 +987,7 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>0.78</v>
+        <v>1.06</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>TC-SEL-014</t>
+          <t>TC_WEB_AUTH_014</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1028,7 +1028,7 @@
         </is>
       </c>
       <c r="G15" t="n">
-        <v>0.8</v>
+        <v>0.46</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -1040,7 +1040,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>TC-SEL-015</t>
+          <t>TC_WEB_AUTH_015</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1060,7 +1060,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1069,7 +1069,7 @@
         </is>
       </c>
       <c r="G16" t="n">
-        <v>0.45</v>
+        <v>0.47</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>TC-SEL-016</t>
+          <t>TC_WEB_AUTH_016</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1110,7 +1110,7 @@
         </is>
       </c>
       <c r="G17" t="n">
-        <v>1.05</v>
+        <v>0.65</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>TC-SEL-017</t>
+          <t>TC_WEB_AUTH_017</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1142,7 +1142,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1151,7 +1151,7 @@
         </is>
       </c>
       <c r="G18" t="n">
-        <v>0.72</v>
+        <v>0.86</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>TC-SEL-018</t>
+          <t>TC_WEB_AUTH_018</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1183,7 +1183,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1192,7 +1192,7 @@
         </is>
       </c>
       <c r="G19" t="n">
-        <v>0.66</v>
+        <v>0.46</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -1204,7 +1204,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>TC-SEL-019</t>
+          <t>TC_WEB_AUTH_019</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1224,7 +1224,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1233,7 +1233,7 @@
         </is>
       </c>
       <c r="G20" t="n">
-        <v>0.65</v>
+        <v>1.08</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -1245,7 +1245,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>TC-SEL-020</t>
+          <t>TC_WEB_AUTH_020</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1274,7 +1274,7 @@
         </is>
       </c>
       <c r="G21" t="n">
-        <v>1.07</v>
+        <v>0.73</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -1286,7 +1286,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>TC-SEL-021</t>
+          <t>TC_WEB_AUTH_021</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1306,7 +1306,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1315,7 +1315,7 @@
         </is>
       </c>
       <c r="G22" t="n">
-        <v>0.67</v>
+        <v>0.43</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
@@ -1327,7 +1327,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>TC-SEL-022</t>
+          <t>TC_WEB_AUTH_022</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1356,7 +1356,7 @@
         </is>
       </c>
       <c r="G23" t="n">
-        <v>0.88</v>
+        <v>1.1</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
@@ -1368,7 +1368,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>TC-SEL-023</t>
+          <t>TC_WEB_AUTH_023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1397,7 +1397,7 @@
         </is>
       </c>
       <c r="G24" t="n">
-        <v>0.83</v>
+        <v>0.79</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
@@ -1409,7 +1409,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>TC-SEL-024</t>
+          <t>TC_WEB_AUTH_024</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1438,7 +1438,7 @@
         </is>
       </c>
       <c r="G25" t="n">
-        <v>0.47</v>
+        <v>0.82</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
@@ -1450,7 +1450,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>TC-SEL-025</t>
+          <t>TC_WEB_AUTH_025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1479,7 +1479,7 @@
         </is>
       </c>
       <c r="G26" t="n">
-        <v>0.57</v>
+        <v>0.64</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>TC-SEL-026</t>
+          <t>TC_WEB_AUTH_026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1520,7 +1520,7 @@
         </is>
       </c>
       <c r="G27" t="n">
-        <v>0.68</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
@@ -1532,7 +1532,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>TC-SEL-027</t>
+          <t>TC_WEB_AUTH_027</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1552,7 +1552,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1561,7 +1561,7 @@
         </is>
       </c>
       <c r="G28" t="n">
-        <v>0.62</v>
+        <v>0.79</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
@@ -1573,7 +1573,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>TC-SEL-028</t>
+          <t>TC_WEB_AUTH_028</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1593,7 +1593,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1602,7 +1602,7 @@
         </is>
       </c>
       <c r="G29" t="n">
-        <v>0.85</v>
+        <v>0.87</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
@@ -1614,7 +1614,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>TC-SEL-029</t>
+          <t>TC_WEB_AUTH_029</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1643,7 +1643,7 @@
         </is>
       </c>
       <c r="G30" t="n">
-        <v>0.55</v>
+        <v>1.05</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
@@ -1655,7 +1655,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>TC-SEL-030</t>
+          <t>TC_WEB_AUTH_030</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1675,7 +1675,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1684,7 +1684,7 @@
         </is>
       </c>
       <c r="G31" t="n">
-        <v>0.91</v>
+        <v>0.8</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
@@ -1696,7 +1696,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>TC-SEL-031</t>
+          <t>TC_WEB_AUTH_031</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1716,7 +1716,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1725,7 +1725,7 @@
         </is>
       </c>
       <c r="G32" t="n">
-        <v>1.12</v>
+        <v>0.55</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
@@ -1737,7 +1737,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>TC-SEL-032</t>
+          <t>TC_WEB_AUTH_032</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1766,7 +1766,7 @@
         </is>
       </c>
       <c r="G33" t="n">
-        <v>0.79</v>
+        <v>1.1</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
@@ -1778,7 +1778,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>TC-SEL-033</t>
+          <t>TC_WEB_AUTH_033</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1798,7 +1798,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1807,7 +1807,7 @@
         </is>
       </c>
       <c r="G34" t="n">
-        <v>1.07</v>
+        <v>0.45</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
@@ -1819,7 +1819,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>TC-SEL-034</t>
+          <t>TC_WEB_AUTH_034</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1839,7 +1839,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1848,7 +1848,7 @@
         </is>
       </c>
       <c r="G35" t="n">
-        <v>1.12</v>
+        <v>0.9</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
@@ -1860,7 +1860,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>TC-SEL-035</t>
+          <t>TC_WEB_AUTH_035</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1880,7 +1880,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1889,7 +1889,7 @@
         </is>
       </c>
       <c r="G36" t="n">
-        <v>1.07</v>
+        <v>0.77</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
@@ -1901,7 +1901,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>TC-SEL-036</t>
+          <t>TC_WEB_RBAC_001</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1930,7 +1930,7 @@
         </is>
       </c>
       <c r="G37" t="n">
-        <v>0.6</v>
+        <v>0.98</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
@@ -1942,7 +1942,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>TC-SEL-037</t>
+          <t>TC_WEB_RBAC_002</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1962,7 +1962,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1971,7 +1971,7 @@
         </is>
       </c>
       <c r="G38" t="n">
-        <v>0.95</v>
+        <v>0.55</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
@@ -1983,7 +1983,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>TC-SEL-038</t>
+          <t>TC_WEB_RBAC_003</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2012,7 +2012,7 @@
         </is>
       </c>
       <c r="G39" t="n">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
@@ -2024,7 +2024,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>TC-SEL-039</t>
+          <t>TC_WEB_RBAC_004</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2044,7 +2044,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -2053,7 +2053,7 @@
         </is>
       </c>
       <c r="G40" t="n">
-        <v>0.64</v>
+        <v>0.89</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
@@ -2065,7 +2065,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>TC-SEL-040</t>
+          <t>TC_WEB_RBAC_005</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2085,7 +2085,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -2094,7 +2094,7 @@
         </is>
       </c>
       <c r="G41" t="n">
-        <v>1.06</v>
+        <v>0.54</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
@@ -2106,7 +2106,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>TC-SEL-041</t>
+          <t>TC_WEB_RBAC_006</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2147,7 +2147,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>TC-SEL-042</t>
+          <t>TC_WEB_RBAC_007</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2176,7 +2176,7 @@
         </is>
       </c>
       <c r="G43" t="n">
-        <v>0.5</v>
+        <v>0.58</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
@@ -2188,7 +2188,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>TC-SEL-043</t>
+          <t>TC_WEB_RBAC_008</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2208,7 +2208,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -2217,7 +2217,7 @@
         </is>
       </c>
       <c r="G44" t="n">
-        <v>0.51</v>
+        <v>0.84</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
@@ -2229,7 +2229,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>TC-SEL-044</t>
+          <t>TC_WEB_RBAC_009</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2258,7 +2258,7 @@
         </is>
       </c>
       <c r="G45" t="n">
-        <v>0.86</v>
+        <v>0.88</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
@@ -2270,7 +2270,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>TC-SEL-045</t>
+          <t>TC_WEB_RBAC_010</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2290,7 +2290,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2299,7 +2299,7 @@
         </is>
       </c>
       <c r="G46" t="n">
-        <v>0.76</v>
+        <v>0.92</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
@@ -2311,7 +2311,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>TC-SEL-046</t>
+          <t>TC_WEB_RBAC_011</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2352,7 +2352,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>TC-SEL-047</t>
+          <t>TC_WEB_RBAC_012</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2372,7 +2372,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2381,7 +2381,7 @@
         </is>
       </c>
       <c r="G48" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.99</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
@@ -2393,7 +2393,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>TC-SEL-048</t>
+          <t>TC_WEB_RBAC_013</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2413,7 +2413,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2422,7 +2422,7 @@
         </is>
       </c>
       <c r="G49" t="n">
-        <v>0.82</v>
+        <v>1.02</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
@@ -2434,7 +2434,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>TC-SEL-049</t>
+          <t>TC_WEB_RBAC_014</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2454,7 +2454,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2463,7 +2463,7 @@
         </is>
       </c>
       <c r="G50" t="n">
-        <v>0.49</v>
+        <v>1.04</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>TC-SEL-050</t>
+          <t>TC_WEB_RBAC_015</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2516,7 +2516,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>TC-SEL-051</t>
+          <t>TC_WEB_RBAC_016</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2545,7 +2545,7 @@
         </is>
       </c>
       <c r="G52" t="n">
-        <v>0.96</v>
+        <v>1.08</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
@@ -2557,7 +2557,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>TC-SEL-052</t>
+          <t>TC_WEB_RBAC_017</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2577,7 +2577,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2586,7 +2586,7 @@
         </is>
       </c>
       <c r="G53" t="n">
-        <v>0.78</v>
+        <v>0.76</v>
       </c>
       <c r="H53" t="inlineStr">
         <is>
@@ -2598,7 +2598,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>TC-SEL-053</t>
+          <t>TC_WEB_RBAC_018</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2627,7 +2627,7 @@
         </is>
       </c>
       <c r="G54" t="n">
-        <v>0.83</v>
+        <v>0.55</v>
       </c>
       <c r="H54" t="inlineStr">
         <is>
@@ -2639,7 +2639,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>TC-SEL-054</t>
+          <t>TC_WEB_RBAC_019</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2659,7 +2659,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2668,7 +2668,7 @@
         </is>
       </c>
       <c r="G55" t="n">
-        <v>0.97</v>
+        <v>0.62</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
@@ -2680,7 +2680,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>TC-SEL-055</t>
+          <t>TC_WEB_RBAC_020</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2709,7 +2709,7 @@
         </is>
       </c>
       <c r="G56" t="n">
-        <v>0.66</v>
+        <v>0.98</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
@@ -2721,7 +2721,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>TC-SEL-056</t>
+          <t>TC_WEB_RBAC_021</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2741,7 +2741,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2750,7 +2750,7 @@
         </is>
       </c>
       <c r="G57" t="n">
-        <v>0.74</v>
+        <v>1.13</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
@@ -2762,7 +2762,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>TC-SEL-057</t>
+          <t>TC_WEB_RBAC_022</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2782,7 +2782,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2791,7 +2791,7 @@
         </is>
       </c>
       <c r="G58" t="n">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="H58" t="inlineStr">
         <is>
@@ -2803,7 +2803,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>TC-SEL-058</t>
+          <t>TC_WEB_RBAC_023</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2832,7 +2832,7 @@
         </is>
       </c>
       <c r="G59" t="n">
-        <v>1.14</v>
+        <v>0.78</v>
       </c>
       <c r="H59" t="inlineStr">
         <is>
@@ -2844,7 +2844,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>TC-SEL-059</t>
+          <t>TC_WEB_RBAC_024</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2864,7 +2864,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2873,7 +2873,7 @@
         </is>
       </c>
       <c r="G60" t="n">
-        <v>0.51</v>
+        <v>0.54</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
@@ -2885,7 +2885,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>TC-SEL-060</t>
+          <t>TC_WEB_RBAC_025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2905,7 +2905,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2914,7 +2914,7 @@
         </is>
       </c>
       <c r="G61" t="n">
-        <v>0.99</v>
+        <v>0.54</v>
       </c>
       <c r="H61" t="inlineStr">
         <is>
@@ -2926,7 +2926,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>TC-SEL-061</t>
+          <t>TC_WEB_RBAC_026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2955,7 +2955,7 @@
         </is>
       </c>
       <c r="G62" t="n">
-        <v>0.62</v>
+        <v>0.43</v>
       </c>
       <c r="H62" t="inlineStr">
         <is>
@@ -2967,7 +2967,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>TC-SEL-062</t>
+          <t>TC_WEB_RBAC_027</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2987,7 +2987,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2996,7 +2996,7 @@
         </is>
       </c>
       <c r="G63" t="n">
-        <v>0.52</v>
+        <v>0.91</v>
       </c>
       <c r="H63" t="inlineStr">
         <is>
@@ -3008,7 +3008,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>TC-SEL-063</t>
+          <t>TC_WEB_RBAC_028</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -3037,7 +3037,7 @@
         </is>
       </c>
       <c r="G64" t="n">
-        <v>0.91</v>
+        <v>0.49</v>
       </c>
       <c r="H64" t="inlineStr">
         <is>
@@ -3049,7 +3049,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>TC-SEL-064</t>
+          <t>TC_WEB_RBAC_029</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -3078,7 +3078,7 @@
         </is>
       </c>
       <c r="G65" t="n">
-        <v>1.06</v>
+        <v>0.42</v>
       </c>
       <c r="H65" t="inlineStr">
         <is>
@@ -3090,7 +3090,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>TC-SEL-065</t>
+          <t>TC_WEB_RBAC_030</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -3110,7 +3110,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -3119,7 +3119,7 @@
         </is>
       </c>
       <c r="G66" t="n">
-        <v>0.61</v>
+        <v>0.74</v>
       </c>
       <c r="H66" t="inlineStr">
         <is>
@@ -3131,7 +3131,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>TC-SEL-066</t>
+          <t>TC_WEB_ISSUE_001</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -3160,7 +3160,7 @@
         </is>
       </c>
       <c r="G67" t="n">
-        <v>0.76</v>
+        <v>1.15</v>
       </c>
       <c r="H67" t="inlineStr">
         <is>
@@ -3172,7 +3172,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>TC-SEL-067</t>
+          <t>TC_WEB_ISSUE_002</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -3192,7 +3192,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -3201,7 +3201,7 @@
         </is>
       </c>
       <c r="G68" t="n">
-        <v>0.7</v>
+        <v>0.71</v>
       </c>
       <c r="H68" t="inlineStr">
         <is>
@@ -3213,7 +3213,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>TC-SEL-068</t>
+          <t>TC_WEB_ISSUE_003</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -3233,7 +3233,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -3242,7 +3242,7 @@
         </is>
       </c>
       <c r="G69" t="n">
-        <v>0.68</v>
+        <v>0.91</v>
       </c>
       <c r="H69" t="inlineStr">
         <is>
@@ -3254,7 +3254,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>TC-SEL-069</t>
+          <t>TC_WEB_ISSUE_004</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -3274,7 +3274,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -3283,7 +3283,7 @@
         </is>
       </c>
       <c r="G70" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="H70" t="inlineStr">
         <is>
@@ -3295,7 +3295,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>TC-SEL-070</t>
+          <t>TC_WEB_ISSUE_005</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3315,7 +3315,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -3324,7 +3324,7 @@
         </is>
       </c>
       <c r="G71" t="n">
-        <v>0.53</v>
+        <v>0.45</v>
       </c>
       <c r="H71" t="inlineStr">
         <is>
@@ -3336,7 +3336,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>TC-SEL-071</t>
+          <t>TC_WEB_ISSUE_006</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3365,7 +3365,7 @@
         </is>
       </c>
       <c r="G72" t="n">
-        <v>0.45</v>
+        <v>0.76</v>
       </c>
       <c r="H72" t="inlineStr">
         <is>
@@ -3377,7 +3377,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>TC-SEL-072</t>
+          <t>TC_WEB_ISSUE_007</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3406,7 +3406,7 @@
         </is>
       </c>
       <c r="G73" t="n">
-        <v>0.65</v>
+        <v>0.71</v>
       </c>
       <c r="H73" t="inlineStr">
         <is>
@@ -3418,7 +3418,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>TC-SEL-073</t>
+          <t>TC_WEB_ISSUE_008</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3447,7 +3447,7 @@
         </is>
       </c>
       <c r="G74" t="n">
-        <v>0.8100000000000001</v>
+        <v>1.11</v>
       </c>
       <c r="H74" t="inlineStr">
         <is>
@@ -3459,7 +3459,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>TC-SEL-074</t>
+          <t>TC_WEB_ISSUE_009</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3488,7 +3488,7 @@
         </is>
       </c>
       <c r="G75" t="n">
-        <v>1.14</v>
+        <v>0.83</v>
       </c>
       <c r="H75" t="inlineStr">
         <is>
@@ -3500,7 +3500,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>TC-SEL-075</t>
+          <t>TC_WEB_ISSUE_010</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3520,7 +3520,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3529,7 +3529,7 @@
         </is>
       </c>
       <c r="G76" t="n">
-        <v>0.47</v>
+        <v>1.08</v>
       </c>
       <c r="H76" t="inlineStr">
         <is>
@@ -3541,7 +3541,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>TC-SEL-076</t>
+          <t>TC_WEB_ISSUE_011</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3561,7 +3561,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3570,7 +3570,7 @@
         </is>
       </c>
       <c r="G77" t="n">
-        <v>0.6</v>
+        <v>0.99</v>
       </c>
       <c r="H77" t="inlineStr">
         <is>
@@ -3582,7 +3582,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>TC-SEL-077</t>
+          <t>TC_WEB_ISSUE_012</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3602,7 +3602,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3611,7 +3611,7 @@
         </is>
       </c>
       <c r="G78" t="n">
-        <v>0.72</v>
+        <v>0.49</v>
       </c>
       <c r="H78" t="inlineStr">
         <is>
@@ -3623,7 +3623,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>TC-SEL-078</t>
+          <t>TC_WEB_ISSUE_013</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3643,7 +3643,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3652,7 +3652,7 @@
         </is>
       </c>
       <c r="G79" t="n">
-        <v>0.99</v>
+        <v>0.51</v>
       </c>
       <c r="H79" t="inlineStr">
         <is>
@@ -3664,7 +3664,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>TC-SEL-079</t>
+          <t>TC_WEB_ISSUE_014</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3693,7 +3693,7 @@
         </is>
       </c>
       <c r="G80" t="n">
-        <v>1.09</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H80" t="inlineStr">
         <is>
@@ -3705,7 +3705,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>TC-SEL-080</t>
+          <t>TC_WEB_ISSUE_015</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3725,7 +3725,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3734,7 +3734,7 @@
         </is>
       </c>
       <c r="G81" t="n">
-        <v>0.71</v>
+        <v>1.12</v>
       </c>
       <c r="H81" t="inlineStr">
         <is>
@@ -3746,7 +3746,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>TC-SEL-081</t>
+          <t>TC_WEB_ISSUE_016</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3766,7 +3766,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3775,7 +3775,7 @@
         </is>
       </c>
       <c r="G82" t="n">
-        <v>1.08</v>
+        <v>0.92</v>
       </c>
       <c r="H82" t="inlineStr">
         <is>
@@ -3787,7 +3787,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>TC-SEL-082</t>
+          <t>TC_WEB_ISSUE_017</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3807,7 +3807,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3816,7 +3816,7 @@
         </is>
       </c>
       <c r="G83" t="n">
-        <v>0.99</v>
+        <v>1.03</v>
       </c>
       <c r="H83" t="inlineStr">
         <is>
@@ -3828,7 +3828,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>TC-SEL-083</t>
+          <t>TC_WEB_ISSUE_018</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3848,7 +3848,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3857,7 +3857,7 @@
         </is>
       </c>
       <c r="G84" t="n">
-        <v>0.71</v>
+        <v>0.64</v>
       </c>
       <c r="H84" t="inlineStr">
         <is>
@@ -3869,7 +3869,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>TC-SEL-084</t>
+          <t>TC_WEB_ISSUE_019</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3898,7 +3898,7 @@
         </is>
       </c>
       <c r="G85" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="H85" t="inlineStr">
         <is>
@@ -3910,7 +3910,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>TC-SEL-085</t>
+          <t>TC_WEB_ISSUE_020</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3930,7 +3930,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3939,7 +3939,7 @@
         </is>
       </c>
       <c r="G86" t="n">
-        <v>1.15</v>
+        <v>0.49</v>
       </c>
       <c r="H86" t="inlineStr">
         <is>
@@ -3951,7 +3951,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>TC-SEL-086</t>
+          <t>TC_WEB_ISSUE_021</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3980,7 +3980,7 @@
         </is>
       </c>
       <c r="G87" t="n">
-        <v>0.49</v>
+        <v>1</v>
       </c>
       <c r="H87" t="inlineStr">
         <is>
@@ -3992,7 +3992,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>TC-SEL-087</t>
+          <t>TC_WEB_ISSUE_022</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -4012,7 +4012,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -4021,7 +4021,7 @@
         </is>
       </c>
       <c r="G88" t="n">
-        <v>0.84</v>
+        <v>0.68</v>
       </c>
       <c r="H88" t="inlineStr">
         <is>
@@ -4033,7 +4033,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>TC-SEL-088</t>
+          <t>TC_WEB_ISSUE_023</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -4053,7 +4053,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -4062,7 +4062,7 @@
         </is>
       </c>
       <c r="G89" t="n">
-        <v>1.13</v>
+        <v>0.48</v>
       </c>
       <c r="H89" t="inlineStr">
         <is>
@@ -4074,7 +4074,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>TC-SEL-089</t>
+          <t>TC_WEB_ISSUE_024</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -4094,7 +4094,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -4103,7 +4103,7 @@
         </is>
       </c>
       <c r="G90" t="n">
-        <v>0.91</v>
+        <v>0.75</v>
       </c>
       <c r="H90" t="inlineStr">
         <is>
@@ -4115,7 +4115,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>TC-SEL-090</t>
+          <t>TC_WEB_ISSUE_025</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -4135,7 +4135,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -4144,7 +4144,7 @@
         </is>
       </c>
       <c r="G91" t="n">
-        <v>0.53</v>
+        <v>0.74</v>
       </c>
       <c r="H91" t="inlineStr">
         <is>
@@ -4156,7 +4156,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>TC-SEL-091</t>
+          <t>TC_WEB_ISSUE_026</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -4185,7 +4185,7 @@
         </is>
       </c>
       <c r="G92" t="n">
-        <v>0.43</v>
+        <v>1</v>
       </c>
       <c r="H92" t="inlineStr">
         <is>
@@ -4197,7 +4197,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>TC-SEL-092</t>
+          <t>TC_WEB_ISSUE_027</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -4226,7 +4226,7 @@
         </is>
       </c>
       <c r="G93" t="n">
-        <v>1.05</v>
+        <v>0.44</v>
       </c>
       <c r="H93" t="inlineStr">
         <is>
@@ -4238,7 +4238,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>TC-SEL-093</t>
+          <t>TC_WEB_ISSUE_028</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -4258,7 +4258,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -4267,7 +4267,7 @@
         </is>
       </c>
       <c r="G94" t="n">
-        <v>0.84</v>
+        <v>0.86</v>
       </c>
       <c r="H94" t="inlineStr">
         <is>
@@ -4279,7 +4279,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>TC-SEL-094</t>
+          <t>TC_WEB_ISSUE_029</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -4299,7 +4299,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -4308,7 +4308,7 @@
         </is>
       </c>
       <c r="G95" t="n">
-        <v>0.99</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H95" t="inlineStr">
         <is>
@@ -4320,7 +4320,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>TC-SEL-095</t>
+          <t>TC_WEB_ISSUE_030</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -4340,7 +4340,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -4361,7 +4361,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>TC-SEL-096</t>
+          <t>TC_WEB_ISSUE_031</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -4381,7 +4381,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -4390,7 +4390,7 @@
         </is>
       </c>
       <c r="G97" t="n">
-        <v>1.14</v>
+        <v>0.54</v>
       </c>
       <c r="H97" t="inlineStr">
         <is>
@@ -4402,7 +4402,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>TC-SEL-097</t>
+          <t>TC_WEB_ISSUE_032</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -4422,7 +4422,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -4431,7 +4431,7 @@
         </is>
       </c>
       <c r="G98" t="n">
-        <v>0.8</v>
+        <v>0.93</v>
       </c>
       <c r="H98" t="inlineStr">
         <is>
@@ -4443,7 +4443,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>TC-SEL-098</t>
+          <t>TC_WEB_ISSUE_033</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -4463,7 +4463,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -4472,7 +4472,7 @@
         </is>
       </c>
       <c r="G99" t="n">
-        <v>0.78</v>
+        <v>0.45</v>
       </c>
       <c r="H99" t="inlineStr">
         <is>
@@ -4484,7 +4484,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>TC-SEL-099</t>
+          <t>TC_WEB_ISSUE_034</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -4504,7 +4504,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -4513,7 +4513,7 @@
         </is>
       </c>
       <c r="G100" t="n">
-        <v>1.12</v>
+        <v>0.42</v>
       </c>
       <c r="H100" t="inlineStr">
         <is>
@@ -4525,7 +4525,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>TC-SEL-100</t>
+          <t>TC_WEB_ISSUE_035</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -4545,7 +4545,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -4554,7 +4554,7 @@
         </is>
       </c>
       <c r="G101" t="n">
-        <v>0.53</v>
+        <v>1.06</v>
       </c>
       <c r="H101" t="inlineStr">
         <is>
@@ -4566,7 +4566,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>TC-SEL-101</t>
+          <t>TC_WEB_BATCH_001</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -4586,7 +4586,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -4595,7 +4595,7 @@
         </is>
       </c>
       <c r="G102" t="n">
-        <v>0.44</v>
+        <v>1</v>
       </c>
       <c r="H102" t="inlineStr">
         <is>
@@ -4607,7 +4607,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>TC-SEL-102</t>
+          <t>TC_WEB_BATCH_002</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -4636,7 +4636,7 @@
         </is>
       </c>
       <c r="G103" t="n">
-        <v>0.54</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H103" t="inlineStr">
         <is>
@@ -4648,7 +4648,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>TC-SEL-103</t>
+          <t>TC_WEB_BATCH_003</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -4668,7 +4668,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4677,7 +4677,7 @@
         </is>
       </c>
       <c r="G104" t="n">
-        <v>0.71</v>
+        <v>1</v>
       </c>
       <c r="H104" t="inlineStr">
         <is>
@@ -4689,7 +4689,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>TC-SEL-104</t>
+          <t>TC_WEB_BATCH_004</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -4709,7 +4709,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4718,7 +4718,7 @@
         </is>
       </c>
       <c r="G105" t="n">
-        <v>0.72</v>
+        <v>0.46</v>
       </c>
       <c r="H105" t="inlineStr">
         <is>
@@ -4730,7 +4730,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>TC-SEL-105</t>
+          <t>TC_WEB_BATCH_005</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -4759,7 +4759,7 @@
         </is>
       </c>
       <c r="G106" t="n">
-        <v>0.63</v>
+        <v>0.9</v>
       </c>
       <c r="H106" t="inlineStr">
         <is>
@@ -4771,7 +4771,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>TC-SEL-106</t>
+          <t>TC_WEB_BATCH_006</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -4800,7 +4800,7 @@
         </is>
       </c>
       <c r="G107" t="n">
-        <v>0.87</v>
+        <v>0.66</v>
       </c>
       <c r="H107" t="inlineStr">
         <is>
@@ -4812,7 +4812,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>TC-SEL-107</t>
+          <t>TC_WEB_BATCH_007</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -4832,7 +4832,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4841,7 +4841,7 @@
         </is>
       </c>
       <c r="G108" t="n">
-        <v>0.82</v>
+        <v>0.98</v>
       </c>
       <c r="H108" t="inlineStr">
         <is>
@@ -4853,7 +4853,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>TC-SEL-108</t>
+          <t>TC_WEB_BATCH_008</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -4882,7 +4882,7 @@
         </is>
       </c>
       <c r="G109" t="n">
-        <v>0.73</v>
+        <v>0.47</v>
       </c>
       <c r="H109" t="inlineStr">
         <is>
@@ -4894,7 +4894,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>TC-SEL-109</t>
+          <t>TC_WEB_BATCH_009</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -4923,7 +4923,7 @@
         </is>
       </c>
       <c r="G110" t="n">
-        <v>1.14</v>
+        <v>0.66</v>
       </c>
       <c r="H110" t="inlineStr">
         <is>
@@ -4935,7 +4935,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>TC-SEL-110</t>
+          <t>TC_WEB_BATCH_010</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -4955,7 +4955,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4964,7 +4964,7 @@
         </is>
       </c>
       <c r="G111" t="n">
-        <v>0.85</v>
+        <v>1.15</v>
       </c>
       <c r="H111" t="inlineStr">
         <is>
@@ -4976,7 +4976,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>TC-SEL-111</t>
+          <t>TC_WEB_BATCH_011</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -4996,7 +4996,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -5005,7 +5005,7 @@
         </is>
       </c>
       <c r="G112" t="n">
-        <v>1.03</v>
+        <v>0.67</v>
       </c>
       <c r="H112" t="inlineStr">
         <is>
@@ -5017,7 +5017,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>TC-SEL-112</t>
+          <t>TC_WEB_BATCH_012</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -5037,7 +5037,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -5046,7 +5046,7 @@
         </is>
       </c>
       <c r="G113" t="n">
-        <v>0.44</v>
+        <v>0.7</v>
       </c>
       <c r="H113" t="inlineStr">
         <is>
@@ -5058,7 +5058,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>TC-SEL-113</t>
+          <t>TC_WEB_BATCH_013</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -5078,7 +5078,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -5087,7 +5087,7 @@
         </is>
       </c>
       <c r="G114" t="n">
-        <v>0.98</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H114" t="inlineStr">
         <is>
@@ -5099,7 +5099,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>TC-SEL-114</t>
+          <t>TC_WEB_BATCH_014</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -5119,7 +5119,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -5128,7 +5128,7 @@
         </is>
       </c>
       <c r="G115" t="n">
-        <v>0.98</v>
+        <v>0.72</v>
       </c>
       <c r="H115" t="inlineStr">
         <is>
@@ -5140,7 +5140,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>TC-SEL-115</t>
+          <t>TC_WEB_BATCH_015</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -5169,7 +5169,7 @@
         </is>
       </c>
       <c r="G116" t="n">
-        <v>0.64</v>
+        <v>0.88</v>
       </c>
       <c r="H116" t="inlineStr">
         <is>
@@ -5181,7 +5181,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>TC-SEL-116</t>
+          <t>TC_WEB_BATCH_016</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -5210,7 +5210,7 @@
         </is>
       </c>
       <c r="G117" t="n">
-        <v>0.71</v>
+        <v>0.53</v>
       </c>
       <c r="H117" t="inlineStr">
         <is>
@@ -5222,7 +5222,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>TC-SEL-117</t>
+          <t>TC_WEB_BATCH_017</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -5251,7 +5251,7 @@
         </is>
       </c>
       <c r="G118" t="n">
-        <v>0.96</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H118" t="inlineStr">
         <is>
@@ -5263,7 +5263,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>TC-SEL-118</t>
+          <t>TC_WEB_BATCH_018</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -5292,7 +5292,7 @@
         </is>
       </c>
       <c r="G119" t="n">
-        <v>0.98</v>
+        <v>0.43</v>
       </c>
       <c r="H119" t="inlineStr">
         <is>
@@ -5304,7 +5304,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>TC-SEL-119</t>
+          <t>TC_WEB_BATCH_019</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -5324,7 +5324,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -5333,7 +5333,7 @@
         </is>
       </c>
       <c r="G120" t="n">
-        <v>0.57</v>
+        <v>0.73</v>
       </c>
       <c r="H120" t="inlineStr">
         <is>
@@ -5345,7 +5345,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>TC-SEL-120</t>
+          <t>TC_WEB_BATCH_020</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -5365,7 +5365,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -5374,7 +5374,7 @@
         </is>
       </c>
       <c r="G121" t="n">
-        <v>0.89</v>
+        <v>0.63</v>
       </c>
       <c r="H121" t="inlineStr">
         <is>
@@ -5386,7 +5386,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>TC-SEL-121</t>
+          <t>TC_WEB_BATCH_021</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -5415,7 +5415,7 @@
         </is>
       </c>
       <c r="G122" t="n">
-        <v>0.88</v>
+        <v>0.48</v>
       </c>
       <c r="H122" t="inlineStr">
         <is>
@@ -5427,7 +5427,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>TC-SEL-122</t>
+          <t>TC_WEB_BATCH_022</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -5456,7 +5456,7 @@
         </is>
       </c>
       <c r="G123" t="n">
-        <v>0.52</v>
+        <v>0.47</v>
       </c>
       <c r="H123" t="inlineStr">
         <is>
@@ -5468,7 +5468,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>TC-SEL-123</t>
+          <t>TC_WEB_BATCH_023</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -5488,7 +5488,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -5509,7 +5509,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>TC-SEL-124</t>
+          <t>TC_WEB_BATCH_024</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -5529,7 +5529,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -5538,7 +5538,7 @@
         </is>
       </c>
       <c r="G125" t="n">
-        <v>0.7</v>
+        <v>0.66</v>
       </c>
       <c r="H125" t="inlineStr">
         <is>
@@ -5550,7 +5550,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>TC-SEL-125</t>
+          <t>TC_WEB_BATCH_025</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -5570,7 +5570,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -5579,7 +5579,7 @@
         </is>
       </c>
       <c r="G126" t="n">
-        <v>0.51</v>
+        <v>0.61</v>
       </c>
       <c r="H126" t="inlineStr">
         <is>
@@ -5591,7 +5591,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>TC-SEL-126</t>
+          <t>TC_WEB_BATCH_026</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -5611,7 +5611,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -5620,7 +5620,7 @@
         </is>
       </c>
       <c r="G127" t="n">
-        <v>0.57</v>
+        <v>0.72</v>
       </c>
       <c r="H127" t="inlineStr">
         <is>
@@ -5632,7 +5632,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>TC-SEL-127</t>
+          <t>TC_WEB_BATCH_027</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -5652,7 +5652,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -5661,7 +5661,7 @@
         </is>
       </c>
       <c r="G128" t="n">
-        <v>0.87</v>
+        <v>1.05</v>
       </c>
       <c r="H128" t="inlineStr">
         <is>
@@ -5673,7 +5673,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>TC-SEL-128</t>
+          <t>TC_WEB_BATCH_028</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -5693,7 +5693,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -5702,7 +5702,7 @@
         </is>
       </c>
       <c r="G129" t="n">
-        <v>0.92</v>
+        <v>0.57</v>
       </c>
       <c r="H129" t="inlineStr">
         <is>
@@ -5714,7 +5714,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>TC-SEL-129</t>
+          <t>TC_WEB_BATCH_029</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -5734,7 +5734,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -5743,7 +5743,7 @@
         </is>
       </c>
       <c r="G130" t="n">
-        <v>0.67</v>
+        <v>0.75</v>
       </c>
       <c r="H130" t="inlineStr">
         <is>
@@ -5755,7 +5755,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>TC-SEL-130</t>
+          <t>TC_WEB_BATCH_030</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -5775,7 +5775,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -5784,7 +5784,7 @@
         </is>
       </c>
       <c r="G131" t="n">
-        <v>0.85</v>
+        <v>1.08</v>
       </c>
       <c r="H131" t="inlineStr">
         <is>
@@ -5796,7 +5796,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>TC-SEL-131</t>
+          <t>TC_WEB_VERIFY_001</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -5816,7 +5816,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -5825,7 +5825,7 @@
         </is>
       </c>
       <c r="G132" t="n">
-        <v>0.66</v>
+        <v>1</v>
       </c>
       <c r="H132" t="inlineStr">
         <is>
@@ -5837,7 +5837,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>TC-SEL-132</t>
+          <t>TC_WEB_VERIFY_002</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -5857,7 +5857,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -5866,7 +5866,7 @@
         </is>
       </c>
       <c r="G133" t="n">
-        <v>0.83</v>
+        <v>1.07</v>
       </c>
       <c r="H133" t="inlineStr">
         <is>
@@ -5878,7 +5878,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>TC-SEL-133</t>
+          <t>TC_WEB_VERIFY_003</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -5898,7 +5898,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -5907,7 +5907,7 @@
         </is>
       </c>
       <c r="G134" t="n">
-        <v>0.76</v>
+        <v>0.78</v>
       </c>
       <c r="H134" t="inlineStr">
         <is>
@@ -5919,7 +5919,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>TC-SEL-134</t>
+          <t>TC_WEB_VERIFY_004</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -5939,7 +5939,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -5948,7 +5948,7 @@
         </is>
       </c>
       <c r="G135" t="n">
-        <v>0.92</v>
+        <v>0.83</v>
       </c>
       <c r="H135" t="inlineStr">
         <is>
@@ -5960,7 +5960,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>TC-SEL-135</t>
+          <t>TC_WEB_VERIFY_005</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -5989,7 +5989,7 @@
         </is>
       </c>
       <c r="G136" t="n">
-        <v>0.96</v>
+        <v>0.44</v>
       </c>
       <c r="H136" t="inlineStr">
         <is>
@@ -6001,7 +6001,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>TC-SEL-136</t>
+          <t>TC_WEB_VERIFY_006</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -6021,7 +6021,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -6030,7 +6030,7 @@
         </is>
       </c>
       <c r="G137" t="n">
-        <v>0.76</v>
+        <v>0.78</v>
       </c>
       <c r="H137" t="inlineStr">
         <is>
@@ -6042,7 +6042,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>TC-SEL-137</t>
+          <t>TC_WEB_VERIFY_007</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -6062,7 +6062,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -6071,7 +6071,7 @@
         </is>
       </c>
       <c r="G138" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H138" t="inlineStr">
         <is>
@@ -6083,7 +6083,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>TC-SEL-138</t>
+          <t>TC_WEB_VERIFY_008</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -6112,7 +6112,7 @@
         </is>
       </c>
       <c r="G139" t="n">
-        <v>0.59</v>
+        <v>1.05</v>
       </c>
       <c r="H139" t="inlineStr">
         <is>
@@ -6124,7 +6124,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>TC-SEL-139</t>
+          <t>TC_WEB_VERIFY_009</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -6144,7 +6144,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -6153,7 +6153,7 @@
         </is>
       </c>
       <c r="G140" t="n">
-        <v>1.09</v>
+        <v>0.54</v>
       </c>
       <c r="H140" t="inlineStr">
         <is>
@@ -6165,7 +6165,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>TC-SEL-140</t>
+          <t>TC_WEB_VERIFY_010</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -6185,7 +6185,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -6194,7 +6194,7 @@
         </is>
       </c>
       <c r="G141" t="n">
-        <v>0.86</v>
+        <v>0.61</v>
       </c>
       <c r="H141" t="inlineStr">
         <is>
@@ -6206,7 +6206,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>TC-SEL-141</t>
+          <t>TC_WEB_VERIFY_011</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -6226,7 +6226,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -6235,7 +6235,7 @@
         </is>
       </c>
       <c r="G142" t="n">
-        <v>0.61</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H142" t="inlineStr">
         <is>
@@ -6247,7 +6247,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>TC-SEL-142</t>
+          <t>TC_WEB_VERIFY_012</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -6267,7 +6267,7 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -6276,7 +6276,7 @@
         </is>
       </c>
       <c r="G143" t="n">
-        <v>0.91</v>
+        <v>1.09</v>
       </c>
       <c r="H143" t="inlineStr">
         <is>
@@ -6288,7 +6288,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>TC-SEL-143</t>
+          <t>TC_WEB_VERIFY_013</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -6317,7 +6317,7 @@
         </is>
       </c>
       <c r="G144" t="n">
-        <v>0.44</v>
+        <v>1.12</v>
       </c>
       <c r="H144" t="inlineStr">
         <is>
@@ -6329,7 +6329,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>TC-SEL-144</t>
+          <t>TC_WEB_VERIFY_014</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -6358,7 +6358,7 @@
         </is>
       </c>
       <c r="G145" t="n">
-        <v>1</v>
+        <v>0.43</v>
       </c>
       <c r="H145" t="inlineStr">
         <is>
@@ -6370,7 +6370,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>TC-SEL-145</t>
+          <t>TC_WEB_VERIFY_015</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -6390,7 +6390,7 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
@@ -6399,7 +6399,7 @@
         </is>
       </c>
       <c r="G146" t="n">
-        <v>1.12</v>
+        <v>0.98</v>
       </c>
       <c r="H146" t="inlineStr">
         <is>
@@ -6411,7 +6411,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>TC-SEL-146</t>
+          <t>TC_WEB_VERIFY_016</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -6431,7 +6431,7 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
@@ -6452,7 +6452,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>TC-SEL-147</t>
+          <t>TC_WEB_VERIFY_017</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -6481,7 +6481,7 @@
         </is>
       </c>
       <c r="G148" t="n">
-        <v>0.85</v>
+        <v>1.08</v>
       </c>
       <c r="H148" t="inlineStr">
         <is>
@@ -6493,7 +6493,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>TC-SEL-148</t>
+          <t>TC_WEB_VERIFY_018</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -6513,7 +6513,7 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
@@ -6522,7 +6522,7 @@
         </is>
       </c>
       <c r="G149" t="n">
-        <v>0.6</v>
+        <v>1.14</v>
       </c>
       <c r="H149" t="inlineStr">
         <is>
@@ -6534,7 +6534,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>TC-SEL-149</t>
+          <t>TC_WEB_VERIFY_019</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -6554,7 +6554,7 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
@@ -6563,7 +6563,7 @@
         </is>
       </c>
       <c r="G150" t="n">
-        <v>0.97</v>
+        <v>0.66</v>
       </c>
       <c r="H150" t="inlineStr">
         <is>
@@ -6575,7 +6575,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>TC-SEL-150</t>
+          <t>TC_WEB_VERIFY_020</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -6595,7 +6595,7 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
@@ -6604,7 +6604,7 @@
         </is>
       </c>
       <c r="G151" t="n">
-        <v>0.6</v>
+        <v>0.86</v>
       </c>
       <c r="H151" t="inlineStr">
         <is>
@@ -6616,7 +6616,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>TC-SEL-151</t>
+          <t>TC_WEB_VERIFY_021</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -6645,7 +6645,7 @@
         </is>
       </c>
       <c r="G152" t="n">
-        <v>0.73</v>
+        <v>0.86</v>
       </c>
       <c r="H152" t="inlineStr">
         <is>
@@ -6657,7 +6657,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>TC-SEL-152</t>
+          <t>TC_WEB_VERIFY_022</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -6686,7 +6686,7 @@
         </is>
       </c>
       <c r="G153" t="n">
-        <v>0.59</v>
+        <v>1.12</v>
       </c>
       <c r="H153" t="inlineStr">
         <is>
@@ -6698,7 +6698,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>TC-SEL-153</t>
+          <t>TC_WEB_VERIFY_023</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -6718,7 +6718,7 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
@@ -6727,7 +6727,7 @@
         </is>
       </c>
       <c r="G154" t="n">
-        <v>0.79</v>
+        <v>0.83</v>
       </c>
       <c r="H154" t="inlineStr">
         <is>
@@ -6739,7 +6739,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>TC-SEL-154</t>
+          <t>TC_WEB_VERIFY_024</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -6759,7 +6759,7 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
@@ -6768,7 +6768,7 @@
         </is>
       </c>
       <c r="G155" t="n">
-        <v>1.12</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H155" t="inlineStr">
         <is>
@@ -6780,7 +6780,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>TC-SEL-155</t>
+          <t>TC_WEB_VERIFY_025</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -6800,7 +6800,7 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
@@ -6809,7 +6809,7 @@
         </is>
       </c>
       <c r="G156" t="n">
-        <v>0.8</v>
+        <v>1.07</v>
       </c>
       <c r="H156" t="inlineStr">
         <is>
@@ -6821,7 +6821,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>TC-SEL-156</t>
+          <t>TC_WEB_VERIFY_026</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -6841,7 +6841,7 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
@@ -6850,7 +6850,7 @@
         </is>
       </c>
       <c r="G157" t="n">
-        <v>1.12</v>
+        <v>0.87</v>
       </c>
       <c r="H157" t="inlineStr">
         <is>
@@ -6862,7 +6862,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>TC-SEL-157</t>
+          <t>TC_WEB_VERIFY_027</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -6891,7 +6891,7 @@
         </is>
       </c>
       <c r="G158" t="n">
-        <v>0.58</v>
+        <v>0.93</v>
       </c>
       <c r="H158" t="inlineStr">
         <is>
@@ -6903,7 +6903,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>TC-SEL-158</t>
+          <t>TC_WEB_VERIFY_028</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -6923,7 +6923,7 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
@@ -6932,7 +6932,7 @@
         </is>
       </c>
       <c r="G159" t="n">
-        <v>0.64</v>
+        <v>0.63</v>
       </c>
       <c r="H159" t="inlineStr">
         <is>
@@ -6944,7 +6944,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>TC-SEL-159</t>
+          <t>TC_WEB_VERIFY_029</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -6964,7 +6964,7 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
@@ -6973,7 +6973,7 @@
         </is>
       </c>
       <c r="G160" t="n">
-        <v>0.54</v>
+        <v>1.04</v>
       </c>
       <c r="H160" t="inlineStr">
         <is>
@@ -6985,7 +6985,7 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>TC-SEL-160</t>
+          <t>TC_WEB_VERIFY_030</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -7005,7 +7005,7 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
@@ -7014,7 +7014,7 @@
         </is>
       </c>
       <c r="G161" t="n">
-        <v>0.46</v>
+        <v>0.79</v>
       </c>
       <c r="H161" t="inlineStr">
         <is>
@@ -7026,7 +7026,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>TC-SEL-161</t>
+          <t>TC_WEB_VERIFY_031</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -7046,7 +7046,7 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
@@ -7055,7 +7055,7 @@
         </is>
       </c>
       <c r="G162" t="n">
-        <v>0.64</v>
+        <v>0.83</v>
       </c>
       <c r="H162" t="inlineStr">
         <is>
@@ -7067,7 +7067,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>TC-SEL-162</t>
+          <t>TC_WEB_VERIFY_032</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -7096,7 +7096,7 @@
         </is>
       </c>
       <c r="G163" t="n">
-        <v>1.14</v>
+        <v>0.86</v>
       </c>
       <c r="H163" t="inlineStr">
         <is>
@@ -7108,7 +7108,7 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>TC-SEL-163</t>
+          <t>TC_WEB_VERIFY_033</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -7128,7 +7128,7 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
@@ -7137,7 +7137,7 @@
         </is>
       </c>
       <c r="G164" t="n">
-        <v>0.99</v>
+        <v>1.11</v>
       </c>
       <c r="H164" t="inlineStr">
         <is>
@@ -7149,7 +7149,7 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>TC-SEL-164</t>
+          <t>TC_WEB_VERIFY_034</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -7169,7 +7169,7 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
@@ -7178,7 +7178,7 @@
         </is>
       </c>
       <c r="G165" t="n">
-        <v>0.84</v>
+        <v>0.71</v>
       </c>
       <c r="H165" t="inlineStr">
         <is>
@@ -7190,7 +7190,7 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>TC-SEL-165</t>
+          <t>TC_WEB_VERIFY_035</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -7210,7 +7210,7 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
@@ -7219,7 +7219,7 @@
         </is>
       </c>
       <c r="G166" t="n">
-        <v>0.64</v>
+        <v>0.75</v>
       </c>
       <c r="H166" t="inlineStr">
         <is>
@@ -7231,7 +7231,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>TC-SEL-166</t>
+          <t>TC_WEB_DASH_001</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -7260,7 +7260,7 @@
         </is>
       </c>
       <c r="G167" t="n">
-        <v>0.58</v>
+        <v>0.46</v>
       </c>
       <c r="H167" t="inlineStr">
         <is>
@@ -7272,7 +7272,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>TC-SEL-167</t>
+          <t>TC_WEB_DASH_002</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -7301,7 +7301,7 @@
         </is>
       </c>
       <c r="G168" t="n">
-        <v>0.59</v>
+        <v>0.98</v>
       </c>
       <c r="H168" t="inlineStr">
         <is>
@@ -7313,7 +7313,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>TC-SEL-168</t>
+          <t>TC_WEB_DASH_003</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -7333,7 +7333,7 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
@@ -7342,7 +7342,7 @@
         </is>
       </c>
       <c r="G169" t="n">
-        <v>0.76</v>
+        <v>1.01</v>
       </c>
       <c r="H169" t="inlineStr">
         <is>
@@ -7354,7 +7354,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>TC-SEL-169</t>
+          <t>TC_WEB_DASH_004</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -7374,7 +7374,7 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
@@ -7383,7 +7383,7 @@
         </is>
       </c>
       <c r="G170" t="n">
-        <v>0.98</v>
+        <v>0.48</v>
       </c>
       <c r="H170" t="inlineStr">
         <is>
@@ -7395,7 +7395,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>TC-SEL-170</t>
+          <t>TC_WEB_DASH_005</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -7415,7 +7415,7 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
@@ -7424,7 +7424,7 @@
         </is>
       </c>
       <c r="G171" t="n">
-        <v>1</v>
+        <v>0.54</v>
       </c>
       <c r="H171" t="inlineStr">
         <is>
@@ -7436,7 +7436,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>TC-SEL-171</t>
+          <t>TC_WEB_DASH_006</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -7456,7 +7456,7 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
@@ -7465,7 +7465,7 @@
         </is>
       </c>
       <c r="G172" t="n">
-        <v>0.89</v>
+        <v>1</v>
       </c>
       <c r="H172" t="inlineStr">
         <is>
@@ -7477,7 +7477,7 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>TC-SEL-172</t>
+          <t>TC_WEB_DASH_007</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -7497,7 +7497,7 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
@@ -7506,7 +7506,7 @@
         </is>
       </c>
       <c r="G173" t="n">
-        <v>0.95</v>
+        <v>0.55</v>
       </c>
       <c r="H173" t="inlineStr">
         <is>
@@ -7518,7 +7518,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>TC-SEL-173</t>
+          <t>TC_WEB_DASH_008</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -7538,7 +7538,7 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
@@ -7547,7 +7547,7 @@
         </is>
       </c>
       <c r="G174" t="n">
-        <v>0.73</v>
+        <v>0.54</v>
       </c>
       <c r="H174" t="inlineStr">
         <is>
@@ -7559,7 +7559,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>TC-SEL-174</t>
+          <t>TC_WEB_DASH_009</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -7579,7 +7579,7 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
@@ -7588,7 +7588,7 @@
         </is>
       </c>
       <c r="G175" t="n">
-        <v>0.79</v>
+        <v>0.62</v>
       </c>
       <c r="H175" t="inlineStr">
         <is>
@@ -7600,7 +7600,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>TC-SEL-175</t>
+          <t>TC_WEB_DASH_010</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -7629,7 +7629,7 @@
         </is>
       </c>
       <c r="G176" t="n">
-        <v>0.66</v>
+        <v>0.89</v>
       </c>
       <c r="H176" t="inlineStr">
         <is>
@@ -7641,7 +7641,7 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>TC-SEL-176</t>
+          <t>TC_WEB_DASH_011</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -7661,7 +7661,7 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
@@ -7670,7 +7670,7 @@
         </is>
       </c>
       <c r="G177" t="n">
-        <v>1.13</v>
+        <v>0.59</v>
       </c>
       <c r="H177" t="inlineStr">
         <is>
@@ -7682,7 +7682,7 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>TC-SEL-177</t>
+          <t>TC_WEB_DASH_012</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -7702,7 +7702,7 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
@@ -7711,7 +7711,7 @@
         </is>
       </c>
       <c r="G178" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="H178" t="inlineStr">
         <is>
@@ -7723,7 +7723,7 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>TC-SEL-178</t>
+          <t>TC_WEB_DASH_013</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -7743,7 +7743,7 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
@@ -7752,7 +7752,7 @@
         </is>
       </c>
       <c r="G179" t="n">
-        <v>1.13</v>
+        <v>0.74</v>
       </c>
       <c r="H179" t="inlineStr">
         <is>
@@ -7764,7 +7764,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>TC-SEL-179</t>
+          <t>TC_WEB_DASH_014</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -7784,7 +7784,7 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
@@ -7793,7 +7793,7 @@
         </is>
       </c>
       <c r="G180" t="n">
-        <v>0.58</v>
+        <v>0.43</v>
       </c>
       <c r="H180" t="inlineStr">
         <is>
@@ -7805,7 +7805,7 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>TC-SEL-180</t>
+          <t>TC_WEB_DASH_015</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -7834,7 +7834,7 @@
         </is>
       </c>
       <c r="G181" t="n">
-        <v>1.01</v>
+        <v>0.6</v>
       </c>
       <c r="H181" t="inlineStr">
         <is>
@@ -7846,7 +7846,7 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>TC-SEL-181</t>
+          <t>TC_WEB_DASH_016</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -7875,7 +7875,7 @@
         </is>
       </c>
       <c r="G182" t="n">
-        <v>0.51</v>
+        <v>0.62</v>
       </c>
       <c r="H182" t="inlineStr">
         <is>
@@ -7887,7 +7887,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>TC-SEL-182</t>
+          <t>TC_WEB_DASH_017</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -7907,7 +7907,7 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
@@ -7916,7 +7916,7 @@
         </is>
       </c>
       <c r="G183" t="n">
-        <v>0.65</v>
+        <v>0.55</v>
       </c>
       <c r="H183" t="inlineStr">
         <is>
@@ -7928,7 +7928,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>TC-SEL-183</t>
+          <t>TC_WEB_DASH_018</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -7948,7 +7948,7 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
@@ -7957,7 +7957,7 @@
         </is>
       </c>
       <c r="G184" t="n">
-        <v>1.01</v>
+        <v>0.87</v>
       </c>
       <c r="H184" t="inlineStr">
         <is>
@@ -7969,7 +7969,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>TC-SEL-184</t>
+          <t>TC_WEB_DASH_019</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -7989,7 +7989,7 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
@@ -7998,7 +7998,7 @@
         </is>
       </c>
       <c r="G185" t="n">
-        <v>0.9</v>
+        <v>0.97</v>
       </c>
       <c r="H185" t="inlineStr">
         <is>
@@ -8010,7 +8010,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>TC-SEL-185</t>
+          <t>TC_WEB_DASH_020</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -8039,7 +8039,7 @@
         </is>
       </c>
       <c r="G186" t="n">
-        <v>0.99</v>
+        <v>0.43</v>
       </c>
       <c r="H186" t="inlineStr">
         <is>
@@ -8051,7 +8051,7 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>TC-SEL-186</t>
+          <t>TC_WEB_DASH_021</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -8071,7 +8071,7 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
@@ -8080,7 +8080,7 @@
         </is>
       </c>
       <c r="G187" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.53</v>
       </c>
       <c r="H187" t="inlineStr">
         <is>
@@ -8092,7 +8092,7 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>TC-SEL-187</t>
+          <t>TC_WEB_DASH_022</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -8112,7 +8112,7 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
@@ -8121,7 +8121,7 @@
         </is>
       </c>
       <c r="G188" t="n">
-        <v>0.76</v>
+        <v>1.11</v>
       </c>
       <c r="H188" t="inlineStr">
         <is>
@@ -8133,7 +8133,7 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>TC-SEL-188</t>
+          <t>TC_WEB_DASH_023</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -8153,7 +8153,7 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
@@ -8162,7 +8162,7 @@
         </is>
       </c>
       <c r="G189" t="n">
-        <v>0.95</v>
+        <v>1.1</v>
       </c>
       <c r="H189" t="inlineStr">
         <is>
@@ -8174,7 +8174,7 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>TC-SEL-189</t>
+          <t>TC_WEB_DASH_024</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -8194,7 +8194,7 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
@@ -8203,7 +8203,7 @@
         </is>
       </c>
       <c r="G190" t="n">
-        <v>1.06</v>
+        <v>0.9</v>
       </c>
       <c r="H190" t="inlineStr">
         <is>
@@ -8215,7 +8215,7 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>TC-SEL-190</t>
+          <t>TC_WEB_DASH_025</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -8235,7 +8235,7 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
@@ -8244,7 +8244,7 @@
         </is>
       </c>
       <c r="G191" t="n">
-        <v>0.75</v>
+        <v>0.53</v>
       </c>
       <c r="H191" t="inlineStr">
         <is>
@@ -8256,7 +8256,7 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>TC-SEL-191</t>
+          <t>TC_WEB_DASH_026</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -8276,7 +8276,7 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
@@ -8285,7 +8285,7 @@
         </is>
       </c>
       <c r="G192" t="n">
-        <v>0.99</v>
+        <v>1.08</v>
       </c>
       <c r="H192" t="inlineStr">
         <is>
@@ -8297,7 +8297,7 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>TC-SEL-192</t>
+          <t>TC_WEB_DASH_027</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -8317,7 +8317,7 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
@@ -8326,7 +8326,7 @@
         </is>
       </c>
       <c r="G193" t="n">
-        <v>0.52</v>
+        <v>0.75</v>
       </c>
       <c r="H193" t="inlineStr">
         <is>
@@ -8338,7 +8338,7 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>TC-SEL-193</t>
+          <t>TC_WEB_DASH_028</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -8358,7 +8358,7 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
@@ -8367,7 +8367,7 @@
         </is>
       </c>
       <c r="G194" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="H194" t="inlineStr">
         <is>
@@ -8379,7 +8379,7 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>TC-SEL-194</t>
+          <t>TC_WEB_DASH_029</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -8399,7 +8399,7 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
@@ -8408,7 +8408,7 @@
         </is>
       </c>
       <c r="G195" t="n">
-        <v>0.74</v>
+        <v>0.55</v>
       </c>
       <c r="H195" t="inlineStr">
         <is>
@@ -8420,7 +8420,7 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>TC-SEL-195</t>
+          <t>TC_WEB_DASH_030</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -8440,7 +8440,7 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
@@ -8449,7 +8449,7 @@
         </is>
       </c>
       <c r="G196" t="n">
-        <v>0.6</v>
+        <v>0.85</v>
       </c>
       <c r="H196" t="inlineStr">
         <is>
@@ -8461,7 +8461,7 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>TC-SEL-196</t>
+          <t>TC_WEB_WALLET_001</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -8481,7 +8481,7 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
@@ -8490,7 +8490,7 @@
         </is>
       </c>
       <c r="G197" t="n">
-        <v>0.54</v>
+        <v>0.63</v>
       </c>
       <c r="H197" t="inlineStr">
         <is>
@@ -8502,7 +8502,7 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>TC-SEL-197</t>
+          <t>TC_WEB_WALLET_002</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -8522,7 +8522,7 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
@@ -8531,7 +8531,7 @@
         </is>
       </c>
       <c r="G198" t="n">
-        <v>0.73</v>
+        <v>0.68</v>
       </c>
       <c r="H198" t="inlineStr">
         <is>
@@ -8543,7 +8543,7 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>TC-SEL-198</t>
+          <t>TC_WEB_WALLET_003</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -8563,7 +8563,7 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
@@ -8572,7 +8572,7 @@
         </is>
       </c>
       <c r="G199" t="n">
-        <v>0.77</v>
+        <v>0.7</v>
       </c>
       <c r="H199" t="inlineStr">
         <is>
@@ -8584,7 +8584,7 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>TC-SEL-199</t>
+          <t>TC_WEB_WALLET_004</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -8604,7 +8604,7 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
@@ -8613,7 +8613,7 @@
         </is>
       </c>
       <c r="G200" t="n">
-        <v>0.46</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H200" t="inlineStr">
         <is>
@@ -8625,7 +8625,7 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>TC-SEL-200</t>
+          <t>TC_WEB_WALLET_005</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -8645,7 +8645,7 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
@@ -8654,7 +8654,7 @@
         </is>
       </c>
       <c r="G201" t="n">
-        <v>1.14</v>
+        <v>0.74</v>
       </c>
       <c r="H201" t="inlineStr">
         <is>
@@ -8666,7 +8666,7 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>TC-SEL-201</t>
+          <t>TC_WEB_WALLET_006</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -8695,7 +8695,7 @@
         </is>
       </c>
       <c r="G202" t="n">
-        <v>0.57</v>
+        <v>0.59</v>
       </c>
       <c r="H202" t="inlineStr">
         <is>
@@ -8707,7 +8707,7 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>TC-SEL-202</t>
+          <t>TC_WEB_WALLET_007</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -8736,7 +8736,7 @@
         </is>
       </c>
       <c r="G203" t="n">
-        <v>0.6</v>
+        <v>0.64</v>
       </c>
       <c r="H203" t="inlineStr">
         <is>
@@ -8748,7 +8748,7 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>TC-SEL-203</t>
+          <t>TC_WEB_WALLET_008</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -8768,7 +8768,7 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
@@ -8777,7 +8777,7 @@
         </is>
       </c>
       <c r="G204" t="n">
-        <v>1.1</v>
+        <v>0.78</v>
       </c>
       <c r="H204" t="inlineStr">
         <is>
@@ -8789,7 +8789,7 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>TC-SEL-204</t>
+          <t>TC_WEB_WALLET_009</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -8818,7 +8818,7 @@
         </is>
       </c>
       <c r="G205" t="n">
-        <v>1.14</v>
+        <v>0.65</v>
       </c>
       <c r="H205" t="inlineStr">
         <is>
@@ -8830,7 +8830,7 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>TC-SEL-205</t>
+          <t>TC_WEB_WALLET_010</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -8850,7 +8850,7 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
@@ -8859,7 +8859,7 @@
         </is>
       </c>
       <c r="G206" t="n">
-        <v>0.52</v>
+        <v>0.59</v>
       </c>
       <c r="H206" t="inlineStr">
         <is>
@@ -8871,7 +8871,7 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>TC-SEL-206</t>
+          <t>TC_WEB_WALLET_011</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -8891,7 +8891,7 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
@@ -8900,7 +8900,7 @@
         </is>
       </c>
       <c r="G207" t="n">
-        <v>0.55</v>
+        <v>0.44</v>
       </c>
       <c r="H207" t="inlineStr">
         <is>
@@ -8912,7 +8912,7 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>TC-SEL-207</t>
+          <t>TC_WEB_WALLET_012</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -8932,7 +8932,7 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
@@ -8941,7 +8941,7 @@
         </is>
       </c>
       <c r="G208" t="n">
-        <v>0.48</v>
+        <v>0.91</v>
       </c>
       <c r="H208" t="inlineStr">
         <is>
@@ -8953,7 +8953,7 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>TC-SEL-208</t>
+          <t>TC_WEB_WALLET_013</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -8973,7 +8973,7 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
@@ -8982,7 +8982,7 @@
         </is>
       </c>
       <c r="G209" t="n">
-        <v>1.06</v>
+        <v>0.85</v>
       </c>
       <c r="H209" t="inlineStr">
         <is>
@@ -8994,7 +8994,7 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>TC-SEL-209</t>
+          <t>TC_WEB_WALLET_014</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -9023,7 +9023,7 @@
         </is>
       </c>
       <c r="G210" t="n">
-        <v>0.6899999999999999</v>
+        <v>1.02</v>
       </c>
       <c r="H210" t="inlineStr">
         <is>
@@ -9035,7 +9035,7 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>TC-SEL-210</t>
+          <t>TC_WEB_WALLET_015</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -9064,7 +9064,7 @@
         </is>
       </c>
       <c r="G211" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.59</v>
       </c>
       <c r="H211" t="inlineStr">
         <is>
@@ -9076,7 +9076,7 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>TC-SEL-211</t>
+          <t>TC_WEB_WALLET_016</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -9105,7 +9105,7 @@
         </is>
       </c>
       <c r="G212" t="n">
-        <v>0.9</v>
+        <v>0.88</v>
       </c>
       <c r="H212" t="inlineStr">
         <is>
@@ -9117,7 +9117,7 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>TC-SEL-212</t>
+          <t>TC_WEB_WALLET_017</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -9137,7 +9137,7 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
@@ -9146,7 +9146,7 @@
         </is>
       </c>
       <c r="G213" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.93</v>
       </c>
       <c r="H213" t="inlineStr">
         <is>
@@ -9158,7 +9158,7 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>TC-SEL-213</t>
+          <t>TC_WEB_WALLET_018</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -9178,7 +9178,7 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
@@ -9187,7 +9187,7 @@
         </is>
       </c>
       <c r="G214" t="n">
-        <v>0.85</v>
+        <v>0.63</v>
       </c>
       <c r="H214" t="inlineStr">
         <is>
@@ -9199,7 +9199,7 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>TC-SEL-214</t>
+          <t>TC_WEB_WALLET_019</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -9219,7 +9219,7 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
@@ -9228,7 +9228,7 @@
         </is>
       </c>
       <c r="G215" t="n">
-        <v>0.62</v>
+        <v>0.42</v>
       </c>
       <c r="H215" t="inlineStr">
         <is>
@@ -9240,7 +9240,7 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>TC-SEL-215</t>
+          <t>TC_WEB_WALLET_020</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -9260,7 +9260,7 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
@@ -9269,7 +9269,7 @@
         </is>
       </c>
       <c r="G216" t="n">
-        <v>0.46</v>
+        <v>1.1</v>
       </c>
       <c r="H216" t="inlineStr">
         <is>
@@ -9281,7 +9281,7 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>TC-SEL-216</t>
+          <t>TC_WEB_WALLET_021</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -9310,7 +9310,7 @@
         </is>
       </c>
       <c r="G217" t="n">
-        <v>0.65</v>
+        <v>0.43</v>
       </c>
       <c r="H217" t="inlineStr">
         <is>
@@ -9322,7 +9322,7 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>TC-SEL-217</t>
+          <t>TC_WEB_WALLET_022</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -9342,7 +9342,7 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
@@ -9351,7 +9351,7 @@
         </is>
       </c>
       <c r="G218" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.75</v>
       </c>
       <c r="H218" t="inlineStr">
         <is>
@@ -9363,7 +9363,7 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>TC-SEL-218</t>
+          <t>TC_WEB_WALLET_023</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -9392,7 +9392,7 @@
         </is>
       </c>
       <c r="G219" t="n">
-        <v>0.47</v>
+        <v>1.11</v>
       </c>
       <c r="H219" t="inlineStr">
         <is>
@@ -9404,7 +9404,7 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>TC-SEL-219</t>
+          <t>TC_WEB_WALLET_024</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -9433,7 +9433,7 @@
         </is>
       </c>
       <c r="G220" t="n">
-        <v>0.45</v>
+        <v>0.93</v>
       </c>
       <c r="H220" t="inlineStr">
         <is>
@@ -9445,7 +9445,7 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>TC-SEL-220</t>
+          <t>TC_WEB_WALLET_025</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -9474,7 +9474,7 @@
         </is>
       </c>
       <c r="G221" t="n">
-        <v>0.58</v>
+        <v>1</v>
       </c>
       <c r="H221" t="inlineStr">
         <is>
@@ -9486,7 +9486,7 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>TC-SEL-221</t>
+          <t>TC_WEB_WALLET_026</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -9506,7 +9506,7 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
@@ -9515,7 +9515,7 @@
         </is>
       </c>
       <c r="G222" t="n">
-        <v>0.87</v>
+        <v>1</v>
       </c>
       <c r="H222" t="inlineStr">
         <is>
@@ -9527,7 +9527,7 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>TC-SEL-222</t>
+          <t>TC_WEB_WALLET_027</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -9547,7 +9547,7 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
@@ -9556,7 +9556,7 @@
         </is>
       </c>
       <c r="G223" t="n">
-        <v>0.52</v>
+        <v>0.62</v>
       </c>
       <c r="H223" t="inlineStr">
         <is>
@@ -9568,7 +9568,7 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>TC-SEL-223</t>
+          <t>TC_WEB_WALLET_028</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -9588,7 +9588,7 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
@@ -9597,7 +9597,7 @@
         </is>
       </c>
       <c r="G224" t="n">
-        <v>0.78</v>
+        <v>0.43</v>
       </c>
       <c r="H224" t="inlineStr">
         <is>
@@ -9609,7 +9609,7 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>TC-SEL-224</t>
+          <t>TC_WEB_WALLET_029</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -9629,7 +9629,7 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
@@ -9638,7 +9638,7 @@
         </is>
       </c>
       <c r="G225" t="n">
-        <v>0.59</v>
+        <v>0.91</v>
       </c>
       <c r="H225" t="inlineStr">
         <is>
@@ -9650,7 +9650,7 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>TC-SEL-225</t>
+          <t>TC_WEB_WALLET_030</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -9670,7 +9670,7 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
@@ -9679,7 +9679,7 @@
         </is>
       </c>
       <c r="G226" t="n">
-        <v>1</v>
+        <v>0.68</v>
       </c>
       <c r="H226" t="inlineStr">
         <is>
@@ -9691,7 +9691,7 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>TC-SEL-226</t>
+          <t>TC_WEB_EXPORT_001</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -9711,7 +9711,7 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
@@ -9720,7 +9720,7 @@
         </is>
       </c>
       <c r="G227" t="n">
-        <v>0.99</v>
+        <v>0.42</v>
       </c>
       <c r="H227" t="inlineStr">
         <is>
@@ -9732,7 +9732,7 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>TC-SEL-227</t>
+          <t>TC_WEB_EXPORT_002</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -9761,7 +9761,7 @@
         </is>
       </c>
       <c r="G228" t="n">
-        <v>0.71</v>
+        <v>1.07</v>
       </c>
       <c r="H228" t="inlineStr">
         <is>
@@ -9773,7 +9773,7 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>TC-SEL-228</t>
+          <t>TC_WEB_EXPORT_003</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -9793,7 +9793,7 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
@@ -9802,7 +9802,7 @@
         </is>
       </c>
       <c r="G229" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="H229" t="inlineStr">
         <is>
@@ -9814,7 +9814,7 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>TC-SEL-229</t>
+          <t>TC_WEB_EXPORT_004</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -9843,7 +9843,7 @@
         </is>
       </c>
       <c r="G230" t="n">
-        <v>0.59</v>
+        <v>0.45</v>
       </c>
       <c r="H230" t="inlineStr">
         <is>
@@ -9855,7 +9855,7 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>TC-SEL-230</t>
+          <t>TC_WEB_EXPORT_005</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -9884,7 +9884,7 @@
         </is>
       </c>
       <c r="G231" t="n">
-        <v>1.04</v>
+        <v>0.52</v>
       </c>
       <c r="H231" t="inlineStr">
         <is>
@@ -9896,7 +9896,7 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>TC-SEL-231</t>
+          <t>TC_WEB_EXPORT_006</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -9916,7 +9916,7 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
@@ -9925,7 +9925,7 @@
         </is>
       </c>
       <c r="G232" t="n">
-        <v>0.46</v>
+        <v>0.74</v>
       </c>
       <c r="H232" t="inlineStr">
         <is>
@@ -9937,7 +9937,7 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>TC-SEL-232</t>
+          <t>TC_WEB_EXPORT_007</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -9957,7 +9957,7 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
@@ -9966,7 +9966,7 @@
         </is>
       </c>
       <c r="G233" t="n">
-        <v>0.44</v>
+        <v>1.04</v>
       </c>
       <c r="H233" t="inlineStr">
         <is>
@@ -9978,7 +9978,7 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>TC-SEL-233</t>
+          <t>TC_WEB_EXPORT_008</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -9998,7 +9998,7 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
@@ -10007,7 +10007,7 @@
         </is>
       </c>
       <c r="G234" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.59</v>
       </c>
       <c r="H234" t="inlineStr">
         <is>
@@ -10019,7 +10019,7 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>TC-SEL-234</t>
+          <t>TC_WEB_EXPORT_009</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -10039,7 +10039,7 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
@@ -10048,7 +10048,7 @@
         </is>
       </c>
       <c r="G235" t="n">
-        <v>0.6</v>
+        <v>0.84</v>
       </c>
       <c r="H235" t="inlineStr">
         <is>
@@ -10060,7 +10060,7 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>TC-SEL-235</t>
+          <t>TC_WEB_EXPORT_010</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -10080,7 +10080,7 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
@@ -10089,7 +10089,7 @@
         </is>
       </c>
       <c r="G236" t="n">
-        <v>1.06</v>
+        <v>0.84</v>
       </c>
       <c r="H236" t="inlineStr">
         <is>
@@ -10101,7 +10101,7 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>TC-SEL-236</t>
+          <t>TC_WEB_EXPORT_011</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -10121,7 +10121,7 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
@@ -10130,7 +10130,7 @@
         </is>
       </c>
       <c r="G237" t="n">
-        <v>0.44</v>
+        <v>0.83</v>
       </c>
       <c r="H237" t="inlineStr">
         <is>
@@ -10142,7 +10142,7 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>TC-SEL-237</t>
+          <t>TC_WEB_EXPORT_012</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -10162,7 +10162,7 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
@@ -10171,7 +10171,7 @@
         </is>
       </c>
       <c r="G238" t="n">
-        <v>0.49</v>
+        <v>0.54</v>
       </c>
       <c r="H238" t="inlineStr">
         <is>
@@ -10183,7 +10183,7 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>TC-SEL-238</t>
+          <t>TC_WEB_EXPORT_013</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -10203,7 +10203,7 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
@@ -10212,7 +10212,7 @@
         </is>
       </c>
       <c r="G239" t="n">
-        <v>0.45</v>
+        <v>1</v>
       </c>
       <c r="H239" t="inlineStr">
         <is>
@@ -10224,7 +10224,7 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>TC-SEL-239</t>
+          <t>TC_WEB_EXPORT_014</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -10244,7 +10244,7 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
@@ -10253,7 +10253,7 @@
         </is>
       </c>
       <c r="G240" t="n">
-        <v>0.9</v>
+        <v>1.07</v>
       </c>
       <c r="H240" t="inlineStr">
         <is>
@@ -10265,7 +10265,7 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>TC-SEL-240</t>
+          <t>TC_WEB_EXPORT_015</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -10285,7 +10285,7 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
@@ -10294,7 +10294,7 @@
         </is>
       </c>
       <c r="G241" t="n">
-        <v>0.57</v>
+        <v>0.97</v>
       </c>
       <c r="H241" t="inlineStr">
         <is>
@@ -10306,7 +10306,7 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>TC-SEL-241</t>
+          <t>TC_WEB_EXPORT_016</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -10326,7 +10326,7 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
@@ -10335,7 +10335,7 @@
         </is>
       </c>
       <c r="G242" t="n">
-        <v>0.5600000000000001</v>
+        <v>1.11</v>
       </c>
       <c r="H242" t="inlineStr">
         <is>
@@ -10347,7 +10347,7 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>TC-SEL-242</t>
+          <t>TC_WEB_EXPORT_017</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -10367,7 +10367,7 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
@@ -10376,7 +10376,7 @@
         </is>
       </c>
       <c r="G243" t="n">
-        <v>0.74</v>
+        <v>0.52</v>
       </c>
       <c r="H243" t="inlineStr">
         <is>
@@ -10388,7 +10388,7 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>TC-SEL-243</t>
+          <t>TC_WEB_EXPORT_018</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -10408,7 +10408,7 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
@@ -10417,7 +10417,7 @@
         </is>
       </c>
       <c r="G244" t="n">
-        <v>0.45</v>
+        <v>1.04</v>
       </c>
       <c r="H244" t="inlineStr">
         <is>
@@ -10429,7 +10429,7 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>TC-SEL-244</t>
+          <t>TC_WEB_EXPORT_019</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -10449,7 +10449,7 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
@@ -10458,7 +10458,7 @@
         </is>
       </c>
       <c r="G245" t="n">
-        <v>0.64</v>
+        <v>1.07</v>
       </c>
       <c r="H245" t="inlineStr">
         <is>
@@ -10470,7 +10470,7 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>TC-SEL-245</t>
+          <t>TC_WEB_EXPORT_020</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -10490,7 +10490,7 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
@@ -10499,7 +10499,7 @@
         </is>
       </c>
       <c r="G246" t="n">
-        <v>0.48</v>
+        <v>0.52</v>
       </c>
       <c r="H246" t="inlineStr">
         <is>
@@ -10511,7 +10511,7 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>TC-SEL-246</t>
+          <t>TC_WEB_EXPORT_021</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -10531,7 +10531,7 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
@@ -10540,7 +10540,7 @@
         </is>
       </c>
       <c r="G247" t="n">
-        <v>1.13</v>
+        <v>0.76</v>
       </c>
       <c r="H247" t="inlineStr">
         <is>
@@ -10552,7 +10552,7 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>TC-SEL-247</t>
+          <t>TC_WEB_EXPORT_022</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -10572,7 +10572,7 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
@@ -10581,7 +10581,7 @@
         </is>
       </c>
       <c r="G248" t="n">
-        <v>0.51</v>
+        <v>0.44</v>
       </c>
       <c r="H248" t="inlineStr">
         <is>
@@ -10593,7 +10593,7 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>TC-SEL-248</t>
+          <t>TC_WEB_EXPORT_023</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -10613,7 +10613,7 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
@@ -10622,7 +10622,7 @@
         </is>
       </c>
       <c r="G249" t="n">
-        <v>1.01</v>
+        <v>0.44</v>
       </c>
       <c r="H249" t="inlineStr">
         <is>
@@ -10634,7 +10634,7 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>TC-SEL-249</t>
+          <t>TC_WEB_EXPORT_024</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -10654,7 +10654,7 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
@@ -10663,7 +10663,7 @@
         </is>
       </c>
       <c r="G250" t="n">
-        <v>0.76</v>
+        <v>1.08</v>
       </c>
       <c r="H250" t="inlineStr">
         <is>
@@ -10675,7 +10675,7 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>TC-SEL-250</t>
+          <t>TC_WEB_EXPORT_025</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -10704,7 +10704,7 @@
         </is>
       </c>
       <c r="G251" t="n">
-        <v>0.46</v>
+        <v>0.88</v>
       </c>
       <c r="H251" t="inlineStr">
         <is>
@@ -10716,7 +10716,7 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>TC-SEL-251</t>
+          <t>TC_WEB_SEC_001</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -10736,7 +10736,7 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
@@ -10745,7 +10745,7 @@
         </is>
       </c>
       <c r="G252" t="n">
-        <v>0.58</v>
+        <v>1.14</v>
       </c>
       <c r="H252" t="inlineStr">
         <is>
@@ -10757,7 +10757,7 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>TC-SEL-252</t>
+          <t>TC_WEB_SEC_002</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -10777,7 +10777,7 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
@@ -10786,7 +10786,7 @@
         </is>
       </c>
       <c r="G253" t="n">
-        <v>0.53</v>
+        <v>0.84</v>
       </c>
       <c r="H253" t="inlineStr">
         <is>
@@ -10798,7 +10798,7 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>TC-SEL-253</t>
+          <t>TC_WEB_SEC_003</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -10827,7 +10827,7 @@
         </is>
       </c>
       <c r="G254" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="H254" t="inlineStr">
         <is>
@@ -10839,7 +10839,7 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>TC-SEL-254</t>
+          <t>TC_WEB_SEC_004</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -10868,7 +10868,7 @@
         </is>
       </c>
       <c r="G255" t="n">
-        <v>0.49</v>
+        <v>0.89</v>
       </c>
       <c r="H255" t="inlineStr">
         <is>
@@ -10880,7 +10880,7 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>TC-SEL-255</t>
+          <t>TC_WEB_SEC_005</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -10900,7 +10900,7 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
@@ -10909,7 +10909,7 @@
         </is>
       </c>
       <c r="G256" t="n">
-        <v>0.67</v>
+        <v>0.61</v>
       </c>
       <c r="H256" t="inlineStr">
         <is>
@@ -10921,7 +10921,7 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>TC-SEL-256</t>
+          <t>TC_WEB_SEC_006</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -10941,7 +10941,7 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
@@ -10950,7 +10950,7 @@
         </is>
       </c>
       <c r="G257" t="n">
-        <v>0.63</v>
+        <v>0.46</v>
       </c>
       <c r="H257" t="inlineStr">
         <is>
@@ -10962,7 +10962,7 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>TC-SEL-257</t>
+          <t>TC_WEB_SEC_007</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -10982,7 +10982,7 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
@@ -10991,7 +10991,7 @@
         </is>
       </c>
       <c r="G258" t="n">
-        <v>0.51</v>
+        <v>1.13</v>
       </c>
       <c r="H258" t="inlineStr">
         <is>
@@ -11003,7 +11003,7 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>TC-SEL-258</t>
+          <t>TC_WEB_SEC_008</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -11023,7 +11023,7 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
@@ -11032,7 +11032,7 @@
         </is>
       </c>
       <c r="G259" t="n">
-        <v>0.61</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H259" t="inlineStr">
         <is>
@@ -11044,7 +11044,7 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>TC-SEL-259</t>
+          <t>TC_WEB_SEC_009</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -11064,7 +11064,7 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
@@ -11073,7 +11073,7 @@
         </is>
       </c>
       <c r="G260" t="n">
-        <v>0.73</v>
+        <v>0.8</v>
       </c>
       <c r="H260" t="inlineStr">
         <is>
@@ -11085,7 +11085,7 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>TC-SEL-260</t>
+          <t>TC_WEB_SEC_010</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -11105,7 +11105,7 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
@@ -11114,7 +11114,7 @@
         </is>
       </c>
       <c r="G261" t="n">
-        <v>0.62</v>
+        <v>0.49</v>
       </c>
       <c r="H261" t="inlineStr">
         <is>
@@ -11126,7 +11126,7 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>TC-SEL-261</t>
+          <t>TC_WEB_SEC_011</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -11146,7 +11146,7 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
@@ -11155,7 +11155,7 @@
         </is>
       </c>
       <c r="G262" t="n">
-        <v>0.52</v>
+        <v>1.14</v>
       </c>
       <c r="H262" t="inlineStr">
         <is>
@@ -11167,7 +11167,7 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>TC-SEL-262</t>
+          <t>TC_WEB_SEC_012</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -11187,7 +11187,7 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
@@ -11196,7 +11196,7 @@
         </is>
       </c>
       <c r="G263" t="n">
-        <v>0.53</v>
+        <v>0.99</v>
       </c>
       <c r="H263" t="inlineStr">
         <is>
@@ -11208,7 +11208,7 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>TC-SEL-263</t>
+          <t>TC_WEB_SEC_013</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -11237,7 +11237,7 @@
         </is>
       </c>
       <c r="G264" t="n">
-        <v>0.79</v>
+        <v>0.52</v>
       </c>
       <c r="H264" t="inlineStr">
         <is>
@@ -11249,7 +11249,7 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>TC-SEL-264</t>
+          <t>TC_WEB_SEC_014</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -11269,7 +11269,7 @@
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
@@ -11278,7 +11278,7 @@
         </is>
       </c>
       <c r="G265" t="n">
-        <v>0.78</v>
+        <v>1.1</v>
       </c>
       <c r="H265" t="inlineStr">
         <is>
@@ -11290,7 +11290,7 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>TC-SEL-265</t>
+          <t>TC_WEB_SEC_015</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -11310,7 +11310,7 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
@@ -11319,7 +11319,7 @@
         </is>
       </c>
       <c r="G266" t="n">
-        <v>0.45</v>
+        <v>0.77</v>
       </c>
       <c r="H266" t="inlineStr">
         <is>
@@ -11331,7 +11331,7 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>TC-SEL-266</t>
+          <t>TC_WEB_SEC_016</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -11360,7 +11360,7 @@
         </is>
       </c>
       <c r="G267" t="n">
-        <v>0.91</v>
+        <v>0.44</v>
       </c>
       <c r="H267" t="inlineStr">
         <is>
@@ -11372,7 +11372,7 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>TC-SEL-267</t>
+          <t>TC_WEB_SEC_017</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
@@ -11392,7 +11392,7 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
@@ -11401,7 +11401,7 @@
         </is>
       </c>
       <c r="G268" t="n">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="H268" t="inlineStr">
         <is>
@@ -11413,7 +11413,7 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>TC-SEL-268</t>
+          <t>TC_WEB_SEC_018</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
@@ -11433,7 +11433,7 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
@@ -11442,7 +11442,7 @@
         </is>
       </c>
       <c r="G269" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.48</v>
       </c>
       <c r="H269" t="inlineStr">
         <is>
@@ -11454,7 +11454,7 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>TC-SEL-269</t>
+          <t>TC_WEB_SEC_019</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
@@ -11474,7 +11474,7 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
@@ -11483,7 +11483,7 @@
         </is>
       </c>
       <c r="G270" t="n">
-        <v>0.91</v>
+        <v>0.57</v>
       </c>
       <c r="H270" t="inlineStr">
         <is>
@@ -11495,7 +11495,7 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>TC-SEL-270</t>
+          <t>TC_WEB_SEC_020</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
@@ -11515,7 +11515,7 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
@@ -11524,7 +11524,7 @@
         </is>
       </c>
       <c r="G271" t="n">
-        <v>1.04</v>
+        <v>0.6</v>
       </c>
       <c r="H271" t="inlineStr">
         <is>
@@ -11536,7 +11536,7 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>TC-SEL-271</t>
+          <t>TC_WEB_SEC_021</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
@@ -11556,7 +11556,7 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
@@ -11565,7 +11565,7 @@
         </is>
       </c>
       <c r="G272" t="n">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="H272" t="inlineStr">
         <is>
@@ -11577,7 +11577,7 @@
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>TC-SEL-272</t>
+          <t>TC_WEB_SEC_022</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
@@ -11597,7 +11597,7 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
@@ -11606,7 +11606,7 @@
         </is>
       </c>
       <c r="G273" t="n">
-        <v>0.48</v>
+        <v>0.74</v>
       </c>
       <c r="H273" t="inlineStr">
         <is>
@@ -11618,7 +11618,7 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>TC-SEL-273</t>
+          <t>TC_WEB_SEC_023</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
@@ -11638,7 +11638,7 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
@@ -11647,7 +11647,7 @@
         </is>
       </c>
       <c r="G274" t="n">
-        <v>0.73</v>
+        <v>1.11</v>
       </c>
       <c r="H274" t="inlineStr">
         <is>
@@ -11659,7 +11659,7 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>TC-SEL-274</t>
+          <t>TC_WEB_SEC_024</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
@@ -11679,7 +11679,7 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
@@ -11688,7 +11688,7 @@
         </is>
       </c>
       <c r="G275" t="n">
-        <v>0.74</v>
+        <v>1.01</v>
       </c>
       <c r="H275" t="inlineStr">
         <is>
@@ -11700,7 +11700,7 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>TC-SEL-275</t>
+          <t>TC_WEB_SEC_025</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
@@ -11720,7 +11720,7 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
@@ -11729,7 +11729,7 @@
         </is>
       </c>
       <c r="G276" t="n">
-        <v>0.63</v>
+        <v>0.95</v>
       </c>
       <c r="H276" t="inlineStr">
         <is>
@@ -11741,7 +11741,7 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>TC-SEL-276</t>
+          <t>TC_WEB_PERF_001</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
@@ -11761,7 +11761,7 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
@@ -11770,7 +11770,7 @@
         </is>
       </c>
       <c r="G277" t="n">
-        <v>0.75</v>
+        <v>1.15</v>
       </c>
       <c r="H277" t="inlineStr">
         <is>
@@ -11782,7 +11782,7 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>TC-SEL-277</t>
+          <t>TC_WEB_PERF_002</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
@@ -11802,7 +11802,7 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
@@ -11811,7 +11811,7 @@
         </is>
       </c>
       <c r="G278" t="n">
-        <v>0.92</v>
+        <v>0.87</v>
       </c>
       <c r="H278" t="inlineStr">
         <is>
@@ -11823,7 +11823,7 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>TC-SEL-278</t>
+          <t>TC_WEB_PERF_003</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
@@ -11843,7 +11843,7 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
@@ -11852,7 +11852,7 @@
         </is>
       </c>
       <c r="G279" t="n">
-        <v>0.51</v>
+        <v>1.1</v>
       </c>
       <c r="H279" t="inlineStr">
         <is>
@@ -11864,7 +11864,7 @@
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>TC-SEL-279</t>
+          <t>TC_WEB_PERF_004</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
@@ -11884,7 +11884,7 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
@@ -11893,7 +11893,7 @@
         </is>
       </c>
       <c r="G280" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.74</v>
       </c>
       <c r="H280" t="inlineStr">
         <is>
@@ -11905,7 +11905,7 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>TC-SEL-280</t>
+          <t>TC_WEB_PERF_005</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
@@ -11925,7 +11925,7 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
@@ -11934,7 +11934,7 @@
         </is>
       </c>
       <c r="G281" t="n">
-        <v>1.14</v>
+        <v>0.9</v>
       </c>
       <c r="H281" t="inlineStr">
         <is>
@@ -11946,7 +11946,7 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>TC-SEL-281</t>
+          <t>TC_WEB_PERF_006</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
@@ -11966,7 +11966,7 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
@@ -11975,7 +11975,7 @@
         </is>
       </c>
       <c r="G282" t="n">
-        <v>1</v>
+        <v>0.66</v>
       </c>
       <c r="H282" t="inlineStr">
         <is>
@@ -11987,7 +11987,7 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>TC-SEL-282</t>
+          <t>TC_WEB_PERF_007</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
@@ -12016,7 +12016,7 @@
         </is>
       </c>
       <c r="G283" t="n">
-        <v>1.03</v>
+        <v>0.49</v>
       </c>
       <c r="H283" t="inlineStr">
         <is>
@@ -12028,7 +12028,7 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>TC-SEL-283</t>
+          <t>TC_WEB_PERF_008</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
@@ -12048,7 +12048,7 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
@@ -12057,7 +12057,7 @@
         </is>
       </c>
       <c r="G284" t="n">
-        <v>0.45</v>
+        <v>0.84</v>
       </c>
       <c r="H284" t="inlineStr">
         <is>
@@ -12069,7 +12069,7 @@
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>TC-SEL-284</t>
+          <t>TC_WEB_PERF_009</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
@@ -12089,7 +12089,7 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
@@ -12098,7 +12098,7 @@
         </is>
       </c>
       <c r="G285" t="n">
-        <v>0.72</v>
+        <v>0.82</v>
       </c>
       <c r="H285" t="inlineStr">
         <is>
@@ -12110,7 +12110,7 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>TC-SEL-285</t>
+          <t>TC_WEB_PERF_010</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
@@ -12130,7 +12130,7 @@
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
@@ -12139,7 +12139,7 @@
         </is>
       </c>
       <c r="G286" t="n">
-        <v>1.05</v>
+        <v>0.79</v>
       </c>
       <c r="H286" t="inlineStr">
         <is>
@@ -12151,7 +12151,7 @@
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>TC-SEL-286</t>
+          <t>TC_WEB_PERF_011</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
@@ -12171,7 +12171,7 @@
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
@@ -12180,7 +12180,7 @@
         </is>
       </c>
       <c r="G287" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.88</v>
       </c>
       <c r="H287" t="inlineStr">
         <is>
@@ -12192,7 +12192,7 @@
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>TC-SEL-287</t>
+          <t>TC_WEB_PERF_012</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
@@ -12212,7 +12212,7 @@
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
@@ -12221,7 +12221,7 @@
         </is>
       </c>
       <c r="G288" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="H288" t="inlineStr">
         <is>
@@ -12233,7 +12233,7 @@
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>TC-SEL-288</t>
+          <t>TC_WEB_PERF_013</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
@@ -12253,7 +12253,7 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
@@ -12262,7 +12262,7 @@
         </is>
       </c>
       <c r="G289" t="n">
-        <v>1.13</v>
+        <v>0.96</v>
       </c>
       <c r="H289" t="inlineStr">
         <is>
@@ -12274,7 +12274,7 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>TC-SEL-289</t>
+          <t>TC_WEB_PERF_014</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
@@ -12294,7 +12294,7 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
@@ -12303,7 +12303,7 @@
         </is>
       </c>
       <c r="G290" t="n">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="H290" t="inlineStr">
         <is>
@@ -12315,7 +12315,7 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>TC-SEL-290</t>
+          <t>TC_WEB_PERF_015</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
@@ -12335,7 +12335,7 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
@@ -12344,7 +12344,7 @@
         </is>
       </c>
       <c r="G291" t="n">
-        <v>0.67</v>
+        <v>0.73</v>
       </c>
       <c r="H291" t="inlineStr">
         <is>
@@ -12356,7 +12356,7 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>TC-SEL-291</t>
+          <t>TC_WEB_PERF_016</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
@@ -12385,7 +12385,7 @@
         </is>
       </c>
       <c r="G292" t="n">
-        <v>1.01</v>
+        <v>0.55</v>
       </c>
       <c r="H292" t="inlineStr">
         <is>
@@ -12397,7 +12397,7 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>TC-SEL-292</t>
+          <t>TC_WEB_PERF_017</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
@@ -12426,7 +12426,7 @@
         </is>
       </c>
       <c r="G293" t="n">
-        <v>0.91</v>
+        <v>1.11</v>
       </c>
       <c r="H293" t="inlineStr">
         <is>
@@ -12438,7 +12438,7 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>TC-SEL-293</t>
+          <t>TC_WEB_PERF_018</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
@@ -12458,7 +12458,7 @@
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
@@ -12467,7 +12467,7 @@
         </is>
       </c>
       <c r="G294" t="n">
-        <v>0.89</v>
+        <v>0.61</v>
       </c>
       <c r="H294" t="inlineStr">
         <is>
@@ -12479,7 +12479,7 @@
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>TC-SEL-294</t>
+          <t>TC_WEB_PERF_019</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
@@ -12499,7 +12499,7 @@
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
@@ -12508,7 +12508,7 @@
         </is>
       </c>
       <c r="G295" t="n">
-        <v>0.7</v>
+        <v>0.92</v>
       </c>
       <c r="H295" t="inlineStr">
         <is>
@@ -12520,7 +12520,7 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>TC-SEL-295</t>
+          <t>TC_WEB_PERF_020</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
@@ -12540,7 +12540,7 @@
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
@@ -12561,7 +12561,7 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>TC-SEL-296</t>
+          <t>TC_WEB_PERF_021</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
@@ -12581,7 +12581,7 @@
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
@@ -12590,7 +12590,7 @@
         </is>
       </c>
       <c r="G297" t="n">
-        <v>0.45</v>
+        <v>0.57</v>
       </c>
       <c r="H297" t="inlineStr">
         <is>
@@ -12602,7 +12602,7 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>TC-SEL-297</t>
+          <t>TC_WEB_PERF_022</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
@@ -12622,7 +12622,7 @@
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
@@ -12631,7 +12631,7 @@
         </is>
       </c>
       <c r="G298" t="n">
-        <v>0.78</v>
+        <v>0.63</v>
       </c>
       <c r="H298" t="inlineStr">
         <is>
@@ -12643,7 +12643,7 @@
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>TC-SEL-298</t>
+          <t>TC_WEB_PERF_023</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
@@ -12672,7 +12672,7 @@
         </is>
       </c>
       <c r="G299" t="n">
-        <v>1.01</v>
+        <v>0.52</v>
       </c>
       <c r="H299" t="inlineStr">
         <is>
@@ -12684,7 +12684,7 @@
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>TC-SEL-299</t>
+          <t>TC_WEB_PERF_024</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
@@ -12704,7 +12704,7 @@
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
@@ -12713,7 +12713,7 @@
         </is>
       </c>
       <c r="G300" t="n">
-        <v>1.09</v>
+        <v>0.71</v>
       </c>
       <c r="H300" t="inlineStr">
         <is>
@@ -12725,7 +12725,7 @@
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>TC-SEL-300</t>
+          <t>TC_WEB_PERF_025</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
@@ -12754,7 +12754,7 @@
         </is>
       </c>
       <c r="G301" t="n">
-        <v>0.5</v>
+        <v>0.72</v>
       </c>
       <c r="H301" t="inlineStr">
         <is>

--- a/reports/Passed_Test_Cases.xlsx
+++ b/reports/Passed_Test_Cases.xlsx
@@ -486,7 +486,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -495,7 +495,7 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>1.03</v>
+        <v>0.88</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -527,7 +527,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0.7</v>
+        <v>0.51</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -568,7 +568,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -577,7 +577,7 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0.82</v>
+        <v>0.55</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -609,7 +609,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -618,7 +618,7 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>1.08</v>
+        <v>0.47</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>0.58</v>
+        <v>0.63</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -691,7 +691,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -700,7 +700,7 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>0.88</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -732,7 +732,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -741,7 +741,7 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>0.61</v>
+        <v>0.84</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -773,7 +773,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -782,7 +782,7 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>0.57</v>
+        <v>0.64</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -814,7 +814,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -823,7 +823,7 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>0.75</v>
+        <v>1.14</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -855,7 +855,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -864,7 +864,7 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>0.46</v>
+        <v>0.79</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>0.74</v>
+        <v>0.97</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -937,7 +937,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -946,7 +946,7 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>0.71</v>
+        <v>0.68</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -978,7 +978,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1028,7 +1028,7 @@
         </is>
       </c>
       <c r="G15" t="n">
-        <v>0.46</v>
+        <v>0.71</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -1069,7 +1069,7 @@
         </is>
       </c>
       <c r="G16" t="n">
-        <v>0.47</v>
+        <v>0.45</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -1101,7 +1101,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1110,7 +1110,7 @@
         </is>
       </c>
       <c r="G17" t="n">
-        <v>0.65</v>
+        <v>1.01</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
         </is>
       </c>
       <c r="G18" t="n">
-        <v>0.86</v>
+        <v>1.1</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -1192,7 +1192,7 @@
         </is>
       </c>
       <c r="G19" t="n">
-        <v>0.46</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1233,7 +1233,7 @@
         </is>
       </c>
       <c r="G20" t="n">
-        <v>1.08</v>
+        <v>0.43</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -1265,7 +1265,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1274,7 +1274,7 @@
         </is>
       </c>
       <c r="G21" t="n">
-        <v>0.73</v>
+        <v>0.71</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -1306,7 +1306,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1315,7 +1315,7 @@
         </is>
       </c>
       <c r="G22" t="n">
-        <v>0.43</v>
+        <v>1</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
@@ -1356,7 +1356,7 @@
         </is>
       </c>
       <c r="G23" t="n">
-        <v>1.1</v>
+        <v>0.76</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1397,7 +1397,7 @@
         </is>
       </c>
       <c r="G24" t="n">
-        <v>0.79</v>
+        <v>0.49</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
@@ -1438,7 +1438,7 @@
         </is>
       </c>
       <c r="G25" t="n">
-        <v>0.82</v>
+        <v>0.87</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
@@ -1470,7 +1470,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1479,7 +1479,7 @@
         </is>
       </c>
       <c r="G26" t="n">
-        <v>0.64</v>
+        <v>0.71</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
@@ -1511,7 +1511,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1520,7 +1520,7 @@
         </is>
       </c>
       <c r="G27" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.45</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
@@ -1552,7 +1552,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1561,7 +1561,7 @@
         </is>
       </c>
       <c r="G28" t="n">
-        <v>0.79</v>
+        <v>0.93</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
@@ -1593,7 +1593,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1602,7 +1602,7 @@
         </is>
       </c>
       <c r="G29" t="n">
-        <v>0.87</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
@@ -1634,7 +1634,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1643,7 +1643,7 @@
         </is>
       </c>
       <c r="G30" t="n">
-        <v>1.05</v>
+        <v>0.47</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
@@ -1675,7 +1675,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1684,7 +1684,7 @@
         </is>
       </c>
       <c r="G31" t="n">
-        <v>0.8</v>
+        <v>1.02</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
@@ -1716,7 +1716,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1725,7 +1725,7 @@
         </is>
       </c>
       <c r="G32" t="n">
-        <v>0.55</v>
+        <v>1.14</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
@@ -1757,7 +1757,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1766,7 +1766,7 @@
         </is>
       </c>
       <c r="G33" t="n">
-        <v>1.1</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
@@ -1807,7 +1807,7 @@
         </is>
       </c>
       <c r="G34" t="n">
-        <v>0.45</v>
+        <v>1.12</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
@@ -1848,7 +1848,7 @@
         </is>
       </c>
       <c r="G35" t="n">
-        <v>0.9</v>
+        <v>0.55</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
         </is>
       </c>
       <c r="G36" t="n">
-        <v>0.77</v>
+        <v>0.92</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1930,7 +1930,7 @@
         </is>
       </c>
       <c r="G37" t="n">
-        <v>0.98</v>
+        <v>0.7</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
@@ -1962,7 +1962,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1971,7 +1971,7 @@
         </is>
       </c>
       <c r="G38" t="n">
-        <v>0.55</v>
+        <v>0.96</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
@@ -2003,7 +2003,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -2012,7 +2012,7 @@
         </is>
       </c>
       <c r="G39" t="n">
-        <v>1.11</v>
+        <v>0.66</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
@@ -2044,7 +2044,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -2053,7 +2053,7 @@
         </is>
       </c>
       <c r="G40" t="n">
-        <v>0.89</v>
+        <v>0.62</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
@@ -2085,7 +2085,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -2094,7 +2094,7 @@
         </is>
       </c>
       <c r="G41" t="n">
-        <v>0.54</v>
+        <v>0.8</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
@@ -2135,7 +2135,7 @@
         </is>
       </c>
       <c r="G42" t="n">
-        <v>0.83</v>
+        <v>0.66</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
@@ -2167,7 +2167,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -2176,7 +2176,7 @@
         </is>
       </c>
       <c r="G43" t="n">
-        <v>0.58</v>
+        <v>0.82</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
@@ -2208,7 +2208,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -2249,7 +2249,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2258,7 +2258,7 @@
         </is>
       </c>
       <c r="G45" t="n">
-        <v>0.88</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
@@ -2290,7 +2290,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2299,7 +2299,7 @@
         </is>
       </c>
       <c r="G46" t="n">
-        <v>0.92</v>
+        <v>0.75</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
@@ -2331,7 +2331,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2340,7 +2340,7 @@
         </is>
       </c>
       <c r="G47" t="n">
-        <v>0.89</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
@@ -2372,7 +2372,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2381,7 +2381,7 @@
         </is>
       </c>
       <c r="G48" t="n">
-        <v>0.99</v>
+        <v>0.89</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
@@ -2413,7 +2413,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2422,7 +2422,7 @@
         </is>
       </c>
       <c r="G49" t="n">
-        <v>1.02</v>
+        <v>0.79</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
@@ -2454,7 +2454,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2463,7 +2463,7 @@
         </is>
       </c>
       <c r="G50" t="n">
-        <v>1.04</v>
+        <v>0.47</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
@@ -2495,7 +2495,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2504,7 +2504,7 @@
         </is>
       </c>
       <c r="G51" t="n">
-        <v>0.47</v>
+        <v>1.01</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
@@ -2536,7 +2536,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2545,7 +2545,7 @@
         </is>
       </c>
       <c r="G52" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
@@ -2577,7 +2577,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2586,7 +2586,7 @@
         </is>
       </c>
       <c r="G53" t="n">
-        <v>0.76</v>
+        <v>1.06</v>
       </c>
       <c r="H53" t="inlineStr">
         <is>
@@ -2627,7 +2627,7 @@
         </is>
       </c>
       <c r="G54" t="n">
-        <v>0.55</v>
+        <v>0.82</v>
       </c>
       <c r="H54" t="inlineStr">
         <is>
@@ -2659,7 +2659,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2668,7 +2668,7 @@
         </is>
       </c>
       <c r="G55" t="n">
-        <v>0.62</v>
+        <v>0.96</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
@@ -2709,7 +2709,7 @@
         </is>
       </c>
       <c r="G56" t="n">
-        <v>0.98</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
@@ -2741,7 +2741,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2750,7 +2750,7 @@
         </is>
       </c>
       <c r="G57" t="n">
-        <v>1.13</v>
+        <v>0.83</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
@@ -2782,7 +2782,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2791,7 +2791,7 @@
         </is>
       </c>
       <c r="G58" t="n">
-        <v>1.12</v>
+        <v>0.62</v>
       </c>
       <c r="H58" t="inlineStr">
         <is>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2832,7 +2832,7 @@
         </is>
       </c>
       <c r="G59" t="n">
-        <v>0.78</v>
+        <v>0.43</v>
       </c>
       <c r="H59" t="inlineStr">
         <is>
@@ -2864,7 +2864,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2873,7 +2873,7 @@
         </is>
       </c>
       <c r="G60" t="n">
-        <v>0.54</v>
+        <v>0.45</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
@@ -2914,7 +2914,7 @@
         </is>
       </c>
       <c r="G61" t="n">
-        <v>0.54</v>
+        <v>1.06</v>
       </c>
       <c r="H61" t="inlineStr">
         <is>
@@ -2946,7 +2946,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2955,7 +2955,7 @@
         </is>
       </c>
       <c r="G62" t="n">
-        <v>0.43</v>
+        <v>0.74</v>
       </c>
       <c r="H62" t="inlineStr">
         <is>
@@ -2987,7 +2987,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2996,7 +2996,7 @@
         </is>
       </c>
       <c r="G63" t="n">
-        <v>0.91</v>
+        <v>0.58</v>
       </c>
       <c r="H63" t="inlineStr">
         <is>
@@ -3028,7 +3028,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -3037,7 +3037,7 @@
         </is>
       </c>
       <c r="G64" t="n">
-        <v>0.49</v>
+        <v>0.78</v>
       </c>
       <c r="H64" t="inlineStr">
         <is>
@@ -3078,7 +3078,7 @@
         </is>
       </c>
       <c r="G65" t="n">
-        <v>0.42</v>
+        <v>0.44</v>
       </c>
       <c r="H65" t="inlineStr">
         <is>
@@ -3110,7 +3110,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -3119,7 +3119,7 @@
         </is>
       </c>
       <c r="G66" t="n">
-        <v>0.74</v>
+        <v>0.62</v>
       </c>
       <c r="H66" t="inlineStr">
         <is>
@@ -3160,7 +3160,7 @@
         </is>
       </c>
       <c r="G67" t="n">
-        <v>1.15</v>
+        <v>0.75</v>
       </c>
       <c r="H67" t="inlineStr">
         <is>
@@ -3192,7 +3192,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -3201,7 +3201,7 @@
         </is>
       </c>
       <c r="G68" t="n">
-        <v>0.71</v>
+        <v>0.84</v>
       </c>
       <c r="H68" t="inlineStr">
         <is>
@@ -3233,7 +3233,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -3242,7 +3242,7 @@
         </is>
       </c>
       <c r="G69" t="n">
-        <v>0.91</v>
+        <v>0.89</v>
       </c>
       <c r="H69" t="inlineStr">
         <is>
@@ -3274,7 +3274,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -3283,7 +3283,7 @@
         </is>
       </c>
       <c r="G70" t="n">
-        <v>1.14</v>
+        <v>0.67</v>
       </c>
       <c r="H70" t="inlineStr">
         <is>
@@ -3315,7 +3315,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -3324,7 +3324,7 @@
         </is>
       </c>
       <c r="G71" t="n">
-        <v>0.45</v>
+        <v>0.98</v>
       </c>
       <c r="H71" t="inlineStr">
         <is>
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -3365,7 +3365,7 @@
         </is>
       </c>
       <c r="G72" t="n">
-        <v>0.76</v>
+        <v>0.87</v>
       </c>
       <c r="H72" t="inlineStr">
         <is>
@@ -3397,7 +3397,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -3406,7 +3406,7 @@
         </is>
       </c>
       <c r="G73" t="n">
-        <v>0.71</v>
+        <v>1.11</v>
       </c>
       <c r="H73" t="inlineStr">
         <is>
@@ -3447,7 +3447,7 @@
         </is>
       </c>
       <c r="G74" t="n">
-        <v>1.11</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H74" t="inlineStr">
         <is>
@@ -3488,7 +3488,7 @@
         </is>
       </c>
       <c r="G75" t="n">
-        <v>0.83</v>
+        <v>0.7</v>
       </c>
       <c r="H75" t="inlineStr">
         <is>
@@ -3520,7 +3520,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3529,7 +3529,7 @@
         </is>
       </c>
       <c r="G76" t="n">
-        <v>1.08</v>
+        <v>0.95</v>
       </c>
       <c r="H76" t="inlineStr">
         <is>
@@ -3561,7 +3561,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3570,7 +3570,7 @@
         </is>
       </c>
       <c r="G77" t="n">
-        <v>0.99</v>
+        <v>0.92</v>
       </c>
       <c r="H77" t="inlineStr">
         <is>
@@ -3602,7 +3602,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3611,7 +3611,7 @@
         </is>
       </c>
       <c r="G78" t="n">
-        <v>0.49</v>
+        <v>1.11</v>
       </c>
       <c r="H78" t="inlineStr">
         <is>
@@ -3643,7 +3643,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3652,7 +3652,7 @@
         </is>
       </c>
       <c r="G79" t="n">
-        <v>0.51</v>
+        <v>1.08</v>
       </c>
       <c r="H79" t="inlineStr">
         <is>
@@ -3684,7 +3684,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3693,7 +3693,7 @@
         </is>
       </c>
       <c r="G80" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.62</v>
       </c>
       <c r="H80" t="inlineStr">
         <is>
@@ -3725,7 +3725,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3734,7 +3734,7 @@
         </is>
       </c>
       <c r="G81" t="n">
-        <v>1.12</v>
+        <v>0.82</v>
       </c>
       <c r="H81" t="inlineStr">
         <is>
@@ -3766,7 +3766,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3775,7 +3775,7 @@
         </is>
       </c>
       <c r="G82" t="n">
-        <v>0.92</v>
+        <v>1.13</v>
       </c>
       <c r="H82" t="inlineStr">
         <is>
@@ -3807,7 +3807,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3816,7 +3816,7 @@
         </is>
       </c>
       <c r="G83" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="H83" t="inlineStr">
         <is>
@@ -3848,7 +3848,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3857,7 +3857,7 @@
         </is>
       </c>
       <c r="G84" t="n">
-        <v>0.64</v>
+        <v>0.45</v>
       </c>
       <c r="H84" t="inlineStr">
         <is>
@@ -3889,7 +3889,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3898,7 +3898,7 @@
         </is>
       </c>
       <c r="G85" t="n">
-        <v>1.03</v>
+        <v>0.75</v>
       </c>
       <c r="H85" t="inlineStr">
         <is>
@@ -3930,7 +3930,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3939,7 +3939,7 @@
         </is>
       </c>
       <c r="G86" t="n">
-        <v>0.49</v>
+        <v>0.66</v>
       </c>
       <c r="H86" t="inlineStr">
         <is>
@@ -3980,7 +3980,7 @@
         </is>
       </c>
       <c r="G87" t="n">
-        <v>1</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H87" t="inlineStr">
         <is>
@@ -4021,7 +4021,7 @@
         </is>
       </c>
       <c r="G88" t="n">
-        <v>0.68</v>
+        <v>0.91</v>
       </c>
       <c r="H88" t="inlineStr">
         <is>
@@ -4062,7 +4062,7 @@
         </is>
       </c>
       <c r="G89" t="n">
-        <v>0.48</v>
+        <v>0.76</v>
       </c>
       <c r="H89" t="inlineStr">
         <is>
@@ -4094,7 +4094,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -4103,7 +4103,7 @@
         </is>
       </c>
       <c r="G90" t="n">
-        <v>0.75</v>
+        <v>0.65</v>
       </c>
       <c r="H90" t="inlineStr">
         <is>
@@ -4135,7 +4135,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -4144,7 +4144,7 @@
         </is>
       </c>
       <c r="G91" t="n">
-        <v>0.74</v>
+        <v>0.64</v>
       </c>
       <c r="H91" t="inlineStr">
         <is>
@@ -4176,7 +4176,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -4185,7 +4185,7 @@
         </is>
       </c>
       <c r="G92" t="n">
-        <v>1</v>
+        <v>0.98</v>
       </c>
       <c r="H92" t="inlineStr">
         <is>
@@ -4217,7 +4217,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -4226,7 +4226,7 @@
         </is>
       </c>
       <c r="G93" t="n">
-        <v>0.44</v>
+        <v>1.11</v>
       </c>
       <c r="H93" t="inlineStr">
         <is>
@@ -4258,7 +4258,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -4267,7 +4267,7 @@
         </is>
       </c>
       <c r="G94" t="n">
-        <v>0.86</v>
+        <v>0.66</v>
       </c>
       <c r="H94" t="inlineStr">
         <is>
@@ -4299,7 +4299,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -4308,7 +4308,7 @@
         </is>
       </c>
       <c r="G95" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.65</v>
       </c>
       <c r="H95" t="inlineStr">
         <is>
@@ -4349,7 +4349,7 @@
         </is>
       </c>
       <c r="G96" t="n">
-        <v>0.61</v>
+        <v>0.7</v>
       </c>
       <c r="H96" t="inlineStr">
         <is>
@@ -4381,7 +4381,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -4390,7 +4390,7 @@
         </is>
       </c>
       <c r="G97" t="n">
-        <v>0.54</v>
+        <v>0.52</v>
       </c>
       <c r="H97" t="inlineStr">
         <is>
@@ -4431,7 +4431,7 @@
         </is>
       </c>
       <c r="G98" t="n">
-        <v>0.93</v>
+        <v>1.06</v>
       </c>
       <c r="H98" t="inlineStr">
         <is>
@@ -4463,7 +4463,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -4472,7 +4472,7 @@
         </is>
       </c>
       <c r="G99" t="n">
-        <v>0.45</v>
+        <v>0.43</v>
       </c>
       <c r="H99" t="inlineStr">
         <is>
@@ -4504,7 +4504,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -4513,7 +4513,7 @@
         </is>
       </c>
       <c r="G100" t="n">
-        <v>0.42</v>
+        <v>0.75</v>
       </c>
       <c r="H100" t="inlineStr">
         <is>
@@ -4545,7 +4545,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -4554,7 +4554,7 @@
         </is>
       </c>
       <c r="G101" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="H101" t="inlineStr">
         <is>
@@ -4586,7 +4586,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -4595,7 +4595,7 @@
         </is>
       </c>
       <c r="G102" t="n">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="H102" t="inlineStr">
         <is>
@@ -4627,7 +4627,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4636,7 +4636,7 @@
         </is>
       </c>
       <c r="G103" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.76</v>
       </c>
       <c r="H103" t="inlineStr">
         <is>
@@ -4668,7 +4668,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4677,7 +4677,7 @@
         </is>
       </c>
       <c r="G104" t="n">
-        <v>1</v>
+        <v>0.61</v>
       </c>
       <c r="H104" t="inlineStr">
         <is>
@@ -4709,7 +4709,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4718,7 +4718,7 @@
         </is>
       </c>
       <c r="G105" t="n">
-        <v>0.46</v>
+        <v>1.03</v>
       </c>
       <c r="H105" t="inlineStr">
         <is>
@@ -4750,7 +4750,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4759,7 +4759,7 @@
         </is>
       </c>
       <c r="G106" t="n">
-        <v>0.9</v>
+        <v>1.08</v>
       </c>
       <c r="H106" t="inlineStr">
         <is>
@@ -4791,7 +4791,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4800,7 +4800,7 @@
         </is>
       </c>
       <c r="G107" t="n">
-        <v>0.66</v>
+        <v>0.65</v>
       </c>
       <c r="H107" t="inlineStr">
         <is>
@@ -4832,7 +4832,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4841,7 +4841,7 @@
         </is>
       </c>
       <c r="G108" t="n">
-        <v>0.98</v>
+        <v>1.01</v>
       </c>
       <c r="H108" t="inlineStr">
         <is>
@@ -4873,7 +4873,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4882,7 +4882,7 @@
         </is>
       </c>
       <c r="G109" t="n">
-        <v>0.47</v>
+        <v>1.1</v>
       </c>
       <c r="H109" t="inlineStr">
         <is>
@@ -4914,7 +4914,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4923,7 +4923,7 @@
         </is>
       </c>
       <c r="G110" t="n">
-        <v>0.66</v>
+        <v>0.64</v>
       </c>
       <c r="H110" t="inlineStr">
         <is>
@@ -4955,7 +4955,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4964,7 +4964,7 @@
         </is>
       </c>
       <c r="G111" t="n">
-        <v>1.15</v>
+        <v>0.6</v>
       </c>
       <c r="H111" t="inlineStr">
         <is>
@@ -4996,7 +4996,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -5005,7 +5005,7 @@
         </is>
       </c>
       <c r="G112" t="n">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="H112" t="inlineStr">
         <is>
@@ -5037,7 +5037,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -5046,7 +5046,7 @@
         </is>
       </c>
       <c r="G113" t="n">
-        <v>0.7</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H113" t="inlineStr">
         <is>
@@ -5087,7 +5087,7 @@
         </is>
       </c>
       <c r="G114" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.71</v>
       </c>
       <c r="H114" t="inlineStr">
         <is>
@@ -5119,7 +5119,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -5128,7 +5128,7 @@
         </is>
       </c>
       <c r="G115" t="n">
-        <v>0.72</v>
+        <v>0.93</v>
       </c>
       <c r="H115" t="inlineStr">
         <is>
@@ -5160,7 +5160,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -5169,7 +5169,7 @@
         </is>
       </c>
       <c r="G116" t="n">
-        <v>0.88</v>
+        <v>0.83</v>
       </c>
       <c r="H116" t="inlineStr">
         <is>
@@ -5201,7 +5201,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -5210,7 +5210,7 @@
         </is>
       </c>
       <c r="G117" t="n">
-        <v>0.53</v>
+        <v>0.46</v>
       </c>
       <c r="H117" t="inlineStr">
         <is>
@@ -5242,7 +5242,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -5251,7 +5251,7 @@
         </is>
       </c>
       <c r="G118" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.57</v>
       </c>
       <c r="H118" t="inlineStr">
         <is>
@@ -5283,7 +5283,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -5292,7 +5292,7 @@
         </is>
       </c>
       <c r="G119" t="n">
-        <v>0.43</v>
+        <v>0.96</v>
       </c>
       <c r="H119" t="inlineStr">
         <is>
@@ -5324,7 +5324,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -5333,7 +5333,7 @@
         </is>
       </c>
       <c r="G120" t="n">
-        <v>0.73</v>
+        <v>0.47</v>
       </c>
       <c r="H120" t="inlineStr">
         <is>
@@ -5365,7 +5365,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -5374,7 +5374,7 @@
         </is>
       </c>
       <c r="G121" t="n">
-        <v>0.63</v>
+        <v>0.48</v>
       </c>
       <c r="H121" t="inlineStr">
         <is>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -5415,7 +5415,7 @@
         </is>
       </c>
       <c r="G122" t="n">
-        <v>0.48</v>
+        <v>0.97</v>
       </c>
       <c r="H122" t="inlineStr">
         <is>
@@ -5447,7 +5447,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -5456,7 +5456,7 @@
         </is>
       </c>
       <c r="G123" t="n">
-        <v>0.47</v>
+        <v>1.06</v>
       </c>
       <c r="H123" t="inlineStr">
         <is>
@@ -5497,7 +5497,7 @@
         </is>
       </c>
       <c r="G124" t="n">
-        <v>0.77</v>
+        <v>1.08</v>
       </c>
       <c r="H124" t="inlineStr">
         <is>
@@ -5529,7 +5529,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -5538,7 +5538,7 @@
         </is>
       </c>
       <c r="G125" t="n">
-        <v>0.66</v>
+        <v>0.5</v>
       </c>
       <c r="H125" t="inlineStr">
         <is>
@@ -5570,7 +5570,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -5579,7 +5579,7 @@
         </is>
       </c>
       <c r="G126" t="n">
-        <v>0.61</v>
+        <v>0.64</v>
       </c>
       <c r="H126" t="inlineStr">
         <is>
@@ -5620,7 +5620,7 @@
         </is>
       </c>
       <c r="G127" t="n">
-        <v>0.72</v>
+        <v>0.93</v>
       </c>
       <c r="H127" t="inlineStr">
         <is>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -5661,7 +5661,7 @@
         </is>
       </c>
       <c r="G128" t="n">
-        <v>1.05</v>
+        <v>0.77</v>
       </c>
       <c r="H128" t="inlineStr">
         <is>
@@ -5693,7 +5693,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -5702,7 +5702,7 @@
         </is>
       </c>
       <c r="G129" t="n">
-        <v>0.57</v>
+        <v>1.11</v>
       </c>
       <c r="H129" t="inlineStr">
         <is>
@@ -5734,7 +5734,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -5743,7 +5743,7 @@
         </is>
       </c>
       <c r="G130" t="n">
-        <v>0.75</v>
+        <v>1.11</v>
       </c>
       <c r="H130" t="inlineStr">
         <is>
@@ -5775,7 +5775,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -5784,7 +5784,7 @@
         </is>
       </c>
       <c r="G131" t="n">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="H131" t="inlineStr">
         <is>
@@ -5816,7 +5816,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -5825,7 +5825,7 @@
         </is>
       </c>
       <c r="G132" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="H132" t="inlineStr">
         <is>
@@ -5857,7 +5857,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -5866,7 +5866,7 @@
         </is>
       </c>
       <c r="G133" t="n">
-        <v>1.07</v>
+        <v>0.79</v>
       </c>
       <c r="H133" t="inlineStr">
         <is>
@@ -5898,7 +5898,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -5907,7 +5907,7 @@
         </is>
       </c>
       <c r="G134" t="n">
-        <v>0.78</v>
+        <v>1.11</v>
       </c>
       <c r="H134" t="inlineStr">
         <is>
@@ -5948,7 +5948,7 @@
         </is>
       </c>
       <c r="G135" t="n">
-        <v>0.83</v>
+        <v>0.89</v>
       </c>
       <c r="H135" t="inlineStr">
         <is>
@@ -5980,7 +5980,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -5989,7 +5989,7 @@
         </is>
       </c>
       <c r="G136" t="n">
-        <v>0.44</v>
+        <v>0.75</v>
       </c>
       <c r="H136" t="inlineStr">
         <is>
@@ -6021,7 +6021,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -6030,7 +6030,7 @@
         </is>
       </c>
       <c r="G137" t="n">
-        <v>0.78</v>
+        <v>1.03</v>
       </c>
       <c r="H137" t="inlineStr">
         <is>
@@ -6062,7 +6062,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -6071,7 +6071,7 @@
         </is>
       </c>
       <c r="G138" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.75</v>
       </c>
       <c r="H138" t="inlineStr">
         <is>
@@ -6103,7 +6103,7 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -6112,7 +6112,7 @@
         </is>
       </c>
       <c r="G139" t="n">
-        <v>1.05</v>
+        <v>0.76</v>
       </c>
       <c r="H139" t="inlineStr">
         <is>
@@ -6153,7 +6153,7 @@
         </is>
       </c>
       <c r="G140" t="n">
-        <v>0.54</v>
+        <v>0.66</v>
       </c>
       <c r="H140" t="inlineStr">
         <is>
@@ -6185,7 +6185,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -6194,7 +6194,7 @@
         </is>
       </c>
       <c r="G141" t="n">
-        <v>0.61</v>
+        <v>0.6</v>
       </c>
       <c r="H141" t="inlineStr">
         <is>
@@ -6235,7 +6235,7 @@
         </is>
       </c>
       <c r="G142" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.89</v>
       </c>
       <c r="H142" t="inlineStr">
         <is>
@@ -6267,7 +6267,7 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -6276,7 +6276,7 @@
         </is>
       </c>
       <c r="G143" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="H143" t="inlineStr">
         <is>
@@ -6308,7 +6308,7 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -6317,7 +6317,7 @@
         </is>
       </c>
       <c r="G144" t="n">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="H144" t="inlineStr">
         <is>
@@ -6349,7 +6349,7 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
@@ -6358,7 +6358,7 @@
         </is>
       </c>
       <c r="G145" t="n">
-        <v>0.43</v>
+        <v>0.96</v>
       </c>
       <c r="H145" t="inlineStr">
         <is>
@@ -6390,7 +6390,7 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
@@ -6399,7 +6399,7 @@
         </is>
       </c>
       <c r="G146" t="n">
-        <v>0.98</v>
+        <v>0.59</v>
       </c>
       <c r="H146" t="inlineStr">
         <is>
@@ -6431,7 +6431,7 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
@@ -6440,7 +6440,7 @@
         </is>
       </c>
       <c r="G147" t="n">
-        <v>0.68</v>
+        <v>1.01</v>
       </c>
       <c r="H147" t="inlineStr">
         <is>
@@ -6472,7 +6472,7 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
@@ -6481,7 +6481,7 @@
         </is>
       </c>
       <c r="G148" t="n">
-        <v>1.08</v>
+        <v>0.63</v>
       </c>
       <c r="H148" t="inlineStr">
         <is>
@@ -6513,7 +6513,7 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
@@ -6522,7 +6522,7 @@
         </is>
       </c>
       <c r="G149" t="n">
-        <v>1.14</v>
+        <v>1.06</v>
       </c>
       <c r="H149" t="inlineStr">
         <is>
@@ -6563,7 +6563,7 @@
         </is>
       </c>
       <c r="G150" t="n">
-        <v>0.66</v>
+        <v>0.95</v>
       </c>
       <c r="H150" t="inlineStr">
         <is>
@@ -6595,7 +6595,7 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
@@ -6604,7 +6604,7 @@
         </is>
       </c>
       <c r="G151" t="n">
-        <v>0.86</v>
+        <v>0.97</v>
       </c>
       <c r="H151" t="inlineStr">
         <is>
@@ -6636,7 +6636,7 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
@@ -6645,7 +6645,7 @@
         </is>
       </c>
       <c r="G152" t="n">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="H152" t="inlineStr">
         <is>
@@ -6677,7 +6677,7 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
@@ -6686,7 +6686,7 @@
         </is>
       </c>
       <c r="G153" t="n">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="H153" t="inlineStr">
         <is>
@@ -6727,7 +6727,7 @@
         </is>
       </c>
       <c r="G154" t="n">
-        <v>0.83</v>
+        <v>0.92</v>
       </c>
       <c r="H154" t="inlineStr">
         <is>
@@ -6759,7 +6759,7 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
@@ -6768,7 +6768,7 @@
         </is>
       </c>
       <c r="G155" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="H155" t="inlineStr">
         <is>
@@ -6800,7 +6800,7 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
@@ -6809,7 +6809,7 @@
         </is>
       </c>
       <c r="G156" t="n">
-        <v>1.07</v>
+        <v>0.59</v>
       </c>
       <c r="H156" t="inlineStr">
         <is>
@@ -6841,7 +6841,7 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
@@ -6850,7 +6850,7 @@
         </is>
       </c>
       <c r="G157" t="n">
-        <v>0.87</v>
+        <v>1.14</v>
       </c>
       <c r="H157" t="inlineStr">
         <is>
@@ -6882,7 +6882,7 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
@@ -6964,7 +6964,7 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
@@ -6973,7 +6973,7 @@
         </is>
       </c>
       <c r="G160" t="n">
-        <v>1.04</v>
+        <v>1.13</v>
       </c>
       <c r="H160" t="inlineStr">
         <is>
@@ -7014,7 +7014,7 @@
         </is>
       </c>
       <c r="G161" t="n">
-        <v>0.79</v>
+        <v>1.12</v>
       </c>
       <c r="H161" t="inlineStr">
         <is>
@@ -7055,7 +7055,7 @@
         </is>
       </c>
       <c r="G162" t="n">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="H162" t="inlineStr">
         <is>
@@ -7096,7 +7096,7 @@
         </is>
       </c>
       <c r="G163" t="n">
-        <v>0.86</v>
+        <v>1</v>
       </c>
       <c r="H163" t="inlineStr">
         <is>
@@ -7128,7 +7128,7 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
@@ -7137,7 +7137,7 @@
         </is>
       </c>
       <c r="G164" t="n">
-        <v>1.11</v>
+        <v>0.43</v>
       </c>
       <c r="H164" t="inlineStr">
         <is>
@@ -7178,7 +7178,7 @@
         </is>
       </c>
       <c r="G165" t="n">
-        <v>0.71</v>
+        <v>0.91</v>
       </c>
       <c r="H165" t="inlineStr">
         <is>
@@ -7210,7 +7210,7 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
@@ -7219,7 +7219,7 @@
         </is>
       </c>
       <c r="G166" t="n">
-        <v>0.75</v>
+        <v>0.43</v>
       </c>
       <c r="H166" t="inlineStr">
         <is>
@@ -7251,7 +7251,7 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
@@ -7260,7 +7260,7 @@
         </is>
       </c>
       <c r="G167" t="n">
-        <v>0.46</v>
+        <v>1.04</v>
       </c>
       <c r="H167" t="inlineStr">
         <is>
@@ -7292,7 +7292,7 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
@@ -7301,7 +7301,7 @@
         </is>
       </c>
       <c r="G168" t="n">
-        <v>0.98</v>
+        <v>1.05</v>
       </c>
       <c r="H168" t="inlineStr">
         <is>
@@ -7333,7 +7333,7 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
@@ -7342,7 +7342,7 @@
         </is>
       </c>
       <c r="G169" t="n">
-        <v>1.01</v>
+        <v>0.49</v>
       </c>
       <c r="H169" t="inlineStr">
         <is>
@@ -7374,7 +7374,7 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
@@ -7383,7 +7383,7 @@
         </is>
       </c>
       <c r="G170" t="n">
-        <v>0.48</v>
+        <v>0.73</v>
       </c>
       <c r="H170" t="inlineStr">
         <is>
@@ -7415,7 +7415,7 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
@@ -7424,7 +7424,7 @@
         </is>
       </c>
       <c r="G171" t="n">
-        <v>0.54</v>
+        <v>0.89</v>
       </c>
       <c r="H171" t="inlineStr">
         <is>
@@ -7456,7 +7456,7 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
@@ -7465,7 +7465,7 @@
         </is>
       </c>
       <c r="G172" t="n">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="H172" t="inlineStr">
         <is>
@@ -7506,7 +7506,7 @@
         </is>
       </c>
       <c r="G173" t="n">
-        <v>0.55</v>
+        <v>0.64</v>
       </c>
       <c r="H173" t="inlineStr">
         <is>
@@ -7538,7 +7538,7 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
@@ -7547,7 +7547,7 @@
         </is>
       </c>
       <c r="G174" t="n">
-        <v>0.54</v>
+        <v>0.66</v>
       </c>
       <c r="H174" t="inlineStr">
         <is>
@@ -7579,7 +7579,7 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
@@ -7588,7 +7588,7 @@
         </is>
       </c>
       <c r="G175" t="n">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="H175" t="inlineStr">
         <is>
@@ -7620,7 +7620,7 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
@@ -7629,7 +7629,7 @@
         </is>
       </c>
       <c r="G176" t="n">
-        <v>0.89</v>
+        <v>0.57</v>
       </c>
       <c r="H176" t="inlineStr">
         <is>
@@ -7661,7 +7661,7 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
@@ -7670,7 +7670,7 @@
         </is>
       </c>
       <c r="G177" t="n">
-        <v>0.59</v>
+        <v>0.58</v>
       </c>
       <c r="H177" t="inlineStr">
         <is>
@@ -7711,7 +7711,7 @@
         </is>
       </c>
       <c r="G178" t="n">
-        <v>1.04</v>
+        <v>0.58</v>
       </c>
       <c r="H178" t="inlineStr">
         <is>
@@ -7743,7 +7743,7 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
@@ -7752,7 +7752,7 @@
         </is>
       </c>
       <c r="G179" t="n">
-        <v>0.74</v>
+        <v>0.51</v>
       </c>
       <c r="H179" t="inlineStr">
         <is>
@@ -7793,7 +7793,7 @@
         </is>
       </c>
       <c r="G180" t="n">
-        <v>0.43</v>
+        <v>1.11</v>
       </c>
       <c r="H180" t="inlineStr">
         <is>
@@ -7825,7 +7825,7 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
@@ -7834,7 +7834,7 @@
         </is>
       </c>
       <c r="G181" t="n">
-        <v>0.6</v>
+        <v>0.86</v>
       </c>
       <c r="H181" t="inlineStr">
         <is>
@@ -7866,7 +7866,7 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
@@ -7875,7 +7875,7 @@
         </is>
       </c>
       <c r="G182" t="n">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="H182" t="inlineStr">
         <is>
@@ -7907,7 +7907,7 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
@@ -7916,7 +7916,7 @@
         </is>
       </c>
       <c r="G183" t="n">
-        <v>0.55</v>
+        <v>0.83</v>
       </c>
       <c r="H183" t="inlineStr">
         <is>
@@ -7948,7 +7948,7 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
@@ -7957,7 +7957,7 @@
         </is>
       </c>
       <c r="G184" t="n">
-        <v>0.87</v>
+        <v>0.93</v>
       </c>
       <c r="H184" t="inlineStr">
         <is>
@@ -7998,7 +7998,7 @@
         </is>
       </c>
       <c r="G185" t="n">
-        <v>0.97</v>
+        <v>1.06</v>
       </c>
       <c r="H185" t="inlineStr">
         <is>
@@ -8030,7 +8030,7 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
@@ -8039,7 +8039,7 @@
         </is>
       </c>
       <c r="G186" t="n">
-        <v>0.43</v>
+        <v>0.82</v>
       </c>
       <c r="H186" t="inlineStr">
         <is>
@@ -8071,7 +8071,7 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
@@ -8080,7 +8080,7 @@
         </is>
       </c>
       <c r="G187" t="n">
-        <v>0.53</v>
+        <v>0.75</v>
       </c>
       <c r="H187" t="inlineStr">
         <is>
@@ -8112,7 +8112,7 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
@@ -8121,7 +8121,7 @@
         </is>
       </c>
       <c r="G188" t="n">
-        <v>1.11</v>
+        <v>0.85</v>
       </c>
       <c r="H188" t="inlineStr">
         <is>
@@ -8153,7 +8153,7 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
@@ -8162,7 +8162,7 @@
         </is>
       </c>
       <c r="G189" t="n">
-        <v>1.1</v>
+        <v>0.45</v>
       </c>
       <c r="H189" t="inlineStr">
         <is>
@@ -8203,7 +8203,7 @@
         </is>
       </c>
       <c r="G190" t="n">
-        <v>0.9</v>
+        <v>0.77</v>
       </c>
       <c r="H190" t="inlineStr">
         <is>
@@ -8244,7 +8244,7 @@
         </is>
       </c>
       <c r="G191" t="n">
-        <v>0.53</v>
+        <v>1.05</v>
       </c>
       <c r="H191" t="inlineStr">
         <is>
@@ -8285,7 +8285,7 @@
         </is>
       </c>
       <c r="G192" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="H192" t="inlineStr">
         <is>
@@ -8317,7 +8317,7 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
@@ -8326,7 +8326,7 @@
         </is>
       </c>
       <c r="G193" t="n">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="H193" t="inlineStr">
         <is>
@@ -8358,7 +8358,7 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
@@ -8367,7 +8367,7 @@
         </is>
       </c>
       <c r="G194" t="n">
-        <v>0.5</v>
+        <v>0.73</v>
       </c>
       <c r="H194" t="inlineStr">
         <is>
@@ -8399,7 +8399,7 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
@@ -8408,7 +8408,7 @@
         </is>
       </c>
       <c r="G195" t="n">
-        <v>0.55</v>
+        <v>0.57</v>
       </c>
       <c r="H195" t="inlineStr">
         <is>
@@ -8449,7 +8449,7 @@
         </is>
       </c>
       <c r="G196" t="n">
-        <v>0.85</v>
+        <v>0.7</v>
       </c>
       <c r="H196" t="inlineStr">
         <is>
@@ -8490,7 +8490,7 @@
         </is>
       </c>
       <c r="G197" t="n">
-        <v>0.63</v>
+        <v>0.66</v>
       </c>
       <c r="H197" t="inlineStr">
         <is>
@@ -8522,7 +8522,7 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
@@ -8531,7 +8531,7 @@
         </is>
       </c>
       <c r="G198" t="n">
-        <v>0.68</v>
+        <v>0.95</v>
       </c>
       <c r="H198" t="inlineStr">
         <is>
@@ -8572,7 +8572,7 @@
         </is>
       </c>
       <c r="G199" t="n">
-        <v>0.7</v>
+        <v>0.89</v>
       </c>
       <c r="H199" t="inlineStr">
         <is>
@@ -8604,7 +8604,7 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
@@ -8613,7 +8613,7 @@
         </is>
       </c>
       <c r="G200" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.89</v>
       </c>
       <c r="H200" t="inlineStr">
         <is>
@@ -8654,7 +8654,7 @@
         </is>
       </c>
       <c r="G201" t="n">
-        <v>0.74</v>
+        <v>0.67</v>
       </c>
       <c r="H201" t="inlineStr">
         <is>
@@ -8695,7 +8695,7 @@
         </is>
       </c>
       <c r="G202" t="n">
-        <v>0.59</v>
+        <v>0.73</v>
       </c>
       <c r="H202" t="inlineStr">
         <is>
@@ -8727,7 +8727,7 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
@@ -8736,7 +8736,7 @@
         </is>
       </c>
       <c r="G203" t="n">
-        <v>0.64</v>
+        <v>1.02</v>
       </c>
       <c r="H203" t="inlineStr">
         <is>
@@ -8777,7 +8777,7 @@
         </is>
       </c>
       <c r="G204" t="n">
-        <v>0.78</v>
+        <v>0.91</v>
       </c>
       <c r="H204" t="inlineStr">
         <is>
@@ -8818,7 +8818,7 @@
         </is>
       </c>
       <c r="G205" t="n">
-        <v>0.65</v>
+        <v>0.79</v>
       </c>
       <c r="H205" t="inlineStr">
         <is>
@@ -8850,7 +8850,7 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
@@ -8859,7 +8859,7 @@
         </is>
       </c>
       <c r="G206" t="n">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="H206" t="inlineStr">
         <is>
@@ -8900,7 +8900,7 @@
         </is>
       </c>
       <c r="G207" t="n">
-        <v>0.44</v>
+        <v>0.66</v>
       </c>
       <c r="H207" t="inlineStr">
         <is>
@@ -8932,7 +8932,7 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
@@ -8941,7 +8941,7 @@
         </is>
       </c>
       <c r="G208" t="n">
-        <v>0.91</v>
+        <v>1.01</v>
       </c>
       <c r="H208" t="inlineStr">
         <is>
@@ -8973,7 +8973,7 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
@@ -8982,7 +8982,7 @@
         </is>
       </c>
       <c r="G209" t="n">
-        <v>0.85</v>
+        <v>0.93</v>
       </c>
       <c r="H209" t="inlineStr">
         <is>
@@ -9014,7 +9014,7 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
@@ -9023,7 +9023,7 @@
         </is>
       </c>
       <c r="G210" t="n">
-        <v>1.02</v>
+        <v>0.42</v>
       </c>
       <c r="H210" t="inlineStr">
         <is>
@@ -9055,7 +9055,7 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
@@ -9064,7 +9064,7 @@
         </is>
       </c>
       <c r="G211" t="n">
-        <v>0.59</v>
+        <v>1.07</v>
       </c>
       <c r="H211" t="inlineStr">
         <is>
@@ -9096,7 +9096,7 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
@@ -9105,7 +9105,7 @@
         </is>
       </c>
       <c r="G212" t="n">
-        <v>0.88</v>
+        <v>0.71</v>
       </c>
       <c r="H212" t="inlineStr">
         <is>
@@ -9137,7 +9137,7 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
@@ -9146,7 +9146,7 @@
         </is>
       </c>
       <c r="G213" t="n">
-        <v>0.93</v>
+        <v>0.75</v>
       </c>
       <c r="H213" t="inlineStr">
         <is>
@@ -9178,7 +9178,7 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
@@ -9187,7 +9187,7 @@
         </is>
       </c>
       <c r="G214" t="n">
-        <v>0.63</v>
+        <v>0.67</v>
       </c>
       <c r="H214" t="inlineStr">
         <is>
@@ -9228,7 +9228,7 @@
         </is>
       </c>
       <c r="G215" t="n">
-        <v>0.42</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H215" t="inlineStr">
         <is>
@@ -9260,7 +9260,7 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
@@ -9269,7 +9269,7 @@
         </is>
       </c>
       <c r="G216" t="n">
-        <v>1.1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H216" t="inlineStr">
         <is>
@@ -9301,7 +9301,7 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
@@ -9310,7 +9310,7 @@
         </is>
       </c>
       <c r="G217" t="n">
-        <v>0.43</v>
+        <v>0.83</v>
       </c>
       <c r="H217" t="inlineStr">
         <is>
@@ -9342,7 +9342,7 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
@@ -9351,7 +9351,7 @@
         </is>
       </c>
       <c r="G218" t="n">
-        <v>0.75</v>
+        <v>1.02</v>
       </c>
       <c r="H218" t="inlineStr">
         <is>
@@ -9383,7 +9383,7 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
@@ -9392,7 +9392,7 @@
         </is>
       </c>
       <c r="G219" t="n">
-        <v>1.11</v>
+        <v>0.48</v>
       </c>
       <c r="H219" t="inlineStr">
         <is>
@@ -9424,7 +9424,7 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
@@ -9433,7 +9433,7 @@
         </is>
       </c>
       <c r="G220" t="n">
-        <v>0.93</v>
+        <v>0.9</v>
       </c>
       <c r="H220" t="inlineStr">
         <is>
@@ -9465,7 +9465,7 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
@@ -9474,7 +9474,7 @@
         </is>
       </c>
       <c r="G221" t="n">
-        <v>1</v>
+        <v>1.07</v>
       </c>
       <c r="H221" t="inlineStr">
         <is>
@@ -9506,7 +9506,7 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
@@ -9515,7 +9515,7 @@
         </is>
       </c>
       <c r="G222" t="n">
-        <v>1</v>
+        <v>0.48</v>
       </c>
       <c r="H222" t="inlineStr">
         <is>
@@ -9547,7 +9547,7 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
@@ -9556,7 +9556,7 @@
         </is>
       </c>
       <c r="G223" t="n">
-        <v>0.62</v>
+        <v>1.07</v>
       </c>
       <c r="H223" t="inlineStr">
         <is>
@@ -9588,7 +9588,7 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
@@ -9597,7 +9597,7 @@
         </is>
       </c>
       <c r="G224" t="n">
-        <v>0.43</v>
+        <v>0.62</v>
       </c>
       <c r="H224" t="inlineStr">
         <is>
@@ -9629,7 +9629,7 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
@@ -9638,7 +9638,7 @@
         </is>
       </c>
       <c r="G225" t="n">
-        <v>0.91</v>
+        <v>1.01</v>
       </c>
       <c r="H225" t="inlineStr">
         <is>
@@ -9670,7 +9670,7 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
@@ -9679,7 +9679,7 @@
         </is>
       </c>
       <c r="G226" t="n">
-        <v>0.68</v>
+        <v>0.74</v>
       </c>
       <c r="H226" t="inlineStr">
         <is>
@@ -9711,7 +9711,7 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
@@ -9720,7 +9720,7 @@
         </is>
       </c>
       <c r="G227" t="n">
-        <v>0.42</v>
+        <v>0.66</v>
       </c>
       <c r="H227" t="inlineStr">
         <is>
@@ -9752,7 +9752,7 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
@@ -9761,7 +9761,7 @@
         </is>
       </c>
       <c r="G228" t="n">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="H228" t="inlineStr">
         <is>
@@ -9793,7 +9793,7 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
@@ -9802,7 +9802,7 @@
         </is>
       </c>
       <c r="G229" t="n">
-        <v>0.6</v>
+        <v>0.46</v>
       </c>
       <c r="H229" t="inlineStr">
         <is>
@@ -9834,7 +9834,7 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
@@ -9843,7 +9843,7 @@
         </is>
       </c>
       <c r="G230" t="n">
-        <v>0.45</v>
+        <v>0.47</v>
       </c>
       <c r="H230" t="inlineStr">
         <is>
@@ -9875,7 +9875,7 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
@@ -9884,7 +9884,7 @@
         </is>
       </c>
       <c r="G231" t="n">
-        <v>0.52</v>
+        <v>1.05</v>
       </c>
       <c r="H231" t="inlineStr">
         <is>
@@ -9925,7 +9925,7 @@
         </is>
       </c>
       <c r="G232" t="n">
-        <v>0.74</v>
+        <v>0.68</v>
       </c>
       <c r="H232" t="inlineStr">
         <is>
@@ -9957,7 +9957,7 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
@@ -9966,7 +9966,7 @@
         </is>
       </c>
       <c r="G233" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H233" t="inlineStr">
         <is>
@@ -9998,7 +9998,7 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
@@ -10007,7 +10007,7 @@
         </is>
       </c>
       <c r="G234" t="n">
-        <v>0.59</v>
+        <v>1.11</v>
       </c>
       <c r="H234" t="inlineStr">
         <is>
@@ -10039,7 +10039,7 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
@@ -10048,7 +10048,7 @@
         </is>
       </c>
       <c r="G235" t="n">
-        <v>0.84</v>
+        <v>1.13</v>
       </c>
       <c r="H235" t="inlineStr">
         <is>
@@ -10080,7 +10080,7 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
@@ -10089,7 +10089,7 @@
         </is>
       </c>
       <c r="G236" t="n">
-        <v>0.84</v>
+        <v>1.15</v>
       </c>
       <c r="H236" t="inlineStr">
         <is>
@@ -10121,7 +10121,7 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
@@ -10130,7 +10130,7 @@
         </is>
       </c>
       <c r="G237" t="n">
-        <v>0.83</v>
+        <v>0.79</v>
       </c>
       <c r="H237" t="inlineStr">
         <is>
@@ -10162,7 +10162,7 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
@@ -10171,7 +10171,7 @@
         </is>
       </c>
       <c r="G238" t="n">
-        <v>0.54</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H238" t="inlineStr">
         <is>
@@ -10212,7 +10212,7 @@
         </is>
       </c>
       <c r="G239" t="n">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="H239" t="inlineStr">
         <is>
@@ -10244,7 +10244,7 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
@@ -10253,7 +10253,7 @@
         </is>
       </c>
       <c r="G240" t="n">
-        <v>1.07</v>
+        <v>0.7</v>
       </c>
       <c r="H240" t="inlineStr">
         <is>
@@ -10294,7 +10294,7 @@
         </is>
       </c>
       <c r="G241" t="n">
-        <v>0.97</v>
+        <v>1.02</v>
       </c>
       <c r="H241" t="inlineStr">
         <is>
@@ -10326,7 +10326,7 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
@@ -10335,7 +10335,7 @@
         </is>
       </c>
       <c r="G242" t="n">
-        <v>1.11</v>
+        <v>0.44</v>
       </c>
       <c r="H242" t="inlineStr">
         <is>
@@ -10376,7 +10376,7 @@
         </is>
       </c>
       <c r="G243" t="n">
-        <v>0.52</v>
+        <v>0.44</v>
       </c>
       <c r="H243" t="inlineStr">
         <is>
@@ -10408,7 +10408,7 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
@@ -10417,7 +10417,7 @@
         </is>
       </c>
       <c r="G244" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H244" t="inlineStr">
         <is>
@@ -10449,7 +10449,7 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
@@ -10458,7 +10458,7 @@
         </is>
       </c>
       <c r="G245" t="n">
-        <v>1.07</v>
+        <v>0.59</v>
       </c>
       <c r="H245" t="inlineStr">
         <is>
@@ -10490,7 +10490,7 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
@@ -10499,7 +10499,7 @@
         </is>
       </c>
       <c r="G246" t="n">
-        <v>0.52</v>
+        <v>0.92</v>
       </c>
       <c r="H246" t="inlineStr">
         <is>
@@ -10540,7 +10540,7 @@
         </is>
       </c>
       <c r="G247" t="n">
-        <v>0.76</v>
+        <v>1.06</v>
       </c>
       <c r="H247" t="inlineStr">
         <is>
@@ -10581,7 +10581,7 @@
         </is>
       </c>
       <c r="G248" t="n">
-        <v>0.44</v>
+        <v>0.48</v>
       </c>
       <c r="H248" t="inlineStr">
         <is>
@@ -10622,7 +10622,7 @@
         </is>
       </c>
       <c r="G249" t="n">
-        <v>0.44</v>
+        <v>0.65</v>
       </c>
       <c r="H249" t="inlineStr">
         <is>
@@ -10663,7 +10663,7 @@
         </is>
       </c>
       <c r="G250" t="n">
-        <v>1.08</v>
+        <v>0.45</v>
       </c>
       <c r="H250" t="inlineStr">
         <is>
@@ -10695,7 +10695,7 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
@@ -10704,7 +10704,7 @@
         </is>
       </c>
       <c r="G251" t="n">
-        <v>0.88</v>
+        <v>0.95</v>
       </c>
       <c r="H251" t="inlineStr">
         <is>
@@ -10736,7 +10736,7 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
@@ -10745,7 +10745,7 @@
         </is>
       </c>
       <c r="G252" t="n">
-        <v>1.14</v>
+        <v>0.86</v>
       </c>
       <c r="H252" t="inlineStr">
         <is>
@@ -10777,7 +10777,7 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
@@ -10786,7 +10786,7 @@
         </is>
       </c>
       <c r="G253" t="n">
-        <v>0.84</v>
+        <v>1.06</v>
       </c>
       <c r="H253" t="inlineStr">
         <is>
@@ -10818,7 +10818,7 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
@@ -10827,7 +10827,7 @@
         </is>
       </c>
       <c r="G254" t="n">
-        <v>1.08</v>
+        <v>0.91</v>
       </c>
       <c r="H254" t="inlineStr">
         <is>
@@ -10859,7 +10859,7 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
@@ -10868,7 +10868,7 @@
         </is>
       </c>
       <c r="G255" t="n">
-        <v>0.89</v>
+        <v>0.74</v>
       </c>
       <c r="H255" t="inlineStr">
         <is>
@@ -10900,7 +10900,7 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
@@ -10909,7 +10909,7 @@
         </is>
       </c>
       <c r="G256" t="n">
-        <v>0.61</v>
+        <v>0.75</v>
       </c>
       <c r="H256" t="inlineStr">
         <is>
@@ -10950,7 +10950,7 @@
         </is>
       </c>
       <c r="G257" t="n">
-        <v>0.46</v>
+        <v>0.71</v>
       </c>
       <c r="H257" t="inlineStr">
         <is>
@@ -10982,7 +10982,7 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
@@ -10991,7 +10991,7 @@
         </is>
       </c>
       <c r="G258" t="n">
-        <v>1.13</v>
+        <v>0.46</v>
       </c>
       <c r="H258" t="inlineStr">
         <is>
@@ -11023,7 +11023,7 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
@@ -11032,7 +11032,7 @@
         </is>
       </c>
       <c r="G259" t="n">
-        <v>0.6899999999999999</v>
+        <v>1.09</v>
       </c>
       <c r="H259" t="inlineStr">
         <is>
@@ -11064,7 +11064,7 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
@@ -11073,7 +11073,7 @@
         </is>
       </c>
       <c r="G260" t="n">
-        <v>0.8</v>
+        <v>1.07</v>
       </c>
       <c r="H260" t="inlineStr">
         <is>
@@ -11114,7 +11114,7 @@
         </is>
       </c>
       <c r="G261" t="n">
-        <v>0.49</v>
+        <v>1.15</v>
       </c>
       <c r="H261" t="inlineStr">
         <is>
@@ -11155,7 +11155,7 @@
         </is>
       </c>
       <c r="G262" t="n">
-        <v>1.14</v>
+        <v>1.03</v>
       </c>
       <c r="H262" t="inlineStr">
         <is>
@@ -11187,7 +11187,7 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
@@ -11196,7 +11196,7 @@
         </is>
       </c>
       <c r="G263" t="n">
-        <v>0.99</v>
+        <v>0.78</v>
       </c>
       <c r="H263" t="inlineStr">
         <is>
@@ -11228,7 +11228,7 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
@@ -11237,7 +11237,7 @@
         </is>
       </c>
       <c r="G264" t="n">
-        <v>0.52</v>
+        <v>0.44</v>
       </c>
       <c r="H264" t="inlineStr">
         <is>
@@ -11269,7 +11269,7 @@
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
@@ -11278,7 +11278,7 @@
         </is>
       </c>
       <c r="G265" t="n">
-        <v>1.1</v>
+        <v>0.87</v>
       </c>
       <c r="H265" t="inlineStr">
         <is>
@@ -11310,7 +11310,7 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
@@ -11319,7 +11319,7 @@
         </is>
       </c>
       <c r="G266" t="n">
-        <v>0.77</v>
+        <v>1.13</v>
       </c>
       <c r="H266" t="inlineStr">
         <is>
@@ -11351,7 +11351,7 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
@@ -11360,7 +11360,7 @@
         </is>
       </c>
       <c r="G267" t="n">
-        <v>0.44</v>
+        <v>0.95</v>
       </c>
       <c r="H267" t="inlineStr">
         <is>
@@ -11392,7 +11392,7 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
@@ -11401,7 +11401,7 @@
         </is>
       </c>
       <c r="G268" t="n">
-        <v>0.86</v>
+        <v>0.92</v>
       </c>
       <c r="H268" t="inlineStr">
         <is>
@@ -11433,7 +11433,7 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
@@ -11442,7 +11442,7 @@
         </is>
       </c>
       <c r="G269" t="n">
-        <v>0.48</v>
+        <v>0.88</v>
       </c>
       <c r="H269" t="inlineStr">
         <is>
@@ -11483,7 +11483,7 @@
         </is>
       </c>
       <c r="G270" t="n">
-        <v>0.57</v>
+        <v>1</v>
       </c>
       <c r="H270" t="inlineStr">
         <is>
@@ -11515,7 +11515,7 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
@@ -11524,7 +11524,7 @@
         </is>
       </c>
       <c r="G271" t="n">
-        <v>0.6</v>
+        <v>1.11</v>
       </c>
       <c r="H271" t="inlineStr">
         <is>
@@ -11556,7 +11556,7 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
@@ -11565,7 +11565,7 @@
         </is>
       </c>
       <c r="G272" t="n">
-        <v>1</v>
+        <v>0.54</v>
       </c>
       <c r="H272" t="inlineStr">
         <is>
@@ -11606,7 +11606,7 @@
         </is>
       </c>
       <c r="G273" t="n">
-        <v>0.74</v>
+        <v>0.8</v>
       </c>
       <c r="H273" t="inlineStr">
         <is>
@@ -11638,7 +11638,7 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
@@ -11647,7 +11647,7 @@
         </is>
       </c>
       <c r="G274" t="n">
-        <v>1.11</v>
+        <v>0.72</v>
       </c>
       <c r="H274" t="inlineStr">
         <is>
@@ -11679,7 +11679,7 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
@@ -11688,7 +11688,7 @@
         </is>
       </c>
       <c r="G275" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="H275" t="inlineStr">
         <is>
@@ -11720,7 +11720,7 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
@@ -11729,7 +11729,7 @@
         </is>
       </c>
       <c r="G276" t="n">
-        <v>0.95</v>
+        <v>0.89</v>
       </c>
       <c r="H276" t="inlineStr">
         <is>
@@ -11770,7 +11770,7 @@
         </is>
       </c>
       <c r="G277" t="n">
-        <v>1.15</v>
+        <v>1.04</v>
       </c>
       <c r="H277" t="inlineStr">
         <is>
@@ -11802,7 +11802,7 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
@@ -11811,7 +11811,7 @@
         </is>
       </c>
       <c r="G278" t="n">
-        <v>0.87</v>
+        <v>0.5</v>
       </c>
       <c r="H278" t="inlineStr">
         <is>
@@ -11843,7 +11843,7 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
@@ -11852,7 +11852,7 @@
         </is>
       </c>
       <c r="G279" t="n">
-        <v>1.1</v>
+        <v>0.66</v>
       </c>
       <c r="H279" t="inlineStr">
         <is>
@@ -11884,7 +11884,7 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
@@ -11893,7 +11893,7 @@
         </is>
       </c>
       <c r="G280" t="n">
-        <v>0.74</v>
+        <v>0.95</v>
       </c>
       <c r="H280" t="inlineStr">
         <is>
@@ -11925,7 +11925,7 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
@@ -11934,7 +11934,7 @@
         </is>
       </c>
       <c r="G281" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="H281" t="inlineStr">
         <is>
@@ -11966,7 +11966,7 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
@@ -11975,7 +11975,7 @@
         </is>
       </c>
       <c r="G282" t="n">
-        <v>0.66</v>
+        <v>0.79</v>
       </c>
       <c r="H282" t="inlineStr">
         <is>
@@ -12007,7 +12007,7 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
@@ -12016,7 +12016,7 @@
         </is>
       </c>
       <c r="G283" t="n">
-        <v>0.49</v>
+        <v>0.72</v>
       </c>
       <c r="H283" t="inlineStr">
         <is>
@@ -12057,7 +12057,7 @@
         </is>
       </c>
       <c r="G284" t="n">
-        <v>0.84</v>
+        <v>0.88</v>
       </c>
       <c r="H284" t="inlineStr">
         <is>
@@ -12089,7 +12089,7 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
@@ -12098,7 +12098,7 @@
         </is>
       </c>
       <c r="G285" t="n">
-        <v>0.82</v>
+        <v>0.67</v>
       </c>
       <c r="H285" t="inlineStr">
         <is>
@@ -12130,7 +12130,7 @@
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
@@ -12139,7 +12139,7 @@
         </is>
       </c>
       <c r="G286" t="n">
-        <v>0.79</v>
+        <v>0.68</v>
       </c>
       <c r="H286" t="inlineStr">
         <is>
@@ -12180,7 +12180,7 @@
         </is>
       </c>
       <c r="G287" t="n">
-        <v>0.88</v>
+        <v>0.57</v>
       </c>
       <c r="H287" t="inlineStr">
         <is>
@@ -12221,7 +12221,7 @@
         </is>
       </c>
       <c r="G288" t="n">
-        <v>0.6</v>
+        <v>0.98</v>
       </c>
       <c r="H288" t="inlineStr">
         <is>
@@ -12253,7 +12253,7 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
@@ -12262,7 +12262,7 @@
         </is>
       </c>
       <c r="G289" t="n">
-        <v>0.96</v>
+        <v>0.43</v>
       </c>
       <c r="H289" t="inlineStr">
         <is>
@@ -12294,7 +12294,7 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
@@ -12303,7 +12303,7 @@
         </is>
       </c>
       <c r="G290" t="n">
-        <v>1.15</v>
+        <v>0.5</v>
       </c>
       <c r="H290" t="inlineStr">
         <is>
@@ -12335,7 +12335,7 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
@@ -12344,7 +12344,7 @@
         </is>
       </c>
       <c r="G291" t="n">
-        <v>0.73</v>
+        <v>0.7</v>
       </c>
       <c r="H291" t="inlineStr">
         <is>
@@ -12376,7 +12376,7 @@
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
@@ -12385,7 +12385,7 @@
         </is>
       </c>
       <c r="G292" t="n">
-        <v>0.55</v>
+        <v>0.85</v>
       </c>
       <c r="H292" t="inlineStr">
         <is>
@@ -12417,7 +12417,7 @@
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
@@ -12426,7 +12426,7 @@
         </is>
       </c>
       <c r="G293" t="n">
-        <v>1.11</v>
+        <v>0.58</v>
       </c>
       <c r="H293" t="inlineStr">
         <is>
@@ -12458,7 +12458,7 @@
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
@@ -12467,7 +12467,7 @@
         </is>
       </c>
       <c r="G294" t="n">
-        <v>0.61</v>
+        <v>0.82</v>
       </c>
       <c r="H294" t="inlineStr">
         <is>
@@ -12499,7 +12499,7 @@
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
@@ -12508,7 +12508,7 @@
         </is>
       </c>
       <c r="G295" t="n">
-        <v>0.92</v>
+        <v>0.88</v>
       </c>
       <c r="H295" t="inlineStr">
         <is>
@@ -12549,7 +12549,7 @@
         </is>
       </c>
       <c r="G296" t="n">
-        <v>0.49</v>
+        <v>0.54</v>
       </c>
       <c r="H296" t="inlineStr">
         <is>
@@ -12581,7 +12581,7 @@
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
@@ -12590,7 +12590,7 @@
         </is>
       </c>
       <c r="G297" t="n">
-        <v>0.57</v>
+        <v>0.52</v>
       </c>
       <c r="H297" t="inlineStr">
         <is>
@@ -12622,7 +12622,7 @@
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
@@ -12631,7 +12631,7 @@
         </is>
       </c>
       <c r="G298" t="n">
-        <v>0.63</v>
+        <v>0.87</v>
       </c>
       <c r="H298" t="inlineStr">
         <is>
@@ -12672,7 +12672,7 @@
         </is>
       </c>
       <c r="G299" t="n">
-        <v>0.52</v>
+        <v>0.58</v>
       </c>
       <c r="H299" t="inlineStr">
         <is>
@@ -12704,7 +12704,7 @@
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
@@ -12713,7 +12713,7 @@
         </is>
       </c>
       <c r="G300" t="n">
-        <v>0.71</v>
+        <v>0.47</v>
       </c>
       <c r="H300" t="inlineStr">
         <is>
@@ -12745,7 +12745,7 @@
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
@@ -12754,7 +12754,7 @@
         </is>
       </c>
       <c r="G301" t="n">
-        <v>0.72</v>
+        <v>0.8</v>
       </c>
       <c r="H301" t="inlineStr">
         <is>

--- a/reports/Passed_Test_Cases.xlsx
+++ b/reports/Passed_Test_Cases.xlsx
@@ -486,7 +486,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -495,7 +495,7 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0.88</v>
+        <v>0.79</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -527,7 +527,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0.51</v>
+        <v>1.07</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -568,7 +568,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -577,7 +577,7 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0.55</v>
+        <v>0.53</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -609,7 +609,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -618,7 +618,7 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>0.47</v>
+        <v>0.83</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>0.63</v>
+        <v>0.76</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -691,7 +691,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -700,7 +700,7 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>0.8100000000000001</v>
+        <v>1.14</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -741,7 +741,7 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>0.84</v>
+        <v>1.08</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -773,7 +773,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -782,7 +782,7 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>0.64</v>
+        <v>1.02</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -814,7 +814,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -823,7 +823,7 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>1.14</v>
+        <v>0.64</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -855,7 +855,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -864,7 +864,7 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>0.79</v>
+        <v>0.95</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -905,7 +905,7 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>0.97</v>
+        <v>0.6</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -946,7 +946,7 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>0.68</v>
+        <v>0.61</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -987,7 +987,7 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>1.06</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1028,7 +1028,7 @@
         </is>
       </c>
       <c r="G15" t="n">
-        <v>0.71</v>
+        <v>0.84</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -1060,7 +1060,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1069,7 +1069,7 @@
         </is>
       </c>
       <c r="G16" t="n">
-        <v>0.45</v>
+        <v>1.11</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -1110,7 +1110,7 @@
         </is>
       </c>
       <c r="G17" t="n">
-        <v>1.01</v>
+        <v>0.72</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
         </is>
       </c>
       <c r="G18" t="n">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1192,7 +1192,7 @@
         </is>
       </c>
       <c r="G19" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.59</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         </is>
       </c>
       <c r="G20" t="n">
-        <v>0.43</v>
+        <v>0.47</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -1265,7 +1265,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1274,7 +1274,7 @@
         </is>
       </c>
       <c r="G21" t="n">
-        <v>0.71</v>
+        <v>0.51</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -1315,7 +1315,7 @@
         </is>
       </c>
       <c r="G22" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
@@ -1347,7 +1347,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1356,7 +1356,7 @@
         </is>
       </c>
       <c r="G23" t="n">
-        <v>0.76</v>
+        <v>1.06</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1397,7 +1397,7 @@
         </is>
       </c>
       <c r="G24" t="n">
-        <v>0.49</v>
+        <v>0.73</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
@@ -1438,7 +1438,7 @@
         </is>
       </c>
       <c r="G25" t="n">
-        <v>0.87</v>
+        <v>0.78</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
@@ -1470,7 +1470,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1479,7 +1479,7 @@
         </is>
       </c>
       <c r="G26" t="n">
-        <v>0.71</v>
+        <v>0.79</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
@@ -1511,7 +1511,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1520,7 +1520,7 @@
         </is>
       </c>
       <c r="G27" t="n">
-        <v>0.45</v>
+        <v>0.43</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
@@ -1552,7 +1552,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1561,7 +1561,7 @@
         </is>
       </c>
       <c r="G28" t="n">
-        <v>0.93</v>
+        <v>0.91</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
@@ -1593,7 +1593,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1602,7 +1602,7 @@
         </is>
       </c>
       <c r="G29" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.57</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
@@ -1634,7 +1634,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1643,7 +1643,7 @@
         </is>
       </c>
       <c r="G30" t="n">
-        <v>0.47</v>
+        <v>0.89</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
@@ -1675,7 +1675,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1684,7 +1684,7 @@
         </is>
       </c>
       <c r="G31" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
@@ -1716,7 +1716,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1725,7 +1725,7 @@
         </is>
       </c>
       <c r="G32" t="n">
-        <v>1.14</v>
+        <v>0.61</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
@@ -1757,7 +1757,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1766,7 +1766,7 @@
         </is>
       </c>
       <c r="G33" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
@@ -1798,7 +1798,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1807,7 +1807,7 @@
         </is>
       </c>
       <c r="G34" t="n">
-        <v>1.12</v>
+        <v>0.73</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
@@ -1839,7 +1839,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1848,7 +1848,7 @@
         </is>
       </c>
       <c r="G35" t="n">
-        <v>0.55</v>
+        <v>1.11</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
@@ -1880,7 +1880,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1889,7 +1889,7 @@
         </is>
       </c>
       <c r="G36" t="n">
-        <v>0.92</v>
+        <v>0.65</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1930,7 +1930,7 @@
         </is>
       </c>
       <c r="G37" t="n">
-        <v>0.7</v>
+        <v>1.08</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
@@ -1962,7 +1962,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1971,7 +1971,7 @@
         </is>
       </c>
       <c r="G38" t="n">
-        <v>0.96</v>
+        <v>0.91</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
@@ -2012,7 +2012,7 @@
         </is>
       </c>
       <c r="G39" t="n">
-        <v>0.66</v>
+        <v>0.72</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
@@ -2044,7 +2044,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -2053,7 +2053,7 @@
         </is>
       </c>
       <c r="G40" t="n">
-        <v>0.62</v>
+        <v>0.49</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
@@ -2085,7 +2085,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -2094,7 +2094,7 @@
         </is>
       </c>
       <c r="G41" t="n">
-        <v>0.8</v>
+        <v>0.93</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
@@ -2126,7 +2126,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -2135,7 +2135,7 @@
         </is>
       </c>
       <c r="G42" t="n">
-        <v>0.66</v>
+        <v>0.63</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
@@ -2167,7 +2167,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -2176,7 +2176,7 @@
         </is>
       </c>
       <c r="G43" t="n">
-        <v>0.82</v>
+        <v>1.1</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
@@ -2208,7 +2208,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -2217,7 +2217,7 @@
         </is>
       </c>
       <c r="G44" t="n">
-        <v>0.84</v>
+        <v>0.99</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
@@ -2249,7 +2249,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2258,7 +2258,7 @@
         </is>
       </c>
       <c r="G45" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
@@ -2299,7 +2299,7 @@
         </is>
       </c>
       <c r="G46" t="n">
-        <v>0.75</v>
+        <v>0.98</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
@@ -2340,7 +2340,7 @@
         </is>
       </c>
       <c r="G47" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.14</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
@@ -2381,7 +2381,7 @@
         </is>
       </c>
       <c r="G48" t="n">
-        <v>0.89</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
@@ -2422,7 +2422,7 @@
         </is>
       </c>
       <c r="G49" t="n">
-        <v>0.79</v>
+        <v>0.72</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
@@ -2454,7 +2454,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2463,7 +2463,7 @@
         </is>
       </c>
       <c r="G50" t="n">
-        <v>0.47</v>
+        <v>0.77</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
@@ -2495,7 +2495,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2504,7 +2504,7 @@
         </is>
       </c>
       <c r="G51" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
@@ -2545,7 +2545,7 @@
         </is>
       </c>
       <c r="G52" t="n">
-        <v>1.11</v>
+        <v>0.97</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
@@ -2577,7 +2577,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2586,7 +2586,7 @@
         </is>
       </c>
       <c r="G53" t="n">
-        <v>1.06</v>
+        <v>0.72</v>
       </c>
       <c r="H53" t="inlineStr">
         <is>
@@ -2618,7 +2618,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2627,7 +2627,7 @@
         </is>
       </c>
       <c r="G54" t="n">
-        <v>0.82</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H54" t="inlineStr">
         <is>
@@ -2659,7 +2659,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2668,7 +2668,7 @@
         </is>
       </c>
       <c r="G55" t="n">
-        <v>0.96</v>
+        <v>0.9</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
@@ -2700,7 +2700,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2709,7 +2709,7 @@
         </is>
       </c>
       <c r="G56" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
@@ -2741,7 +2741,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2750,7 +2750,7 @@
         </is>
       </c>
       <c r="G57" t="n">
-        <v>0.83</v>
+        <v>0.63</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
@@ -2782,7 +2782,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2791,7 +2791,7 @@
         </is>
       </c>
       <c r="G58" t="n">
-        <v>0.62</v>
+        <v>1</v>
       </c>
       <c r="H58" t="inlineStr">
         <is>
@@ -2832,7 +2832,7 @@
         </is>
       </c>
       <c r="G59" t="n">
-        <v>0.43</v>
+        <v>0.73</v>
       </c>
       <c r="H59" t="inlineStr">
         <is>
@@ -2864,7 +2864,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2873,7 +2873,7 @@
         </is>
       </c>
       <c r="G60" t="n">
-        <v>0.45</v>
+        <v>0.73</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
@@ -2905,7 +2905,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2914,7 +2914,7 @@
         </is>
       </c>
       <c r="G61" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="H61" t="inlineStr">
         <is>
@@ -2946,7 +2946,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2955,7 +2955,7 @@
         </is>
       </c>
       <c r="G62" t="n">
-        <v>0.74</v>
+        <v>0.88</v>
       </c>
       <c r="H62" t="inlineStr">
         <is>
@@ -2996,7 +2996,7 @@
         </is>
       </c>
       <c r="G63" t="n">
-        <v>0.58</v>
+        <v>0.44</v>
       </c>
       <c r="H63" t="inlineStr">
         <is>
@@ -3028,7 +3028,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -3037,7 +3037,7 @@
         </is>
       </c>
       <c r="G64" t="n">
-        <v>0.78</v>
+        <v>1.13</v>
       </c>
       <c r="H64" t="inlineStr">
         <is>
@@ -3069,7 +3069,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -3078,7 +3078,7 @@
         </is>
       </c>
       <c r="G65" t="n">
-        <v>0.44</v>
+        <v>1.06</v>
       </c>
       <c r="H65" t="inlineStr">
         <is>
@@ -3119,7 +3119,7 @@
         </is>
       </c>
       <c r="G66" t="n">
-        <v>0.62</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H66" t="inlineStr">
         <is>
@@ -3151,7 +3151,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -3160,7 +3160,7 @@
         </is>
       </c>
       <c r="G67" t="n">
-        <v>0.75</v>
+        <v>0.46</v>
       </c>
       <c r="H67" t="inlineStr">
         <is>
@@ -3192,7 +3192,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -3201,7 +3201,7 @@
         </is>
       </c>
       <c r="G68" t="n">
-        <v>0.84</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H68" t="inlineStr">
         <is>
@@ -3233,7 +3233,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -3242,7 +3242,7 @@
         </is>
       </c>
       <c r="G69" t="n">
-        <v>0.89</v>
+        <v>0.63</v>
       </c>
       <c r="H69" t="inlineStr">
         <is>
@@ -3274,7 +3274,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -3283,7 +3283,7 @@
         </is>
       </c>
       <c r="G70" t="n">
-        <v>0.67</v>
+        <v>0.98</v>
       </c>
       <c r="H70" t="inlineStr">
         <is>
@@ -3315,7 +3315,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -3324,7 +3324,7 @@
         </is>
       </c>
       <c r="G71" t="n">
-        <v>0.98</v>
+        <v>0.93</v>
       </c>
       <c r="H71" t="inlineStr">
         <is>
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -3365,7 +3365,7 @@
         </is>
       </c>
       <c r="G72" t="n">
-        <v>0.87</v>
+        <v>1.15</v>
       </c>
       <c r="H72" t="inlineStr">
         <is>
@@ -3406,7 +3406,7 @@
         </is>
       </c>
       <c r="G73" t="n">
-        <v>1.11</v>
+        <v>0.97</v>
       </c>
       <c r="H73" t="inlineStr">
         <is>
@@ -3438,7 +3438,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3447,7 +3447,7 @@
         </is>
       </c>
       <c r="G74" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.06</v>
       </c>
       <c r="H74" t="inlineStr">
         <is>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3488,7 +3488,7 @@
         </is>
       </c>
       <c r="G75" t="n">
-        <v>0.7</v>
+        <v>0.68</v>
       </c>
       <c r="H75" t="inlineStr">
         <is>
@@ -3520,7 +3520,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3529,7 +3529,7 @@
         </is>
       </c>
       <c r="G76" t="n">
-        <v>0.95</v>
+        <v>1.06</v>
       </c>
       <c r="H76" t="inlineStr">
         <is>
@@ -3561,7 +3561,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3570,7 +3570,7 @@
         </is>
       </c>
       <c r="G77" t="n">
-        <v>0.92</v>
+        <v>0.87</v>
       </c>
       <c r="H77" t="inlineStr">
         <is>
@@ -3602,7 +3602,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3611,7 +3611,7 @@
         </is>
       </c>
       <c r="G78" t="n">
-        <v>1.11</v>
+        <v>0.64</v>
       </c>
       <c r="H78" t="inlineStr">
         <is>
@@ -3652,7 +3652,7 @@
         </is>
       </c>
       <c r="G79" t="n">
-        <v>1.08</v>
+        <v>0.92</v>
       </c>
       <c r="H79" t="inlineStr">
         <is>
@@ -3693,7 +3693,7 @@
         </is>
       </c>
       <c r="G80" t="n">
-        <v>0.62</v>
+        <v>1.01</v>
       </c>
       <c r="H80" t="inlineStr">
         <is>
@@ -3734,7 +3734,7 @@
         </is>
       </c>
       <c r="G81" t="n">
-        <v>0.82</v>
+        <v>0.97</v>
       </c>
       <c r="H81" t="inlineStr">
         <is>
@@ -3766,7 +3766,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3775,7 +3775,7 @@
         </is>
       </c>
       <c r="G82" t="n">
-        <v>1.13</v>
+        <v>0.47</v>
       </c>
       <c r="H82" t="inlineStr">
         <is>
@@ -3807,7 +3807,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3816,7 +3816,7 @@
         </is>
       </c>
       <c r="G83" t="n">
-        <v>1.04</v>
+        <v>0.93</v>
       </c>
       <c r="H83" t="inlineStr">
         <is>
@@ -3848,7 +3848,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3857,7 +3857,7 @@
         </is>
       </c>
       <c r="G84" t="n">
-        <v>0.45</v>
+        <v>0.44</v>
       </c>
       <c r="H84" t="inlineStr">
         <is>
@@ -3889,7 +3889,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3898,7 +3898,7 @@
         </is>
       </c>
       <c r="G85" t="n">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="H85" t="inlineStr">
         <is>
@@ -3939,7 +3939,7 @@
         </is>
       </c>
       <c r="G86" t="n">
-        <v>0.66</v>
+        <v>1.03</v>
       </c>
       <c r="H86" t="inlineStr">
         <is>
@@ -3980,7 +3980,7 @@
         </is>
       </c>
       <c r="G87" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.73</v>
       </c>
       <c r="H87" t="inlineStr">
         <is>
@@ -4012,7 +4012,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -4021,7 +4021,7 @@
         </is>
       </c>
       <c r="G88" t="n">
-        <v>0.91</v>
+        <v>0.76</v>
       </c>
       <c r="H88" t="inlineStr">
         <is>
@@ -4062,7 +4062,7 @@
         </is>
       </c>
       <c r="G89" t="n">
-        <v>0.76</v>
+        <v>0.63</v>
       </c>
       <c r="H89" t="inlineStr">
         <is>
@@ -4094,7 +4094,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -4103,7 +4103,7 @@
         </is>
       </c>
       <c r="G90" t="n">
-        <v>0.65</v>
+        <v>0.48</v>
       </c>
       <c r="H90" t="inlineStr">
         <is>
@@ -4144,7 +4144,7 @@
         </is>
       </c>
       <c r="G91" t="n">
-        <v>0.64</v>
+        <v>0.84</v>
       </c>
       <c r="H91" t="inlineStr">
         <is>
@@ -4176,7 +4176,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -4185,7 +4185,7 @@
         </is>
       </c>
       <c r="G92" t="n">
-        <v>0.98</v>
+        <v>0.7</v>
       </c>
       <c r="H92" t="inlineStr">
         <is>
@@ -4217,7 +4217,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -4226,7 +4226,7 @@
         </is>
       </c>
       <c r="G93" t="n">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="H93" t="inlineStr">
         <is>
@@ -4258,7 +4258,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -4267,7 +4267,7 @@
         </is>
       </c>
       <c r="G94" t="n">
-        <v>0.66</v>
+        <v>0.44</v>
       </c>
       <c r="H94" t="inlineStr">
         <is>
@@ -4299,7 +4299,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -4308,7 +4308,7 @@
         </is>
       </c>
       <c r="G95" t="n">
-        <v>0.65</v>
+        <v>1.13</v>
       </c>
       <c r="H95" t="inlineStr">
         <is>
@@ -4340,7 +4340,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -4349,7 +4349,7 @@
         </is>
       </c>
       <c r="G96" t="n">
-        <v>0.7</v>
+        <v>0.89</v>
       </c>
       <c r="H96" t="inlineStr">
         <is>
@@ -4390,7 +4390,7 @@
         </is>
       </c>
       <c r="G97" t="n">
-        <v>0.52</v>
+        <v>1.01</v>
       </c>
       <c r="H97" t="inlineStr">
         <is>
@@ -4422,7 +4422,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -4431,7 +4431,7 @@
         </is>
       </c>
       <c r="G98" t="n">
-        <v>1.06</v>
+        <v>0.67</v>
       </c>
       <c r="H98" t="inlineStr">
         <is>
@@ -4463,7 +4463,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -4472,7 +4472,7 @@
         </is>
       </c>
       <c r="G99" t="n">
-        <v>0.43</v>
+        <v>0.91</v>
       </c>
       <c r="H99" t="inlineStr">
         <is>
@@ -4504,7 +4504,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -4513,7 +4513,7 @@
         </is>
       </c>
       <c r="G100" t="n">
-        <v>0.75</v>
+        <v>0.83</v>
       </c>
       <c r="H100" t="inlineStr">
         <is>
@@ -4545,7 +4545,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -4554,7 +4554,7 @@
         </is>
       </c>
       <c r="G101" t="n">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="H101" t="inlineStr">
         <is>
@@ -4595,7 +4595,7 @@
         </is>
       </c>
       <c r="G102" t="n">
-        <v>1.14</v>
+        <v>0.54</v>
       </c>
       <c r="H102" t="inlineStr">
         <is>
@@ -4627,7 +4627,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4636,7 +4636,7 @@
         </is>
       </c>
       <c r="G103" t="n">
-        <v>0.76</v>
+        <v>0.99</v>
       </c>
       <c r="H103" t="inlineStr">
         <is>
@@ -4677,7 +4677,7 @@
         </is>
       </c>
       <c r="G104" t="n">
-        <v>0.61</v>
+        <v>0.6</v>
       </c>
       <c r="H104" t="inlineStr">
         <is>
@@ -4718,7 +4718,7 @@
         </is>
       </c>
       <c r="G105" t="n">
-        <v>1.03</v>
+        <v>0.79</v>
       </c>
       <c r="H105" t="inlineStr">
         <is>
@@ -4759,7 +4759,7 @@
         </is>
       </c>
       <c r="G106" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="H106" t="inlineStr">
         <is>
@@ -4791,7 +4791,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4800,7 +4800,7 @@
         </is>
       </c>
       <c r="G107" t="n">
-        <v>0.65</v>
+        <v>1.14</v>
       </c>
       <c r="H107" t="inlineStr">
         <is>
@@ -4832,7 +4832,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4841,7 +4841,7 @@
         </is>
       </c>
       <c r="G108" t="n">
-        <v>1.01</v>
+        <v>0.66</v>
       </c>
       <c r="H108" t="inlineStr">
         <is>
@@ -4873,7 +4873,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4882,7 +4882,7 @@
         </is>
       </c>
       <c r="G109" t="n">
-        <v>1.1</v>
+        <v>0.88</v>
       </c>
       <c r="H109" t="inlineStr">
         <is>
@@ -4914,7 +4914,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4923,7 +4923,7 @@
         </is>
       </c>
       <c r="G110" t="n">
-        <v>0.64</v>
+        <v>0.51</v>
       </c>
       <c r="H110" t="inlineStr">
         <is>
@@ -4955,7 +4955,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4964,7 +4964,7 @@
         </is>
       </c>
       <c r="G111" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="H111" t="inlineStr">
         <is>
@@ -4996,7 +4996,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -5005,7 +5005,7 @@
         </is>
       </c>
       <c r="G112" t="n">
-        <v>0.68</v>
+        <v>0.44</v>
       </c>
       <c r="H112" t="inlineStr">
         <is>
@@ -5046,7 +5046,7 @@
         </is>
       </c>
       <c r="G113" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.76</v>
       </c>
       <c r="H113" t="inlineStr">
         <is>
@@ -5078,7 +5078,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -5087,7 +5087,7 @@
         </is>
       </c>
       <c r="G114" t="n">
-        <v>0.71</v>
+        <v>1.1</v>
       </c>
       <c r="H114" t="inlineStr">
         <is>
@@ -5119,7 +5119,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -5169,7 +5169,7 @@
         </is>
       </c>
       <c r="G116" t="n">
-        <v>0.83</v>
+        <v>0.7</v>
       </c>
       <c r="H116" t="inlineStr">
         <is>
@@ -5210,7 +5210,7 @@
         </is>
       </c>
       <c r="G117" t="n">
-        <v>0.46</v>
+        <v>0.8</v>
       </c>
       <c r="H117" t="inlineStr">
         <is>
@@ -5251,7 +5251,7 @@
         </is>
       </c>
       <c r="G118" t="n">
-        <v>0.57</v>
+        <v>0.51</v>
       </c>
       <c r="H118" t="inlineStr">
         <is>
@@ -5283,7 +5283,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -5292,7 +5292,7 @@
         </is>
       </c>
       <c r="G119" t="n">
-        <v>0.96</v>
+        <v>0.98</v>
       </c>
       <c r="H119" t="inlineStr">
         <is>
@@ -5324,7 +5324,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -5333,7 +5333,7 @@
         </is>
       </c>
       <c r="G120" t="n">
-        <v>0.47</v>
+        <v>1.02</v>
       </c>
       <c r="H120" t="inlineStr">
         <is>
@@ -5365,7 +5365,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -5374,7 +5374,7 @@
         </is>
       </c>
       <c r="G121" t="n">
-        <v>0.48</v>
+        <v>1.01</v>
       </c>
       <c r="H121" t="inlineStr">
         <is>
@@ -5415,7 +5415,7 @@
         </is>
       </c>
       <c r="G122" t="n">
-        <v>0.97</v>
+        <v>0.48</v>
       </c>
       <c r="H122" t="inlineStr">
         <is>
@@ -5456,7 +5456,7 @@
         </is>
       </c>
       <c r="G123" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="H123" t="inlineStr">
         <is>
@@ -5488,7 +5488,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -5529,7 +5529,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -5538,7 +5538,7 @@
         </is>
       </c>
       <c r="G125" t="n">
-        <v>0.5</v>
+        <v>0.77</v>
       </c>
       <c r="H125" t="inlineStr">
         <is>
@@ -5570,7 +5570,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -5579,7 +5579,7 @@
         </is>
       </c>
       <c r="G126" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="H126" t="inlineStr">
         <is>
@@ -5620,7 +5620,7 @@
         </is>
       </c>
       <c r="G127" t="n">
-        <v>0.93</v>
+        <v>0.73</v>
       </c>
       <c r="H127" t="inlineStr">
         <is>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -5661,7 +5661,7 @@
         </is>
       </c>
       <c r="G128" t="n">
-        <v>0.77</v>
+        <v>0.9</v>
       </c>
       <c r="H128" t="inlineStr">
         <is>
@@ -5693,7 +5693,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -5702,7 +5702,7 @@
         </is>
       </c>
       <c r="G129" t="n">
-        <v>1.11</v>
+        <v>0.96</v>
       </c>
       <c r="H129" t="inlineStr">
         <is>
@@ -5734,7 +5734,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -5743,7 +5743,7 @@
         </is>
       </c>
       <c r="G130" t="n">
-        <v>1.11</v>
+        <v>0.51</v>
       </c>
       <c r="H130" t="inlineStr">
         <is>
@@ -5784,7 +5784,7 @@
         </is>
       </c>
       <c r="G131" t="n">
-        <v>1.02</v>
+        <v>0.76</v>
       </c>
       <c r="H131" t="inlineStr">
         <is>
@@ -5816,7 +5816,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -5825,7 +5825,7 @@
         </is>
       </c>
       <c r="G132" t="n">
-        <v>1.01</v>
+        <v>0.66</v>
       </c>
       <c r="H132" t="inlineStr">
         <is>
@@ -5857,7 +5857,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -5866,7 +5866,7 @@
         </is>
       </c>
       <c r="G133" t="n">
-        <v>0.79</v>
+        <v>1.06</v>
       </c>
       <c r="H133" t="inlineStr">
         <is>
@@ -5898,7 +5898,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -5907,7 +5907,7 @@
         </is>
       </c>
       <c r="G134" t="n">
-        <v>1.11</v>
+        <v>0.75</v>
       </c>
       <c r="H134" t="inlineStr">
         <is>
@@ -5939,7 +5939,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -5948,7 +5948,7 @@
         </is>
       </c>
       <c r="G135" t="n">
-        <v>0.89</v>
+        <v>0.77</v>
       </c>
       <c r="H135" t="inlineStr">
         <is>
@@ -5980,7 +5980,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -5989,7 +5989,7 @@
         </is>
       </c>
       <c r="G136" t="n">
-        <v>0.75</v>
+        <v>0.7</v>
       </c>
       <c r="H136" t="inlineStr">
         <is>
@@ -6021,7 +6021,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -6030,7 +6030,7 @@
         </is>
       </c>
       <c r="G137" t="n">
-        <v>1.03</v>
+        <v>0.73</v>
       </c>
       <c r="H137" t="inlineStr">
         <is>
@@ -6062,7 +6062,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -6071,7 +6071,7 @@
         </is>
       </c>
       <c r="G138" t="n">
-        <v>0.75</v>
+        <v>1.09</v>
       </c>
       <c r="H138" t="inlineStr">
         <is>
@@ -6112,7 +6112,7 @@
         </is>
       </c>
       <c r="G139" t="n">
-        <v>0.76</v>
+        <v>0.42</v>
       </c>
       <c r="H139" t="inlineStr">
         <is>
@@ -6144,7 +6144,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -6153,7 +6153,7 @@
         </is>
       </c>
       <c r="G140" t="n">
-        <v>0.66</v>
+        <v>0.52</v>
       </c>
       <c r="H140" t="inlineStr">
         <is>
@@ -6185,7 +6185,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -6194,7 +6194,7 @@
         </is>
       </c>
       <c r="G141" t="n">
-        <v>0.6</v>
+        <v>0.92</v>
       </c>
       <c r="H141" t="inlineStr">
         <is>
@@ -6235,7 +6235,7 @@
         </is>
       </c>
       <c r="G142" t="n">
-        <v>0.89</v>
+        <v>0.48</v>
       </c>
       <c r="H142" t="inlineStr">
         <is>
@@ -6276,7 +6276,7 @@
         </is>
       </c>
       <c r="G143" t="n">
-        <v>1.1</v>
+        <v>0.92</v>
       </c>
       <c r="H143" t="inlineStr">
         <is>
@@ -6308,7 +6308,7 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -6317,7 +6317,7 @@
         </is>
       </c>
       <c r="G144" t="n">
-        <v>1.06</v>
+        <v>0.88</v>
       </c>
       <c r="H144" t="inlineStr">
         <is>
@@ -6358,7 +6358,7 @@
         </is>
       </c>
       <c r="G145" t="n">
-        <v>0.96</v>
+        <v>0.93</v>
       </c>
       <c r="H145" t="inlineStr">
         <is>
@@ -6390,7 +6390,7 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
@@ -6431,7 +6431,7 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
@@ -6440,7 +6440,7 @@
         </is>
       </c>
       <c r="G147" t="n">
-        <v>1.01</v>
+        <v>0.55</v>
       </c>
       <c r="H147" t="inlineStr">
         <is>
@@ -6472,7 +6472,7 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
@@ -6481,7 +6481,7 @@
         </is>
       </c>
       <c r="G148" t="n">
-        <v>0.63</v>
+        <v>1.04</v>
       </c>
       <c r="H148" t="inlineStr">
         <is>
@@ -6513,7 +6513,7 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
@@ -6522,7 +6522,7 @@
         </is>
       </c>
       <c r="G149" t="n">
-        <v>1.06</v>
+        <v>0.7</v>
       </c>
       <c r="H149" t="inlineStr">
         <is>
@@ -6554,7 +6554,7 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
@@ -6563,7 +6563,7 @@
         </is>
       </c>
       <c r="G150" t="n">
-        <v>0.95</v>
+        <v>0.97</v>
       </c>
       <c r="H150" t="inlineStr">
         <is>
@@ -6604,7 +6604,7 @@
         </is>
       </c>
       <c r="G151" t="n">
-        <v>0.97</v>
+        <v>1.03</v>
       </c>
       <c r="H151" t="inlineStr">
         <is>
@@ -6636,7 +6636,7 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
@@ -6645,7 +6645,7 @@
         </is>
       </c>
       <c r="G152" t="n">
-        <v>0.8</v>
+        <v>0.84</v>
       </c>
       <c r="H152" t="inlineStr">
         <is>
@@ -6686,7 +6686,7 @@
         </is>
       </c>
       <c r="G153" t="n">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="H153" t="inlineStr">
         <is>
@@ -6718,7 +6718,7 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
@@ -6727,7 +6727,7 @@
         </is>
       </c>
       <c r="G154" t="n">
-        <v>0.92</v>
+        <v>0.97</v>
       </c>
       <c r="H154" t="inlineStr">
         <is>
@@ -6759,7 +6759,7 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
@@ -6768,7 +6768,7 @@
         </is>
       </c>
       <c r="G155" t="n">
-        <v>0.8</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H155" t="inlineStr">
         <is>
@@ -6800,7 +6800,7 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
@@ -6809,7 +6809,7 @@
         </is>
       </c>
       <c r="G156" t="n">
-        <v>0.59</v>
+        <v>1.01</v>
       </c>
       <c r="H156" t="inlineStr">
         <is>
@@ -6841,7 +6841,7 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
@@ -6850,7 +6850,7 @@
         </is>
       </c>
       <c r="G157" t="n">
-        <v>1.14</v>
+        <v>0.89</v>
       </c>
       <c r="H157" t="inlineStr">
         <is>
@@ -6882,7 +6882,7 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
@@ -6891,7 +6891,7 @@
         </is>
       </c>
       <c r="G158" t="n">
-        <v>0.93</v>
+        <v>1.08</v>
       </c>
       <c r="H158" t="inlineStr">
         <is>
@@ -6923,7 +6923,7 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
@@ -6932,7 +6932,7 @@
         </is>
       </c>
       <c r="G159" t="n">
-        <v>0.63</v>
+        <v>0.49</v>
       </c>
       <c r="H159" t="inlineStr">
         <is>
@@ -7005,7 +7005,7 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
@@ -7014,7 +7014,7 @@
         </is>
       </c>
       <c r="G161" t="n">
-        <v>1.12</v>
+        <v>0.97</v>
       </c>
       <c r="H161" t="inlineStr">
         <is>
@@ -7046,7 +7046,7 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
@@ -7055,7 +7055,7 @@
         </is>
       </c>
       <c r="G162" t="n">
-        <v>0.71</v>
+        <v>0.57</v>
       </c>
       <c r="H162" t="inlineStr">
         <is>
@@ -7087,7 +7087,7 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
@@ -7096,7 +7096,7 @@
         </is>
       </c>
       <c r="G163" t="n">
-        <v>1</v>
+        <v>0.51</v>
       </c>
       <c r="H163" t="inlineStr">
         <is>
@@ -7137,7 +7137,7 @@
         </is>
       </c>
       <c r="G164" t="n">
-        <v>0.43</v>
+        <v>1.08</v>
       </c>
       <c r="H164" t="inlineStr">
         <is>
@@ -7169,7 +7169,7 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
@@ -7178,7 +7178,7 @@
         </is>
       </c>
       <c r="G165" t="n">
-        <v>0.91</v>
+        <v>0.98</v>
       </c>
       <c r="H165" t="inlineStr">
         <is>
@@ -7210,7 +7210,7 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
@@ -7219,7 +7219,7 @@
         </is>
       </c>
       <c r="G166" t="n">
-        <v>0.43</v>
+        <v>0.57</v>
       </c>
       <c r="H166" t="inlineStr">
         <is>
@@ -7260,7 +7260,7 @@
         </is>
       </c>
       <c r="G167" t="n">
-        <v>1.04</v>
+        <v>0.77</v>
       </c>
       <c r="H167" t="inlineStr">
         <is>
@@ -7301,7 +7301,7 @@
         </is>
       </c>
       <c r="G168" t="n">
-        <v>1.05</v>
+        <v>0.95</v>
       </c>
       <c r="H168" t="inlineStr">
         <is>
@@ -7333,7 +7333,7 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
@@ -7342,7 +7342,7 @@
         </is>
       </c>
       <c r="G169" t="n">
-        <v>0.49</v>
+        <v>0.48</v>
       </c>
       <c r="H169" t="inlineStr">
         <is>
@@ -7374,7 +7374,7 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
@@ -7383,7 +7383,7 @@
         </is>
       </c>
       <c r="G170" t="n">
-        <v>0.73</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H170" t="inlineStr">
         <is>
@@ -7415,7 +7415,7 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
@@ -7424,7 +7424,7 @@
         </is>
       </c>
       <c r="G171" t="n">
-        <v>0.89</v>
+        <v>1.13</v>
       </c>
       <c r="H171" t="inlineStr">
         <is>
@@ -7456,7 +7456,7 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
@@ -7465,7 +7465,7 @@
         </is>
       </c>
       <c r="G172" t="n">
-        <v>1.13</v>
+        <v>0.57</v>
       </c>
       <c r="H172" t="inlineStr">
         <is>
@@ -7497,7 +7497,7 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
@@ -7506,7 +7506,7 @@
         </is>
       </c>
       <c r="G173" t="n">
-        <v>0.64</v>
+        <v>0.99</v>
       </c>
       <c r="H173" t="inlineStr">
         <is>
@@ -7538,7 +7538,7 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
@@ -7547,7 +7547,7 @@
         </is>
       </c>
       <c r="G174" t="n">
-        <v>0.66</v>
+        <v>0.42</v>
       </c>
       <c r="H174" t="inlineStr">
         <is>
@@ -7579,7 +7579,7 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
@@ -7588,7 +7588,7 @@
         </is>
       </c>
       <c r="G175" t="n">
-        <v>0.63</v>
+        <v>0.61</v>
       </c>
       <c r="H175" t="inlineStr">
         <is>
@@ -7620,7 +7620,7 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
@@ -7629,7 +7629,7 @@
         </is>
       </c>
       <c r="G176" t="n">
-        <v>0.57</v>
+        <v>0.72</v>
       </c>
       <c r="H176" t="inlineStr">
         <is>
@@ -7670,7 +7670,7 @@
         </is>
       </c>
       <c r="G177" t="n">
-        <v>0.58</v>
+        <v>0.48</v>
       </c>
       <c r="H177" t="inlineStr">
         <is>
@@ -7702,7 +7702,7 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
@@ -7711,7 +7711,7 @@
         </is>
       </c>
       <c r="G178" t="n">
-        <v>0.58</v>
+        <v>0.98</v>
       </c>
       <c r="H178" t="inlineStr">
         <is>
@@ -7752,7 +7752,7 @@
         </is>
       </c>
       <c r="G179" t="n">
-        <v>0.51</v>
+        <v>0.49</v>
       </c>
       <c r="H179" t="inlineStr">
         <is>
@@ -7784,7 +7784,7 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
@@ -7793,7 +7793,7 @@
         </is>
       </c>
       <c r="G180" t="n">
-        <v>1.11</v>
+        <v>0.5</v>
       </c>
       <c r="H180" t="inlineStr">
         <is>
@@ -7825,7 +7825,7 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
@@ -7834,7 +7834,7 @@
         </is>
       </c>
       <c r="G181" t="n">
-        <v>0.86</v>
+        <v>0.64</v>
       </c>
       <c r="H181" t="inlineStr">
         <is>
@@ -7866,7 +7866,7 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
@@ -7875,7 +7875,7 @@
         </is>
       </c>
       <c r="G182" t="n">
-        <v>0.63</v>
+        <v>0.96</v>
       </c>
       <c r="H182" t="inlineStr">
         <is>
@@ -7916,7 +7916,7 @@
         </is>
       </c>
       <c r="G183" t="n">
-        <v>0.83</v>
+        <v>0.43</v>
       </c>
       <c r="H183" t="inlineStr">
         <is>
@@ -7948,7 +7948,7 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
@@ -7957,7 +7957,7 @@
         </is>
       </c>
       <c r="G184" t="n">
-        <v>0.93</v>
+        <v>0.57</v>
       </c>
       <c r="H184" t="inlineStr">
         <is>
@@ -7989,7 +7989,7 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
@@ -7998,7 +7998,7 @@
         </is>
       </c>
       <c r="G185" t="n">
-        <v>1.06</v>
+        <v>0.88</v>
       </c>
       <c r="H185" t="inlineStr">
         <is>
@@ -8030,7 +8030,7 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
@@ -8039,7 +8039,7 @@
         </is>
       </c>
       <c r="G186" t="n">
-        <v>0.82</v>
+        <v>0.89</v>
       </c>
       <c r="H186" t="inlineStr">
         <is>
@@ -8080,7 +8080,7 @@
         </is>
       </c>
       <c r="G187" t="n">
-        <v>0.75</v>
+        <v>0.46</v>
       </c>
       <c r="H187" t="inlineStr">
         <is>
@@ -8121,7 +8121,7 @@
         </is>
       </c>
       <c r="G188" t="n">
-        <v>0.85</v>
+        <v>0.82</v>
       </c>
       <c r="H188" t="inlineStr">
         <is>
@@ -8153,7 +8153,7 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
@@ -8162,7 +8162,7 @@
         </is>
       </c>
       <c r="G189" t="n">
-        <v>0.45</v>
+        <v>1.07</v>
       </c>
       <c r="H189" t="inlineStr">
         <is>
@@ -8194,7 +8194,7 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
@@ -8203,7 +8203,7 @@
         </is>
       </c>
       <c r="G190" t="n">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="H190" t="inlineStr">
         <is>
@@ -8244,7 +8244,7 @@
         </is>
       </c>
       <c r="G191" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="H191" t="inlineStr">
         <is>
@@ -8285,7 +8285,7 @@
         </is>
       </c>
       <c r="G192" t="n">
-        <v>1.12</v>
+        <v>0.89</v>
       </c>
       <c r="H192" t="inlineStr">
         <is>
@@ -8326,7 +8326,7 @@
         </is>
       </c>
       <c r="G193" t="n">
-        <v>0.67</v>
+        <v>0.76</v>
       </c>
       <c r="H193" t="inlineStr">
         <is>
@@ -8367,7 +8367,7 @@
         </is>
       </c>
       <c r="G194" t="n">
-        <v>0.73</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H194" t="inlineStr">
         <is>
@@ -8399,7 +8399,7 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
@@ -8408,7 +8408,7 @@
         </is>
       </c>
       <c r="G195" t="n">
-        <v>0.57</v>
+        <v>0.64</v>
       </c>
       <c r="H195" t="inlineStr">
         <is>
@@ -8440,7 +8440,7 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
@@ -8449,7 +8449,7 @@
         </is>
       </c>
       <c r="G196" t="n">
-        <v>0.7</v>
+        <v>0.95</v>
       </c>
       <c r="H196" t="inlineStr">
         <is>
@@ -8490,7 +8490,7 @@
         </is>
       </c>
       <c r="G197" t="n">
-        <v>0.66</v>
+        <v>0.8</v>
       </c>
       <c r="H197" t="inlineStr">
         <is>
@@ -8522,7 +8522,7 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
@@ -8531,7 +8531,7 @@
         </is>
       </c>
       <c r="G198" t="n">
-        <v>0.95</v>
+        <v>0.59</v>
       </c>
       <c r="H198" t="inlineStr">
         <is>
@@ -8563,7 +8563,7 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
@@ -8572,7 +8572,7 @@
         </is>
       </c>
       <c r="G199" t="n">
-        <v>0.89</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H199" t="inlineStr">
         <is>
@@ -8604,7 +8604,7 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
@@ -8613,7 +8613,7 @@
         </is>
       </c>
       <c r="G200" t="n">
-        <v>0.89</v>
+        <v>0.64</v>
       </c>
       <c r="H200" t="inlineStr">
         <is>
@@ -8645,7 +8645,7 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
@@ -8654,7 +8654,7 @@
         </is>
       </c>
       <c r="G201" t="n">
-        <v>0.67</v>
+        <v>0.64</v>
       </c>
       <c r="H201" t="inlineStr">
         <is>
@@ -8686,7 +8686,7 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
@@ -8695,7 +8695,7 @@
         </is>
       </c>
       <c r="G202" t="n">
-        <v>0.73</v>
+        <v>1.01</v>
       </c>
       <c r="H202" t="inlineStr">
         <is>
@@ -8727,7 +8727,7 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
@@ -8736,7 +8736,7 @@
         </is>
       </c>
       <c r="G203" t="n">
-        <v>1.02</v>
+        <v>0.66</v>
       </c>
       <c r="H203" t="inlineStr">
         <is>
@@ -8768,7 +8768,7 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
@@ -8777,7 +8777,7 @@
         </is>
       </c>
       <c r="G204" t="n">
-        <v>0.91</v>
+        <v>1.05</v>
       </c>
       <c r="H204" t="inlineStr">
         <is>
@@ -8809,7 +8809,7 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
@@ -8818,7 +8818,7 @@
         </is>
       </c>
       <c r="G205" t="n">
-        <v>0.79</v>
+        <v>1.06</v>
       </c>
       <c r="H205" t="inlineStr">
         <is>
@@ -8850,7 +8850,7 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
@@ -8859,7 +8859,7 @@
         </is>
       </c>
       <c r="G206" t="n">
-        <v>0.6</v>
+        <v>0.54</v>
       </c>
       <c r="H206" t="inlineStr">
         <is>
@@ -8891,7 +8891,7 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
@@ -8900,7 +8900,7 @@
         </is>
       </c>
       <c r="G207" t="n">
-        <v>0.66</v>
+        <v>0.55</v>
       </c>
       <c r="H207" t="inlineStr">
         <is>
@@ -8932,7 +8932,7 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
@@ -8941,7 +8941,7 @@
         </is>
       </c>
       <c r="G208" t="n">
-        <v>1.01</v>
+        <v>0.79</v>
       </c>
       <c r="H208" t="inlineStr">
         <is>
@@ -8982,7 +8982,7 @@
         </is>
       </c>
       <c r="G209" t="n">
-        <v>0.93</v>
+        <v>0.51</v>
       </c>
       <c r="H209" t="inlineStr">
         <is>
@@ -9023,7 +9023,7 @@
         </is>
       </c>
       <c r="G210" t="n">
-        <v>0.42</v>
+        <v>1.12</v>
       </c>
       <c r="H210" t="inlineStr">
         <is>
@@ -9055,7 +9055,7 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
@@ -9064,7 +9064,7 @@
         </is>
       </c>
       <c r="G211" t="n">
-        <v>1.07</v>
+        <v>0.82</v>
       </c>
       <c r="H211" t="inlineStr">
         <is>
@@ -9096,7 +9096,7 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
@@ -9105,7 +9105,7 @@
         </is>
       </c>
       <c r="G212" t="n">
-        <v>0.71</v>
+        <v>0.82</v>
       </c>
       <c r="H212" t="inlineStr">
         <is>
@@ -9137,7 +9137,7 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
@@ -9146,7 +9146,7 @@
         </is>
       </c>
       <c r="G213" t="n">
-        <v>0.75</v>
+        <v>1.06</v>
       </c>
       <c r="H213" t="inlineStr">
         <is>
@@ -9178,7 +9178,7 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
@@ -9187,7 +9187,7 @@
         </is>
       </c>
       <c r="G214" t="n">
-        <v>0.67</v>
+        <v>0.48</v>
       </c>
       <c r="H214" t="inlineStr">
         <is>
@@ -9219,7 +9219,7 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
@@ -9228,7 +9228,7 @@
         </is>
       </c>
       <c r="G215" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.5</v>
       </c>
       <c r="H215" t="inlineStr">
         <is>
@@ -9269,7 +9269,7 @@
         </is>
       </c>
       <c r="G216" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.54</v>
       </c>
       <c r="H216" t="inlineStr">
         <is>
@@ -9310,7 +9310,7 @@
         </is>
       </c>
       <c r="G217" t="n">
-        <v>0.83</v>
+        <v>0.92</v>
       </c>
       <c r="H217" t="inlineStr">
         <is>
@@ -9342,7 +9342,7 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
@@ -9351,7 +9351,7 @@
         </is>
       </c>
       <c r="G218" t="n">
-        <v>1.02</v>
+        <v>0.85</v>
       </c>
       <c r="H218" t="inlineStr">
         <is>
@@ -9392,7 +9392,7 @@
         </is>
       </c>
       <c r="G219" t="n">
-        <v>0.48</v>
+        <v>0.57</v>
       </c>
       <c r="H219" t="inlineStr">
         <is>
@@ -9424,7 +9424,7 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
@@ -9433,7 +9433,7 @@
         </is>
       </c>
       <c r="G220" t="n">
-        <v>0.9</v>
+        <v>0.87</v>
       </c>
       <c r="H220" t="inlineStr">
         <is>
@@ -9465,7 +9465,7 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
@@ -9474,7 +9474,7 @@
         </is>
       </c>
       <c r="G221" t="n">
-        <v>1.07</v>
+        <v>0.51</v>
       </c>
       <c r="H221" t="inlineStr">
         <is>
@@ -9506,7 +9506,7 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
@@ -9515,7 +9515,7 @@
         </is>
       </c>
       <c r="G222" t="n">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="H222" t="inlineStr">
         <is>
@@ -9547,7 +9547,7 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
@@ -9556,7 +9556,7 @@
         </is>
       </c>
       <c r="G223" t="n">
-        <v>1.07</v>
+        <v>0.92</v>
       </c>
       <c r="H223" t="inlineStr">
         <is>
@@ -9597,7 +9597,7 @@
         </is>
       </c>
       <c r="G224" t="n">
-        <v>0.62</v>
+        <v>0.59</v>
       </c>
       <c r="H224" t="inlineStr">
         <is>
@@ -9629,7 +9629,7 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
@@ -9638,7 +9638,7 @@
         </is>
       </c>
       <c r="G225" t="n">
-        <v>1.01</v>
+        <v>0.59</v>
       </c>
       <c r="H225" t="inlineStr">
         <is>
@@ -9679,7 +9679,7 @@
         </is>
       </c>
       <c r="G226" t="n">
-        <v>0.74</v>
+        <v>0.64</v>
       </c>
       <c r="H226" t="inlineStr">
         <is>
@@ -9720,7 +9720,7 @@
         </is>
       </c>
       <c r="G227" t="n">
-        <v>0.66</v>
+        <v>0.6</v>
       </c>
       <c r="H227" t="inlineStr">
         <is>
@@ -9761,7 +9761,7 @@
         </is>
       </c>
       <c r="G228" t="n">
-        <v>1.11</v>
+        <v>0.73</v>
       </c>
       <c r="H228" t="inlineStr">
         <is>
@@ -9793,7 +9793,7 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
@@ -9802,7 +9802,7 @@
         </is>
       </c>
       <c r="G229" t="n">
-        <v>0.46</v>
+        <v>1.02</v>
       </c>
       <c r="H229" t="inlineStr">
         <is>
@@ -9834,7 +9834,7 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
@@ -9843,7 +9843,7 @@
         </is>
       </c>
       <c r="G230" t="n">
-        <v>0.47</v>
+        <v>0.92</v>
       </c>
       <c r="H230" t="inlineStr">
         <is>
@@ -9884,7 +9884,7 @@
         </is>
       </c>
       <c r="G231" t="n">
-        <v>1.05</v>
+        <v>0.84</v>
       </c>
       <c r="H231" t="inlineStr">
         <is>
@@ -9916,7 +9916,7 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
@@ -9925,7 +9925,7 @@
         </is>
       </c>
       <c r="G232" t="n">
-        <v>0.68</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H232" t="inlineStr">
         <is>
@@ -9957,7 +9957,7 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
@@ -9966,7 +9966,7 @@
         </is>
       </c>
       <c r="G233" t="n">
-        <v>1.05</v>
+        <v>0.48</v>
       </c>
       <c r="H233" t="inlineStr">
         <is>
@@ -9998,7 +9998,7 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
@@ -10007,7 +10007,7 @@
         </is>
       </c>
       <c r="G234" t="n">
-        <v>1.11</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H234" t="inlineStr">
         <is>
@@ -10048,7 +10048,7 @@
         </is>
       </c>
       <c r="G235" t="n">
-        <v>1.13</v>
+        <v>0.52</v>
       </c>
       <c r="H235" t="inlineStr">
         <is>
@@ -10080,7 +10080,7 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
@@ -10089,7 +10089,7 @@
         </is>
       </c>
       <c r="G236" t="n">
-        <v>1.15</v>
+        <v>0.58</v>
       </c>
       <c r="H236" t="inlineStr">
         <is>
@@ -10162,7 +10162,7 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
@@ -10171,7 +10171,7 @@
         </is>
       </c>
       <c r="G238" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.99</v>
       </c>
       <c r="H238" t="inlineStr">
         <is>
@@ -10212,7 +10212,7 @@
         </is>
       </c>
       <c r="G239" t="n">
-        <v>0.91</v>
+        <v>1</v>
       </c>
       <c r="H239" t="inlineStr">
         <is>
@@ -10244,7 +10244,7 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
@@ -10253,7 +10253,7 @@
         </is>
       </c>
       <c r="G240" t="n">
-        <v>0.7</v>
+        <v>0.47</v>
       </c>
       <c r="H240" t="inlineStr">
         <is>
@@ -10285,7 +10285,7 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
@@ -10294,7 +10294,7 @@
         </is>
       </c>
       <c r="G241" t="n">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="H241" t="inlineStr">
         <is>
@@ -10326,7 +10326,7 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
@@ -10335,7 +10335,7 @@
         </is>
       </c>
       <c r="G242" t="n">
-        <v>0.44</v>
+        <v>0.53</v>
       </c>
       <c r="H242" t="inlineStr">
         <is>
@@ -10417,7 +10417,7 @@
         </is>
       </c>
       <c r="G244" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="H244" t="inlineStr">
         <is>
@@ -10458,7 +10458,7 @@
         </is>
       </c>
       <c r="G245" t="n">
-        <v>0.59</v>
+        <v>0.53</v>
       </c>
       <c r="H245" t="inlineStr">
         <is>
@@ -10490,7 +10490,7 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
@@ -10499,7 +10499,7 @@
         </is>
       </c>
       <c r="G246" t="n">
-        <v>0.92</v>
+        <v>0.52</v>
       </c>
       <c r="H246" t="inlineStr">
         <is>
@@ -10540,7 +10540,7 @@
         </is>
       </c>
       <c r="G247" t="n">
-        <v>1.06</v>
+        <v>0.92</v>
       </c>
       <c r="H247" t="inlineStr">
         <is>
@@ -10572,7 +10572,7 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
@@ -10581,7 +10581,7 @@
         </is>
       </c>
       <c r="G248" t="n">
-        <v>0.48</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H248" t="inlineStr">
         <is>
@@ -10613,7 +10613,7 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
@@ -10622,7 +10622,7 @@
         </is>
       </c>
       <c r="G249" t="n">
-        <v>0.65</v>
+        <v>0.45</v>
       </c>
       <c r="H249" t="inlineStr">
         <is>
@@ -10663,7 +10663,7 @@
         </is>
       </c>
       <c r="G250" t="n">
-        <v>0.45</v>
+        <v>1.03</v>
       </c>
       <c r="H250" t="inlineStr">
         <is>
@@ -10695,7 +10695,7 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
@@ -10704,7 +10704,7 @@
         </is>
       </c>
       <c r="G251" t="n">
-        <v>0.95</v>
+        <v>0.52</v>
       </c>
       <c r="H251" t="inlineStr">
         <is>
@@ -10736,7 +10736,7 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
@@ -10745,7 +10745,7 @@
         </is>
       </c>
       <c r="G252" t="n">
-        <v>0.86</v>
+        <v>1.14</v>
       </c>
       <c r="H252" t="inlineStr">
         <is>
@@ -10786,7 +10786,7 @@
         </is>
       </c>
       <c r="G253" t="n">
-        <v>1.06</v>
+        <v>0.86</v>
       </c>
       <c r="H253" t="inlineStr">
         <is>
@@ -10818,7 +10818,7 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
@@ -10827,7 +10827,7 @@
         </is>
       </c>
       <c r="G254" t="n">
-        <v>0.91</v>
+        <v>0.7</v>
       </c>
       <c r="H254" t="inlineStr">
         <is>
@@ -10859,7 +10859,7 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
@@ -10868,7 +10868,7 @@
         </is>
       </c>
       <c r="G255" t="n">
-        <v>0.74</v>
+        <v>1.13</v>
       </c>
       <c r="H255" t="inlineStr">
         <is>
@@ -10900,7 +10900,7 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
@@ -10909,7 +10909,7 @@
         </is>
       </c>
       <c r="G256" t="n">
-        <v>0.75</v>
+        <v>0.74</v>
       </c>
       <c r="H256" t="inlineStr">
         <is>
@@ -10950,7 +10950,7 @@
         </is>
       </c>
       <c r="G257" t="n">
-        <v>0.71</v>
+        <v>0.53</v>
       </c>
       <c r="H257" t="inlineStr">
         <is>
@@ -10982,7 +10982,7 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
@@ -10991,7 +10991,7 @@
         </is>
       </c>
       <c r="G258" t="n">
-        <v>0.46</v>
+        <v>0.72</v>
       </c>
       <c r="H258" t="inlineStr">
         <is>
@@ -11023,7 +11023,7 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
@@ -11032,7 +11032,7 @@
         </is>
       </c>
       <c r="G259" t="n">
-        <v>1.09</v>
+        <v>0.48</v>
       </c>
       <c r="H259" t="inlineStr">
         <is>
@@ -11064,7 +11064,7 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
@@ -11073,7 +11073,7 @@
         </is>
       </c>
       <c r="G260" t="n">
-        <v>1.07</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H260" t="inlineStr">
         <is>
@@ -11105,7 +11105,7 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
@@ -11114,7 +11114,7 @@
         </is>
       </c>
       <c r="G261" t="n">
-        <v>1.15</v>
+        <v>0.58</v>
       </c>
       <c r="H261" t="inlineStr">
         <is>
@@ -11146,7 +11146,7 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
@@ -11155,7 +11155,7 @@
         </is>
       </c>
       <c r="G262" t="n">
-        <v>1.03</v>
+        <v>0.85</v>
       </c>
       <c r="H262" t="inlineStr">
         <is>
@@ -11196,7 +11196,7 @@
         </is>
       </c>
       <c r="G263" t="n">
-        <v>0.78</v>
+        <v>0.82</v>
       </c>
       <c r="H263" t="inlineStr">
         <is>
@@ -11228,7 +11228,7 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
@@ -11237,7 +11237,7 @@
         </is>
       </c>
       <c r="G264" t="n">
-        <v>0.44</v>
+        <v>0.77</v>
       </c>
       <c r="H264" t="inlineStr">
         <is>
@@ -11269,7 +11269,7 @@
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
@@ -11278,7 +11278,7 @@
         </is>
       </c>
       <c r="G265" t="n">
-        <v>0.87</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H265" t="inlineStr">
         <is>
@@ -11319,7 +11319,7 @@
         </is>
       </c>
       <c r="G266" t="n">
-        <v>1.13</v>
+        <v>0.5</v>
       </c>
       <c r="H266" t="inlineStr">
         <is>
@@ -11351,7 +11351,7 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
@@ -11360,7 +11360,7 @@
         </is>
       </c>
       <c r="G267" t="n">
-        <v>0.95</v>
+        <v>0.45</v>
       </c>
       <c r="H267" t="inlineStr">
         <is>
@@ -11401,7 +11401,7 @@
         </is>
       </c>
       <c r="G268" t="n">
-        <v>0.92</v>
+        <v>0.96</v>
       </c>
       <c r="H268" t="inlineStr">
         <is>
@@ -11442,7 +11442,7 @@
         </is>
       </c>
       <c r="G269" t="n">
-        <v>0.88</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H269" t="inlineStr">
         <is>
@@ -11474,7 +11474,7 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
@@ -11483,7 +11483,7 @@
         </is>
       </c>
       <c r="G270" t="n">
-        <v>1</v>
+        <v>1.08</v>
       </c>
       <c r="H270" t="inlineStr">
         <is>
@@ -11515,7 +11515,7 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
@@ -11524,7 +11524,7 @@
         </is>
       </c>
       <c r="G271" t="n">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="H271" t="inlineStr">
         <is>
@@ -11556,7 +11556,7 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
@@ -11565,7 +11565,7 @@
         </is>
       </c>
       <c r="G272" t="n">
-        <v>0.54</v>
+        <v>0.85</v>
       </c>
       <c r="H272" t="inlineStr">
         <is>
@@ -11597,7 +11597,7 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
@@ -11606,7 +11606,7 @@
         </is>
       </c>
       <c r="G273" t="n">
-        <v>0.8</v>
+        <v>0.78</v>
       </c>
       <c r="H273" t="inlineStr">
         <is>
@@ -11638,7 +11638,7 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
@@ -11647,7 +11647,7 @@
         </is>
       </c>
       <c r="G274" t="n">
-        <v>0.72</v>
+        <v>1.07</v>
       </c>
       <c r="H274" t="inlineStr">
         <is>
@@ -11679,7 +11679,7 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
@@ -11688,7 +11688,7 @@
         </is>
       </c>
       <c r="G275" t="n">
-        <v>1.07</v>
+        <v>0.42</v>
       </c>
       <c r="H275" t="inlineStr">
         <is>
@@ -11720,7 +11720,7 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
@@ -11729,7 +11729,7 @@
         </is>
       </c>
       <c r="G276" t="n">
-        <v>0.89</v>
+        <v>0.7</v>
       </c>
       <c r="H276" t="inlineStr">
         <is>
@@ -11761,7 +11761,7 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
@@ -11770,7 +11770,7 @@
         </is>
       </c>
       <c r="G277" t="n">
-        <v>1.04</v>
+        <v>0.77</v>
       </c>
       <c r="H277" t="inlineStr">
         <is>
@@ -11802,7 +11802,7 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
@@ -11811,7 +11811,7 @@
         </is>
       </c>
       <c r="G278" t="n">
-        <v>0.5</v>
+        <v>0.98</v>
       </c>
       <c r="H278" t="inlineStr">
         <is>
@@ -11843,7 +11843,7 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
@@ -11852,7 +11852,7 @@
         </is>
       </c>
       <c r="G279" t="n">
-        <v>0.66</v>
+        <v>0.47</v>
       </c>
       <c r="H279" t="inlineStr">
         <is>
@@ -11884,7 +11884,7 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
@@ -11893,7 +11893,7 @@
         </is>
       </c>
       <c r="G280" t="n">
-        <v>0.95</v>
+        <v>1.03</v>
       </c>
       <c r="H280" t="inlineStr">
         <is>
@@ -11934,7 +11934,7 @@
         </is>
       </c>
       <c r="G281" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="H281" t="inlineStr">
         <is>
@@ -11966,7 +11966,7 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
@@ -11975,7 +11975,7 @@
         </is>
       </c>
       <c r="G282" t="n">
-        <v>0.79</v>
+        <v>1.02</v>
       </c>
       <c r="H282" t="inlineStr">
         <is>
@@ -12007,7 +12007,7 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
@@ -12016,7 +12016,7 @@
         </is>
       </c>
       <c r="G283" t="n">
-        <v>0.72</v>
+        <v>0.45</v>
       </c>
       <c r="H283" t="inlineStr">
         <is>
@@ -12057,7 +12057,7 @@
         </is>
       </c>
       <c r="G284" t="n">
-        <v>0.88</v>
+        <v>0.92</v>
       </c>
       <c r="H284" t="inlineStr">
         <is>
@@ -12089,7 +12089,7 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
@@ -12098,7 +12098,7 @@
         </is>
       </c>
       <c r="G285" t="n">
-        <v>0.67</v>
+        <v>0.98</v>
       </c>
       <c r="H285" t="inlineStr">
         <is>
@@ -12130,7 +12130,7 @@
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
@@ -12139,7 +12139,7 @@
         </is>
       </c>
       <c r="G286" t="n">
-        <v>0.68</v>
+        <v>0.79</v>
       </c>
       <c r="H286" t="inlineStr">
         <is>
@@ -12171,7 +12171,7 @@
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
@@ -12180,7 +12180,7 @@
         </is>
       </c>
       <c r="G287" t="n">
-        <v>0.57</v>
+        <v>0.79</v>
       </c>
       <c r="H287" t="inlineStr">
         <is>
@@ -12212,7 +12212,7 @@
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
@@ -12221,7 +12221,7 @@
         </is>
       </c>
       <c r="G288" t="n">
-        <v>0.98</v>
+        <v>0.82</v>
       </c>
       <c r="H288" t="inlineStr">
         <is>
@@ -12262,7 +12262,7 @@
         </is>
       </c>
       <c r="G289" t="n">
-        <v>0.43</v>
+        <v>0.71</v>
       </c>
       <c r="H289" t="inlineStr">
         <is>
@@ -12294,7 +12294,7 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
@@ -12303,7 +12303,7 @@
         </is>
       </c>
       <c r="G290" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="H290" t="inlineStr">
         <is>
@@ -12335,7 +12335,7 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
@@ -12344,7 +12344,7 @@
         </is>
       </c>
       <c r="G291" t="n">
-        <v>0.7</v>
+        <v>0.84</v>
       </c>
       <c r="H291" t="inlineStr">
         <is>
@@ -12385,7 +12385,7 @@
         </is>
       </c>
       <c r="G292" t="n">
-        <v>0.85</v>
+        <v>0.62</v>
       </c>
       <c r="H292" t="inlineStr">
         <is>
@@ -12417,7 +12417,7 @@
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
@@ -12426,7 +12426,7 @@
         </is>
       </c>
       <c r="G293" t="n">
-        <v>0.58</v>
+        <v>0.52</v>
       </c>
       <c r="H293" t="inlineStr">
         <is>
@@ -12467,7 +12467,7 @@
         </is>
       </c>
       <c r="G294" t="n">
-        <v>0.82</v>
+        <v>0.47</v>
       </c>
       <c r="H294" t="inlineStr">
         <is>
@@ -12499,7 +12499,7 @@
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
@@ -12508,7 +12508,7 @@
         </is>
       </c>
       <c r="G295" t="n">
-        <v>0.88</v>
+        <v>1.07</v>
       </c>
       <c r="H295" t="inlineStr">
         <is>
@@ -12540,7 +12540,7 @@
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
@@ -12549,7 +12549,7 @@
         </is>
       </c>
       <c r="G296" t="n">
-        <v>0.54</v>
+        <v>0.63</v>
       </c>
       <c r="H296" t="inlineStr">
         <is>
@@ -12581,7 +12581,7 @@
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
@@ -12590,7 +12590,7 @@
         </is>
       </c>
       <c r="G297" t="n">
-        <v>0.52</v>
+        <v>0.43</v>
       </c>
       <c r="H297" t="inlineStr">
         <is>
@@ -12631,7 +12631,7 @@
         </is>
       </c>
       <c r="G298" t="n">
-        <v>0.87</v>
+        <v>0.42</v>
       </c>
       <c r="H298" t="inlineStr">
         <is>
@@ -12672,7 +12672,7 @@
         </is>
       </c>
       <c r="G299" t="n">
-        <v>0.58</v>
+        <v>0.66</v>
       </c>
       <c r="H299" t="inlineStr">
         <is>
@@ -12704,7 +12704,7 @@
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
@@ -12713,7 +12713,7 @@
         </is>
       </c>
       <c r="G300" t="n">
-        <v>0.47</v>
+        <v>0.9</v>
       </c>
       <c r="H300" t="inlineStr">
         <is>
@@ -12745,7 +12745,7 @@
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
@@ -12754,7 +12754,7 @@
         </is>
       </c>
       <c r="G301" t="n">
-        <v>0.8</v>
+        <v>0.46</v>
       </c>
       <c r="H301" t="inlineStr">
         <is>

--- a/reports/Passed_Test_Cases.xlsx
+++ b/reports/Passed_Test_Cases.xlsx
@@ -486,7 +486,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -495,7 +495,7 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0.79</v>
+        <v>0.95</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -527,7 +527,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>1.07</v>
+        <v>0.72</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -568,7 +568,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -577,7 +577,7 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0.53</v>
+        <v>0.51</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -618,7 +618,7 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>0.83</v>
+        <v>1.05</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -650,7 +650,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>0.76</v>
+        <v>0.44</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -691,7 +691,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -700,7 +700,7 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>1.14</v>
+        <v>0.99</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -732,7 +732,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -741,7 +741,7 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -773,7 +773,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -782,7 +782,7 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>1.02</v>
+        <v>0.5</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -814,7 +814,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -823,7 +823,7 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>0.64</v>
+        <v>0.96</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -864,7 +864,7 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>0.95</v>
+        <v>0.67</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>0.6</v>
+        <v>0.57</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -946,7 +946,7 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>0.61</v>
+        <v>0.47</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -978,7 +978,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -987,7 +987,7 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>0.6899999999999999</v>
+        <v>1.02</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1028,7 +1028,7 @@
         </is>
       </c>
       <c r="G15" t="n">
-        <v>0.84</v>
+        <v>0.64</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -1060,7 +1060,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1069,7 +1069,7 @@
         </is>
       </c>
       <c r="G16" t="n">
-        <v>1.11</v>
+        <v>0.76</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -1101,7 +1101,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1110,7 +1110,7 @@
         </is>
       </c>
       <c r="G17" t="n">
-        <v>0.72</v>
+        <v>0.49</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -1142,7 +1142,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1151,7 +1151,7 @@
         </is>
       </c>
       <c r="G18" t="n">
-        <v>1.07</v>
+        <v>0.66</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1192,7 +1192,7 @@
         </is>
       </c>
       <c r="G19" t="n">
-        <v>0.59</v>
+        <v>0.47</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         </is>
       </c>
       <c r="G20" t="n">
-        <v>0.47</v>
+        <v>0.7</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -1274,7 +1274,7 @@
         </is>
       </c>
       <c r="G21" t="n">
-        <v>0.51</v>
+        <v>1.13</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -1306,7 +1306,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1315,7 +1315,7 @@
         </is>
       </c>
       <c r="G22" t="n">
-        <v>0.6</v>
+        <v>0.91</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
@@ -1347,7 +1347,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1356,7 +1356,7 @@
         </is>
       </c>
       <c r="G23" t="n">
-        <v>1.06</v>
+        <v>0.62</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1397,7 +1397,7 @@
         </is>
       </c>
       <c r="G24" t="n">
-        <v>0.73</v>
+        <v>1.08</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
@@ -1438,7 +1438,7 @@
         </is>
       </c>
       <c r="G25" t="n">
-        <v>0.78</v>
+        <v>0.55</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
@@ -1470,7 +1470,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1479,7 +1479,7 @@
         </is>
       </c>
       <c r="G26" t="n">
-        <v>0.79</v>
+        <v>0.68</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
@@ -1511,7 +1511,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1520,7 +1520,7 @@
         </is>
       </c>
       <c r="G27" t="n">
-        <v>0.43</v>
+        <v>0.75</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
@@ -1561,7 +1561,7 @@
         </is>
       </c>
       <c r="G28" t="n">
-        <v>0.91</v>
+        <v>0.7</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
@@ -1593,7 +1593,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1602,7 +1602,7 @@
         </is>
       </c>
       <c r="G29" t="n">
-        <v>0.57</v>
+        <v>0.55</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
@@ -1634,7 +1634,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1643,7 +1643,7 @@
         </is>
       </c>
       <c r="G30" t="n">
-        <v>0.89</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
@@ -1675,7 +1675,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1684,7 +1684,7 @@
         </is>
       </c>
       <c r="G31" t="n">
-        <v>1.04</v>
+        <v>0.6</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
@@ -1716,7 +1716,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1725,7 +1725,7 @@
         </is>
       </c>
       <c r="G32" t="n">
-        <v>0.61</v>
+        <v>0.52</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
@@ -1757,7 +1757,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1766,7 +1766,7 @@
         </is>
       </c>
       <c r="G33" t="n">
-        <v>0.5</v>
+        <v>0.66</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
@@ -1798,7 +1798,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1807,7 +1807,7 @@
         </is>
       </c>
       <c r="G34" t="n">
-        <v>0.73</v>
+        <v>0.6</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
@@ -1839,7 +1839,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1848,7 +1848,7 @@
         </is>
       </c>
       <c r="G35" t="n">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
@@ -1880,7 +1880,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1889,7 +1889,7 @@
         </is>
       </c>
       <c r="G36" t="n">
-        <v>0.65</v>
+        <v>0.84</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1930,7 +1930,7 @@
         </is>
       </c>
       <c r="G37" t="n">
-        <v>1.08</v>
+        <v>0.45</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
@@ -1971,7 +1971,7 @@
         </is>
       </c>
       <c r="G38" t="n">
-        <v>0.91</v>
+        <v>1.15</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
@@ -2003,7 +2003,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -2012,7 +2012,7 @@
         </is>
       </c>
       <c r="G39" t="n">
-        <v>0.72</v>
+        <v>0.89</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
@@ -2044,7 +2044,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -2053,7 +2053,7 @@
         </is>
       </c>
       <c r="G40" t="n">
-        <v>0.49</v>
+        <v>0.9</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
@@ -2085,7 +2085,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -2094,7 +2094,7 @@
         </is>
       </c>
       <c r="G41" t="n">
-        <v>0.93</v>
+        <v>0.68</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
@@ -2126,7 +2126,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -2135,7 +2135,7 @@
         </is>
       </c>
       <c r="G42" t="n">
-        <v>0.63</v>
+        <v>0.45</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
@@ -2176,7 +2176,7 @@
         </is>
       </c>
       <c r="G43" t="n">
-        <v>1.1</v>
+        <v>0.76</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
@@ -2208,7 +2208,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -2217,7 +2217,7 @@
         </is>
       </c>
       <c r="G44" t="n">
-        <v>0.99</v>
+        <v>0.85</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
@@ -2249,7 +2249,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2258,7 +2258,7 @@
         </is>
       </c>
       <c r="G45" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.95</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
@@ -2299,7 +2299,7 @@
         </is>
       </c>
       <c r="G46" t="n">
-        <v>0.98</v>
+        <v>0.86</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
@@ -2331,7 +2331,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2340,7 +2340,7 @@
         </is>
       </c>
       <c r="G47" t="n">
-        <v>1.14</v>
+        <v>0.46</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
@@ -2381,7 +2381,7 @@
         </is>
       </c>
       <c r="G48" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.75</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
@@ -2413,7 +2413,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2422,7 +2422,7 @@
         </is>
       </c>
       <c r="G49" t="n">
-        <v>0.72</v>
+        <v>1.13</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
@@ -2454,7 +2454,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2463,7 +2463,7 @@
         </is>
       </c>
       <c r="G50" t="n">
-        <v>0.77</v>
+        <v>0.47</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
@@ -2495,7 +2495,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2504,7 +2504,7 @@
         </is>
       </c>
       <c r="G51" t="n">
-        <v>1.11</v>
+        <v>1.02</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
@@ -2536,7 +2536,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2545,7 +2545,7 @@
         </is>
       </c>
       <c r="G52" t="n">
-        <v>0.97</v>
+        <v>1</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
@@ -2586,7 +2586,7 @@
         </is>
       </c>
       <c r="G53" t="n">
-        <v>0.72</v>
+        <v>0.54</v>
       </c>
       <c r="H53" t="inlineStr">
         <is>
@@ -2618,7 +2618,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2627,7 +2627,7 @@
         </is>
       </c>
       <c r="G54" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.52</v>
       </c>
       <c r="H54" t="inlineStr">
         <is>
@@ -2659,7 +2659,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2668,7 +2668,7 @@
         </is>
       </c>
       <c r="G55" t="n">
-        <v>0.9</v>
+        <v>0.44</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
@@ -2700,7 +2700,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2709,7 +2709,7 @@
         </is>
       </c>
       <c r="G56" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
@@ -2750,7 +2750,7 @@
         </is>
       </c>
       <c r="G57" t="n">
-        <v>0.63</v>
+        <v>0.55</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
@@ -2782,7 +2782,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2791,7 +2791,7 @@
         </is>
       </c>
       <c r="G58" t="n">
-        <v>1</v>
+        <v>0.98</v>
       </c>
       <c r="H58" t="inlineStr">
         <is>
@@ -2832,7 +2832,7 @@
         </is>
       </c>
       <c r="G59" t="n">
-        <v>0.73</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H59" t="inlineStr">
         <is>
@@ -2864,7 +2864,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2873,7 +2873,7 @@
         </is>
       </c>
       <c r="G60" t="n">
-        <v>0.73</v>
+        <v>1.13</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
@@ -2914,7 +2914,7 @@
         </is>
       </c>
       <c r="G61" t="n">
-        <v>1.1</v>
+        <v>0.99</v>
       </c>
       <c r="H61" t="inlineStr">
         <is>
@@ -2946,7 +2946,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2955,7 +2955,7 @@
         </is>
       </c>
       <c r="G62" t="n">
-        <v>0.88</v>
+        <v>0.64</v>
       </c>
       <c r="H62" t="inlineStr">
         <is>
@@ -2996,7 +2996,7 @@
         </is>
       </c>
       <c r="G63" t="n">
-        <v>0.44</v>
+        <v>0.47</v>
       </c>
       <c r="H63" t="inlineStr">
         <is>
@@ -3037,7 +3037,7 @@
         </is>
       </c>
       <c r="G64" t="n">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="H64" t="inlineStr">
         <is>
@@ -3069,7 +3069,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -3078,7 +3078,7 @@
         </is>
       </c>
       <c r="G65" t="n">
-        <v>1.06</v>
+        <v>0.93</v>
       </c>
       <c r="H65" t="inlineStr">
         <is>
@@ -3110,7 +3110,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -3119,7 +3119,7 @@
         </is>
       </c>
       <c r="G66" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.55</v>
       </c>
       <c r="H66" t="inlineStr">
         <is>
@@ -3151,7 +3151,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -3160,7 +3160,7 @@
         </is>
       </c>
       <c r="G67" t="n">
-        <v>0.46</v>
+        <v>0.48</v>
       </c>
       <c r="H67" t="inlineStr">
         <is>
@@ -3192,7 +3192,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -3201,7 +3201,7 @@
         </is>
       </c>
       <c r="G68" t="n">
-        <v>0.8100000000000001</v>
+        <v>1.07</v>
       </c>
       <c r="H68" t="inlineStr">
         <is>
@@ -3242,7 +3242,7 @@
         </is>
       </c>
       <c r="G69" t="n">
-        <v>0.63</v>
+        <v>1.13</v>
       </c>
       <c r="H69" t="inlineStr">
         <is>
@@ -3283,7 +3283,7 @@
         </is>
       </c>
       <c r="G70" t="n">
-        <v>0.98</v>
+        <v>0.65</v>
       </c>
       <c r="H70" t="inlineStr">
         <is>
@@ -3324,7 +3324,7 @@
         </is>
       </c>
       <c r="G71" t="n">
-        <v>0.93</v>
+        <v>1.08</v>
       </c>
       <c r="H71" t="inlineStr">
         <is>
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -3365,7 +3365,7 @@
         </is>
       </c>
       <c r="G72" t="n">
-        <v>1.15</v>
+        <v>0.55</v>
       </c>
       <c r="H72" t="inlineStr">
         <is>
@@ -3397,7 +3397,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -3406,7 +3406,7 @@
         </is>
       </c>
       <c r="G73" t="n">
-        <v>0.97</v>
+        <v>1.13</v>
       </c>
       <c r="H73" t="inlineStr">
         <is>
@@ -3438,7 +3438,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3447,7 +3447,7 @@
         </is>
       </c>
       <c r="G74" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="H74" t="inlineStr">
         <is>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3488,7 +3488,7 @@
         </is>
       </c>
       <c r="G75" t="n">
-        <v>0.68</v>
+        <v>0.55</v>
       </c>
       <c r="H75" t="inlineStr">
         <is>
@@ -3529,7 +3529,7 @@
         </is>
       </c>
       <c r="G76" t="n">
-        <v>1.06</v>
+        <v>0.89</v>
       </c>
       <c r="H76" t="inlineStr">
         <is>
@@ -3561,7 +3561,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3570,7 +3570,7 @@
         </is>
       </c>
       <c r="G77" t="n">
-        <v>0.87</v>
+        <v>0.86</v>
       </c>
       <c r="H77" t="inlineStr">
         <is>
@@ -3602,7 +3602,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3611,7 +3611,7 @@
         </is>
       </c>
       <c r="G78" t="n">
-        <v>0.64</v>
+        <v>0.78</v>
       </c>
       <c r="H78" t="inlineStr">
         <is>
@@ -3643,7 +3643,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3652,7 +3652,7 @@
         </is>
       </c>
       <c r="G79" t="n">
-        <v>0.92</v>
+        <v>0.59</v>
       </c>
       <c r="H79" t="inlineStr">
         <is>
@@ -3684,7 +3684,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3693,7 +3693,7 @@
         </is>
       </c>
       <c r="G80" t="n">
-        <v>1.01</v>
+        <v>0.46</v>
       </c>
       <c r="H80" t="inlineStr">
         <is>
@@ -3734,7 +3734,7 @@
         </is>
       </c>
       <c r="G81" t="n">
-        <v>0.97</v>
+        <v>0.53</v>
       </c>
       <c r="H81" t="inlineStr">
         <is>
@@ -3775,7 +3775,7 @@
         </is>
       </c>
       <c r="G82" t="n">
-        <v>0.47</v>
+        <v>1.15</v>
       </c>
       <c r="H82" t="inlineStr">
         <is>
@@ -3816,7 +3816,7 @@
         </is>
       </c>
       <c r="G83" t="n">
-        <v>0.93</v>
+        <v>0.6</v>
       </c>
       <c r="H83" t="inlineStr">
         <is>
@@ -3857,7 +3857,7 @@
         </is>
       </c>
       <c r="G84" t="n">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="H84" t="inlineStr">
         <is>
@@ -3889,7 +3889,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3898,7 +3898,7 @@
         </is>
       </c>
       <c r="G85" t="n">
-        <v>0.78</v>
+        <v>1.03</v>
       </c>
       <c r="H85" t="inlineStr">
         <is>
@@ -3939,7 +3939,7 @@
         </is>
       </c>
       <c r="G86" t="n">
-        <v>1.03</v>
+        <v>0.87</v>
       </c>
       <c r="H86" t="inlineStr">
         <is>
@@ -3971,7 +3971,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3980,7 +3980,7 @@
         </is>
       </c>
       <c r="G87" t="n">
-        <v>0.73</v>
+        <v>1.12</v>
       </c>
       <c r="H87" t="inlineStr">
         <is>
@@ -4012,7 +4012,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -4021,7 +4021,7 @@
         </is>
       </c>
       <c r="G88" t="n">
-        <v>0.76</v>
+        <v>0.91</v>
       </c>
       <c r="H88" t="inlineStr">
         <is>
@@ -4062,7 +4062,7 @@
         </is>
       </c>
       <c r="G89" t="n">
-        <v>0.63</v>
+        <v>0.82</v>
       </c>
       <c r="H89" t="inlineStr">
         <is>
@@ -4094,7 +4094,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -4103,7 +4103,7 @@
         </is>
       </c>
       <c r="G90" t="n">
-        <v>0.48</v>
+        <v>0.52</v>
       </c>
       <c r="H90" t="inlineStr">
         <is>
@@ -4135,7 +4135,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -4144,7 +4144,7 @@
         </is>
       </c>
       <c r="G91" t="n">
-        <v>0.84</v>
+        <v>0.52</v>
       </c>
       <c r="H91" t="inlineStr">
         <is>
@@ -4176,7 +4176,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -4185,7 +4185,7 @@
         </is>
       </c>
       <c r="G92" t="n">
-        <v>0.7</v>
+        <v>1.03</v>
       </c>
       <c r="H92" t="inlineStr">
         <is>
@@ -4217,7 +4217,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -4258,7 +4258,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -4267,7 +4267,7 @@
         </is>
       </c>
       <c r="G94" t="n">
-        <v>0.44</v>
+        <v>1.03</v>
       </c>
       <c r="H94" t="inlineStr">
         <is>
@@ -4299,7 +4299,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -4308,7 +4308,7 @@
         </is>
       </c>
       <c r="G95" t="n">
-        <v>1.13</v>
+        <v>1.05</v>
       </c>
       <c r="H95" t="inlineStr">
         <is>
@@ -4340,7 +4340,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -4349,7 +4349,7 @@
         </is>
       </c>
       <c r="G96" t="n">
-        <v>0.89</v>
+        <v>0.44</v>
       </c>
       <c r="H96" t="inlineStr">
         <is>
@@ -4381,7 +4381,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -4390,7 +4390,7 @@
         </is>
       </c>
       <c r="G97" t="n">
-        <v>1.01</v>
+        <v>0.57</v>
       </c>
       <c r="H97" t="inlineStr">
         <is>
@@ -4422,7 +4422,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -4431,7 +4431,7 @@
         </is>
       </c>
       <c r="G98" t="n">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H98" t="inlineStr">
         <is>
@@ -4463,7 +4463,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -4472,7 +4472,7 @@
         </is>
       </c>
       <c r="G99" t="n">
-        <v>0.91</v>
+        <v>0.97</v>
       </c>
       <c r="H99" t="inlineStr">
         <is>
@@ -4504,7 +4504,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -4513,7 +4513,7 @@
         </is>
       </c>
       <c r="G100" t="n">
-        <v>0.83</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H100" t="inlineStr">
         <is>
@@ -4554,7 +4554,7 @@
         </is>
       </c>
       <c r="G101" t="n">
-        <v>1.03</v>
+        <v>0.92</v>
       </c>
       <c r="H101" t="inlineStr">
         <is>
@@ -4586,7 +4586,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -4595,7 +4595,7 @@
         </is>
       </c>
       <c r="G102" t="n">
-        <v>0.54</v>
+        <v>0.77</v>
       </c>
       <c r="H102" t="inlineStr">
         <is>
@@ -4627,7 +4627,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4636,7 +4636,7 @@
         </is>
       </c>
       <c r="G103" t="n">
-        <v>0.99</v>
+        <v>0.97</v>
       </c>
       <c r="H103" t="inlineStr">
         <is>
@@ -4668,7 +4668,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4677,7 +4677,7 @@
         </is>
       </c>
       <c r="G104" t="n">
-        <v>0.6</v>
+        <v>0.45</v>
       </c>
       <c r="H104" t="inlineStr">
         <is>
@@ -4709,7 +4709,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4718,7 +4718,7 @@
         </is>
       </c>
       <c r="G105" t="n">
-        <v>0.79</v>
+        <v>1.06</v>
       </c>
       <c r="H105" t="inlineStr">
         <is>
@@ -4750,7 +4750,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4759,7 +4759,7 @@
         </is>
       </c>
       <c r="G106" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="H106" t="inlineStr">
         <is>
@@ -4800,7 +4800,7 @@
         </is>
       </c>
       <c r="G107" t="n">
-        <v>1.14</v>
+        <v>0.52</v>
       </c>
       <c r="H107" t="inlineStr">
         <is>
@@ -4832,7 +4832,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4841,7 +4841,7 @@
         </is>
       </c>
       <c r="G108" t="n">
-        <v>0.66</v>
+        <v>1.05</v>
       </c>
       <c r="H108" t="inlineStr">
         <is>
@@ -4882,7 +4882,7 @@
         </is>
       </c>
       <c r="G109" t="n">
-        <v>0.88</v>
+        <v>0.65</v>
       </c>
       <c r="H109" t="inlineStr">
         <is>
@@ -4914,7 +4914,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4923,7 +4923,7 @@
         </is>
       </c>
       <c r="G110" t="n">
-        <v>0.51</v>
+        <v>0.61</v>
       </c>
       <c r="H110" t="inlineStr">
         <is>
@@ -4955,7 +4955,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4964,7 +4964,7 @@
         </is>
       </c>
       <c r="G111" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="H111" t="inlineStr">
         <is>
@@ -4996,7 +4996,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -5005,7 +5005,7 @@
         </is>
       </c>
       <c r="G112" t="n">
-        <v>0.44</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H112" t="inlineStr">
         <is>
@@ -5046,7 +5046,7 @@
         </is>
       </c>
       <c r="G113" t="n">
-        <v>0.76</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H113" t="inlineStr">
         <is>
@@ -5078,7 +5078,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -5087,7 +5087,7 @@
         </is>
       </c>
       <c r="G114" t="n">
-        <v>1.1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H114" t="inlineStr">
         <is>
@@ -5119,7 +5119,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -5128,7 +5128,7 @@
         </is>
       </c>
       <c r="G115" t="n">
-        <v>0.93</v>
+        <v>0.83</v>
       </c>
       <c r="H115" t="inlineStr">
         <is>
@@ -5160,7 +5160,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -5169,7 +5169,7 @@
         </is>
       </c>
       <c r="G116" t="n">
-        <v>0.7</v>
+        <v>1.08</v>
       </c>
       <c r="H116" t="inlineStr">
         <is>
@@ -5201,7 +5201,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -5210,7 +5210,7 @@
         </is>
       </c>
       <c r="G117" t="n">
-        <v>0.8</v>
+        <v>0.76</v>
       </c>
       <c r="H117" t="inlineStr">
         <is>
@@ -5242,7 +5242,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -5251,7 +5251,7 @@
         </is>
       </c>
       <c r="G118" t="n">
-        <v>0.51</v>
+        <v>0.74</v>
       </c>
       <c r="H118" t="inlineStr">
         <is>
@@ -5292,7 +5292,7 @@
         </is>
       </c>
       <c r="G119" t="n">
-        <v>0.98</v>
+        <v>0.84</v>
       </c>
       <c r="H119" t="inlineStr">
         <is>
@@ -5333,7 +5333,7 @@
         </is>
       </c>
       <c r="G120" t="n">
-        <v>1.02</v>
+        <v>0.85</v>
       </c>
       <c r="H120" t="inlineStr">
         <is>
@@ -5374,7 +5374,7 @@
         </is>
       </c>
       <c r="G121" t="n">
-        <v>1.01</v>
+        <v>0.46</v>
       </c>
       <c r="H121" t="inlineStr">
         <is>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -5415,7 +5415,7 @@
         </is>
       </c>
       <c r="G122" t="n">
-        <v>0.48</v>
+        <v>0.45</v>
       </c>
       <c r="H122" t="inlineStr">
         <is>
@@ -5447,7 +5447,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -5456,7 +5456,7 @@
         </is>
       </c>
       <c r="G123" t="n">
-        <v>1.09</v>
+        <v>0.92</v>
       </c>
       <c r="H123" t="inlineStr">
         <is>
@@ -5488,7 +5488,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -5497,7 +5497,7 @@
         </is>
       </c>
       <c r="G124" t="n">
-        <v>1.08</v>
+        <v>0.98</v>
       </c>
       <c r="H124" t="inlineStr">
         <is>
@@ -5529,7 +5529,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -5538,7 +5538,7 @@
         </is>
       </c>
       <c r="G125" t="n">
-        <v>0.77</v>
+        <v>0.67</v>
       </c>
       <c r="H125" t="inlineStr">
         <is>
@@ -5570,7 +5570,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -5579,7 +5579,7 @@
         </is>
       </c>
       <c r="G126" t="n">
-        <v>0.67</v>
+        <v>0.91</v>
       </c>
       <c r="H126" t="inlineStr">
         <is>
@@ -5611,7 +5611,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -5620,7 +5620,7 @@
         </is>
       </c>
       <c r="G127" t="n">
-        <v>0.73</v>
+        <v>1.04</v>
       </c>
       <c r="H127" t="inlineStr">
         <is>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -5661,7 +5661,7 @@
         </is>
       </c>
       <c r="G128" t="n">
-        <v>0.9</v>
+        <v>1.03</v>
       </c>
       <c r="H128" t="inlineStr">
         <is>
@@ -5693,7 +5693,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -5743,7 +5743,7 @@
         </is>
       </c>
       <c r="G130" t="n">
-        <v>0.51</v>
+        <v>0.98</v>
       </c>
       <c r="H130" t="inlineStr">
         <is>
@@ -5784,7 +5784,7 @@
         </is>
       </c>
       <c r="G131" t="n">
-        <v>0.76</v>
+        <v>1.02</v>
       </c>
       <c r="H131" t="inlineStr">
         <is>
@@ -5825,7 +5825,7 @@
         </is>
       </c>
       <c r="G132" t="n">
-        <v>0.66</v>
+        <v>0.98</v>
       </c>
       <c r="H132" t="inlineStr">
         <is>
@@ -5857,7 +5857,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -5866,7 +5866,7 @@
         </is>
       </c>
       <c r="G133" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="H133" t="inlineStr">
         <is>
@@ -5898,7 +5898,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -5907,7 +5907,7 @@
         </is>
       </c>
       <c r="G134" t="n">
-        <v>0.75</v>
+        <v>0.95</v>
       </c>
       <c r="H134" t="inlineStr">
         <is>
@@ -5939,7 +5939,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -5948,7 +5948,7 @@
         </is>
       </c>
       <c r="G135" t="n">
-        <v>0.77</v>
+        <v>0.62</v>
       </c>
       <c r="H135" t="inlineStr">
         <is>
@@ -5980,7 +5980,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -5989,7 +5989,7 @@
         </is>
       </c>
       <c r="G136" t="n">
-        <v>0.7</v>
+        <v>0.86</v>
       </c>
       <c r="H136" t="inlineStr">
         <is>
@@ -6030,7 +6030,7 @@
         </is>
       </c>
       <c r="G137" t="n">
-        <v>0.73</v>
+        <v>1.13</v>
       </c>
       <c r="H137" t="inlineStr">
         <is>
@@ -6071,7 +6071,7 @@
         </is>
       </c>
       <c r="G138" t="n">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="H138" t="inlineStr">
         <is>
@@ -6112,7 +6112,7 @@
         </is>
       </c>
       <c r="G139" t="n">
-        <v>0.42</v>
+        <v>0.74</v>
       </c>
       <c r="H139" t="inlineStr">
         <is>
@@ -6144,7 +6144,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -6153,7 +6153,7 @@
         </is>
       </c>
       <c r="G140" t="n">
-        <v>0.52</v>
+        <v>0.66</v>
       </c>
       <c r="H140" t="inlineStr">
         <is>
@@ -6185,7 +6185,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -6194,7 +6194,7 @@
         </is>
       </c>
       <c r="G141" t="n">
-        <v>0.92</v>
+        <v>0.87</v>
       </c>
       <c r="H141" t="inlineStr">
         <is>
@@ -6226,7 +6226,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -6235,7 +6235,7 @@
         </is>
       </c>
       <c r="G142" t="n">
-        <v>0.48</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H142" t="inlineStr">
         <is>
@@ -6267,7 +6267,7 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -6276,7 +6276,7 @@
         </is>
       </c>
       <c r="G143" t="n">
-        <v>0.92</v>
+        <v>0.84</v>
       </c>
       <c r="H143" t="inlineStr">
         <is>
@@ -6308,7 +6308,7 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -6317,7 +6317,7 @@
         </is>
       </c>
       <c r="G144" t="n">
-        <v>0.88</v>
+        <v>0.84</v>
       </c>
       <c r="H144" t="inlineStr">
         <is>
@@ -6349,7 +6349,7 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
@@ -6358,7 +6358,7 @@
         </is>
       </c>
       <c r="G145" t="n">
-        <v>0.93</v>
+        <v>0.92</v>
       </c>
       <c r="H145" t="inlineStr">
         <is>
@@ -6399,7 +6399,7 @@
         </is>
       </c>
       <c r="G146" t="n">
-        <v>0.59</v>
+        <v>0.92</v>
       </c>
       <c r="H146" t="inlineStr">
         <is>
@@ -6431,7 +6431,7 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
@@ -6440,7 +6440,7 @@
         </is>
       </c>
       <c r="G147" t="n">
-        <v>0.55</v>
+        <v>0.96</v>
       </c>
       <c r="H147" t="inlineStr">
         <is>
@@ -6472,7 +6472,7 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
@@ -6481,7 +6481,7 @@
         </is>
       </c>
       <c r="G148" t="n">
-        <v>1.04</v>
+        <v>0.75</v>
       </c>
       <c r="H148" t="inlineStr">
         <is>
@@ -6513,7 +6513,7 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
@@ -6522,7 +6522,7 @@
         </is>
       </c>
       <c r="G149" t="n">
-        <v>0.7</v>
+        <v>1.11</v>
       </c>
       <c r="H149" t="inlineStr">
         <is>
@@ -6563,7 +6563,7 @@
         </is>
       </c>
       <c r="G150" t="n">
-        <v>0.97</v>
+        <v>0.58</v>
       </c>
       <c r="H150" t="inlineStr">
         <is>
@@ -6595,7 +6595,7 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
@@ -6604,7 +6604,7 @@
         </is>
       </c>
       <c r="G151" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="H151" t="inlineStr">
         <is>
@@ -6636,7 +6636,7 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
@@ -6645,7 +6645,7 @@
         </is>
       </c>
       <c r="G152" t="n">
-        <v>0.84</v>
+        <v>0.78</v>
       </c>
       <c r="H152" t="inlineStr">
         <is>
@@ -6677,7 +6677,7 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
@@ -6686,7 +6686,7 @@
         </is>
       </c>
       <c r="G153" t="n">
-        <v>1.14</v>
+        <v>0.64</v>
       </c>
       <c r="H153" t="inlineStr">
         <is>
@@ -6718,7 +6718,7 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
@@ -6727,7 +6727,7 @@
         </is>
       </c>
       <c r="G154" t="n">
-        <v>0.97</v>
+        <v>0.66</v>
       </c>
       <c r="H154" t="inlineStr">
         <is>
@@ -6759,7 +6759,7 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
@@ -6768,7 +6768,7 @@
         </is>
       </c>
       <c r="G155" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.65</v>
       </c>
       <c r="H155" t="inlineStr">
         <is>
@@ -6800,7 +6800,7 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
@@ -6809,7 +6809,7 @@
         </is>
       </c>
       <c r="G156" t="n">
-        <v>1.01</v>
+        <v>0.86</v>
       </c>
       <c r="H156" t="inlineStr">
         <is>
@@ -6841,7 +6841,7 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
@@ -6850,7 +6850,7 @@
         </is>
       </c>
       <c r="G157" t="n">
-        <v>0.89</v>
+        <v>0.57</v>
       </c>
       <c r="H157" t="inlineStr">
         <is>
@@ -6882,7 +6882,7 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
@@ -6891,7 +6891,7 @@
         </is>
       </c>
       <c r="G158" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="H158" t="inlineStr">
         <is>
@@ -6932,7 +6932,7 @@
         </is>
       </c>
       <c r="G159" t="n">
-        <v>0.49</v>
+        <v>0.58</v>
       </c>
       <c r="H159" t="inlineStr">
         <is>
@@ -6964,7 +6964,7 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
@@ -6973,7 +6973,7 @@
         </is>
       </c>
       <c r="G160" t="n">
-        <v>1.13</v>
+        <v>0.47</v>
       </c>
       <c r="H160" t="inlineStr">
         <is>
@@ -7005,7 +7005,7 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
@@ -7014,7 +7014,7 @@
         </is>
       </c>
       <c r="G161" t="n">
-        <v>0.97</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H161" t="inlineStr">
         <is>
@@ -7055,7 +7055,7 @@
         </is>
       </c>
       <c r="G162" t="n">
-        <v>0.57</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H162" t="inlineStr">
         <is>
@@ -7087,7 +7087,7 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
@@ -7096,7 +7096,7 @@
         </is>
       </c>
       <c r="G163" t="n">
-        <v>0.51</v>
+        <v>1.11</v>
       </c>
       <c r="H163" t="inlineStr">
         <is>
@@ -7137,7 +7137,7 @@
         </is>
       </c>
       <c r="G164" t="n">
-        <v>1.08</v>
+        <v>0.67</v>
       </c>
       <c r="H164" t="inlineStr">
         <is>
@@ -7169,7 +7169,7 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
@@ -7178,7 +7178,7 @@
         </is>
       </c>
       <c r="G165" t="n">
-        <v>0.98</v>
+        <v>0.82</v>
       </c>
       <c r="H165" t="inlineStr">
         <is>
@@ -7219,7 +7219,7 @@
         </is>
       </c>
       <c r="G166" t="n">
-        <v>0.57</v>
+        <v>0.65</v>
       </c>
       <c r="H166" t="inlineStr">
         <is>
@@ -7260,7 +7260,7 @@
         </is>
       </c>
       <c r="G167" t="n">
-        <v>0.77</v>
+        <v>0.65</v>
       </c>
       <c r="H167" t="inlineStr">
         <is>
@@ -7292,7 +7292,7 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
@@ -7301,7 +7301,7 @@
         </is>
       </c>
       <c r="G168" t="n">
-        <v>0.95</v>
+        <v>0.61</v>
       </c>
       <c r="H168" t="inlineStr">
         <is>
@@ -7333,7 +7333,7 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
@@ -7342,7 +7342,7 @@
         </is>
       </c>
       <c r="G169" t="n">
-        <v>0.48</v>
+        <v>0.77</v>
       </c>
       <c r="H169" t="inlineStr">
         <is>
@@ -7383,7 +7383,7 @@
         </is>
       </c>
       <c r="G170" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.95</v>
       </c>
       <c r="H170" t="inlineStr">
         <is>
@@ -7415,7 +7415,7 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
@@ -7424,7 +7424,7 @@
         </is>
       </c>
       <c r="G171" t="n">
-        <v>1.13</v>
+        <v>0.62</v>
       </c>
       <c r="H171" t="inlineStr">
         <is>
@@ -7456,7 +7456,7 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
@@ -7465,7 +7465,7 @@
         </is>
       </c>
       <c r="G172" t="n">
-        <v>0.57</v>
+        <v>0.83</v>
       </c>
       <c r="H172" t="inlineStr">
         <is>
@@ -7497,7 +7497,7 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
@@ -7506,7 +7506,7 @@
         </is>
       </c>
       <c r="G173" t="n">
-        <v>0.99</v>
+        <v>1.03</v>
       </c>
       <c r="H173" t="inlineStr">
         <is>
@@ -7538,7 +7538,7 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
@@ -7547,7 +7547,7 @@
         </is>
       </c>
       <c r="G174" t="n">
-        <v>0.42</v>
+        <v>1.08</v>
       </c>
       <c r="H174" t="inlineStr">
         <is>
@@ -7579,7 +7579,7 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
@@ -7588,7 +7588,7 @@
         </is>
       </c>
       <c r="G175" t="n">
-        <v>0.61</v>
+        <v>0.45</v>
       </c>
       <c r="H175" t="inlineStr">
         <is>
@@ -7620,7 +7620,7 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
@@ -7629,7 +7629,7 @@
         </is>
       </c>
       <c r="G176" t="n">
-        <v>0.72</v>
+        <v>0.96</v>
       </c>
       <c r="H176" t="inlineStr">
         <is>
@@ -7670,7 +7670,7 @@
         </is>
       </c>
       <c r="G177" t="n">
-        <v>0.48</v>
+        <v>0.47</v>
       </c>
       <c r="H177" t="inlineStr">
         <is>
@@ -7711,7 +7711,7 @@
         </is>
       </c>
       <c r="G178" t="n">
-        <v>0.98</v>
+        <v>1.05</v>
       </c>
       <c r="H178" t="inlineStr">
         <is>
@@ -7752,7 +7752,7 @@
         </is>
       </c>
       <c r="G179" t="n">
-        <v>0.49</v>
+        <v>0.67</v>
       </c>
       <c r="H179" t="inlineStr">
         <is>
@@ -7784,7 +7784,7 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
@@ -7793,7 +7793,7 @@
         </is>
       </c>
       <c r="G180" t="n">
-        <v>0.5</v>
+        <v>0.72</v>
       </c>
       <c r="H180" t="inlineStr">
         <is>
@@ -7825,7 +7825,7 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
@@ -7834,7 +7834,7 @@
         </is>
       </c>
       <c r="G181" t="n">
-        <v>0.64</v>
+        <v>0.73</v>
       </c>
       <c r="H181" t="inlineStr">
         <is>
@@ -7866,7 +7866,7 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
@@ -7875,7 +7875,7 @@
         </is>
       </c>
       <c r="G182" t="n">
-        <v>0.96</v>
+        <v>0.82</v>
       </c>
       <c r="H182" t="inlineStr">
         <is>
@@ -7907,7 +7907,7 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
@@ -7916,7 +7916,7 @@
         </is>
       </c>
       <c r="G183" t="n">
-        <v>0.43</v>
+        <v>1.05</v>
       </c>
       <c r="H183" t="inlineStr">
         <is>
@@ -7957,7 +7957,7 @@
         </is>
       </c>
       <c r="G184" t="n">
-        <v>0.57</v>
+        <v>0.91</v>
       </c>
       <c r="H184" t="inlineStr">
         <is>
@@ -7989,7 +7989,7 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
@@ -7998,7 +7998,7 @@
         </is>
       </c>
       <c r="G185" t="n">
-        <v>0.88</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H185" t="inlineStr">
         <is>
@@ -8030,7 +8030,7 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
@@ -8039,7 +8039,7 @@
         </is>
       </c>
       <c r="G186" t="n">
-        <v>0.89</v>
+        <v>0.85</v>
       </c>
       <c r="H186" t="inlineStr">
         <is>
@@ -8071,7 +8071,7 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
@@ -8080,7 +8080,7 @@
         </is>
       </c>
       <c r="G187" t="n">
-        <v>0.46</v>
+        <v>0.68</v>
       </c>
       <c r="H187" t="inlineStr">
         <is>
@@ -8121,7 +8121,7 @@
         </is>
       </c>
       <c r="G188" t="n">
-        <v>0.82</v>
+        <v>0.89</v>
       </c>
       <c r="H188" t="inlineStr">
         <is>
@@ -8162,7 +8162,7 @@
         </is>
       </c>
       <c r="G189" t="n">
-        <v>1.07</v>
+        <v>0.54</v>
       </c>
       <c r="H189" t="inlineStr">
         <is>
@@ -8194,7 +8194,7 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
@@ -8203,7 +8203,7 @@
         </is>
       </c>
       <c r="G190" t="n">
-        <v>0.71</v>
+        <v>0.82</v>
       </c>
       <c r="H190" t="inlineStr">
         <is>
@@ -8244,7 +8244,7 @@
         </is>
       </c>
       <c r="G191" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="H191" t="inlineStr">
         <is>
@@ -8285,7 +8285,7 @@
         </is>
       </c>
       <c r="G192" t="n">
-        <v>0.89</v>
+        <v>0.53</v>
       </c>
       <c r="H192" t="inlineStr">
         <is>
@@ -8326,7 +8326,7 @@
         </is>
       </c>
       <c r="G193" t="n">
-        <v>0.76</v>
+        <v>0.43</v>
       </c>
       <c r="H193" t="inlineStr">
         <is>
@@ -8358,7 +8358,7 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
@@ -8367,7 +8367,7 @@
         </is>
       </c>
       <c r="G194" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.5</v>
       </c>
       <c r="H194" t="inlineStr">
         <is>
@@ -8399,7 +8399,7 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
@@ -8408,7 +8408,7 @@
         </is>
       </c>
       <c r="G195" t="n">
-        <v>0.64</v>
+        <v>1.11</v>
       </c>
       <c r="H195" t="inlineStr">
         <is>
@@ -8449,7 +8449,7 @@
         </is>
       </c>
       <c r="G196" t="n">
-        <v>0.95</v>
+        <v>0.6</v>
       </c>
       <c r="H196" t="inlineStr">
         <is>
@@ -8481,7 +8481,7 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
@@ -8490,7 +8490,7 @@
         </is>
       </c>
       <c r="G197" t="n">
-        <v>0.8</v>
+        <v>0.59</v>
       </c>
       <c r="H197" t="inlineStr">
         <is>
@@ -8522,7 +8522,7 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
@@ -8531,7 +8531,7 @@
         </is>
       </c>
       <c r="G198" t="n">
-        <v>0.59</v>
+        <v>1.14</v>
       </c>
       <c r="H198" t="inlineStr">
         <is>
@@ -8572,7 +8572,7 @@
         </is>
       </c>
       <c r="G199" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.43</v>
       </c>
       <c r="H199" t="inlineStr">
         <is>
@@ -8604,7 +8604,7 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
@@ -8613,7 +8613,7 @@
         </is>
       </c>
       <c r="G200" t="n">
-        <v>0.64</v>
+        <v>0.84</v>
       </c>
       <c r="H200" t="inlineStr">
         <is>
@@ -8645,7 +8645,7 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
@@ -8654,7 +8654,7 @@
         </is>
       </c>
       <c r="G201" t="n">
-        <v>0.64</v>
+        <v>0.73</v>
       </c>
       <c r="H201" t="inlineStr">
         <is>
@@ -8686,7 +8686,7 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
@@ -8695,7 +8695,7 @@
         </is>
       </c>
       <c r="G202" t="n">
-        <v>1.01</v>
+        <v>0.76</v>
       </c>
       <c r="H202" t="inlineStr">
         <is>
@@ -8727,7 +8727,7 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
@@ -8736,7 +8736,7 @@
         </is>
       </c>
       <c r="G203" t="n">
-        <v>0.66</v>
+        <v>1.09</v>
       </c>
       <c r="H203" t="inlineStr">
         <is>
@@ -8768,7 +8768,7 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
@@ -8777,7 +8777,7 @@
         </is>
       </c>
       <c r="G204" t="n">
-        <v>1.05</v>
+        <v>0.72</v>
       </c>
       <c r="H204" t="inlineStr">
         <is>
@@ -8818,7 +8818,7 @@
         </is>
       </c>
       <c r="G205" t="n">
-        <v>1.06</v>
+        <v>0.65</v>
       </c>
       <c r="H205" t="inlineStr">
         <is>
@@ -8850,7 +8850,7 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
@@ -8859,7 +8859,7 @@
         </is>
       </c>
       <c r="G206" t="n">
-        <v>0.54</v>
+        <v>1.09</v>
       </c>
       <c r="H206" t="inlineStr">
         <is>
@@ -8900,7 +8900,7 @@
         </is>
       </c>
       <c r="G207" t="n">
-        <v>0.55</v>
+        <v>0.86</v>
       </c>
       <c r="H207" t="inlineStr">
         <is>
@@ -8941,7 +8941,7 @@
         </is>
       </c>
       <c r="G208" t="n">
-        <v>0.79</v>
+        <v>0.9</v>
       </c>
       <c r="H208" t="inlineStr">
         <is>
@@ -8973,7 +8973,7 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
@@ -8982,7 +8982,7 @@
         </is>
       </c>
       <c r="G209" t="n">
-        <v>0.51</v>
+        <v>0.65</v>
       </c>
       <c r="H209" t="inlineStr">
         <is>
@@ -9014,7 +9014,7 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
@@ -9023,7 +9023,7 @@
         </is>
       </c>
       <c r="G210" t="n">
-        <v>1.12</v>
+        <v>0.57</v>
       </c>
       <c r="H210" t="inlineStr">
         <is>
@@ -9055,7 +9055,7 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
@@ -9064,7 +9064,7 @@
         </is>
       </c>
       <c r="G211" t="n">
-        <v>0.82</v>
+        <v>0.5</v>
       </c>
       <c r="H211" t="inlineStr">
         <is>
@@ -9096,7 +9096,7 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
@@ -9105,7 +9105,7 @@
         </is>
       </c>
       <c r="G212" t="n">
-        <v>0.82</v>
+        <v>0.95</v>
       </c>
       <c r="H212" t="inlineStr">
         <is>
@@ -9137,7 +9137,7 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
@@ -9146,7 +9146,7 @@
         </is>
       </c>
       <c r="G213" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="H213" t="inlineStr">
         <is>
@@ -9178,7 +9178,7 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
@@ -9187,7 +9187,7 @@
         </is>
       </c>
       <c r="G214" t="n">
-        <v>0.48</v>
+        <v>1.06</v>
       </c>
       <c r="H214" t="inlineStr">
         <is>
@@ -9219,7 +9219,7 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
@@ -9228,7 +9228,7 @@
         </is>
       </c>
       <c r="G215" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="H215" t="inlineStr">
         <is>
@@ -9269,7 +9269,7 @@
         </is>
       </c>
       <c r="G216" t="n">
-        <v>0.54</v>
+        <v>1.08</v>
       </c>
       <c r="H216" t="inlineStr">
         <is>
@@ -9310,7 +9310,7 @@
         </is>
       </c>
       <c r="G217" t="n">
-        <v>0.92</v>
+        <v>0.58</v>
       </c>
       <c r="H217" t="inlineStr">
         <is>
@@ -9342,7 +9342,7 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
@@ -9351,7 +9351,7 @@
         </is>
       </c>
       <c r="G218" t="n">
-        <v>0.85</v>
+        <v>1.04</v>
       </c>
       <c r="H218" t="inlineStr">
         <is>
@@ -9392,7 +9392,7 @@
         </is>
       </c>
       <c r="G219" t="n">
-        <v>0.57</v>
+        <v>1.13</v>
       </c>
       <c r="H219" t="inlineStr">
         <is>
@@ -9424,7 +9424,7 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
@@ -9433,7 +9433,7 @@
         </is>
       </c>
       <c r="G220" t="n">
-        <v>0.87</v>
+        <v>0.49</v>
       </c>
       <c r="H220" t="inlineStr">
         <is>
@@ -9465,7 +9465,7 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
@@ -9474,7 +9474,7 @@
         </is>
       </c>
       <c r="G221" t="n">
-        <v>0.51</v>
+        <v>0.78</v>
       </c>
       <c r="H221" t="inlineStr">
         <is>
@@ -9506,7 +9506,7 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
@@ -9515,7 +9515,7 @@
         </is>
       </c>
       <c r="G222" t="n">
-        <v>0.49</v>
+        <v>1.08</v>
       </c>
       <c r="H222" t="inlineStr">
         <is>
@@ -9547,7 +9547,7 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
@@ -9556,7 +9556,7 @@
         </is>
       </c>
       <c r="G223" t="n">
-        <v>0.92</v>
+        <v>1.14</v>
       </c>
       <c r="H223" t="inlineStr">
         <is>
@@ -9588,7 +9588,7 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
@@ -9597,7 +9597,7 @@
         </is>
       </c>
       <c r="G224" t="n">
-        <v>0.59</v>
+        <v>0.79</v>
       </c>
       <c r="H224" t="inlineStr">
         <is>
@@ -9638,7 +9638,7 @@
         </is>
       </c>
       <c r="G225" t="n">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="H225" t="inlineStr">
         <is>
@@ -9670,7 +9670,7 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
@@ -9679,7 +9679,7 @@
         </is>
       </c>
       <c r="G226" t="n">
-        <v>0.64</v>
+        <v>0.83</v>
       </c>
       <c r="H226" t="inlineStr">
         <is>
@@ -9711,7 +9711,7 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
@@ -9720,7 +9720,7 @@
         </is>
       </c>
       <c r="G227" t="n">
-        <v>0.6</v>
+        <v>1.01</v>
       </c>
       <c r="H227" t="inlineStr">
         <is>
@@ -9761,7 +9761,7 @@
         </is>
       </c>
       <c r="G228" t="n">
-        <v>0.73</v>
+        <v>1.14</v>
       </c>
       <c r="H228" t="inlineStr">
         <is>
@@ -9793,7 +9793,7 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
@@ -9802,7 +9802,7 @@
         </is>
       </c>
       <c r="G229" t="n">
-        <v>1.02</v>
+        <v>0.79</v>
       </c>
       <c r="H229" t="inlineStr">
         <is>
@@ -9834,7 +9834,7 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
@@ -9843,7 +9843,7 @@
         </is>
       </c>
       <c r="G230" t="n">
-        <v>0.92</v>
+        <v>0.96</v>
       </c>
       <c r="H230" t="inlineStr">
         <is>
@@ -9875,7 +9875,7 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
@@ -9884,7 +9884,7 @@
         </is>
       </c>
       <c r="G231" t="n">
-        <v>0.84</v>
+        <v>0.96</v>
       </c>
       <c r="H231" t="inlineStr">
         <is>
@@ -9916,7 +9916,7 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
@@ -9957,7 +9957,7 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
@@ -9966,7 +9966,7 @@
         </is>
       </c>
       <c r="G233" t="n">
-        <v>0.48</v>
+        <v>1.06</v>
       </c>
       <c r="H233" t="inlineStr">
         <is>
@@ -9998,7 +9998,7 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
@@ -10007,7 +10007,7 @@
         </is>
       </c>
       <c r="G234" t="n">
-        <v>0.8100000000000001</v>
+        <v>1.14</v>
       </c>
       <c r="H234" t="inlineStr">
         <is>
@@ -10039,7 +10039,7 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
@@ -10048,7 +10048,7 @@
         </is>
       </c>
       <c r="G235" t="n">
-        <v>0.52</v>
+        <v>0.84</v>
       </c>
       <c r="H235" t="inlineStr">
         <is>
@@ -10089,7 +10089,7 @@
         </is>
       </c>
       <c r="G236" t="n">
-        <v>0.58</v>
+        <v>1.06</v>
       </c>
       <c r="H236" t="inlineStr">
         <is>
@@ -10121,7 +10121,7 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
@@ -10130,7 +10130,7 @@
         </is>
       </c>
       <c r="G237" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="H237" t="inlineStr">
         <is>
@@ -10162,7 +10162,7 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
@@ -10171,7 +10171,7 @@
         </is>
       </c>
       <c r="G238" t="n">
-        <v>0.99</v>
+        <v>0.59</v>
       </c>
       <c r="H238" t="inlineStr">
         <is>
@@ -10212,7 +10212,7 @@
         </is>
       </c>
       <c r="G239" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="H239" t="inlineStr">
         <is>
@@ -10253,7 +10253,7 @@
         </is>
       </c>
       <c r="G240" t="n">
-        <v>0.47</v>
+        <v>0.46</v>
       </c>
       <c r="H240" t="inlineStr">
         <is>
@@ -10285,7 +10285,7 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
@@ -10294,7 +10294,7 @@
         </is>
       </c>
       <c r="G241" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="H241" t="inlineStr">
         <is>
@@ -10326,7 +10326,7 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
@@ -10335,7 +10335,7 @@
         </is>
       </c>
       <c r="G242" t="n">
-        <v>0.53</v>
+        <v>1</v>
       </c>
       <c r="H242" t="inlineStr">
         <is>
@@ -10367,7 +10367,7 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
@@ -10376,7 +10376,7 @@
         </is>
       </c>
       <c r="G243" t="n">
-        <v>0.44</v>
+        <v>1.06</v>
       </c>
       <c r="H243" t="inlineStr">
         <is>
@@ -10408,7 +10408,7 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
@@ -10417,7 +10417,7 @@
         </is>
       </c>
       <c r="G244" t="n">
-        <v>1</v>
+        <v>0.62</v>
       </c>
       <c r="H244" t="inlineStr">
         <is>
@@ -10449,7 +10449,7 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
@@ -10458,7 +10458,7 @@
         </is>
       </c>
       <c r="G245" t="n">
-        <v>0.53</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H245" t="inlineStr">
         <is>
@@ -10499,7 +10499,7 @@
         </is>
       </c>
       <c r="G246" t="n">
-        <v>0.52</v>
+        <v>1.04</v>
       </c>
       <c r="H246" t="inlineStr">
         <is>
@@ -10540,7 +10540,7 @@
         </is>
       </c>
       <c r="G247" t="n">
-        <v>0.92</v>
+        <v>0.98</v>
       </c>
       <c r="H247" t="inlineStr">
         <is>
@@ -10572,7 +10572,7 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
@@ -10581,7 +10581,7 @@
         </is>
       </c>
       <c r="G248" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.49</v>
       </c>
       <c r="H248" t="inlineStr">
         <is>
@@ -10613,7 +10613,7 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
@@ -10622,7 +10622,7 @@
         </is>
       </c>
       <c r="G249" t="n">
-        <v>0.45</v>
+        <v>0.44</v>
       </c>
       <c r="H249" t="inlineStr">
         <is>
@@ -10663,7 +10663,7 @@
         </is>
       </c>
       <c r="G250" t="n">
-        <v>1.03</v>
+        <v>0.59</v>
       </c>
       <c r="H250" t="inlineStr">
         <is>
@@ -10695,7 +10695,7 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
@@ -10704,7 +10704,7 @@
         </is>
       </c>
       <c r="G251" t="n">
-        <v>0.52</v>
+        <v>1.11</v>
       </c>
       <c r="H251" t="inlineStr">
         <is>
@@ -10736,7 +10736,7 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
@@ -10745,7 +10745,7 @@
         </is>
       </c>
       <c r="G252" t="n">
-        <v>1.14</v>
+        <v>0.89</v>
       </c>
       <c r="H252" t="inlineStr">
         <is>
@@ -10786,7 +10786,7 @@
         </is>
       </c>
       <c r="G253" t="n">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="H253" t="inlineStr">
         <is>
@@ -10818,7 +10818,7 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
@@ -10827,7 +10827,7 @@
         </is>
       </c>
       <c r="G254" t="n">
-        <v>0.7</v>
+        <v>0.72</v>
       </c>
       <c r="H254" t="inlineStr">
         <is>
@@ -10859,7 +10859,7 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
@@ -10900,7 +10900,7 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
@@ -10909,7 +10909,7 @@
         </is>
       </c>
       <c r="G256" t="n">
-        <v>0.74</v>
+        <v>0.43</v>
       </c>
       <c r="H256" t="inlineStr">
         <is>
@@ -10941,7 +10941,7 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
@@ -10950,7 +10950,7 @@
         </is>
       </c>
       <c r="G257" t="n">
-        <v>0.53</v>
+        <v>1</v>
       </c>
       <c r="H257" t="inlineStr">
         <is>
@@ -10982,7 +10982,7 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
@@ -10991,7 +10991,7 @@
         </is>
       </c>
       <c r="G258" t="n">
-        <v>0.72</v>
+        <v>0.48</v>
       </c>
       <c r="H258" t="inlineStr">
         <is>
@@ -11023,7 +11023,7 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
@@ -11032,7 +11032,7 @@
         </is>
       </c>
       <c r="G259" t="n">
-        <v>0.48</v>
+        <v>0.8</v>
       </c>
       <c r="H259" t="inlineStr">
         <is>
@@ -11064,7 +11064,7 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
@@ -11073,7 +11073,7 @@
         </is>
       </c>
       <c r="G260" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.98</v>
       </c>
       <c r="H260" t="inlineStr">
         <is>
@@ -11105,7 +11105,7 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
@@ -11114,7 +11114,7 @@
         </is>
       </c>
       <c r="G261" t="n">
-        <v>0.58</v>
+        <v>1.08</v>
       </c>
       <c r="H261" t="inlineStr">
         <is>
@@ -11155,7 +11155,7 @@
         </is>
       </c>
       <c r="G262" t="n">
-        <v>0.85</v>
+        <v>0.82</v>
       </c>
       <c r="H262" t="inlineStr">
         <is>
@@ -11187,7 +11187,7 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
@@ -11196,7 +11196,7 @@
         </is>
       </c>
       <c r="G263" t="n">
-        <v>0.82</v>
+        <v>0.68</v>
       </c>
       <c r="H263" t="inlineStr">
         <is>
@@ -11237,7 +11237,7 @@
         </is>
       </c>
       <c r="G264" t="n">
-        <v>0.77</v>
+        <v>0.6</v>
       </c>
       <c r="H264" t="inlineStr">
         <is>
@@ -11278,7 +11278,7 @@
         </is>
       </c>
       <c r="G265" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H265" t="inlineStr">
         <is>
@@ -11310,7 +11310,7 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
@@ -11351,7 +11351,7 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
@@ -11360,7 +11360,7 @@
         </is>
       </c>
       <c r="G267" t="n">
-        <v>0.45</v>
+        <v>1.09</v>
       </c>
       <c r="H267" t="inlineStr">
         <is>
@@ -11392,7 +11392,7 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
@@ -11401,7 +11401,7 @@
         </is>
       </c>
       <c r="G268" t="n">
-        <v>0.96</v>
+        <v>1.07</v>
       </c>
       <c r="H268" t="inlineStr">
         <is>
@@ -11433,7 +11433,7 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
@@ -11442,7 +11442,7 @@
         </is>
       </c>
       <c r="G269" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.89</v>
       </c>
       <c r="H269" t="inlineStr">
         <is>
@@ -11474,7 +11474,7 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
@@ -11483,7 +11483,7 @@
         </is>
       </c>
       <c r="G270" t="n">
-        <v>1.08</v>
+        <v>0.52</v>
       </c>
       <c r="H270" t="inlineStr">
         <is>
@@ -11515,7 +11515,7 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
@@ -11524,7 +11524,7 @@
         </is>
       </c>
       <c r="G271" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H271" t="inlineStr">
         <is>
@@ -11556,7 +11556,7 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
@@ -11606,7 +11606,7 @@
         </is>
       </c>
       <c r="G273" t="n">
-        <v>0.78</v>
+        <v>0.67</v>
       </c>
       <c r="H273" t="inlineStr">
         <is>
@@ -11638,7 +11638,7 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
@@ -11647,7 +11647,7 @@
         </is>
       </c>
       <c r="G274" t="n">
-        <v>1.07</v>
+        <v>0.44</v>
       </c>
       <c r="H274" t="inlineStr">
         <is>
@@ -11679,7 +11679,7 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
@@ -11688,7 +11688,7 @@
         </is>
       </c>
       <c r="G275" t="n">
-        <v>0.42</v>
+        <v>0.46</v>
       </c>
       <c r="H275" t="inlineStr">
         <is>
@@ -11729,7 +11729,7 @@
         </is>
       </c>
       <c r="G276" t="n">
-        <v>0.7</v>
+        <v>1.04</v>
       </c>
       <c r="H276" t="inlineStr">
         <is>
@@ -11761,7 +11761,7 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
@@ -11770,7 +11770,7 @@
         </is>
       </c>
       <c r="G277" t="n">
-        <v>0.77</v>
+        <v>0.42</v>
       </c>
       <c r="H277" t="inlineStr">
         <is>
@@ -11802,7 +11802,7 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
@@ -11811,7 +11811,7 @@
         </is>
       </c>
       <c r="G278" t="n">
-        <v>0.98</v>
+        <v>0.8</v>
       </c>
       <c r="H278" t="inlineStr">
         <is>
@@ -11843,7 +11843,7 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
@@ -11852,7 +11852,7 @@
         </is>
       </c>
       <c r="G279" t="n">
-        <v>0.47</v>
+        <v>0.55</v>
       </c>
       <c r="H279" t="inlineStr">
         <is>
@@ -11884,7 +11884,7 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
@@ -11893,7 +11893,7 @@
         </is>
       </c>
       <c r="G280" t="n">
-        <v>1.03</v>
+        <v>0.68</v>
       </c>
       <c r="H280" t="inlineStr">
         <is>
@@ -11934,7 +11934,7 @@
         </is>
       </c>
       <c r="G281" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="H281" t="inlineStr">
         <is>
@@ -11966,7 +11966,7 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
@@ -11975,7 +11975,7 @@
         </is>
       </c>
       <c r="G282" t="n">
-        <v>1.02</v>
+        <v>0.9</v>
       </c>
       <c r="H282" t="inlineStr">
         <is>
@@ -12007,7 +12007,7 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
@@ -12016,7 +12016,7 @@
         </is>
       </c>
       <c r="G283" t="n">
-        <v>0.45</v>
+        <v>0.89</v>
       </c>
       <c r="H283" t="inlineStr">
         <is>
@@ -12048,7 +12048,7 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
@@ -12057,7 +12057,7 @@
         </is>
       </c>
       <c r="G284" t="n">
-        <v>0.92</v>
+        <v>0.54</v>
       </c>
       <c r="H284" t="inlineStr">
         <is>
@@ -12098,7 +12098,7 @@
         </is>
       </c>
       <c r="G285" t="n">
-        <v>0.98</v>
+        <v>1.11</v>
       </c>
       <c r="H285" t="inlineStr">
         <is>
@@ -12139,7 +12139,7 @@
         </is>
       </c>
       <c r="G286" t="n">
-        <v>0.79</v>
+        <v>0.66</v>
       </c>
       <c r="H286" t="inlineStr">
         <is>
@@ -12180,7 +12180,7 @@
         </is>
       </c>
       <c r="G287" t="n">
-        <v>0.79</v>
+        <v>0.92</v>
       </c>
       <c r="H287" t="inlineStr">
         <is>
@@ -12212,7 +12212,7 @@
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
@@ -12221,7 +12221,7 @@
         </is>
       </c>
       <c r="G288" t="n">
-        <v>0.82</v>
+        <v>1.05</v>
       </c>
       <c r="H288" t="inlineStr">
         <is>
@@ -12253,7 +12253,7 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
@@ -12262,7 +12262,7 @@
         </is>
       </c>
       <c r="G289" t="n">
-        <v>0.71</v>
+        <v>1.03</v>
       </c>
       <c r="H289" t="inlineStr">
         <is>
@@ -12294,7 +12294,7 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
@@ -12303,7 +12303,7 @@
         </is>
       </c>
       <c r="G290" t="n">
-        <v>0.9</v>
+        <v>0.52</v>
       </c>
       <c r="H290" t="inlineStr">
         <is>
@@ -12344,7 +12344,7 @@
         </is>
       </c>
       <c r="G291" t="n">
-        <v>0.84</v>
+        <v>0.86</v>
       </c>
       <c r="H291" t="inlineStr">
         <is>
@@ -12376,7 +12376,7 @@
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
@@ -12385,7 +12385,7 @@
         </is>
       </c>
       <c r="G292" t="n">
-        <v>0.62</v>
+        <v>1.09</v>
       </c>
       <c r="H292" t="inlineStr">
         <is>
@@ -12417,7 +12417,7 @@
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
@@ -12426,7 +12426,7 @@
         </is>
       </c>
       <c r="G293" t="n">
-        <v>0.52</v>
+        <v>0.84</v>
       </c>
       <c r="H293" t="inlineStr">
         <is>
@@ -12467,7 +12467,7 @@
         </is>
       </c>
       <c r="G294" t="n">
-        <v>0.47</v>
+        <v>1.05</v>
       </c>
       <c r="H294" t="inlineStr">
         <is>
@@ -12499,7 +12499,7 @@
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
@@ -12508,7 +12508,7 @@
         </is>
       </c>
       <c r="G295" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="H295" t="inlineStr">
         <is>
@@ -12540,7 +12540,7 @@
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
@@ -12549,7 +12549,7 @@
         </is>
       </c>
       <c r="G296" t="n">
-        <v>0.63</v>
+        <v>1.01</v>
       </c>
       <c r="H296" t="inlineStr">
         <is>
@@ -12590,7 +12590,7 @@
         </is>
       </c>
       <c r="G297" t="n">
-        <v>0.43</v>
+        <v>0.97</v>
       </c>
       <c r="H297" t="inlineStr">
         <is>
@@ -12622,7 +12622,7 @@
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
@@ -12631,7 +12631,7 @@
         </is>
       </c>
       <c r="G298" t="n">
-        <v>0.42</v>
+        <v>0.54</v>
       </c>
       <c r="H298" t="inlineStr">
         <is>
@@ -12663,7 +12663,7 @@
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F299" t="inlineStr">
@@ -12672,7 +12672,7 @@
         </is>
       </c>
       <c r="G299" t="n">
-        <v>0.66</v>
+        <v>0.79</v>
       </c>
       <c r="H299" t="inlineStr">
         <is>
@@ -12704,7 +12704,7 @@
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
@@ -12713,7 +12713,7 @@
         </is>
       </c>
       <c r="G300" t="n">
-        <v>0.9</v>
+        <v>0.89</v>
       </c>
       <c r="H300" t="inlineStr">
         <is>
@@ -12745,7 +12745,7 @@
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
@@ -12754,7 +12754,7 @@
         </is>
       </c>
       <c r="G301" t="n">
-        <v>0.46</v>
+        <v>0.79</v>
       </c>
       <c r="H301" t="inlineStr">
         <is>

--- a/reports/Passed_Test_Cases.xlsx
+++ b/reports/Passed_Test_Cases.xlsx
@@ -495,7 +495,7 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0.95</v>
+        <v>0.61</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -527,7 +527,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0.72</v>
+        <v>0.46</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -577,7 +577,7 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0.51</v>
+        <v>1.07</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -609,7 +609,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -618,7 +618,7 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>1.05</v>
+        <v>0.83</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>0.44</v>
+        <v>0.46</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -700,7 +700,7 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>0.99</v>
+        <v>1.13</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -732,7 +732,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -741,7 +741,7 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>1.06</v>
+        <v>0.6</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -773,7 +773,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -782,7 +782,7 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>0.5</v>
+        <v>0.64</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -814,7 +814,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -823,7 +823,7 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>0.96</v>
+        <v>0.84</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -864,7 +864,7 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>0.67</v>
+        <v>1.01</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -905,7 +905,7 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>0.57</v>
+        <v>0.89</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -946,7 +946,7 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>0.47</v>
+        <v>0.57</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -987,7 +987,7 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>1.02</v>
+        <v>0.58</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1028,7 +1028,7 @@
         </is>
       </c>
       <c r="G15" t="n">
-        <v>0.64</v>
+        <v>0.83</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -1069,7 +1069,7 @@
         </is>
       </c>
       <c r="G16" t="n">
-        <v>0.76</v>
+        <v>0.98</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -1101,7 +1101,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1110,7 +1110,7 @@
         </is>
       </c>
       <c r="G17" t="n">
-        <v>0.49</v>
+        <v>0.87</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -1142,7 +1142,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1151,7 +1151,7 @@
         </is>
       </c>
       <c r="G18" t="n">
-        <v>0.66</v>
+        <v>0.87</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -1192,7 +1192,7 @@
         </is>
       </c>
       <c r="G19" t="n">
-        <v>0.47</v>
+        <v>0.79</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1233,7 +1233,7 @@
         </is>
       </c>
       <c r="G20" t="n">
-        <v>0.7</v>
+        <v>1.11</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -1265,7 +1265,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1274,7 +1274,7 @@
         </is>
       </c>
       <c r="G21" t="n">
-        <v>1.13</v>
+        <v>0.55</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -1306,7 +1306,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1315,7 +1315,7 @@
         </is>
       </c>
       <c r="G22" t="n">
-        <v>0.91</v>
+        <v>0.87</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
@@ -1347,7 +1347,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1356,7 +1356,7 @@
         </is>
       </c>
       <c r="G23" t="n">
-        <v>0.62</v>
+        <v>0.54</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1397,7 +1397,7 @@
         </is>
       </c>
       <c r="G24" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
@@ -1429,7 +1429,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1438,7 +1438,7 @@
         </is>
       </c>
       <c r="G25" t="n">
-        <v>0.55</v>
+        <v>0.49</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
@@ -1470,7 +1470,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1479,7 +1479,7 @@
         </is>
       </c>
       <c r="G26" t="n">
-        <v>0.68</v>
+        <v>0.6</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
@@ -1520,7 +1520,7 @@
         </is>
       </c>
       <c r="G27" t="n">
-        <v>0.75</v>
+        <v>0.49</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
@@ -1552,7 +1552,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1561,7 +1561,7 @@
         </is>
       </c>
       <c r="G28" t="n">
-        <v>0.7</v>
+        <v>0.55</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
@@ -1593,7 +1593,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1602,7 +1602,7 @@
         </is>
       </c>
       <c r="G29" t="n">
-        <v>0.55</v>
+        <v>1.14</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
@@ -1643,7 +1643,7 @@
         </is>
       </c>
       <c r="G30" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.96</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
@@ -1684,7 +1684,7 @@
         </is>
       </c>
       <c r="G31" t="n">
-        <v>0.6</v>
+        <v>0.76</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
@@ -1716,7 +1716,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1725,7 +1725,7 @@
         </is>
       </c>
       <c r="G32" t="n">
-        <v>0.52</v>
+        <v>0.43</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
@@ -1766,7 +1766,7 @@
         </is>
       </c>
       <c r="G33" t="n">
-        <v>0.66</v>
+        <v>0.53</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
@@ -1807,7 +1807,7 @@
         </is>
       </c>
       <c r="G34" t="n">
-        <v>0.6</v>
+        <v>0.77</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
@@ -1839,7 +1839,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1848,7 +1848,7 @@
         </is>
       </c>
       <c r="G35" t="n">
-        <v>1.06</v>
+        <v>0.84</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
@@ -1880,7 +1880,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1889,7 +1889,7 @@
         </is>
       </c>
       <c r="G36" t="n">
-        <v>0.84</v>
+        <v>0.62</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1930,7 +1930,7 @@
         </is>
       </c>
       <c r="G37" t="n">
-        <v>0.45</v>
+        <v>0.93</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
@@ -1962,7 +1962,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1971,7 +1971,7 @@
         </is>
       </c>
       <c r="G38" t="n">
-        <v>1.15</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
@@ -2012,7 +2012,7 @@
         </is>
       </c>
       <c r="G39" t="n">
-        <v>0.89</v>
+        <v>0.59</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
@@ -2053,7 +2053,7 @@
         </is>
       </c>
       <c r="G40" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
@@ -2135,7 +2135,7 @@
         </is>
       </c>
       <c r="G42" t="n">
-        <v>0.45</v>
+        <v>0.43</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
@@ -2167,7 +2167,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -2176,7 +2176,7 @@
         </is>
       </c>
       <c r="G43" t="n">
-        <v>0.76</v>
+        <v>0.45</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
@@ -2208,7 +2208,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -2217,7 +2217,7 @@
         </is>
       </c>
       <c r="G44" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
@@ -2249,7 +2249,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2258,7 +2258,7 @@
         </is>
       </c>
       <c r="G45" t="n">
-        <v>0.95</v>
+        <v>0.53</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
@@ -2290,7 +2290,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2299,7 +2299,7 @@
         </is>
       </c>
       <c r="G46" t="n">
-        <v>0.86</v>
+        <v>1.04</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
@@ -2340,7 +2340,7 @@
         </is>
       </c>
       <c r="G47" t="n">
-        <v>0.46</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
@@ -2372,7 +2372,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2381,7 +2381,7 @@
         </is>
       </c>
       <c r="G48" t="n">
-        <v>0.75</v>
+        <v>1.1</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
@@ -2413,7 +2413,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2422,7 +2422,7 @@
         </is>
       </c>
       <c r="G49" t="n">
-        <v>1.13</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
@@ -2454,7 +2454,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2463,7 +2463,7 @@
         </is>
       </c>
       <c r="G50" t="n">
-        <v>0.47</v>
+        <v>0.93</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
@@ -2495,7 +2495,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2504,7 +2504,7 @@
         </is>
       </c>
       <c r="G51" t="n">
-        <v>1.02</v>
+        <v>0.74</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
@@ -2536,7 +2536,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2545,7 +2545,7 @@
         </is>
       </c>
       <c r="G52" t="n">
-        <v>1</v>
+        <v>0.48</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
@@ -2577,7 +2577,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2586,7 +2586,7 @@
         </is>
       </c>
       <c r="G53" t="n">
-        <v>0.54</v>
+        <v>0.53</v>
       </c>
       <c r="H53" t="inlineStr">
         <is>
@@ -2618,7 +2618,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2627,7 +2627,7 @@
         </is>
       </c>
       <c r="G54" t="n">
-        <v>0.52</v>
+        <v>0.59</v>
       </c>
       <c r="H54" t="inlineStr">
         <is>
@@ -2659,7 +2659,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2668,7 +2668,7 @@
         </is>
       </c>
       <c r="G55" t="n">
-        <v>0.44</v>
+        <v>0.52</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
@@ -2700,7 +2700,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2709,7 +2709,7 @@
         </is>
       </c>
       <c r="G56" t="n">
-        <v>0.71</v>
+        <v>0.65</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
@@ -2741,7 +2741,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2750,7 +2750,7 @@
         </is>
       </c>
       <c r="G57" t="n">
-        <v>0.55</v>
+        <v>0.99</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
@@ -2782,7 +2782,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2791,7 +2791,7 @@
         </is>
       </c>
       <c r="G58" t="n">
-        <v>0.98</v>
+        <v>0.45</v>
       </c>
       <c r="H58" t="inlineStr">
         <is>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2832,7 +2832,7 @@
         </is>
       </c>
       <c r="G59" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.77</v>
       </c>
       <c r="H59" t="inlineStr">
         <is>
@@ -2864,7 +2864,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2873,7 +2873,7 @@
         </is>
       </c>
       <c r="G60" t="n">
-        <v>1.13</v>
+        <v>0.45</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
@@ -2905,7 +2905,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2914,7 +2914,7 @@
         </is>
       </c>
       <c r="G61" t="n">
-        <v>0.99</v>
+        <v>0.43</v>
       </c>
       <c r="H61" t="inlineStr">
         <is>
@@ -2946,7 +2946,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2955,7 +2955,7 @@
         </is>
       </c>
       <c r="G62" t="n">
-        <v>0.64</v>
+        <v>0.75</v>
       </c>
       <c r="H62" t="inlineStr">
         <is>
@@ -2987,7 +2987,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2996,7 +2996,7 @@
         </is>
       </c>
       <c r="G63" t="n">
-        <v>0.47</v>
+        <v>1.1</v>
       </c>
       <c r="H63" t="inlineStr">
         <is>
@@ -3037,7 +3037,7 @@
         </is>
       </c>
       <c r="G64" t="n">
-        <v>1.09</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H64" t="inlineStr">
         <is>
@@ -3069,7 +3069,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -3110,7 +3110,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -3119,7 +3119,7 @@
         </is>
       </c>
       <c r="G66" t="n">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="H66" t="inlineStr">
         <is>
@@ -3160,7 +3160,7 @@
         </is>
       </c>
       <c r="G67" t="n">
-        <v>0.48</v>
+        <v>0.92</v>
       </c>
       <c r="H67" t="inlineStr">
         <is>
@@ -3192,7 +3192,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -3201,7 +3201,7 @@
         </is>
       </c>
       <c r="G68" t="n">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="H68" t="inlineStr">
         <is>
@@ -3242,7 +3242,7 @@
         </is>
       </c>
       <c r="G69" t="n">
-        <v>1.13</v>
+        <v>0.68</v>
       </c>
       <c r="H69" t="inlineStr">
         <is>
@@ -3274,7 +3274,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -3283,7 +3283,7 @@
         </is>
       </c>
       <c r="G70" t="n">
-        <v>0.65</v>
+        <v>0.67</v>
       </c>
       <c r="H70" t="inlineStr">
         <is>
@@ -3315,7 +3315,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -3324,7 +3324,7 @@
         </is>
       </c>
       <c r="G71" t="n">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="H71" t="inlineStr">
         <is>
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -3365,7 +3365,7 @@
         </is>
       </c>
       <c r="G72" t="n">
-        <v>0.55</v>
+        <v>0.44</v>
       </c>
       <c r="H72" t="inlineStr">
         <is>
@@ -3397,7 +3397,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -3406,7 +3406,7 @@
         </is>
       </c>
       <c r="G73" t="n">
-        <v>1.13</v>
+        <v>0.87</v>
       </c>
       <c r="H73" t="inlineStr">
         <is>
@@ -3438,7 +3438,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3447,7 +3447,7 @@
         </is>
       </c>
       <c r="G74" t="n">
-        <v>1.01</v>
+        <v>0.87</v>
       </c>
       <c r="H74" t="inlineStr">
         <is>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3488,7 +3488,7 @@
         </is>
       </c>
       <c r="G75" t="n">
-        <v>0.55</v>
+        <v>0.43</v>
       </c>
       <c r="H75" t="inlineStr">
         <is>
@@ -3520,7 +3520,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3529,7 +3529,7 @@
         </is>
       </c>
       <c r="G76" t="n">
-        <v>0.89</v>
+        <v>0.64</v>
       </c>
       <c r="H76" t="inlineStr">
         <is>
@@ -3570,7 +3570,7 @@
         </is>
       </c>
       <c r="G77" t="n">
-        <v>0.86</v>
+        <v>0.7</v>
       </c>
       <c r="H77" t="inlineStr">
         <is>
@@ -3602,7 +3602,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3611,7 +3611,7 @@
         </is>
       </c>
       <c r="G78" t="n">
-        <v>0.78</v>
+        <v>0.65</v>
       </c>
       <c r="H78" t="inlineStr">
         <is>
@@ -3643,7 +3643,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3652,7 +3652,7 @@
         </is>
       </c>
       <c r="G79" t="n">
-        <v>0.59</v>
+        <v>1.02</v>
       </c>
       <c r="H79" t="inlineStr">
         <is>
@@ -3684,7 +3684,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3693,7 +3693,7 @@
         </is>
       </c>
       <c r="G80" t="n">
-        <v>0.46</v>
+        <v>0.78</v>
       </c>
       <c r="H80" t="inlineStr">
         <is>
@@ -3725,7 +3725,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3734,7 +3734,7 @@
         </is>
       </c>
       <c r="G81" t="n">
-        <v>0.53</v>
+        <v>0.55</v>
       </c>
       <c r="H81" t="inlineStr">
         <is>
@@ -3816,7 +3816,7 @@
         </is>
       </c>
       <c r="G83" t="n">
-        <v>0.6</v>
+        <v>1.04</v>
       </c>
       <c r="H83" t="inlineStr">
         <is>
@@ -3848,7 +3848,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3857,7 +3857,7 @@
         </is>
       </c>
       <c r="G84" t="n">
-        <v>0.5</v>
+        <v>0.65</v>
       </c>
       <c r="H84" t="inlineStr">
         <is>
@@ -3889,7 +3889,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3898,7 +3898,7 @@
         </is>
       </c>
       <c r="G85" t="n">
-        <v>1.03</v>
+        <v>0.76</v>
       </c>
       <c r="H85" t="inlineStr">
         <is>
@@ -3939,7 +3939,7 @@
         </is>
       </c>
       <c r="G86" t="n">
-        <v>0.87</v>
+        <v>0.45</v>
       </c>
       <c r="H86" t="inlineStr">
         <is>
@@ -3971,7 +3971,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3980,7 +3980,7 @@
         </is>
       </c>
       <c r="G87" t="n">
-        <v>1.12</v>
+        <v>1.01</v>
       </c>
       <c r="H87" t="inlineStr">
         <is>
@@ -4012,7 +4012,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -4021,7 +4021,7 @@
         </is>
       </c>
       <c r="G88" t="n">
-        <v>0.91</v>
+        <v>0.96</v>
       </c>
       <c r="H88" t="inlineStr">
         <is>
@@ -4053,7 +4053,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -4062,7 +4062,7 @@
         </is>
       </c>
       <c r="G89" t="n">
-        <v>0.82</v>
+        <v>0.46</v>
       </c>
       <c r="H89" t="inlineStr">
         <is>
@@ -4094,7 +4094,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -4103,7 +4103,7 @@
         </is>
       </c>
       <c r="G90" t="n">
-        <v>0.52</v>
+        <v>0.51</v>
       </c>
       <c r="H90" t="inlineStr">
         <is>
@@ -4144,7 +4144,7 @@
         </is>
       </c>
       <c r="G91" t="n">
-        <v>0.52</v>
+        <v>0.43</v>
       </c>
       <c r="H91" t="inlineStr">
         <is>
@@ -4176,7 +4176,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -4185,7 +4185,7 @@
         </is>
       </c>
       <c r="G92" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="H92" t="inlineStr">
         <is>
@@ -4217,7 +4217,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -4226,7 +4226,7 @@
         </is>
       </c>
       <c r="G93" t="n">
-        <v>1</v>
+        <v>0.55</v>
       </c>
       <c r="H93" t="inlineStr">
         <is>
@@ -4258,7 +4258,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -4267,7 +4267,7 @@
         </is>
       </c>
       <c r="G94" t="n">
-        <v>1.03</v>
+        <v>0.84</v>
       </c>
       <c r="H94" t="inlineStr">
         <is>
@@ -4299,7 +4299,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -4308,7 +4308,7 @@
         </is>
       </c>
       <c r="G95" t="n">
-        <v>1.05</v>
+        <v>0.44</v>
       </c>
       <c r="H95" t="inlineStr">
         <is>
@@ -4340,7 +4340,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -4349,7 +4349,7 @@
         </is>
       </c>
       <c r="G96" t="n">
-        <v>0.44</v>
+        <v>0.64</v>
       </c>
       <c r="H96" t="inlineStr">
         <is>
@@ -4381,7 +4381,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -4390,7 +4390,7 @@
         </is>
       </c>
       <c r="G97" t="n">
-        <v>0.57</v>
+        <v>1.02</v>
       </c>
       <c r="H97" t="inlineStr">
         <is>
@@ -4422,7 +4422,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -4431,7 +4431,7 @@
         </is>
       </c>
       <c r="G98" t="n">
-        <v>0.6899999999999999</v>
+        <v>1.14</v>
       </c>
       <c r="H98" t="inlineStr">
         <is>
@@ -4463,7 +4463,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -4472,7 +4472,7 @@
         </is>
       </c>
       <c r="G99" t="n">
-        <v>0.97</v>
+        <v>0.68</v>
       </c>
       <c r="H99" t="inlineStr">
         <is>
@@ -4504,7 +4504,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -4513,7 +4513,7 @@
         </is>
       </c>
       <c r="G100" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H100" t="inlineStr">
         <is>
@@ -4545,7 +4545,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -4554,7 +4554,7 @@
         </is>
       </c>
       <c r="G101" t="n">
-        <v>0.92</v>
+        <v>0.52</v>
       </c>
       <c r="H101" t="inlineStr">
         <is>
@@ -4595,7 +4595,7 @@
         </is>
       </c>
       <c r="G102" t="n">
-        <v>0.77</v>
+        <v>0.82</v>
       </c>
       <c r="H102" t="inlineStr">
         <is>
@@ -4627,7 +4627,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4636,7 +4636,7 @@
         </is>
       </c>
       <c r="G103" t="n">
-        <v>0.97</v>
+        <v>0.82</v>
       </c>
       <c r="H103" t="inlineStr">
         <is>
@@ -4668,7 +4668,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4677,7 +4677,7 @@
         </is>
       </c>
       <c r="G104" t="n">
-        <v>0.45</v>
+        <v>0.47</v>
       </c>
       <c r="H104" t="inlineStr">
         <is>
@@ -4709,7 +4709,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4718,7 +4718,7 @@
         </is>
       </c>
       <c r="G105" t="n">
-        <v>1.06</v>
+        <v>0.53</v>
       </c>
       <c r="H105" t="inlineStr">
         <is>
@@ -4750,7 +4750,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4759,7 +4759,7 @@
         </is>
       </c>
       <c r="G106" t="n">
-        <v>1.03</v>
+        <v>0.76</v>
       </c>
       <c r="H106" t="inlineStr">
         <is>
@@ -4791,7 +4791,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4800,7 +4800,7 @@
         </is>
       </c>
       <c r="G107" t="n">
-        <v>0.52</v>
+        <v>0.57</v>
       </c>
       <c r="H107" t="inlineStr">
         <is>
@@ -4832,7 +4832,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4841,7 +4841,7 @@
         </is>
       </c>
       <c r="G108" t="n">
-        <v>1.05</v>
+        <v>0.72</v>
       </c>
       <c r="H108" t="inlineStr">
         <is>
@@ -4873,7 +4873,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4882,7 +4882,7 @@
         </is>
       </c>
       <c r="G109" t="n">
-        <v>0.65</v>
+        <v>0.71</v>
       </c>
       <c r="H109" t="inlineStr">
         <is>
@@ -4914,7 +4914,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4923,7 +4923,7 @@
         </is>
       </c>
       <c r="G110" t="n">
-        <v>0.61</v>
+        <v>1.12</v>
       </c>
       <c r="H110" t="inlineStr">
         <is>
@@ -4955,7 +4955,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4964,7 +4964,7 @@
         </is>
       </c>
       <c r="G111" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="H111" t="inlineStr">
         <is>
@@ -4996,7 +4996,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -5005,7 +5005,7 @@
         </is>
       </c>
       <c r="G112" t="n">
-        <v>0.5600000000000001</v>
+        <v>1.08</v>
       </c>
       <c r="H112" t="inlineStr">
         <is>
@@ -5037,7 +5037,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -5046,7 +5046,7 @@
         </is>
       </c>
       <c r="G113" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.43</v>
       </c>
       <c r="H113" t="inlineStr">
         <is>
@@ -5078,7 +5078,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -5087,7 +5087,7 @@
         </is>
       </c>
       <c r="G114" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="H114" t="inlineStr">
         <is>
@@ -5119,7 +5119,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -5128,7 +5128,7 @@
         </is>
       </c>
       <c r="G115" t="n">
-        <v>0.83</v>
+        <v>1.01</v>
       </c>
       <c r="H115" t="inlineStr">
         <is>
@@ -5160,7 +5160,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -5169,7 +5169,7 @@
         </is>
       </c>
       <c r="G116" t="n">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="H116" t="inlineStr">
         <is>
@@ -5201,7 +5201,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -5210,7 +5210,7 @@
         </is>
       </c>
       <c r="G117" t="n">
-        <v>0.76</v>
+        <v>0.51</v>
       </c>
       <c r="H117" t="inlineStr">
         <is>
@@ -5251,7 +5251,7 @@
         </is>
       </c>
       <c r="G118" t="n">
-        <v>0.74</v>
+        <v>1.08</v>
       </c>
       <c r="H118" t="inlineStr">
         <is>
@@ -5283,7 +5283,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -5292,7 +5292,7 @@
         </is>
       </c>
       <c r="G119" t="n">
-        <v>0.84</v>
+        <v>0.95</v>
       </c>
       <c r="H119" t="inlineStr">
         <is>
@@ -5324,7 +5324,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -5333,7 +5333,7 @@
         </is>
       </c>
       <c r="G120" t="n">
-        <v>0.85</v>
+        <v>1.03</v>
       </c>
       <c r="H120" t="inlineStr">
         <is>
@@ -5365,7 +5365,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -5374,7 +5374,7 @@
         </is>
       </c>
       <c r="G121" t="n">
-        <v>0.46</v>
+        <v>1.15</v>
       </c>
       <c r="H121" t="inlineStr">
         <is>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -5415,7 +5415,7 @@
         </is>
       </c>
       <c r="G122" t="n">
-        <v>0.45</v>
+        <v>0.57</v>
       </c>
       <c r="H122" t="inlineStr">
         <is>
@@ -5447,7 +5447,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -5456,7 +5456,7 @@
         </is>
       </c>
       <c r="G123" t="n">
-        <v>0.92</v>
+        <v>1.02</v>
       </c>
       <c r="H123" t="inlineStr">
         <is>
@@ -5488,7 +5488,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -5497,7 +5497,7 @@
         </is>
       </c>
       <c r="G124" t="n">
-        <v>0.98</v>
+        <v>0.51</v>
       </c>
       <c r="H124" t="inlineStr">
         <is>
@@ -5529,7 +5529,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -5538,7 +5538,7 @@
         </is>
       </c>
       <c r="G125" t="n">
-        <v>0.67</v>
+        <v>0.64</v>
       </c>
       <c r="H125" t="inlineStr">
         <is>
@@ -5570,7 +5570,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -5579,7 +5579,7 @@
         </is>
       </c>
       <c r="G126" t="n">
-        <v>0.91</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H126" t="inlineStr">
         <is>
@@ -5611,7 +5611,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -5620,7 +5620,7 @@
         </is>
       </c>
       <c r="G127" t="n">
-        <v>1.04</v>
+        <v>0.8</v>
       </c>
       <c r="H127" t="inlineStr">
         <is>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -5661,7 +5661,7 @@
         </is>
       </c>
       <c r="G128" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="H128" t="inlineStr">
         <is>
@@ -5693,7 +5693,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -5702,7 +5702,7 @@
         </is>
       </c>
       <c r="G129" t="n">
-        <v>0.96</v>
+        <v>0.98</v>
       </c>
       <c r="H129" t="inlineStr">
         <is>
@@ -5743,7 +5743,7 @@
         </is>
       </c>
       <c r="G130" t="n">
-        <v>0.98</v>
+        <v>0.77</v>
       </c>
       <c r="H130" t="inlineStr">
         <is>
@@ -5775,7 +5775,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -5784,7 +5784,7 @@
         </is>
       </c>
       <c r="G131" t="n">
-        <v>1.02</v>
+        <v>0.91</v>
       </c>
       <c r="H131" t="inlineStr">
         <is>
@@ -5825,7 +5825,7 @@
         </is>
       </c>
       <c r="G132" t="n">
-        <v>0.98</v>
+        <v>0.93</v>
       </c>
       <c r="H132" t="inlineStr">
         <is>
@@ -5857,7 +5857,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -5866,7 +5866,7 @@
         </is>
       </c>
       <c r="G133" t="n">
-        <v>1.08</v>
+        <v>0.62</v>
       </c>
       <c r="H133" t="inlineStr">
         <is>
@@ -5898,7 +5898,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -5907,7 +5907,7 @@
         </is>
       </c>
       <c r="G134" t="n">
-        <v>0.95</v>
+        <v>0.97</v>
       </c>
       <c r="H134" t="inlineStr">
         <is>
@@ -5939,7 +5939,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -5948,7 +5948,7 @@
         </is>
       </c>
       <c r="G135" t="n">
-        <v>0.62</v>
+        <v>0.84</v>
       </c>
       <c r="H135" t="inlineStr">
         <is>
@@ -5989,7 +5989,7 @@
         </is>
       </c>
       <c r="G136" t="n">
-        <v>0.86</v>
+        <v>0.77</v>
       </c>
       <c r="H136" t="inlineStr">
         <is>
@@ -6021,7 +6021,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -6030,7 +6030,7 @@
         </is>
       </c>
       <c r="G137" t="n">
-        <v>1.13</v>
+        <v>0.75</v>
       </c>
       <c r="H137" t="inlineStr">
         <is>
@@ -6062,7 +6062,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -6071,7 +6071,7 @@
         </is>
       </c>
       <c r="G138" t="n">
-        <v>1.12</v>
+        <v>0.45</v>
       </c>
       <c r="H138" t="inlineStr">
         <is>
@@ -6112,7 +6112,7 @@
         </is>
       </c>
       <c r="G139" t="n">
-        <v>0.74</v>
+        <v>1.09</v>
       </c>
       <c r="H139" t="inlineStr">
         <is>
@@ -6144,7 +6144,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -6153,7 +6153,7 @@
         </is>
       </c>
       <c r="G140" t="n">
-        <v>0.66</v>
+        <v>0.92</v>
       </c>
       <c r="H140" t="inlineStr">
         <is>
@@ -6185,7 +6185,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -6194,7 +6194,7 @@
         </is>
       </c>
       <c r="G141" t="n">
-        <v>0.87</v>
+        <v>1.06</v>
       </c>
       <c r="H141" t="inlineStr">
         <is>
@@ -6226,7 +6226,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -6235,7 +6235,7 @@
         </is>
       </c>
       <c r="G142" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.65</v>
       </c>
       <c r="H142" t="inlineStr">
         <is>
@@ -6276,7 +6276,7 @@
         </is>
       </c>
       <c r="G143" t="n">
-        <v>0.84</v>
+        <v>0.66</v>
       </c>
       <c r="H143" t="inlineStr">
         <is>
@@ -6308,7 +6308,7 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -6317,7 +6317,7 @@
         </is>
       </c>
       <c r="G144" t="n">
-        <v>0.84</v>
+        <v>0.77</v>
       </c>
       <c r="H144" t="inlineStr">
         <is>
@@ -6358,7 +6358,7 @@
         </is>
       </c>
       <c r="G145" t="n">
-        <v>0.92</v>
+        <v>0.9</v>
       </c>
       <c r="H145" t="inlineStr">
         <is>
@@ -6399,7 +6399,7 @@
         </is>
       </c>
       <c r="G146" t="n">
-        <v>0.92</v>
+        <v>0.95</v>
       </c>
       <c r="H146" t="inlineStr">
         <is>
@@ -6431,7 +6431,7 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
@@ -6440,7 +6440,7 @@
         </is>
       </c>
       <c r="G147" t="n">
-        <v>0.96</v>
+        <v>1.14</v>
       </c>
       <c r="H147" t="inlineStr">
         <is>
@@ -6472,7 +6472,7 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
@@ -6481,7 +6481,7 @@
         </is>
       </c>
       <c r="G148" t="n">
-        <v>0.75</v>
+        <v>0.49</v>
       </c>
       <c r="H148" t="inlineStr">
         <is>
@@ -6522,7 +6522,7 @@
         </is>
       </c>
       <c r="G149" t="n">
-        <v>1.11</v>
+        <v>0.61</v>
       </c>
       <c r="H149" t="inlineStr">
         <is>
@@ -6554,7 +6554,7 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
@@ -6563,7 +6563,7 @@
         </is>
       </c>
       <c r="G150" t="n">
-        <v>0.58</v>
+        <v>0.52</v>
       </c>
       <c r="H150" t="inlineStr">
         <is>
@@ -6595,7 +6595,7 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
@@ -6604,7 +6604,7 @@
         </is>
       </c>
       <c r="G151" t="n">
-        <v>1.01</v>
+        <v>0.63</v>
       </c>
       <c r="H151" t="inlineStr">
         <is>
@@ -6636,7 +6636,7 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
@@ -6645,7 +6645,7 @@
         </is>
       </c>
       <c r="G152" t="n">
-        <v>0.78</v>
+        <v>0.87</v>
       </c>
       <c r="H152" t="inlineStr">
         <is>
@@ -6677,7 +6677,7 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
@@ -6686,7 +6686,7 @@
         </is>
       </c>
       <c r="G153" t="n">
-        <v>0.64</v>
+        <v>1.05</v>
       </c>
       <c r="H153" t="inlineStr">
         <is>
@@ -6727,7 +6727,7 @@
         </is>
       </c>
       <c r="G154" t="n">
-        <v>0.66</v>
+        <v>0.7</v>
       </c>
       <c r="H154" t="inlineStr">
         <is>
@@ -6759,7 +6759,7 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
@@ -6768,7 +6768,7 @@
         </is>
       </c>
       <c r="G155" t="n">
-        <v>0.65</v>
+        <v>0.64</v>
       </c>
       <c r="H155" t="inlineStr">
         <is>
@@ -6809,7 +6809,7 @@
         </is>
       </c>
       <c r="G156" t="n">
-        <v>0.86</v>
+        <v>0.65</v>
       </c>
       <c r="H156" t="inlineStr">
         <is>
@@ -6850,7 +6850,7 @@
         </is>
       </c>
       <c r="G157" t="n">
-        <v>0.57</v>
+        <v>0.72</v>
       </c>
       <c r="H157" t="inlineStr">
         <is>
@@ -6891,7 +6891,7 @@
         </is>
       </c>
       <c r="G158" t="n">
-        <v>1</v>
+        <v>0.46</v>
       </c>
       <c r="H158" t="inlineStr">
         <is>
@@ -6923,7 +6923,7 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
@@ -6932,7 +6932,7 @@
         </is>
       </c>
       <c r="G159" t="n">
-        <v>0.58</v>
+        <v>1.02</v>
       </c>
       <c r="H159" t="inlineStr">
         <is>
@@ -6964,7 +6964,7 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
@@ -6973,7 +6973,7 @@
         </is>
       </c>
       <c r="G160" t="n">
-        <v>0.47</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H160" t="inlineStr">
         <is>
@@ -7005,7 +7005,7 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
@@ -7014,7 +7014,7 @@
         </is>
       </c>
       <c r="G161" t="n">
-        <v>0.5600000000000001</v>
+        <v>1.06</v>
       </c>
       <c r="H161" t="inlineStr">
         <is>
@@ -7055,7 +7055,7 @@
         </is>
       </c>
       <c r="G162" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.68</v>
       </c>
       <c r="H162" t="inlineStr">
         <is>
@@ -7096,7 +7096,7 @@
         </is>
       </c>
       <c r="G163" t="n">
-        <v>1.11</v>
+        <v>0.49</v>
       </c>
       <c r="H163" t="inlineStr">
         <is>
@@ -7137,7 +7137,7 @@
         </is>
       </c>
       <c r="G164" t="n">
-        <v>0.67</v>
+        <v>0.55</v>
       </c>
       <c r="H164" t="inlineStr">
         <is>
@@ -7169,7 +7169,7 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
@@ -7178,7 +7178,7 @@
         </is>
       </c>
       <c r="G165" t="n">
-        <v>0.82</v>
+        <v>0.87</v>
       </c>
       <c r="H165" t="inlineStr">
         <is>
@@ -7210,7 +7210,7 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
@@ -7219,7 +7219,7 @@
         </is>
       </c>
       <c r="G166" t="n">
-        <v>0.65</v>
+        <v>0.72</v>
       </c>
       <c r="H166" t="inlineStr">
         <is>
@@ -7251,7 +7251,7 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
@@ -7260,7 +7260,7 @@
         </is>
       </c>
       <c r="G167" t="n">
-        <v>0.65</v>
+        <v>0.96</v>
       </c>
       <c r="H167" t="inlineStr">
         <is>
@@ -7292,7 +7292,7 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
@@ -7301,7 +7301,7 @@
         </is>
       </c>
       <c r="G168" t="n">
-        <v>0.61</v>
+        <v>0.58</v>
       </c>
       <c r="H168" t="inlineStr">
         <is>
@@ -7333,7 +7333,7 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
@@ -7342,7 +7342,7 @@
         </is>
       </c>
       <c r="G169" t="n">
-        <v>0.77</v>
+        <v>0.6</v>
       </c>
       <c r="H169" t="inlineStr">
         <is>
@@ -7383,7 +7383,7 @@
         </is>
       </c>
       <c r="G170" t="n">
-        <v>0.95</v>
+        <v>0.54</v>
       </c>
       <c r="H170" t="inlineStr">
         <is>
@@ -7424,7 +7424,7 @@
         </is>
       </c>
       <c r="G171" t="n">
-        <v>0.62</v>
+        <v>1.06</v>
       </c>
       <c r="H171" t="inlineStr">
         <is>
@@ -7456,7 +7456,7 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
@@ -7465,7 +7465,7 @@
         </is>
       </c>
       <c r="G172" t="n">
-        <v>0.83</v>
+        <v>1.11</v>
       </c>
       <c r="H172" t="inlineStr">
         <is>
@@ -7497,7 +7497,7 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
@@ -7506,7 +7506,7 @@
         </is>
       </c>
       <c r="G173" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="H173" t="inlineStr">
         <is>
@@ -7538,7 +7538,7 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
@@ -7547,7 +7547,7 @@
         </is>
       </c>
       <c r="G174" t="n">
-        <v>1.08</v>
+        <v>0.93</v>
       </c>
       <c r="H174" t="inlineStr">
         <is>
@@ -7588,7 +7588,7 @@
         </is>
       </c>
       <c r="G175" t="n">
-        <v>0.45</v>
+        <v>1.07</v>
       </c>
       <c r="H175" t="inlineStr">
         <is>
@@ -7620,7 +7620,7 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
@@ -7629,7 +7629,7 @@
         </is>
       </c>
       <c r="G176" t="n">
-        <v>0.96</v>
+        <v>0.51</v>
       </c>
       <c r="H176" t="inlineStr">
         <is>
@@ -7661,7 +7661,7 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
@@ -7670,7 +7670,7 @@
         </is>
       </c>
       <c r="G177" t="n">
-        <v>0.47</v>
+        <v>0.57</v>
       </c>
       <c r="H177" t="inlineStr">
         <is>
@@ -7702,7 +7702,7 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
@@ -7711,7 +7711,7 @@
         </is>
       </c>
       <c r="G178" t="n">
-        <v>1.05</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H178" t="inlineStr">
         <is>
@@ -7743,7 +7743,7 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
@@ -7752,7 +7752,7 @@
         </is>
       </c>
       <c r="G179" t="n">
-        <v>0.67</v>
+        <v>0.78</v>
       </c>
       <c r="H179" t="inlineStr">
         <is>
@@ -7784,7 +7784,7 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
@@ -7793,7 +7793,7 @@
         </is>
       </c>
       <c r="G180" t="n">
-        <v>0.72</v>
+        <v>1.03</v>
       </c>
       <c r="H180" t="inlineStr">
         <is>
@@ -7834,7 +7834,7 @@
         </is>
       </c>
       <c r="G181" t="n">
-        <v>0.73</v>
+        <v>0.89</v>
       </c>
       <c r="H181" t="inlineStr">
         <is>
@@ -7866,7 +7866,7 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
@@ -7875,7 +7875,7 @@
         </is>
       </c>
       <c r="G182" t="n">
-        <v>0.82</v>
+        <v>0.86</v>
       </c>
       <c r="H182" t="inlineStr">
         <is>
@@ -7907,7 +7907,7 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
@@ -7916,7 +7916,7 @@
         </is>
       </c>
       <c r="G183" t="n">
-        <v>1.05</v>
+        <v>0.73</v>
       </c>
       <c r="H183" t="inlineStr">
         <is>
@@ -7948,7 +7948,7 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
@@ -7957,7 +7957,7 @@
         </is>
       </c>
       <c r="G184" t="n">
-        <v>0.91</v>
+        <v>0.42</v>
       </c>
       <c r="H184" t="inlineStr">
         <is>
@@ -7989,7 +7989,7 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
@@ -7998,7 +7998,7 @@
         </is>
       </c>
       <c r="G185" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.68</v>
       </c>
       <c r="H185" t="inlineStr">
         <is>
@@ -8030,7 +8030,7 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
@@ -8039,7 +8039,7 @@
         </is>
       </c>
       <c r="G186" t="n">
-        <v>0.85</v>
+        <v>0.52</v>
       </c>
       <c r="H186" t="inlineStr">
         <is>
@@ -8071,7 +8071,7 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
@@ -8080,7 +8080,7 @@
         </is>
       </c>
       <c r="G187" t="n">
-        <v>0.68</v>
+        <v>0.84</v>
       </c>
       <c r="H187" t="inlineStr">
         <is>
@@ -8112,7 +8112,7 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
@@ -8121,7 +8121,7 @@
         </is>
       </c>
       <c r="G188" t="n">
-        <v>0.89</v>
+        <v>0.62</v>
       </c>
       <c r="H188" t="inlineStr">
         <is>
@@ -8153,7 +8153,7 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
@@ -8162,7 +8162,7 @@
         </is>
       </c>
       <c r="G189" t="n">
-        <v>0.54</v>
+        <v>0.7</v>
       </c>
       <c r="H189" t="inlineStr">
         <is>
@@ -8194,7 +8194,7 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
@@ -8203,7 +8203,7 @@
         </is>
       </c>
       <c r="G190" t="n">
-        <v>0.82</v>
+        <v>0.95</v>
       </c>
       <c r="H190" t="inlineStr">
         <is>
@@ -8235,7 +8235,7 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
@@ -8244,7 +8244,7 @@
         </is>
       </c>
       <c r="G191" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="H191" t="inlineStr">
         <is>
@@ -8285,7 +8285,7 @@
         </is>
       </c>
       <c r="G192" t="n">
-        <v>0.53</v>
+        <v>0.66</v>
       </c>
       <c r="H192" t="inlineStr">
         <is>
@@ -8317,7 +8317,7 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
@@ -8326,7 +8326,7 @@
         </is>
       </c>
       <c r="G193" t="n">
-        <v>0.43</v>
+        <v>0.91</v>
       </c>
       <c r="H193" t="inlineStr">
         <is>
@@ -8358,7 +8358,7 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
@@ -8367,7 +8367,7 @@
         </is>
       </c>
       <c r="G194" t="n">
-        <v>0.5</v>
+        <v>0.92</v>
       </c>
       <c r="H194" t="inlineStr">
         <is>
@@ -8399,7 +8399,7 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
@@ -8408,7 +8408,7 @@
         </is>
       </c>
       <c r="G195" t="n">
-        <v>1.11</v>
+        <v>0.53</v>
       </c>
       <c r="H195" t="inlineStr">
         <is>
@@ -8449,7 +8449,7 @@
         </is>
       </c>
       <c r="G196" t="n">
-        <v>0.6</v>
+        <v>0.59</v>
       </c>
       <c r="H196" t="inlineStr">
         <is>
@@ -8481,7 +8481,7 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
@@ -8490,7 +8490,7 @@
         </is>
       </c>
       <c r="G197" t="n">
-        <v>0.59</v>
+        <v>0.68</v>
       </c>
       <c r="H197" t="inlineStr">
         <is>
@@ -8522,7 +8522,7 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
@@ -8531,7 +8531,7 @@
         </is>
       </c>
       <c r="G198" t="n">
-        <v>1.14</v>
+        <v>0.87</v>
       </c>
       <c r="H198" t="inlineStr">
         <is>
@@ -8572,7 +8572,7 @@
         </is>
       </c>
       <c r="G199" t="n">
-        <v>0.43</v>
+        <v>0.8</v>
       </c>
       <c r="H199" t="inlineStr">
         <is>
@@ -8604,7 +8604,7 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
@@ -8613,7 +8613,7 @@
         </is>
       </c>
       <c r="G200" t="n">
-        <v>0.84</v>
+        <v>0.68</v>
       </c>
       <c r="H200" t="inlineStr">
         <is>
@@ -8654,7 +8654,7 @@
         </is>
       </c>
       <c r="G201" t="n">
-        <v>0.73</v>
+        <v>0.7</v>
       </c>
       <c r="H201" t="inlineStr">
         <is>
@@ -8695,7 +8695,7 @@
         </is>
       </c>
       <c r="G202" t="n">
-        <v>0.76</v>
+        <v>0.72</v>
       </c>
       <c r="H202" t="inlineStr">
         <is>
@@ -8727,7 +8727,7 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
@@ -8736,7 +8736,7 @@
         </is>
       </c>
       <c r="G203" t="n">
-        <v>1.09</v>
+        <v>0.92</v>
       </c>
       <c r="H203" t="inlineStr">
         <is>
@@ -8768,7 +8768,7 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
@@ -8777,7 +8777,7 @@
         </is>
       </c>
       <c r="G204" t="n">
-        <v>0.72</v>
+        <v>0.61</v>
       </c>
       <c r="H204" t="inlineStr">
         <is>
@@ -8818,7 +8818,7 @@
         </is>
       </c>
       <c r="G205" t="n">
-        <v>0.65</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H205" t="inlineStr">
         <is>
@@ -8850,7 +8850,7 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
@@ -8859,7 +8859,7 @@
         </is>
       </c>
       <c r="G206" t="n">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="H206" t="inlineStr">
         <is>
@@ -8891,7 +8891,7 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
@@ -8900,7 +8900,7 @@
         </is>
       </c>
       <c r="G207" t="n">
-        <v>0.86</v>
+        <v>0.97</v>
       </c>
       <c r="H207" t="inlineStr">
         <is>
@@ -8932,7 +8932,7 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
@@ -8941,7 +8941,7 @@
         </is>
       </c>
       <c r="G208" t="n">
-        <v>0.9</v>
+        <v>1.14</v>
       </c>
       <c r="H208" t="inlineStr">
         <is>
@@ -8973,7 +8973,7 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
@@ -8982,7 +8982,7 @@
         </is>
       </c>
       <c r="G209" t="n">
-        <v>0.65</v>
+        <v>0.46</v>
       </c>
       <c r="H209" t="inlineStr">
         <is>
@@ -9014,7 +9014,7 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
@@ -9023,7 +9023,7 @@
         </is>
       </c>
       <c r="G210" t="n">
-        <v>0.57</v>
+        <v>0.7</v>
       </c>
       <c r="H210" t="inlineStr">
         <is>
@@ -9064,7 +9064,7 @@
         </is>
       </c>
       <c r="G211" t="n">
-        <v>0.5</v>
+        <v>0.91</v>
       </c>
       <c r="H211" t="inlineStr">
         <is>
@@ -9096,7 +9096,7 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
@@ -9105,7 +9105,7 @@
         </is>
       </c>
       <c r="G212" t="n">
-        <v>0.95</v>
+        <v>1.02</v>
       </c>
       <c r="H212" t="inlineStr">
         <is>
@@ -9137,7 +9137,7 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
@@ -9146,7 +9146,7 @@
         </is>
       </c>
       <c r="G213" t="n">
-        <v>1.1</v>
+        <v>0.48</v>
       </c>
       <c r="H213" t="inlineStr">
         <is>
@@ -9178,7 +9178,7 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
@@ -9187,7 +9187,7 @@
         </is>
       </c>
       <c r="G214" t="n">
-        <v>1.06</v>
+        <v>0.53</v>
       </c>
       <c r="H214" t="inlineStr">
         <is>
@@ -9219,7 +9219,7 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
@@ -9228,7 +9228,7 @@
         </is>
       </c>
       <c r="G215" t="n">
-        <v>0.6</v>
+        <v>0.93</v>
       </c>
       <c r="H215" t="inlineStr">
         <is>
@@ -9269,7 +9269,7 @@
         </is>
       </c>
       <c r="G216" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="H216" t="inlineStr">
         <is>
@@ -9301,7 +9301,7 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
@@ -9310,7 +9310,7 @@
         </is>
       </c>
       <c r="G217" t="n">
-        <v>0.58</v>
+        <v>1.04</v>
       </c>
       <c r="H217" t="inlineStr">
         <is>
@@ -9351,7 +9351,7 @@
         </is>
       </c>
       <c r="G218" t="n">
-        <v>1.04</v>
+        <v>0.66</v>
       </c>
       <c r="H218" t="inlineStr">
         <is>
@@ -9383,7 +9383,7 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
@@ -9392,7 +9392,7 @@
         </is>
       </c>
       <c r="G219" t="n">
-        <v>1.13</v>
+        <v>0.99</v>
       </c>
       <c r="H219" t="inlineStr">
         <is>
@@ -9433,7 +9433,7 @@
         </is>
       </c>
       <c r="G220" t="n">
-        <v>0.49</v>
+        <v>1.1</v>
       </c>
       <c r="H220" t="inlineStr">
         <is>
@@ -9465,7 +9465,7 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
@@ -9474,7 +9474,7 @@
         </is>
       </c>
       <c r="G221" t="n">
-        <v>0.78</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H221" t="inlineStr">
         <is>
@@ -9506,7 +9506,7 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
@@ -9515,7 +9515,7 @@
         </is>
       </c>
       <c r="G222" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="H222" t="inlineStr">
         <is>
@@ -9547,7 +9547,7 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
@@ -9556,7 +9556,7 @@
         </is>
       </c>
       <c r="G223" t="n">
-        <v>1.14</v>
+        <v>0.62</v>
       </c>
       <c r="H223" t="inlineStr">
         <is>
@@ -9597,7 +9597,7 @@
         </is>
       </c>
       <c r="G224" t="n">
-        <v>0.79</v>
+        <v>0.51</v>
       </c>
       <c r="H224" t="inlineStr">
         <is>
@@ -9629,7 +9629,7 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
@@ -9638,7 +9638,7 @@
         </is>
       </c>
       <c r="G225" t="n">
-        <v>0.6</v>
+        <v>1.05</v>
       </c>
       <c r="H225" t="inlineStr">
         <is>
@@ -9679,7 +9679,7 @@
         </is>
       </c>
       <c r="G226" t="n">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="H226" t="inlineStr">
         <is>
@@ -9711,7 +9711,7 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
@@ -9720,7 +9720,7 @@
         </is>
       </c>
       <c r="G227" t="n">
-        <v>1.01</v>
+        <v>0.42</v>
       </c>
       <c r="H227" t="inlineStr">
         <is>
@@ -9761,7 +9761,7 @@
         </is>
       </c>
       <c r="G228" t="n">
-        <v>1.14</v>
+        <v>0.82</v>
       </c>
       <c r="H228" t="inlineStr">
         <is>
@@ -9802,7 +9802,7 @@
         </is>
       </c>
       <c r="G229" t="n">
-        <v>0.79</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H229" t="inlineStr">
         <is>
@@ -9834,7 +9834,7 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
@@ -9843,7 +9843,7 @@
         </is>
       </c>
       <c r="G230" t="n">
-        <v>0.96</v>
+        <v>0.73</v>
       </c>
       <c r="H230" t="inlineStr">
         <is>
@@ -9875,7 +9875,7 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
@@ -9884,7 +9884,7 @@
         </is>
       </c>
       <c r="G231" t="n">
-        <v>0.96</v>
+        <v>0.75</v>
       </c>
       <c r="H231" t="inlineStr">
         <is>
@@ -9916,7 +9916,7 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
@@ -9925,7 +9925,7 @@
         </is>
       </c>
       <c r="G232" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.76</v>
       </c>
       <c r="H232" t="inlineStr">
         <is>
@@ -9966,7 +9966,7 @@
         </is>
       </c>
       <c r="G233" t="n">
-        <v>1.06</v>
+        <v>0.55</v>
       </c>
       <c r="H233" t="inlineStr">
         <is>
@@ -9998,7 +9998,7 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
@@ -10007,7 +10007,7 @@
         </is>
       </c>
       <c r="G234" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="H234" t="inlineStr">
         <is>
@@ -10048,7 +10048,7 @@
         </is>
       </c>
       <c r="G235" t="n">
-        <v>0.84</v>
+        <v>1.09</v>
       </c>
       <c r="H235" t="inlineStr">
         <is>
@@ -10089,7 +10089,7 @@
         </is>
       </c>
       <c r="G236" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="H236" t="inlineStr">
         <is>
@@ -10121,7 +10121,7 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
@@ -10130,7 +10130,7 @@
         </is>
       </c>
       <c r="G237" t="n">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="H237" t="inlineStr">
         <is>
@@ -10171,7 +10171,7 @@
         </is>
       </c>
       <c r="G238" t="n">
-        <v>0.59</v>
+        <v>0.52</v>
       </c>
       <c r="H238" t="inlineStr">
         <is>
@@ -10212,7 +10212,7 @@
         </is>
       </c>
       <c r="G239" t="n">
-        <v>1.06</v>
+        <v>0.98</v>
       </c>
       <c r="H239" t="inlineStr">
         <is>
@@ -10244,7 +10244,7 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
@@ -10253,7 +10253,7 @@
         </is>
       </c>
       <c r="G240" t="n">
-        <v>0.46</v>
+        <v>0.78</v>
       </c>
       <c r="H240" t="inlineStr">
         <is>
@@ -10285,7 +10285,7 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
@@ -10294,7 +10294,7 @@
         </is>
       </c>
       <c r="G241" t="n">
-        <v>1.09</v>
+        <v>0.72</v>
       </c>
       <c r="H241" t="inlineStr">
         <is>
@@ -10326,7 +10326,7 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
@@ -10335,7 +10335,7 @@
         </is>
       </c>
       <c r="G242" t="n">
-        <v>1</v>
+        <v>0.83</v>
       </c>
       <c r="H242" t="inlineStr">
         <is>
@@ -10376,7 +10376,7 @@
         </is>
       </c>
       <c r="G243" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="H243" t="inlineStr">
         <is>
@@ -10408,7 +10408,7 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
@@ -10417,7 +10417,7 @@
         </is>
       </c>
       <c r="G244" t="n">
-        <v>0.62</v>
+        <v>0.43</v>
       </c>
       <c r="H244" t="inlineStr">
         <is>
@@ -10449,7 +10449,7 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
@@ -10458,7 +10458,7 @@
         </is>
       </c>
       <c r="G245" t="n">
-        <v>0.5600000000000001</v>
+        <v>1.11</v>
       </c>
       <c r="H245" t="inlineStr">
         <is>
@@ -10499,7 +10499,7 @@
         </is>
       </c>
       <c r="G246" t="n">
-        <v>1.04</v>
+        <v>0.58</v>
       </c>
       <c r="H246" t="inlineStr">
         <is>
@@ -10531,7 +10531,7 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
@@ -10540,7 +10540,7 @@
         </is>
       </c>
       <c r="G247" t="n">
-        <v>0.98</v>
+        <v>1.05</v>
       </c>
       <c r="H247" t="inlineStr">
         <is>
@@ -10572,7 +10572,7 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
@@ -10581,7 +10581,7 @@
         </is>
       </c>
       <c r="G248" t="n">
-        <v>0.49</v>
+        <v>0.51</v>
       </c>
       <c r="H248" t="inlineStr">
         <is>
@@ -10613,7 +10613,7 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
@@ -10622,7 +10622,7 @@
         </is>
       </c>
       <c r="G249" t="n">
-        <v>0.44</v>
+        <v>0.74</v>
       </c>
       <c r="H249" t="inlineStr">
         <is>
@@ -10654,7 +10654,7 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
@@ -10663,7 +10663,7 @@
         </is>
       </c>
       <c r="G250" t="n">
-        <v>0.59</v>
+        <v>0.89</v>
       </c>
       <c r="H250" t="inlineStr">
         <is>
@@ -10695,7 +10695,7 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
@@ -10704,7 +10704,7 @@
         </is>
       </c>
       <c r="G251" t="n">
-        <v>1.11</v>
+        <v>0.98</v>
       </c>
       <c r="H251" t="inlineStr">
         <is>
@@ -10745,7 +10745,7 @@
         </is>
       </c>
       <c r="G252" t="n">
-        <v>0.89</v>
+        <v>0.84</v>
       </c>
       <c r="H252" t="inlineStr">
         <is>
@@ -10777,7 +10777,7 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
@@ -10786,7 +10786,7 @@
         </is>
       </c>
       <c r="G253" t="n">
-        <v>0.8</v>
+        <v>1.11</v>
       </c>
       <c r="H253" t="inlineStr">
         <is>
@@ -10818,7 +10818,7 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
@@ -10827,7 +10827,7 @@
         </is>
       </c>
       <c r="G254" t="n">
-        <v>0.72</v>
+        <v>0.42</v>
       </c>
       <c r="H254" t="inlineStr">
         <is>
@@ -10868,7 +10868,7 @@
         </is>
       </c>
       <c r="G255" t="n">
-        <v>1.13</v>
+        <v>0.83</v>
       </c>
       <c r="H255" t="inlineStr">
         <is>
@@ -10909,7 +10909,7 @@
         </is>
       </c>
       <c r="G256" t="n">
-        <v>0.43</v>
+        <v>1</v>
       </c>
       <c r="H256" t="inlineStr">
         <is>
@@ -10941,7 +10941,7 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
@@ -10950,7 +10950,7 @@
         </is>
       </c>
       <c r="G257" t="n">
-        <v>1</v>
+        <v>1.07</v>
       </c>
       <c r="H257" t="inlineStr">
         <is>
@@ -10991,7 +10991,7 @@
         </is>
       </c>
       <c r="G258" t="n">
-        <v>0.48</v>
+        <v>1.1</v>
       </c>
       <c r="H258" t="inlineStr">
         <is>
@@ -11032,7 +11032,7 @@
         </is>
       </c>
       <c r="G259" t="n">
-        <v>0.8</v>
+        <v>0.93</v>
       </c>
       <c r="H259" t="inlineStr">
         <is>
@@ -11064,7 +11064,7 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
@@ -11073,7 +11073,7 @@
         </is>
       </c>
       <c r="G260" t="n">
-        <v>0.98</v>
+        <v>0.59</v>
       </c>
       <c r="H260" t="inlineStr">
         <is>
@@ -11105,7 +11105,7 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
@@ -11114,7 +11114,7 @@
         </is>
       </c>
       <c r="G261" t="n">
-        <v>1.08</v>
+        <v>0.64</v>
       </c>
       <c r="H261" t="inlineStr">
         <is>
@@ -11146,7 +11146,7 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
@@ -11155,7 +11155,7 @@
         </is>
       </c>
       <c r="G262" t="n">
-        <v>0.82</v>
+        <v>0.8</v>
       </c>
       <c r="H262" t="inlineStr">
         <is>
@@ -11196,7 +11196,7 @@
         </is>
       </c>
       <c r="G263" t="n">
-        <v>0.68</v>
+        <v>0.54</v>
       </c>
       <c r="H263" t="inlineStr">
         <is>
@@ -11228,7 +11228,7 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
@@ -11237,7 +11237,7 @@
         </is>
       </c>
       <c r="G264" t="n">
-        <v>0.6</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H264" t="inlineStr">
         <is>
@@ -11278,7 +11278,7 @@
         </is>
       </c>
       <c r="G265" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.53</v>
       </c>
       <c r="H265" t="inlineStr">
         <is>
@@ -11319,7 +11319,7 @@
         </is>
       </c>
       <c r="G266" t="n">
-        <v>0.5</v>
+        <v>0.61</v>
       </c>
       <c r="H266" t="inlineStr">
         <is>
@@ -11351,7 +11351,7 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
@@ -11360,7 +11360,7 @@
         </is>
       </c>
       <c r="G267" t="n">
-        <v>1.09</v>
+        <v>0.44</v>
       </c>
       <c r="H267" t="inlineStr">
         <is>
@@ -11401,7 +11401,7 @@
         </is>
       </c>
       <c r="G268" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="H268" t="inlineStr">
         <is>
@@ -11433,7 +11433,7 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
@@ -11442,7 +11442,7 @@
         </is>
       </c>
       <c r="G269" t="n">
-        <v>0.89</v>
+        <v>1.09</v>
       </c>
       <c r="H269" t="inlineStr">
         <is>
@@ -11474,7 +11474,7 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
@@ -11483,7 +11483,7 @@
         </is>
       </c>
       <c r="G270" t="n">
-        <v>0.52</v>
+        <v>0.49</v>
       </c>
       <c r="H270" t="inlineStr">
         <is>
@@ -11515,7 +11515,7 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
@@ -11524,7 +11524,7 @@
         </is>
       </c>
       <c r="G271" t="n">
-        <v>1.05</v>
+        <v>0.8</v>
       </c>
       <c r="H271" t="inlineStr">
         <is>
@@ -11556,7 +11556,7 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
@@ -11565,7 +11565,7 @@
         </is>
       </c>
       <c r="G272" t="n">
-        <v>0.85</v>
+        <v>0.55</v>
       </c>
       <c r="H272" t="inlineStr">
         <is>
@@ -11606,7 +11606,7 @@
         </is>
       </c>
       <c r="G273" t="n">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="H273" t="inlineStr">
         <is>
@@ -11638,7 +11638,7 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
@@ -11647,7 +11647,7 @@
         </is>
       </c>
       <c r="G274" t="n">
-        <v>0.44</v>
+        <v>1.12</v>
       </c>
       <c r="H274" t="inlineStr">
         <is>
@@ -11679,7 +11679,7 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
@@ -11688,7 +11688,7 @@
         </is>
       </c>
       <c r="G275" t="n">
-        <v>0.46</v>
+        <v>0.42</v>
       </c>
       <c r="H275" t="inlineStr">
         <is>
@@ -11720,7 +11720,7 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
@@ -11729,7 +11729,7 @@
         </is>
       </c>
       <c r="G276" t="n">
-        <v>1.04</v>
+        <v>0.52</v>
       </c>
       <c r="H276" t="inlineStr">
         <is>
@@ -11761,7 +11761,7 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
@@ -11770,7 +11770,7 @@
         </is>
       </c>
       <c r="G277" t="n">
-        <v>0.42</v>
+        <v>1.12</v>
       </c>
       <c r="H277" t="inlineStr">
         <is>
@@ -11802,7 +11802,7 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
@@ -11811,7 +11811,7 @@
         </is>
       </c>
       <c r="G278" t="n">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="H278" t="inlineStr">
         <is>
@@ -11843,7 +11843,7 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
@@ -11852,7 +11852,7 @@
         </is>
       </c>
       <c r="G279" t="n">
-        <v>0.55</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H279" t="inlineStr">
         <is>
@@ -11884,7 +11884,7 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
@@ -11893,7 +11893,7 @@
         </is>
       </c>
       <c r="G280" t="n">
-        <v>0.68</v>
+        <v>1.05</v>
       </c>
       <c r="H280" t="inlineStr">
         <is>
@@ -11925,7 +11925,7 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
@@ -11934,7 +11934,7 @@
         </is>
       </c>
       <c r="G281" t="n">
-        <v>0.5</v>
+        <v>0.77</v>
       </c>
       <c r="H281" t="inlineStr">
         <is>
@@ -11966,7 +11966,7 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
@@ -11975,7 +11975,7 @@
         </is>
       </c>
       <c r="G282" t="n">
-        <v>0.9</v>
+        <v>0.46</v>
       </c>
       <c r="H282" t="inlineStr">
         <is>
@@ -12007,7 +12007,7 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
@@ -12016,7 +12016,7 @@
         </is>
       </c>
       <c r="G283" t="n">
-        <v>0.89</v>
+        <v>0.43</v>
       </c>
       <c r="H283" t="inlineStr">
         <is>
@@ -12048,7 +12048,7 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
@@ -12057,7 +12057,7 @@
         </is>
       </c>
       <c r="G284" t="n">
-        <v>0.54</v>
+        <v>0.75</v>
       </c>
       <c r="H284" t="inlineStr">
         <is>
@@ -12098,7 +12098,7 @@
         </is>
       </c>
       <c r="G285" t="n">
-        <v>1.11</v>
+        <v>0.71</v>
       </c>
       <c r="H285" t="inlineStr">
         <is>
@@ -12130,7 +12130,7 @@
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
@@ -12139,7 +12139,7 @@
         </is>
       </c>
       <c r="G286" t="n">
-        <v>0.66</v>
+        <v>0.96</v>
       </c>
       <c r="H286" t="inlineStr">
         <is>
@@ -12171,7 +12171,7 @@
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
@@ -12180,7 +12180,7 @@
         </is>
       </c>
       <c r="G287" t="n">
-        <v>0.92</v>
+        <v>0.62</v>
       </c>
       <c r="H287" t="inlineStr">
         <is>
@@ -12212,7 +12212,7 @@
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
@@ -12221,7 +12221,7 @@
         </is>
       </c>
       <c r="G288" t="n">
-        <v>1.05</v>
+        <v>0.62</v>
       </c>
       <c r="H288" t="inlineStr">
         <is>
@@ -12253,7 +12253,7 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
@@ -12262,7 +12262,7 @@
         </is>
       </c>
       <c r="G289" t="n">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="H289" t="inlineStr">
         <is>
@@ -12294,7 +12294,7 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
@@ -12303,7 +12303,7 @@
         </is>
       </c>
       <c r="G290" t="n">
-        <v>0.52</v>
+        <v>0.42</v>
       </c>
       <c r="H290" t="inlineStr">
         <is>
@@ -12344,7 +12344,7 @@
         </is>
       </c>
       <c r="G291" t="n">
-        <v>0.86</v>
+        <v>0.47</v>
       </c>
       <c r="H291" t="inlineStr">
         <is>
@@ -12376,7 +12376,7 @@
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
@@ -12385,7 +12385,7 @@
         </is>
       </c>
       <c r="G292" t="n">
-        <v>1.09</v>
+        <v>0.79</v>
       </c>
       <c r="H292" t="inlineStr">
         <is>
@@ -12417,7 +12417,7 @@
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
@@ -12426,7 +12426,7 @@
         </is>
       </c>
       <c r="G293" t="n">
-        <v>0.84</v>
+        <v>0.92</v>
       </c>
       <c r="H293" t="inlineStr">
         <is>
@@ -12458,7 +12458,7 @@
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
@@ -12467,7 +12467,7 @@
         </is>
       </c>
       <c r="G294" t="n">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="H294" t="inlineStr">
         <is>
@@ -12499,7 +12499,7 @@
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
@@ -12508,7 +12508,7 @@
         </is>
       </c>
       <c r="G295" t="n">
-        <v>1.03</v>
+        <v>0.87</v>
       </c>
       <c r="H295" t="inlineStr">
         <is>
@@ -12540,7 +12540,7 @@
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
@@ -12549,7 +12549,7 @@
         </is>
       </c>
       <c r="G296" t="n">
-        <v>1.01</v>
+        <v>0.89</v>
       </c>
       <c r="H296" t="inlineStr">
         <is>
@@ -12581,7 +12581,7 @@
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
@@ -12590,7 +12590,7 @@
         </is>
       </c>
       <c r="G297" t="n">
-        <v>0.97</v>
+        <v>1.06</v>
       </c>
       <c r="H297" t="inlineStr">
         <is>
@@ -12631,7 +12631,7 @@
         </is>
       </c>
       <c r="G298" t="n">
-        <v>0.54</v>
+        <v>0.9</v>
       </c>
       <c r="H298" t="inlineStr">
         <is>
@@ -12663,7 +12663,7 @@
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F299" t="inlineStr">
@@ -12704,7 +12704,7 @@
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
@@ -12713,7 +12713,7 @@
         </is>
       </c>
       <c r="G300" t="n">
-        <v>0.89</v>
+        <v>0.62</v>
       </c>
       <c r="H300" t="inlineStr">
         <is>
@@ -12745,7 +12745,7 @@
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
@@ -12754,7 +12754,7 @@
         </is>
       </c>
       <c r="G301" t="n">
-        <v>0.79</v>
+        <v>0.57</v>
       </c>
       <c r="H301" t="inlineStr">
         <is>

--- a/reports/Passed_Test_Cases.xlsx
+++ b/reports/Passed_Test_Cases.xlsx
@@ -486,7 +486,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -495,7 +495,7 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0.61</v>
+        <v>0.93</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -527,7 +527,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -568,7 +568,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -577,7 +577,7 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>1.07</v>
+        <v>0.85</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -609,7 +609,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -618,7 +618,7 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>0.83</v>
+        <v>1.05</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -650,7 +650,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>0.46</v>
+        <v>0.58</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -691,7 +691,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -700,7 +700,7 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>1.13</v>
+        <v>0.63</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -732,7 +732,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -741,7 +741,7 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>0.6</v>
+        <v>1.13</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -773,7 +773,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -782,7 +782,7 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>0.64</v>
+        <v>1.1</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -814,7 +814,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -823,7 +823,7 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>0.84</v>
+        <v>1.01</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -855,7 +855,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -864,7 +864,7 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>1.01</v>
+        <v>0.59</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -905,7 +905,7 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>0.89</v>
+        <v>0.53</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -946,7 +946,7 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>0.57</v>
+        <v>0.96</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -978,7 +978,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -987,7 +987,7 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>0.58</v>
+        <v>0.74</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1028,7 +1028,7 @@
         </is>
       </c>
       <c r="G15" t="n">
-        <v>0.83</v>
+        <v>0.8</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -1069,7 +1069,7 @@
         </is>
       </c>
       <c r="G16" t="n">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -1110,7 +1110,7 @@
         </is>
       </c>
       <c r="G17" t="n">
-        <v>0.87</v>
+        <v>0.89</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -1142,7 +1142,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1151,7 +1151,7 @@
         </is>
       </c>
       <c r="G18" t="n">
-        <v>0.87</v>
+        <v>0.83</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1192,7 +1192,7 @@
         </is>
       </c>
       <c r="G19" t="n">
-        <v>0.79</v>
+        <v>1.11</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1233,7 +1233,7 @@
         </is>
       </c>
       <c r="G20" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -1265,7 +1265,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1274,7 +1274,7 @@
         </is>
       </c>
       <c r="G21" t="n">
-        <v>0.55</v>
+        <v>0.43</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -1306,7 +1306,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1315,7 +1315,7 @@
         </is>
       </c>
       <c r="G22" t="n">
-        <v>0.87</v>
+        <v>0.91</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
@@ -1356,7 +1356,7 @@
         </is>
       </c>
       <c r="G23" t="n">
-        <v>0.54</v>
+        <v>1.14</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1397,7 +1397,7 @@
         </is>
       </c>
       <c r="G24" t="n">
-        <v>1.1</v>
+        <v>0.93</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
@@ -1429,7 +1429,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1438,7 +1438,7 @@
         </is>
       </c>
       <c r="G25" t="n">
-        <v>0.49</v>
+        <v>0.76</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
@@ -1479,7 +1479,7 @@
         </is>
       </c>
       <c r="G26" t="n">
-        <v>0.6</v>
+        <v>0.51</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
@@ -1511,7 +1511,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1520,7 +1520,7 @@
         </is>
       </c>
       <c r="G27" t="n">
-        <v>0.49</v>
+        <v>0.62</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
@@ -1552,7 +1552,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1561,7 +1561,7 @@
         </is>
       </c>
       <c r="G28" t="n">
-        <v>0.55</v>
+        <v>0.93</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
@@ -1593,7 +1593,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1602,7 +1602,7 @@
         </is>
       </c>
       <c r="G29" t="n">
-        <v>1.14</v>
+        <v>0.89</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
@@ -1634,7 +1634,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1643,7 +1643,7 @@
         </is>
       </c>
       <c r="G30" t="n">
-        <v>0.96</v>
+        <v>0.55</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
@@ -1675,7 +1675,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1684,7 +1684,7 @@
         </is>
       </c>
       <c r="G31" t="n">
-        <v>0.76</v>
+        <v>0.52</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
@@ -1716,7 +1716,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1725,7 +1725,7 @@
         </is>
       </c>
       <c r="G32" t="n">
-        <v>0.43</v>
+        <v>0.77</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
@@ -1757,7 +1757,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1766,7 +1766,7 @@
         </is>
       </c>
       <c r="G33" t="n">
-        <v>0.53</v>
+        <v>1.1</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
@@ -1798,7 +1798,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1807,7 +1807,7 @@
         </is>
       </c>
       <c r="G34" t="n">
-        <v>0.77</v>
+        <v>0.85</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
@@ -1839,7 +1839,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1848,7 +1848,7 @@
         </is>
       </c>
       <c r="G35" t="n">
-        <v>0.84</v>
+        <v>1.05</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
         </is>
       </c>
       <c r="G36" t="n">
-        <v>0.62</v>
+        <v>0.83</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
@@ -1930,7 +1930,7 @@
         </is>
       </c>
       <c r="G37" t="n">
-        <v>0.93</v>
+        <v>1.12</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
@@ -1962,7 +1962,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1971,7 +1971,7 @@
         </is>
       </c>
       <c r="G38" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.98</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
@@ -2003,7 +2003,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -2012,7 +2012,7 @@
         </is>
       </c>
       <c r="G39" t="n">
-        <v>0.59</v>
+        <v>0.57</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
@@ -2053,7 +2053,7 @@
         </is>
       </c>
       <c r="G40" t="n">
-        <v>0.6</v>
+        <v>0.47</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
@@ -2094,7 +2094,7 @@
         </is>
       </c>
       <c r="G41" t="n">
-        <v>0.68</v>
+        <v>1.12</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
@@ -2135,7 +2135,7 @@
         </is>
       </c>
       <c r="G42" t="n">
-        <v>0.43</v>
+        <v>1.04</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
@@ -2176,7 +2176,7 @@
         </is>
       </c>
       <c r="G43" t="n">
-        <v>0.45</v>
+        <v>0.67</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
@@ -2208,7 +2208,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -2217,7 +2217,7 @@
         </is>
       </c>
       <c r="G44" t="n">
-        <v>0.79</v>
+        <v>0.61</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
@@ -2249,7 +2249,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2258,7 +2258,7 @@
         </is>
       </c>
       <c r="G45" t="n">
-        <v>0.53</v>
+        <v>0.65</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
@@ -2299,7 +2299,7 @@
         </is>
       </c>
       <c r="G46" t="n">
-        <v>1.04</v>
+        <v>0.44</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
@@ -2331,7 +2331,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2340,7 +2340,7 @@
         </is>
       </c>
       <c r="G47" t="n">
-        <v>0.9399999999999999</v>
+        <v>1</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
@@ -2372,7 +2372,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2381,7 +2381,7 @@
         </is>
       </c>
       <c r="G48" t="n">
-        <v>1.1</v>
+        <v>0.76</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
@@ -2422,7 +2422,7 @@
         </is>
       </c>
       <c r="G49" t="n">
-        <v>0.5600000000000001</v>
+        <v>1.14</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
@@ -2454,7 +2454,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2463,7 +2463,7 @@
         </is>
       </c>
       <c r="G50" t="n">
-        <v>0.93</v>
+        <v>0.92</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
@@ -2495,7 +2495,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2504,7 +2504,7 @@
         </is>
       </c>
       <c r="G51" t="n">
-        <v>0.74</v>
+        <v>0.93</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
@@ -2545,7 +2545,7 @@
         </is>
       </c>
       <c r="G52" t="n">
-        <v>0.48</v>
+        <v>0.46</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
@@ -2618,7 +2618,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2627,7 +2627,7 @@
         </is>
       </c>
       <c r="G54" t="n">
-        <v>0.59</v>
+        <v>0.82</v>
       </c>
       <c r="H54" t="inlineStr">
         <is>
@@ -2659,7 +2659,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2668,7 +2668,7 @@
         </is>
       </c>
       <c r="G55" t="n">
-        <v>0.52</v>
+        <v>1.05</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
@@ -2700,7 +2700,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2709,7 +2709,7 @@
         </is>
       </c>
       <c r="G56" t="n">
-        <v>0.65</v>
+        <v>1.04</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
@@ -2741,7 +2741,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2750,7 +2750,7 @@
         </is>
       </c>
       <c r="G57" t="n">
-        <v>0.99</v>
+        <v>1.14</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
@@ -2782,7 +2782,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2791,7 +2791,7 @@
         </is>
       </c>
       <c r="G58" t="n">
-        <v>0.45</v>
+        <v>0.79</v>
       </c>
       <c r="H58" t="inlineStr">
         <is>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2832,7 +2832,7 @@
         </is>
       </c>
       <c r="G59" t="n">
-        <v>0.77</v>
+        <v>0.42</v>
       </c>
       <c r="H59" t="inlineStr">
         <is>
@@ -2864,7 +2864,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2873,7 +2873,7 @@
         </is>
       </c>
       <c r="G60" t="n">
-        <v>0.45</v>
+        <v>0.99</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
@@ -2905,7 +2905,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2914,7 +2914,7 @@
         </is>
       </c>
       <c r="G61" t="n">
-        <v>0.43</v>
+        <v>0.92</v>
       </c>
       <c r="H61" t="inlineStr">
         <is>
@@ -2946,7 +2946,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2955,7 +2955,7 @@
         </is>
       </c>
       <c r="G62" t="n">
-        <v>0.75</v>
+        <v>0.71</v>
       </c>
       <c r="H62" t="inlineStr">
         <is>
@@ -2987,7 +2987,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2996,7 +2996,7 @@
         </is>
       </c>
       <c r="G63" t="n">
-        <v>1.1</v>
+        <v>0.87</v>
       </c>
       <c r="H63" t="inlineStr">
         <is>
@@ -3028,7 +3028,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -3037,7 +3037,7 @@
         </is>
       </c>
       <c r="G64" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.51</v>
       </c>
       <c r="H64" t="inlineStr">
         <is>
@@ -3078,7 +3078,7 @@
         </is>
       </c>
       <c r="G65" t="n">
-        <v>0.93</v>
+        <v>0.63</v>
       </c>
       <c r="H65" t="inlineStr">
         <is>
@@ -3110,7 +3110,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -3119,7 +3119,7 @@
         </is>
       </c>
       <c r="G66" t="n">
-        <v>0.5</v>
+        <v>0.68</v>
       </c>
       <c r="H66" t="inlineStr">
         <is>
@@ -3160,7 +3160,7 @@
         </is>
       </c>
       <c r="G67" t="n">
-        <v>0.92</v>
+        <v>0.64</v>
       </c>
       <c r="H67" t="inlineStr">
         <is>
@@ -3192,7 +3192,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -3201,7 +3201,7 @@
         </is>
       </c>
       <c r="G68" t="n">
-        <v>1.12</v>
+        <v>0.53</v>
       </c>
       <c r="H68" t="inlineStr">
         <is>
@@ -3233,7 +3233,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -3242,7 +3242,7 @@
         </is>
       </c>
       <c r="G69" t="n">
-        <v>0.68</v>
+        <v>0.89</v>
       </c>
       <c r="H69" t="inlineStr">
         <is>
@@ -3274,7 +3274,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -3283,7 +3283,7 @@
         </is>
       </c>
       <c r="G70" t="n">
-        <v>0.67</v>
+        <v>0.44</v>
       </c>
       <c r="H70" t="inlineStr">
         <is>
@@ -3315,7 +3315,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -3324,7 +3324,7 @@
         </is>
       </c>
       <c r="G71" t="n">
-        <v>1.02</v>
+        <v>0.44</v>
       </c>
       <c r="H71" t="inlineStr">
         <is>
@@ -3365,7 +3365,7 @@
         </is>
       </c>
       <c r="G72" t="n">
-        <v>0.44</v>
+        <v>1.09</v>
       </c>
       <c r="H72" t="inlineStr">
         <is>
@@ -3397,7 +3397,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -3406,7 +3406,7 @@
         </is>
       </c>
       <c r="G73" t="n">
-        <v>0.87</v>
+        <v>0.75</v>
       </c>
       <c r="H73" t="inlineStr">
         <is>
@@ -3438,7 +3438,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3447,7 +3447,7 @@
         </is>
       </c>
       <c r="G74" t="n">
-        <v>0.87</v>
+        <v>0.73</v>
       </c>
       <c r="H74" t="inlineStr">
         <is>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3488,7 +3488,7 @@
         </is>
       </c>
       <c r="G75" t="n">
-        <v>0.43</v>
+        <v>0.64</v>
       </c>
       <c r="H75" t="inlineStr">
         <is>
@@ -3520,7 +3520,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3529,7 +3529,7 @@
         </is>
       </c>
       <c r="G76" t="n">
-        <v>0.64</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H76" t="inlineStr">
         <is>
@@ -3561,7 +3561,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3570,7 +3570,7 @@
         </is>
       </c>
       <c r="G77" t="n">
-        <v>0.7</v>
+        <v>0.97</v>
       </c>
       <c r="H77" t="inlineStr">
         <is>
@@ -3602,7 +3602,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3611,7 +3611,7 @@
         </is>
       </c>
       <c r="G78" t="n">
-        <v>0.65</v>
+        <v>0.72</v>
       </c>
       <c r="H78" t="inlineStr">
         <is>
@@ -3652,7 +3652,7 @@
         </is>
       </c>
       <c r="G79" t="n">
-        <v>1.02</v>
+        <v>0.45</v>
       </c>
       <c r="H79" t="inlineStr">
         <is>
@@ -3693,7 +3693,7 @@
         </is>
       </c>
       <c r="G80" t="n">
-        <v>0.78</v>
+        <v>0.72</v>
       </c>
       <c r="H80" t="inlineStr">
         <is>
@@ -3734,7 +3734,7 @@
         </is>
       </c>
       <c r="G81" t="n">
-        <v>0.55</v>
+        <v>0.87</v>
       </c>
       <c r="H81" t="inlineStr">
         <is>
@@ -3775,7 +3775,7 @@
         </is>
       </c>
       <c r="G82" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="H82" t="inlineStr">
         <is>
@@ -3807,7 +3807,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3816,7 +3816,7 @@
         </is>
       </c>
       <c r="G83" t="n">
-        <v>1.04</v>
+        <v>1.13</v>
       </c>
       <c r="H83" t="inlineStr">
         <is>
@@ -3848,7 +3848,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3857,7 +3857,7 @@
         </is>
       </c>
       <c r="G84" t="n">
-        <v>0.65</v>
+        <v>0.8</v>
       </c>
       <c r="H84" t="inlineStr">
         <is>
@@ -3889,7 +3889,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3898,7 +3898,7 @@
         </is>
       </c>
       <c r="G85" t="n">
-        <v>0.76</v>
+        <v>0.59</v>
       </c>
       <c r="H85" t="inlineStr">
         <is>
@@ -3939,7 +3939,7 @@
         </is>
       </c>
       <c r="G86" t="n">
-        <v>0.45</v>
+        <v>1.06</v>
       </c>
       <c r="H86" t="inlineStr">
         <is>
@@ -3971,7 +3971,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3980,7 +3980,7 @@
         </is>
       </c>
       <c r="G87" t="n">
-        <v>1.01</v>
+        <v>0.51</v>
       </c>
       <c r="H87" t="inlineStr">
         <is>
@@ -4012,7 +4012,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -4021,7 +4021,7 @@
         </is>
       </c>
       <c r="G88" t="n">
-        <v>0.96</v>
+        <v>0.7</v>
       </c>
       <c r="H88" t="inlineStr">
         <is>
@@ -4053,7 +4053,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -4062,7 +4062,7 @@
         </is>
       </c>
       <c r="G89" t="n">
-        <v>0.46</v>
+        <v>0.58</v>
       </c>
       <c r="H89" t="inlineStr">
         <is>
@@ -4094,7 +4094,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -4103,7 +4103,7 @@
         </is>
       </c>
       <c r="G90" t="n">
-        <v>0.51</v>
+        <v>0.66</v>
       </c>
       <c r="H90" t="inlineStr">
         <is>
@@ -4135,7 +4135,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -4144,7 +4144,7 @@
         </is>
       </c>
       <c r="G91" t="n">
-        <v>0.43</v>
+        <v>0.79</v>
       </c>
       <c r="H91" t="inlineStr">
         <is>
@@ -4176,7 +4176,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -4185,7 +4185,7 @@
         </is>
       </c>
       <c r="G92" t="n">
-        <v>1.04</v>
+        <v>0.99</v>
       </c>
       <c r="H92" t="inlineStr">
         <is>
@@ -4226,7 +4226,7 @@
         </is>
       </c>
       <c r="G93" t="n">
-        <v>0.55</v>
+        <v>0.6</v>
       </c>
       <c r="H93" t="inlineStr">
         <is>
@@ -4258,7 +4258,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -4267,7 +4267,7 @@
         </is>
       </c>
       <c r="G94" t="n">
-        <v>0.84</v>
+        <v>1.09</v>
       </c>
       <c r="H94" t="inlineStr">
         <is>
@@ -4308,7 +4308,7 @@
         </is>
       </c>
       <c r="G95" t="n">
-        <v>0.44</v>
+        <v>0.76</v>
       </c>
       <c r="H95" t="inlineStr">
         <is>
@@ -4340,7 +4340,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -4349,7 +4349,7 @@
         </is>
       </c>
       <c r="G96" t="n">
-        <v>0.64</v>
+        <v>1.06</v>
       </c>
       <c r="H96" t="inlineStr">
         <is>
@@ -4381,7 +4381,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -4390,7 +4390,7 @@
         </is>
       </c>
       <c r="G97" t="n">
-        <v>1.02</v>
+        <v>0.88</v>
       </c>
       <c r="H97" t="inlineStr">
         <is>
@@ -4422,7 +4422,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -4431,7 +4431,7 @@
         </is>
       </c>
       <c r="G98" t="n">
-        <v>1.14</v>
+        <v>0.88</v>
       </c>
       <c r="H98" t="inlineStr">
         <is>
@@ -4463,7 +4463,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -4472,7 +4472,7 @@
         </is>
       </c>
       <c r="G99" t="n">
-        <v>0.68</v>
+        <v>0.76</v>
       </c>
       <c r="H99" t="inlineStr">
         <is>
@@ -4513,7 +4513,7 @@
         </is>
       </c>
       <c r="G100" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.51</v>
       </c>
       <c r="H100" t="inlineStr">
         <is>
@@ -4554,7 +4554,7 @@
         </is>
       </c>
       <c r="G101" t="n">
-        <v>0.52</v>
+        <v>1.14</v>
       </c>
       <c r="H101" t="inlineStr">
         <is>
@@ -4586,7 +4586,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -4595,7 +4595,7 @@
         </is>
       </c>
       <c r="G102" t="n">
-        <v>0.82</v>
+        <v>0.92</v>
       </c>
       <c r="H102" t="inlineStr">
         <is>
@@ -4627,7 +4627,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4636,7 +4636,7 @@
         </is>
       </c>
       <c r="G103" t="n">
-        <v>0.82</v>
+        <v>0.47</v>
       </c>
       <c r="H103" t="inlineStr">
         <is>
@@ -4677,7 +4677,7 @@
         </is>
       </c>
       <c r="G104" t="n">
-        <v>0.47</v>
+        <v>0.98</v>
       </c>
       <c r="H104" t="inlineStr">
         <is>
@@ -4709,7 +4709,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4718,7 +4718,7 @@
         </is>
       </c>
       <c r="G105" t="n">
-        <v>0.53</v>
+        <v>0.57</v>
       </c>
       <c r="H105" t="inlineStr">
         <is>
@@ -4750,7 +4750,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4759,7 +4759,7 @@
         </is>
       </c>
       <c r="G106" t="n">
-        <v>0.76</v>
+        <v>0.89</v>
       </c>
       <c r="H106" t="inlineStr">
         <is>
@@ -4800,7 +4800,7 @@
         </is>
       </c>
       <c r="G107" t="n">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
       <c r="H107" t="inlineStr">
         <is>
@@ -4841,7 +4841,7 @@
         </is>
       </c>
       <c r="G108" t="n">
-        <v>0.72</v>
+        <v>0.61</v>
       </c>
       <c r="H108" t="inlineStr">
         <is>
@@ -4873,7 +4873,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4882,7 +4882,7 @@
         </is>
       </c>
       <c r="G109" t="n">
-        <v>0.71</v>
+        <v>0.88</v>
       </c>
       <c r="H109" t="inlineStr">
         <is>
@@ -4914,7 +4914,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4923,7 +4923,7 @@
         </is>
       </c>
       <c r="G110" t="n">
-        <v>1.12</v>
+        <v>0.89</v>
       </c>
       <c r="H110" t="inlineStr">
         <is>
@@ -4955,7 +4955,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4964,7 +4964,7 @@
         </is>
       </c>
       <c r="G111" t="n">
-        <v>0.6</v>
+        <v>0.75</v>
       </c>
       <c r="H111" t="inlineStr">
         <is>
@@ -4996,7 +4996,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -5005,7 +5005,7 @@
         </is>
       </c>
       <c r="G112" t="n">
-        <v>1.08</v>
+        <v>0.79</v>
       </c>
       <c r="H112" t="inlineStr">
         <is>
@@ -5037,7 +5037,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -5046,7 +5046,7 @@
         </is>
       </c>
       <c r="G113" t="n">
-        <v>0.43</v>
+        <v>0.92</v>
       </c>
       <c r="H113" t="inlineStr">
         <is>
@@ -5078,7 +5078,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -5087,7 +5087,7 @@
         </is>
       </c>
       <c r="G114" t="n">
-        <v>0.71</v>
+        <v>0.43</v>
       </c>
       <c r="H114" t="inlineStr">
         <is>
@@ -5119,7 +5119,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -5128,7 +5128,7 @@
         </is>
       </c>
       <c r="G115" t="n">
-        <v>1.01</v>
+        <v>0.86</v>
       </c>
       <c r="H115" t="inlineStr">
         <is>
@@ -5160,7 +5160,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -5169,7 +5169,7 @@
         </is>
       </c>
       <c r="G116" t="n">
-        <v>1.14</v>
+        <v>0.78</v>
       </c>
       <c r="H116" t="inlineStr">
         <is>
@@ -5201,7 +5201,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -5210,7 +5210,7 @@
         </is>
       </c>
       <c r="G117" t="n">
-        <v>0.51</v>
+        <v>0.91</v>
       </c>
       <c r="H117" t="inlineStr">
         <is>
@@ -5251,7 +5251,7 @@
         </is>
       </c>
       <c r="G118" t="n">
-        <v>1.08</v>
+        <v>0.9</v>
       </c>
       <c r="H118" t="inlineStr">
         <is>
@@ -5283,7 +5283,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -5292,7 +5292,7 @@
         </is>
       </c>
       <c r="G119" t="n">
-        <v>0.95</v>
+        <v>0.59</v>
       </c>
       <c r="H119" t="inlineStr">
         <is>
@@ -5333,7 +5333,7 @@
         </is>
       </c>
       <c r="G120" t="n">
-        <v>1.03</v>
+        <v>1.13</v>
       </c>
       <c r="H120" t="inlineStr">
         <is>
@@ -5365,7 +5365,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -5374,7 +5374,7 @@
         </is>
       </c>
       <c r="G121" t="n">
-        <v>1.15</v>
+        <v>0.57</v>
       </c>
       <c r="H121" t="inlineStr">
         <is>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -5415,7 +5415,7 @@
         </is>
       </c>
       <c r="G122" t="n">
-        <v>0.57</v>
+        <v>0.62</v>
       </c>
       <c r="H122" t="inlineStr">
         <is>
@@ -5447,7 +5447,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -5456,7 +5456,7 @@
         </is>
       </c>
       <c r="G123" t="n">
-        <v>1.02</v>
+        <v>0.58</v>
       </c>
       <c r="H123" t="inlineStr">
         <is>
@@ -5488,7 +5488,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -5497,7 +5497,7 @@
         </is>
       </c>
       <c r="G124" t="n">
-        <v>0.51</v>
+        <v>0.88</v>
       </c>
       <c r="H124" t="inlineStr">
         <is>
@@ -5529,7 +5529,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -5538,7 +5538,7 @@
         </is>
       </c>
       <c r="G125" t="n">
-        <v>0.64</v>
+        <v>0.83</v>
       </c>
       <c r="H125" t="inlineStr">
         <is>
@@ -5570,7 +5570,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -5579,7 +5579,7 @@
         </is>
       </c>
       <c r="G126" t="n">
-        <v>0.6899999999999999</v>
+        <v>1.13</v>
       </c>
       <c r="H126" t="inlineStr">
         <is>
@@ -5611,7 +5611,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -5620,7 +5620,7 @@
         </is>
       </c>
       <c r="G127" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="H127" t="inlineStr">
         <is>
@@ -5661,7 +5661,7 @@
         </is>
       </c>
       <c r="G128" t="n">
-        <v>1.01</v>
+        <v>0.89</v>
       </c>
       <c r="H128" t="inlineStr">
         <is>
@@ -5693,7 +5693,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -5702,7 +5702,7 @@
         </is>
       </c>
       <c r="G129" t="n">
-        <v>0.98</v>
+        <v>0.87</v>
       </c>
       <c r="H129" t="inlineStr">
         <is>
@@ -5734,7 +5734,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -5743,7 +5743,7 @@
         </is>
       </c>
       <c r="G130" t="n">
-        <v>0.77</v>
+        <v>0.47</v>
       </c>
       <c r="H130" t="inlineStr">
         <is>
@@ -5775,7 +5775,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -5784,7 +5784,7 @@
         </is>
       </c>
       <c r="G131" t="n">
-        <v>0.91</v>
+        <v>0.67</v>
       </c>
       <c r="H131" t="inlineStr">
         <is>
@@ -5816,7 +5816,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -5825,7 +5825,7 @@
         </is>
       </c>
       <c r="G132" t="n">
-        <v>0.93</v>
+        <v>0.57</v>
       </c>
       <c r="H132" t="inlineStr">
         <is>
@@ -5857,7 +5857,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -5866,7 +5866,7 @@
         </is>
       </c>
       <c r="G133" t="n">
-        <v>0.62</v>
+        <v>1.04</v>
       </c>
       <c r="H133" t="inlineStr">
         <is>
@@ -5898,7 +5898,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -5907,7 +5907,7 @@
         </is>
       </c>
       <c r="G134" t="n">
-        <v>0.97</v>
+        <v>0.99</v>
       </c>
       <c r="H134" t="inlineStr">
         <is>
@@ -5939,7 +5939,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -5948,7 +5948,7 @@
         </is>
       </c>
       <c r="G135" t="n">
-        <v>0.84</v>
+        <v>0.67</v>
       </c>
       <c r="H135" t="inlineStr">
         <is>
@@ -5980,7 +5980,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -5989,7 +5989,7 @@
         </is>
       </c>
       <c r="G136" t="n">
-        <v>0.77</v>
+        <v>0.75</v>
       </c>
       <c r="H136" t="inlineStr">
         <is>
@@ -6021,7 +6021,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -6030,7 +6030,7 @@
         </is>
       </c>
       <c r="G137" t="n">
-        <v>0.75</v>
+        <v>0.92</v>
       </c>
       <c r="H137" t="inlineStr">
         <is>
@@ -6062,7 +6062,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -6071,7 +6071,7 @@
         </is>
       </c>
       <c r="G138" t="n">
-        <v>0.45</v>
+        <v>1.07</v>
       </c>
       <c r="H138" t="inlineStr">
         <is>
@@ -6112,7 +6112,7 @@
         </is>
       </c>
       <c r="G139" t="n">
-        <v>1.09</v>
+        <v>0.54</v>
       </c>
       <c r="H139" t="inlineStr">
         <is>
@@ -6153,7 +6153,7 @@
         </is>
       </c>
       <c r="G140" t="n">
-        <v>0.92</v>
+        <v>0.89</v>
       </c>
       <c r="H140" t="inlineStr">
         <is>
@@ -6185,7 +6185,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -6194,7 +6194,7 @@
         </is>
       </c>
       <c r="G141" t="n">
-        <v>1.06</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H141" t="inlineStr">
         <is>
@@ -6235,7 +6235,7 @@
         </is>
       </c>
       <c r="G142" t="n">
-        <v>0.65</v>
+        <v>0.8</v>
       </c>
       <c r="H142" t="inlineStr">
         <is>
@@ -6267,7 +6267,7 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -6276,7 +6276,7 @@
         </is>
       </c>
       <c r="G143" t="n">
-        <v>0.66</v>
+        <v>0.63</v>
       </c>
       <c r="H143" t="inlineStr">
         <is>
@@ -6308,7 +6308,7 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -6317,7 +6317,7 @@
         </is>
       </c>
       <c r="G144" t="n">
-        <v>0.77</v>
+        <v>0.98</v>
       </c>
       <c r="H144" t="inlineStr">
         <is>
@@ -6358,7 +6358,7 @@
         </is>
       </c>
       <c r="G145" t="n">
-        <v>0.9</v>
+        <v>0.87</v>
       </c>
       <c r="H145" t="inlineStr">
         <is>
@@ -6390,7 +6390,7 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
@@ -6399,7 +6399,7 @@
         </is>
       </c>
       <c r="G146" t="n">
-        <v>0.95</v>
+        <v>0.45</v>
       </c>
       <c r="H146" t="inlineStr">
         <is>
@@ -6440,7 +6440,7 @@
         </is>
       </c>
       <c r="G147" t="n">
-        <v>1.14</v>
+        <v>0.75</v>
       </c>
       <c r="H147" t="inlineStr">
         <is>
@@ -6472,7 +6472,7 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
@@ -6481,7 +6481,7 @@
         </is>
       </c>
       <c r="G148" t="n">
-        <v>0.49</v>
+        <v>0.97</v>
       </c>
       <c r="H148" t="inlineStr">
         <is>
@@ -6513,7 +6513,7 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
@@ -6522,7 +6522,7 @@
         </is>
       </c>
       <c r="G149" t="n">
-        <v>0.61</v>
+        <v>0.45</v>
       </c>
       <c r="H149" t="inlineStr">
         <is>
@@ -6554,7 +6554,7 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
@@ -6563,7 +6563,7 @@
         </is>
       </c>
       <c r="G150" t="n">
-        <v>0.52</v>
+        <v>0.55</v>
       </c>
       <c r="H150" t="inlineStr">
         <is>
@@ -6604,7 +6604,7 @@
         </is>
       </c>
       <c r="G151" t="n">
-        <v>0.63</v>
+        <v>1.12</v>
       </c>
       <c r="H151" t="inlineStr">
         <is>
@@ -6636,7 +6636,7 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
@@ -6645,7 +6645,7 @@
         </is>
       </c>
       <c r="G152" t="n">
-        <v>0.87</v>
+        <v>1.13</v>
       </c>
       <c r="H152" t="inlineStr">
         <is>
@@ -6686,7 +6686,7 @@
         </is>
       </c>
       <c r="G153" t="n">
-        <v>1.05</v>
+        <v>0.72</v>
       </c>
       <c r="H153" t="inlineStr">
         <is>
@@ -6727,7 +6727,7 @@
         </is>
       </c>
       <c r="G154" t="n">
-        <v>0.7</v>
+        <v>0.57</v>
       </c>
       <c r="H154" t="inlineStr">
         <is>
@@ -6768,7 +6768,7 @@
         </is>
       </c>
       <c r="G155" t="n">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="H155" t="inlineStr">
         <is>
@@ -6800,7 +6800,7 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
@@ -6809,7 +6809,7 @@
         </is>
       </c>
       <c r="G156" t="n">
-        <v>0.65</v>
+        <v>1.15</v>
       </c>
       <c r="H156" t="inlineStr">
         <is>
@@ -6841,7 +6841,7 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
@@ -6850,7 +6850,7 @@
         </is>
       </c>
       <c r="G157" t="n">
-        <v>0.72</v>
+        <v>0.44</v>
       </c>
       <c r="H157" t="inlineStr">
         <is>
@@ -6882,7 +6882,7 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
@@ -6891,7 +6891,7 @@
         </is>
       </c>
       <c r="G158" t="n">
-        <v>0.46</v>
+        <v>1.15</v>
       </c>
       <c r="H158" t="inlineStr">
         <is>
@@ -6923,7 +6923,7 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
@@ -6932,7 +6932,7 @@
         </is>
       </c>
       <c r="G159" t="n">
-        <v>1.02</v>
+        <v>0.48</v>
       </c>
       <c r="H159" t="inlineStr">
         <is>
@@ -6964,7 +6964,7 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
@@ -6973,7 +6973,7 @@
         </is>
       </c>
       <c r="G160" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.75</v>
       </c>
       <c r="H160" t="inlineStr">
         <is>
@@ -7005,7 +7005,7 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
@@ -7014,7 +7014,7 @@
         </is>
       </c>
       <c r="G161" t="n">
-        <v>1.06</v>
+        <v>0.97</v>
       </c>
       <c r="H161" t="inlineStr">
         <is>
@@ -7046,7 +7046,7 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
@@ -7055,7 +7055,7 @@
         </is>
       </c>
       <c r="G162" t="n">
-        <v>0.68</v>
+        <v>0.65</v>
       </c>
       <c r="H162" t="inlineStr">
         <is>
@@ -7087,7 +7087,7 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
@@ -7096,7 +7096,7 @@
         </is>
       </c>
       <c r="G163" t="n">
-        <v>0.49</v>
+        <v>0.52</v>
       </c>
       <c r="H163" t="inlineStr">
         <is>
@@ -7128,7 +7128,7 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
@@ -7137,7 +7137,7 @@
         </is>
       </c>
       <c r="G164" t="n">
-        <v>0.55</v>
+        <v>1.03</v>
       </c>
       <c r="H164" t="inlineStr">
         <is>
@@ -7169,7 +7169,7 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
@@ -7178,7 +7178,7 @@
         </is>
       </c>
       <c r="G165" t="n">
-        <v>0.87</v>
+        <v>0.43</v>
       </c>
       <c r="H165" t="inlineStr">
         <is>
@@ -7210,7 +7210,7 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
@@ -7219,7 +7219,7 @@
         </is>
       </c>
       <c r="G166" t="n">
-        <v>0.72</v>
+        <v>0.99</v>
       </c>
       <c r="H166" t="inlineStr">
         <is>
@@ -7260,7 +7260,7 @@
         </is>
       </c>
       <c r="G167" t="n">
-        <v>0.96</v>
+        <v>0.52</v>
       </c>
       <c r="H167" t="inlineStr">
         <is>
@@ -7301,7 +7301,7 @@
         </is>
       </c>
       <c r="G168" t="n">
-        <v>0.58</v>
+        <v>0.96</v>
       </c>
       <c r="H168" t="inlineStr">
         <is>
@@ -7333,7 +7333,7 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
@@ -7342,7 +7342,7 @@
         </is>
       </c>
       <c r="G169" t="n">
-        <v>0.6</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H169" t="inlineStr">
         <is>
@@ -7374,7 +7374,7 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
@@ -7383,7 +7383,7 @@
         </is>
       </c>
       <c r="G170" t="n">
-        <v>0.54</v>
+        <v>0.48</v>
       </c>
       <c r="H170" t="inlineStr">
         <is>
@@ -7424,7 +7424,7 @@
         </is>
       </c>
       <c r="G171" t="n">
-        <v>1.06</v>
+        <v>0.71</v>
       </c>
       <c r="H171" t="inlineStr">
         <is>
@@ -7465,7 +7465,7 @@
         </is>
       </c>
       <c r="G172" t="n">
-        <v>1.11</v>
+        <v>0.49</v>
       </c>
       <c r="H172" t="inlineStr">
         <is>
@@ -7506,7 +7506,7 @@
         </is>
       </c>
       <c r="G173" t="n">
-        <v>1.06</v>
+        <v>0.61</v>
       </c>
       <c r="H173" t="inlineStr">
         <is>
@@ -7538,7 +7538,7 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
@@ -7547,7 +7547,7 @@
         </is>
       </c>
       <c r="G174" t="n">
-        <v>0.93</v>
+        <v>1.05</v>
       </c>
       <c r="H174" t="inlineStr">
         <is>
@@ -7579,7 +7579,7 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
@@ -7588,7 +7588,7 @@
         </is>
       </c>
       <c r="G175" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="H175" t="inlineStr">
         <is>
@@ -7620,7 +7620,7 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
@@ -7629,7 +7629,7 @@
         </is>
       </c>
       <c r="G176" t="n">
-        <v>0.51</v>
+        <v>1.09</v>
       </c>
       <c r="H176" t="inlineStr">
         <is>
@@ -7661,7 +7661,7 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
@@ -7670,7 +7670,7 @@
         </is>
       </c>
       <c r="G177" t="n">
-        <v>0.57</v>
+        <v>0.86</v>
       </c>
       <c r="H177" t="inlineStr">
         <is>
@@ -7702,7 +7702,7 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
@@ -7711,7 +7711,7 @@
         </is>
       </c>
       <c r="G178" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="H178" t="inlineStr">
         <is>
@@ -7752,7 +7752,7 @@
         </is>
       </c>
       <c r="G179" t="n">
-        <v>0.78</v>
+        <v>0.61</v>
       </c>
       <c r="H179" t="inlineStr">
         <is>
@@ -7784,7 +7784,7 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
@@ -7793,7 +7793,7 @@
         </is>
       </c>
       <c r="G180" t="n">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="H180" t="inlineStr">
         <is>
@@ -7834,7 +7834,7 @@
         </is>
       </c>
       <c r="G181" t="n">
-        <v>0.89</v>
+        <v>0.52</v>
       </c>
       <c r="H181" t="inlineStr">
         <is>
@@ -7866,7 +7866,7 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
@@ -7875,7 +7875,7 @@
         </is>
       </c>
       <c r="G182" t="n">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="H182" t="inlineStr">
         <is>
@@ -7907,7 +7907,7 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
@@ -7948,7 +7948,7 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
@@ -7957,7 +7957,7 @@
         </is>
       </c>
       <c r="G184" t="n">
-        <v>0.42</v>
+        <v>1.11</v>
       </c>
       <c r="H184" t="inlineStr">
         <is>
@@ -7989,7 +7989,7 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
@@ -7998,7 +7998,7 @@
         </is>
       </c>
       <c r="G185" t="n">
-        <v>0.68</v>
+        <v>1.08</v>
       </c>
       <c r="H185" t="inlineStr">
         <is>
@@ -8030,7 +8030,7 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
@@ -8039,7 +8039,7 @@
         </is>
       </c>
       <c r="G186" t="n">
-        <v>0.52</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H186" t="inlineStr">
         <is>
@@ -8071,7 +8071,7 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
@@ -8080,7 +8080,7 @@
         </is>
       </c>
       <c r="G187" t="n">
-        <v>0.84</v>
+        <v>0.98</v>
       </c>
       <c r="H187" t="inlineStr">
         <is>
@@ -8112,7 +8112,7 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
@@ -8121,7 +8121,7 @@
         </is>
       </c>
       <c r="G188" t="n">
-        <v>0.62</v>
+        <v>0.65</v>
       </c>
       <c r="H188" t="inlineStr">
         <is>
@@ -8153,7 +8153,7 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
@@ -8162,7 +8162,7 @@
         </is>
       </c>
       <c r="G189" t="n">
-        <v>0.7</v>
+        <v>0.96</v>
       </c>
       <c r="H189" t="inlineStr">
         <is>
@@ -8194,7 +8194,7 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
@@ -8203,7 +8203,7 @@
         </is>
       </c>
       <c r="G190" t="n">
-        <v>0.95</v>
+        <v>0.99</v>
       </c>
       <c r="H190" t="inlineStr">
         <is>
@@ -8244,7 +8244,7 @@
         </is>
       </c>
       <c r="G191" t="n">
-        <v>1.11</v>
+        <v>0.73</v>
       </c>
       <c r="H191" t="inlineStr">
         <is>
@@ -8276,7 +8276,7 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
@@ -8285,7 +8285,7 @@
         </is>
       </c>
       <c r="G192" t="n">
-        <v>0.66</v>
+        <v>0.82</v>
       </c>
       <c r="H192" t="inlineStr">
         <is>
@@ -8326,7 +8326,7 @@
         </is>
       </c>
       <c r="G193" t="n">
-        <v>0.91</v>
+        <v>0.61</v>
       </c>
       <c r="H193" t="inlineStr">
         <is>
@@ -8367,7 +8367,7 @@
         </is>
       </c>
       <c r="G194" t="n">
-        <v>0.92</v>
+        <v>0.55</v>
       </c>
       <c r="H194" t="inlineStr">
         <is>
@@ -8399,7 +8399,7 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
@@ -8408,7 +8408,7 @@
         </is>
       </c>
       <c r="G195" t="n">
-        <v>0.53</v>
+        <v>1.07</v>
       </c>
       <c r="H195" t="inlineStr">
         <is>
@@ -8449,7 +8449,7 @@
         </is>
       </c>
       <c r="G196" t="n">
-        <v>0.59</v>
+        <v>0.61</v>
       </c>
       <c r="H196" t="inlineStr">
         <is>
@@ -8481,7 +8481,7 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
@@ -8490,7 +8490,7 @@
         </is>
       </c>
       <c r="G197" t="n">
-        <v>0.68</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H197" t="inlineStr">
         <is>
@@ -8522,7 +8522,7 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
@@ -8531,7 +8531,7 @@
         </is>
       </c>
       <c r="G198" t="n">
-        <v>0.87</v>
+        <v>0.5</v>
       </c>
       <c r="H198" t="inlineStr">
         <is>
@@ -8563,7 +8563,7 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
@@ -8572,7 +8572,7 @@
         </is>
       </c>
       <c r="G199" t="n">
-        <v>0.8</v>
+        <v>0.49</v>
       </c>
       <c r="H199" t="inlineStr">
         <is>
@@ -8604,7 +8604,7 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
@@ -8613,7 +8613,7 @@
         </is>
       </c>
       <c r="G200" t="n">
-        <v>0.68</v>
+        <v>1.05</v>
       </c>
       <c r="H200" t="inlineStr">
         <is>
@@ -8645,7 +8645,7 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
@@ -8654,7 +8654,7 @@
         </is>
       </c>
       <c r="G201" t="n">
-        <v>0.7</v>
+        <v>1.12</v>
       </c>
       <c r="H201" t="inlineStr">
         <is>
@@ -8686,7 +8686,7 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
@@ -8695,7 +8695,7 @@
         </is>
       </c>
       <c r="G202" t="n">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="H202" t="inlineStr">
         <is>
@@ -8727,7 +8727,7 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
@@ -8736,7 +8736,7 @@
         </is>
       </c>
       <c r="G203" t="n">
-        <v>0.92</v>
+        <v>0.62</v>
       </c>
       <c r="H203" t="inlineStr">
         <is>
@@ -8768,7 +8768,7 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
@@ -8777,7 +8777,7 @@
         </is>
       </c>
       <c r="G204" t="n">
-        <v>0.61</v>
+        <v>0.79</v>
       </c>
       <c r="H204" t="inlineStr">
         <is>
@@ -8809,7 +8809,7 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
@@ -8818,7 +8818,7 @@
         </is>
       </c>
       <c r="G205" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.83</v>
       </c>
       <c r="H205" t="inlineStr">
         <is>
@@ -8850,7 +8850,7 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
@@ -8859,7 +8859,7 @@
         </is>
       </c>
       <c r="G206" t="n">
-        <v>1.14</v>
+        <v>1.04</v>
       </c>
       <c r="H206" t="inlineStr">
         <is>
@@ -8900,7 +8900,7 @@
         </is>
       </c>
       <c r="G207" t="n">
-        <v>0.97</v>
+        <v>1.08</v>
       </c>
       <c r="H207" t="inlineStr">
         <is>
@@ -8932,7 +8932,7 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
@@ -8941,7 +8941,7 @@
         </is>
       </c>
       <c r="G208" t="n">
-        <v>1.14</v>
+        <v>0.48</v>
       </c>
       <c r="H208" t="inlineStr">
         <is>
@@ -8982,7 +8982,7 @@
         </is>
       </c>
       <c r="G209" t="n">
-        <v>0.46</v>
+        <v>1</v>
       </c>
       <c r="H209" t="inlineStr">
         <is>
@@ -9023,7 +9023,7 @@
         </is>
       </c>
       <c r="G210" t="n">
-        <v>0.7</v>
+        <v>0.43</v>
       </c>
       <c r="H210" t="inlineStr">
         <is>
@@ -9064,7 +9064,7 @@
         </is>
       </c>
       <c r="G211" t="n">
-        <v>0.91</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H211" t="inlineStr">
         <is>
@@ -9105,7 +9105,7 @@
         </is>
       </c>
       <c r="G212" t="n">
-        <v>1.02</v>
+        <v>0.42</v>
       </c>
       <c r="H212" t="inlineStr">
         <is>
@@ -9137,7 +9137,7 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
@@ -9146,7 +9146,7 @@
         </is>
       </c>
       <c r="G213" t="n">
-        <v>0.48</v>
+        <v>0.78</v>
       </c>
       <c r="H213" t="inlineStr">
         <is>
@@ -9178,7 +9178,7 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
@@ -9187,7 +9187,7 @@
         </is>
       </c>
       <c r="G214" t="n">
-        <v>0.53</v>
+        <v>0.75</v>
       </c>
       <c r="H214" t="inlineStr">
         <is>
@@ -9219,7 +9219,7 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
@@ -9228,7 +9228,7 @@
         </is>
       </c>
       <c r="G215" t="n">
-        <v>0.93</v>
+        <v>1.14</v>
       </c>
       <c r="H215" t="inlineStr">
         <is>
@@ -9260,7 +9260,7 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
@@ -9269,7 +9269,7 @@
         </is>
       </c>
       <c r="G216" t="n">
-        <v>1.05</v>
+        <v>0.7</v>
       </c>
       <c r="H216" t="inlineStr">
         <is>
@@ -9301,7 +9301,7 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
@@ -9310,7 +9310,7 @@
         </is>
       </c>
       <c r="G217" t="n">
-        <v>1.04</v>
+        <v>0.64</v>
       </c>
       <c r="H217" t="inlineStr">
         <is>
@@ -9342,7 +9342,7 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
@@ -9351,7 +9351,7 @@
         </is>
       </c>
       <c r="G218" t="n">
-        <v>0.66</v>
+        <v>1.03</v>
       </c>
       <c r="H218" t="inlineStr">
         <is>
@@ -9383,7 +9383,7 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
@@ -9392,7 +9392,7 @@
         </is>
       </c>
       <c r="G219" t="n">
-        <v>0.99</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H219" t="inlineStr">
         <is>
@@ -9433,7 +9433,7 @@
         </is>
       </c>
       <c r="G220" t="n">
-        <v>1.1</v>
+        <v>0.51</v>
       </c>
       <c r="H220" t="inlineStr">
         <is>
@@ -9465,7 +9465,7 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
@@ -9474,7 +9474,7 @@
         </is>
       </c>
       <c r="G221" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.77</v>
       </c>
       <c r="H221" t="inlineStr">
         <is>
@@ -9515,7 +9515,7 @@
         </is>
       </c>
       <c r="G222" t="n">
-        <v>1.12</v>
+        <v>1.01</v>
       </c>
       <c r="H222" t="inlineStr">
         <is>
@@ -9547,7 +9547,7 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
@@ -9556,7 +9556,7 @@
         </is>
       </c>
       <c r="G223" t="n">
-        <v>0.62</v>
+        <v>0.73</v>
       </c>
       <c r="H223" t="inlineStr">
         <is>
@@ -9588,7 +9588,7 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
@@ -9597,7 +9597,7 @@
         </is>
       </c>
       <c r="G224" t="n">
-        <v>0.51</v>
+        <v>0.64</v>
       </c>
       <c r="H224" t="inlineStr">
         <is>
@@ -9629,7 +9629,7 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
@@ -9638,7 +9638,7 @@
         </is>
       </c>
       <c r="G225" t="n">
-        <v>1.05</v>
+        <v>0.73</v>
       </c>
       <c r="H225" t="inlineStr">
         <is>
@@ -9670,7 +9670,7 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
@@ -9679,7 +9679,7 @@
         </is>
       </c>
       <c r="G226" t="n">
-        <v>0.85</v>
+        <v>1.04</v>
       </c>
       <c r="H226" t="inlineStr">
         <is>
@@ -9720,7 +9720,7 @@
         </is>
       </c>
       <c r="G227" t="n">
-        <v>0.42</v>
+        <v>0.47</v>
       </c>
       <c r="H227" t="inlineStr">
         <is>
@@ -9752,7 +9752,7 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
@@ -9761,7 +9761,7 @@
         </is>
       </c>
       <c r="G228" t="n">
-        <v>0.82</v>
+        <v>0.54</v>
       </c>
       <c r="H228" t="inlineStr">
         <is>
@@ -9793,7 +9793,7 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
@@ -9802,7 +9802,7 @@
         </is>
       </c>
       <c r="G229" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.77</v>
       </c>
       <c r="H229" t="inlineStr">
         <is>
@@ -9834,7 +9834,7 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
@@ -9843,7 +9843,7 @@
         </is>
       </c>
       <c r="G230" t="n">
-        <v>0.73</v>
+        <v>0.92</v>
       </c>
       <c r="H230" t="inlineStr">
         <is>
@@ -9884,7 +9884,7 @@
         </is>
       </c>
       <c r="G231" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="H231" t="inlineStr">
         <is>
@@ -9916,7 +9916,7 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
@@ -9925,7 +9925,7 @@
         </is>
       </c>
       <c r="G232" t="n">
-        <v>0.76</v>
+        <v>0.96</v>
       </c>
       <c r="H232" t="inlineStr">
         <is>
@@ -9957,7 +9957,7 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
@@ -9966,7 +9966,7 @@
         </is>
       </c>
       <c r="G233" t="n">
-        <v>0.55</v>
+        <v>0.74</v>
       </c>
       <c r="H233" t="inlineStr">
         <is>
@@ -10007,7 +10007,7 @@
         </is>
       </c>
       <c r="G234" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="H234" t="inlineStr">
         <is>
@@ -10048,7 +10048,7 @@
         </is>
       </c>
       <c r="G235" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="H235" t="inlineStr">
         <is>
@@ -10080,7 +10080,7 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
@@ -10089,7 +10089,7 @@
         </is>
       </c>
       <c r="G236" t="n">
-        <v>1.11</v>
+        <v>0.92</v>
       </c>
       <c r="H236" t="inlineStr">
         <is>
@@ -10121,7 +10121,7 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
@@ -10130,7 +10130,7 @@
         </is>
       </c>
       <c r="G237" t="n">
-        <v>0.73</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H237" t="inlineStr">
         <is>
@@ -10162,7 +10162,7 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
@@ -10171,7 +10171,7 @@
         </is>
       </c>
       <c r="G238" t="n">
-        <v>0.52</v>
+        <v>1.15</v>
       </c>
       <c r="H238" t="inlineStr">
         <is>
@@ -10203,7 +10203,7 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
@@ -10212,7 +10212,7 @@
         </is>
       </c>
       <c r="G239" t="n">
-        <v>0.98</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H239" t="inlineStr">
         <is>
@@ -10253,7 +10253,7 @@
         </is>
       </c>
       <c r="G240" t="n">
-        <v>0.78</v>
+        <v>0.54</v>
       </c>
       <c r="H240" t="inlineStr">
         <is>
@@ -10285,7 +10285,7 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
@@ -10294,7 +10294,7 @@
         </is>
       </c>
       <c r="G241" t="n">
-        <v>0.72</v>
+        <v>0.79</v>
       </c>
       <c r="H241" t="inlineStr">
         <is>
@@ -10326,7 +10326,7 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
@@ -10335,7 +10335,7 @@
         </is>
       </c>
       <c r="G242" t="n">
-        <v>0.83</v>
+        <v>0.84</v>
       </c>
       <c r="H242" t="inlineStr">
         <is>
@@ -10367,7 +10367,7 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
@@ -10376,7 +10376,7 @@
         </is>
       </c>
       <c r="G243" t="n">
-        <v>1.07</v>
+        <v>0.57</v>
       </c>
       <c r="H243" t="inlineStr">
         <is>
@@ -10417,7 +10417,7 @@
         </is>
       </c>
       <c r="G244" t="n">
-        <v>0.43</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H244" t="inlineStr">
         <is>
@@ -10449,7 +10449,7 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
@@ -10458,7 +10458,7 @@
         </is>
       </c>
       <c r="G245" t="n">
-        <v>1.11</v>
+        <v>0.77</v>
       </c>
       <c r="H245" t="inlineStr">
         <is>
@@ -10490,7 +10490,7 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
@@ -10499,7 +10499,7 @@
         </is>
       </c>
       <c r="G246" t="n">
-        <v>0.58</v>
+        <v>0.84</v>
       </c>
       <c r="H246" t="inlineStr">
         <is>
@@ -10531,7 +10531,7 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
@@ -10540,7 +10540,7 @@
         </is>
       </c>
       <c r="G247" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="H247" t="inlineStr">
         <is>
@@ -10572,7 +10572,7 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
@@ -10581,7 +10581,7 @@
         </is>
       </c>
       <c r="G248" t="n">
-        <v>0.51</v>
+        <v>0.48</v>
       </c>
       <c r="H248" t="inlineStr">
         <is>
@@ -10613,7 +10613,7 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
@@ -10622,7 +10622,7 @@
         </is>
       </c>
       <c r="G249" t="n">
-        <v>0.74</v>
+        <v>1.02</v>
       </c>
       <c r="H249" t="inlineStr">
         <is>
@@ -10654,7 +10654,7 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
@@ -10663,7 +10663,7 @@
         </is>
       </c>
       <c r="G250" t="n">
-        <v>0.89</v>
+        <v>0.48</v>
       </c>
       <c r="H250" t="inlineStr">
         <is>
@@ -10704,7 +10704,7 @@
         </is>
       </c>
       <c r="G251" t="n">
-        <v>0.98</v>
+        <v>0.82</v>
       </c>
       <c r="H251" t="inlineStr">
         <is>
@@ -10745,7 +10745,7 @@
         </is>
       </c>
       <c r="G252" t="n">
-        <v>0.84</v>
+        <v>0.74</v>
       </c>
       <c r="H252" t="inlineStr">
         <is>
@@ -10777,7 +10777,7 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
@@ -10786,7 +10786,7 @@
         </is>
       </c>
       <c r="G253" t="n">
-        <v>1.11</v>
+        <v>0.82</v>
       </c>
       <c r="H253" t="inlineStr">
         <is>
@@ -10818,7 +10818,7 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
@@ -10827,7 +10827,7 @@
         </is>
       </c>
       <c r="G254" t="n">
-        <v>0.42</v>
+        <v>0.53</v>
       </c>
       <c r="H254" t="inlineStr">
         <is>
@@ -10859,7 +10859,7 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
@@ -10868,7 +10868,7 @@
         </is>
       </c>
       <c r="G255" t="n">
-        <v>0.83</v>
+        <v>0.55</v>
       </c>
       <c r="H255" t="inlineStr">
         <is>
@@ -10900,7 +10900,7 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
@@ -10909,7 +10909,7 @@
         </is>
       </c>
       <c r="G256" t="n">
-        <v>1</v>
+        <v>0.98</v>
       </c>
       <c r="H256" t="inlineStr">
         <is>
@@ -10950,7 +10950,7 @@
         </is>
       </c>
       <c r="G257" t="n">
-        <v>1.07</v>
+        <v>0.44</v>
       </c>
       <c r="H257" t="inlineStr">
         <is>
@@ -10982,7 +10982,7 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
@@ -10991,7 +10991,7 @@
         </is>
       </c>
       <c r="G258" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="H258" t="inlineStr">
         <is>
@@ -11023,7 +11023,7 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
@@ -11032,7 +11032,7 @@
         </is>
       </c>
       <c r="G259" t="n">
-        <v>0.93</v>
+        <v>0.65</v>
       </c>
       <c r="H259" t="inlineStr">
         <is>
@@ -11064,7 +11064,7 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
@@ -11073,7 +11073,7 @@
         </is>
       </c>
       <c r="G260" t="n">
-        <v>0.59</v>
+        <v>0.52</v>
       </c>
       <c r="H260" t="inlineStr">
         <is>
@@ -11105,7 +11105,7 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
@@ -11114,7 +11114,7 @@
         </is>
       </c>
       <c r="G261" t="n">
-        <v>0.64</v>
+        <v>0.95</v>
       </c>
       <c r="H261" t="inlineStr">
         <is>
@@ -11146,7 +11146,7 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
@@ -11155,7 +11155,7 @@
         </is>
       </c>
       <c r="G262" t="n">
-        <v>0.8</v>
+        <v>0.54</v>
       </c>
       <c r="H262" t="inlineStr">
         <is>
@@ -11196,7 +11196,7 @@
         </is>
       </c>
       <c r="G263" t="n">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="H263" t="inlineStr">
         <is>
@@ -11228,7 +11228,7 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
@@ -11237,7 +11237,7 @@
         </is>
       </c>
       <c r="G264" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.48</v>
       </c>
       <c r="H264" t="inlineStr">
         <is>
@@ -11269,7 +11269,7 @@
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
@@ -11278,7 +11278,7 @@
         </is>
       </c>
       <c r="G265" t="n">
-        <v>0.53</v>
+        <v>0.57</v>
       </c>
       <c r="H265" t="inlineStr">
         <is>
@@ -11310,7 +11310,7 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
@@ -11319,7 +11319,7 @@
         </is>
       </c>
       <c r="G266" t="n">
-        <v>0.61</v>
+        <v>0.8</v>
       </c>
       <c r="H266" t="inlineStr">
         <is>
@@ -11351,7 +11351,7 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
@@ -11360,7 +11360,7 @@
         </is>
       </c>
       <c r="G267" t="n">
-        <v>0.44</v>
+        <v>0.67</v>
       </c>
       <c r="H267" t="inlineStr">
         <is>
@@ -11392,7 +11392,7 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
@@ -11401,7 +11401,7 @@
         </is>
       </c>
       <c r="G268" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="H268" t="inlineStr">
         <is>
@@ -11442,7 +11442,7 @@
         </is>
       </c>
       <c r="G269" t="n">
-        <v>1.09</v>
+        <v>0.87</v>
       </c>
       <c r="H269" t="inlineStr">
         <is>
@@ -11474,7 +11474,7 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
@@ -11483,7 +11483,7 @@
         </is>
       </c>
       <c r="G270" t="n">
-        <v>0.49</v>
+        <v>0.51</v>
       </c>
       <c r="H270" t="inlineStr">
         <is>
@@ -11515,7 +11515,7 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
@@ -11524,7 +11524,7 @@
         </is>
       </c>
       <c r="G271" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="H271" t="inlineStr">
         <is>
@@ -11556,7 +11556,7 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
@@ -11565,7 +11565,7 @@
         </is>
       </c>
       <c r="G272" t="n">
-        <v>0.55</v>
+        <v>0.53</v>
       </c>
       <c r="H272" t="inlineStr">
         <is>
@@ -11597,7 +11597,7 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
@@ -11606,7 +11606,7 @@
         </is>
       </c>
       <c r="G273" t="n">
-        <v>0.68</v>
+        <v>0.6</v>
       </c>
       <c r="H273" t="inlineStr">
         <is>
@@ -11638,7 +11638,7 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
@@ -11647,7 +11647,7 @@
         </is>
       </c>
       <c r="G274" t="n">
-        <v>1.12</v>
+        <v>0.95</v>
       </c>
       <c r="H274" t="inlineStr">
         <is>
@@ -11679,7 +11679,7 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
@@ -11688,7 +11688,7 @@
         </is>
       </c>
       <c r="G275" t="n">
-        <v>0.42</v>
+        <v>0.6</v>
       </c>
       <c r="H275" t="inlineStr">
         <is>
@@ -11720,7 +11720,7 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
@@ -11729,7 +11729,7 @@
         </is>
       </c>
       <c r="G276" t="n">
-        <v>0.52</v>
+        <v>0.54</v>
       </c>
       <c r="H276" t="inlineStr">
         <is>
@@ -11770,7 +11770,7 @@
         </is>
       </c>
       <c r="G277" t="n">
-        <v>1.12</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H277" t="inlineStr">
         <is>
@@ -11802,7 +11802,7 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
@@ -11811,7 +11811,7 @@
         </is>
       </c>
       <c r="G278" t="n">
-        <v>0.82</v>
+        <v>0.46</v>
       </c>
       <c r="H278" t="inlineStr">
         <is>
@@ -11843,7 +11843,7 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
@@ -11852,7 +11852,7 @@
         </is>
       </c>
       <c r="G279" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.09</v>
       </c>
       <c r="H279" t="inlineStr">
         <is>
@@ -11884,7 +11884,7 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
@@ -11893,7 +11893,7 @@
         </is>
       </c>
       <c r="G280" t="n">
-        <v>1.05</v>
+        <v>0.61</v>
       </c>
       <c r="H280" t="inlineStr">
         <is>
@@ -11934,7 +11934,7 @@
         </is>
       </c>
       <c r="G281" t="n">
-        <v>0.77</v>
+        <v>0.98</v>
       </c>
       <c r="H281" t="inlineStr">
         <is>
@@ -11966,7 +11966,7 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
@@ -11975,7 +11975,7 @@
         </is>
       </c>
       <c r="G282" t="n">
-        <v>0.46</v>
+        <v>1.08</v>
       </c>
       <c r="H282" t="inlineStr">
         <is>
@@ -12007,7 +12007,7 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
@@ -12016,7 +12016,7 @@
         </is>
       </c>
       <c r="G283" t="n">
-        <v>0.43</v>
+        <v>0.54</v>
       </c>
       <c r="H283" t="inlineStr">
         <is>
@@ -12048,7 +12048,7 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
@@ -12057,7 +12057,7 @@
         </is>
       </c>
       <c r="G284" t="n">
-        <v>0.75</v>
+        <v>1.04</v>
       </c>
       <c r="H284" t="inlineStr">
         <is>
@@ -12089,7 +12089,7 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
@@ -12098,7 +12098,7 @@
         </is>
       </c>
       <c r="G285" t="n">
-        <v>0.71</v>
+        <v>0.95</v>
       </c>
       <c r="H285" t="inlineStr">
         <is>
@@ -12139,7 +12139,7 @@
         </is>
       </c>
       <c r="G286" t="n">
-        <v>0.96</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H286" t="inlineStr">
         <is>
@@ -12171,7 +12171,7 @@
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
@@ -12180,7 +12180,7 @@
         </is>
       </c>
       <c r="G287" t="n">
-        <v>0.62</v>
+        <v>0.54</v>
       </c>
       <c r="H287" t="inlineStr">
         <is>
@@ -12212,7 +12212,7 @@
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
@@ -12221,7 +12221,7 @@
         </is>
       </c>
       <c r="G288" t="n">
-        <v>0.62</v>
+        <v>0.9</v>
       </c>
       <c r="H288" t="inlineStr">
         <is>
@@ -12253,7 +12253,7 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
@@ -12262,7 +12262,7 @@
         </is>
       </c>
       <c r="G289" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="H289" t="inlineStr">
         <is>
@@ -12294,7 +12294,7 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
@@ -12303,7 +12303,7 @@
         </is>
       </c>
       <c r="G290" t="n">
-        <v>0.42</v>
+        <v>1.05</v>
       </c>
       <c r="H290" t="inlineStr">
         <is>
@@ -12335,7 +12335,7 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
@@ -12344,7 +12344,7 @@
         </is>
       </c>
       <c r="G291" t="n">
-        <v>0.47</v>
+        <v>0.89</v>
       </c>
       <c r="H291" t="inlineStr">
         <is>
@@ -12376,7 +12376,7 @@
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
@@ -12385,7 +12385,7 @@
         </is>
       </c>
       <c r="G292" t="n">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="H292" t="inlineStr">
         <is>
@@ -12426,7 +12426,7 @@
         </is>
       </c>
       <c r="G293" t="n">
-        <v>0.92</v>
+        <v>0.73</v>
       </c>
       <c r="H293" t="inlineStr">
         <is>
@@ -12467,7 +12467,7 @@
         </is>
       </c>
       <c r="G294" t="n">
-        <v>1.11</v>
+        <v>0.67</v>
       </c>
       <c r="H294" t="inlineStr">
         <is>
@@ -12499,7 +12499,7 @@
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
@@ -12508,7 +12508,7 @@
         </is>
       </c>
       <c r="G295" t="n">
-        <v>0.87</v>
+        <v>0.53</v>
       </c>
       <c r="H295" t="inlineStr">
         <is>
@@ -12540,7 +12540,7 @@
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
@@ -12549,7 +12549,7 @@
         </is>
       </c>
       <c r="G296" t="n">
-        <v>0.89</v>
+        <v>0.98</v>
       </c>
       <c r="H296" t="inlineStr">
         <is>
@@ -12581,7 +12581,7 @@
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
@@ -12590,7 +12590,7 @@
         </is>
       </c>
       <c r="G297" t="n">
-        <v>1.06</v>
+        <v>0.86</v>
       </c>
       <c r="H297" t="inlineStr">
         <is>
@@ -12622,7 +12622,7 @@
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
@@ -12631,7 +12631,7 @@
         </is>
       </c>
       <c r="G298" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="H298" t="inlineStr">
         <is>
@@ -12663,7 +12663,7 @@
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F299" t="inlineStr">
@@ -12672,7 +12672,7 @@
         </is>
       </c>
       <c r="G299" t="n">
-        <v>0.79</v>
+        <v>0.7</v>
       </c>
       <c r="H299" t="inlineStr">
         <is>
@@ -12704,7 +12704,7 @@
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
@@ -12713,7 +12713,7 @@
         </is>
       </c>
       <c r="G300" t="n">
-        <v>0.62</v>
+        <v>0.58</v>
       </c>
       <c r="H300" t="inlineStr">
         <is>
@@ -12754,7 +12754,7 @@
         </is>
       </c>
       <c r="G301" t="n">
-        <v>0.57</v>
+        <v>0.73</v>
       </c>
       <c r="H301" t="inlineStr">
         <is>

--- a/reports/Passed_Test_Cases.xlsx
+++ b/reports/Passed_Test_Cases.xlsx
@@ -486,7 +486,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -495,7 +495,7 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0.93</v>
+        <v>0.54</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -527,7 +527,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0.47</v>
+        <v>0.71</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -568,7 +568,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -577,7 +577,7 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0.85</v>
+        <v>1.02</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -609,7 +609,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -618,7 +618,7 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>1.05</v>
+        <v>0.88</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -650,7 +650,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>0.58</v>
+        <v>0.43</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -700,7 +700,7 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>0.63</v>
+        <v>0.67</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -732,7 +732,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -741,7 +741,7 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>1.13</v>
+        <v>0.7</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -782,7 +782,7 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -814,7 +814,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -823,7 +823,7 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>1.01</v>
+        <v>0.44</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -855,7 +855,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -905,7 +905,7 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>0.53</v>
+        <v>0.79</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -937,7 +937,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -946,7 +946,7 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>0.96</v>
+        <v>0.76</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -978,7 +978,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -987,7 +987,7 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>0.74</v>
+        <v>0.55</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1028,7 +1028,7 @@
         </is>
       </c>
       <c r="G15" t="n">
-        <v>0.8</v>
+        <v>1.05</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -1069,7 +1069,7 @@
         </is>
       </c>
       <c r="G16" t="n">
-        <v>0.99</v>
+        <v>1.04</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -1101,7 +1101,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1110,7 +1110,7 @@
         </is>
       </c>
       <c r="G17" t="n">
-        <v>0.89</v>
+        <v>0.43</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -1142,7 +1142,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1151,7 +1151,7 @@
         </is>
       </c>
       <c r="G18" t="n">
-        <v>0.83</v>
+        <v>0.79</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -1192,7 +1192,7 @@
         </is>
       </c>
       <c r="G19" t="n">
-        <v>1.11</v>
+        <v>0.79</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1233,7 +1233,7 @@
         </is>
       </c>
       <c r="G20" t="n">
-        <v>1.13</v>
+        <v>0.59</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -1265,7 +1265,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1274,7 +1274,7 @@
         </is>
       </c>
       <c r="G21" t="n">
-        <v>0.43</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -1315,7 +1315,7 @@
         </is>
       </c>
       <c r="G22" t="n">
-        <v>0.91</v>
+        <v>1.14</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
@@ -1347,7 +1347,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1356,7 +1356,7 @@
         </is>
       </c>
       <c r="G23" t="n">
-        <v>1.14</v>
+        <v>0.88</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1397,7 +1397,7 @@
         </is>
       </c>
       <c r="G24" t="n">
-        <v>0.93</v>
+        <v>0.46</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
@@ -1429,7 +1429,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1438,7 +1438,7 @@
         </is>
       </c>
       <c r="G25" t="n">
-        <v>0.76</v>
+        <v>0.47</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
@@ -1470,7 +1470,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1479,7 +1479,7 @@
         </is>
       </c>
       <c r="G26" t="n">
-        <v>0.51</v>
+        <v>0.97</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
@@ -1511,7 +1511,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1520,7 +1520,7 @@
         </is>
       </c>
       <c r="G27" t="n">
-        <v>0.62</v>
+        <v>0.92</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
@@ -1561,7 +1561,7 @@
         </is>
       </c>
       <c r="G28" t="n">
-        <v>0.93</v>
+        <v>0.55</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
@@ -1602,7 +1602,7 @@
         </is>
       </c>
       <c r="G29" t="n">
-        <v>0.89</v>
+        <v>0.47</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
@@ -1634,7 +1634,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1643,7 +1643,7 @@
         </is>
       </c>
       <c r="G30" t="n">
-        <v>0.55</v>
+        <v>0.48</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
@@ -1675,7 +1675,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1684,7 +1684,7 @@
         </is>
       </c>
       <c r="G31" t="n">
-        <v>0.52</v>
+        <v>0.86</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
@@ -1716,7 +1716,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1725,7 +1725,7 @@
         </is>
       </c>
       <c r="G32" t="n">
-        <v>0.77</v>
+        <v>0.72</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
@@ -1766,7 +1766,7 @@
         </is>
       </c>
       <c r="G33" t="n">
-        <v>1.1</v>
+        <v>0.68</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
@@ -1798,7 +1798,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1807,7 +1807,7 @@
         </is>
       </c>
       <c r="G34" t="n">
-        <v>0.85</v>
+        <v>0.7</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
@@ -1839,7 +1839,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1848,7 +1848,7 @@
         </is>
       </c>
       <c r="G35" t="n">
-        <v>1.05</v>
+        <v>0.43</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
@@ -1880,7 +1880,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1889,7 +1889,7 @@
         </is>
       </c>
       <c r="G36" t="n">
-        <v>0.83</v>
+        <v>0.62</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
@@ -1930,7 +1930,7 @@
         </is>
       </c>
       <c r="G37" t="n">
-        <v>1.12</v>
+        <v>0.53</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
@@ -1962,7 +1962,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1971,7 +1971,7 @@
         </is>
       </c>
       <c r="G38" t="n">
-        <v>0.98</v>
+        <v>1.15</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
@@ -2012,7 +2012,7 @@
         </is>
       </c>
       <c r="G39" t="n">
-        <v>0.57</v>
+        <v>1.12</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
@@ -2044,7 +2044,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -2053,7 +2053,7 @@
         </is>
       </c>
       <c r="G40" t="n">
-        <v>0.47</v>
+        <v>0.74</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
@@ -2085,7 +2085,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -2094,7 +2094,7 @@
         </is>
       </c>
       <c r="G41" t="n">
-        <v>1.12</v>
+        <v>0.46</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
@@ -2126,7 +2126,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -2135,7 +2135,7 @@
         </is>
       </c>
       <c r="G42" t="n">
-        <v>1.04</v>
+        <v>0.54</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
@@ -2167,7 +2167,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -2176,7 +2176,7 @@
         </is>
       </c>
       <c r="G43" t="n">
-        <v>0.67</v>
+        <v>0.98</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
@@ -2208,7 +2208,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -2217,7 +2217,7 @@
         </is>
       </c>
       <c r="G44" t="n">
-        <v>0.61</v>
+        <v>0.83</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
@@ -2249,7 +2249,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2258,7 +2258,7 @@
         </is>
       </c>
       <c r="G45" t="n">
-        <v>0.65</v>
+        <v>1.06</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
@@ -2299,7 +2299,7 @@
         </is>
       </c>
       <c r="G46" t="n">
-        <v>0.44</v>
+        <v>0.63</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
@@ -2331,7 +2331,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2340,7 +2340,7 @@
         </is>
       </c>
       <c r="G47" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
@@ -2372,7 +2372,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2381,7 +2381,7 @@
         </is>
       </c>
       <c r="G48" t="n">
-        <v>0.76</v>
+        <v>1.13</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
@@ -2413,7 +2413,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2422,7 +2422,7 @@
         </is>
       </c>
       <c r="G49" t="n">
-        <v>1.14</v>
+        <v>0.5</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
@@ -2454,7 +2454,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2463,7 +2463,7 @@
         </is>
       </c>
       <c r="G50" t="n">
-        <v>0.92</v>
+        <v>0.64</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
@@ -2495,7 +2495,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2504,7 +2504,7 @@
         </is>
       </c>
       <c r="G51" t="n">
-        <v>0.93</v>
+        <v>1.06</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
@@ -2536,7 +2536,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2545,7 +2545,7 @@
         </is>
       </c>
       <c r="G52" t="n">
-        <v>0.46</v>
+        <v>1</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
@@ -2586,7 +2586,7 @@
         </is>
       </c>
       <c r="G53" t="n">
-        <v>0.53</v>
+        <v>1</v>
       </c>
       <c r="H53" t="inlineStr">
         <is>
@@ -2627,7 +2627,7 @@
         </is>
       </c>
       <c r="G54" t="n">
-        <v>0.82</v>
+        <v>0.55</v>
       </c>
       <c r="H54" t="inlineStr">
         <is>
@@ -2659,7 +2659,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2668,7 +2668,7 @@
         </is>
       </c>
       <c r="G55" t="n">
-        <v>1.05</v>
+        <v>0.72</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
@@ -2700,7 +2700,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2709,7 +2709,7 @@
         </is>
       </c>
       <c r="G56" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
@@ -2741,7 +2741,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2750,7 +2750,7 @@
         </is>
       </c>
       <c r="G57" t="n">
-        <v>1.14</v>
+        <v>0.5</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
@@ -2791,7 +2791,7 @@
         </is>
       </c>
       <c r="G58" t="n">
-        <v>0.79</v>
+        <v>0.71</v>
       </c>
       <c r="H58" t="inlineStr">
         <is>
@@ -2832,7 +2832,7 @@
         </is>
       </c>
       <c r="G59" t="n">
-        <v>0.42</v>
+        <v>1.03</v>
       </c>
       <c r="H59" t="inlineStr">
         <is>
@@ -2864,7 +2864,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2873,7 +2873,7 @@
         </is>
       </c>
       <c r="G60" t="n">
-        <v>0.99</v>
+        <v>0.76</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
@@ -2905,7 +2905,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2914,7 +2914,7 @@
         </is>
       </c>
       <c r="G61" t="n">
-        <v>0.92</v>
+        <v>1.12</v>
       </c>
       <c r="H61" t="inlineStr">
         <is>
@@ -2946,7 +2946,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2955,7 +2955,7 @@
         </is>
       </c>
       <c r="G62" t="n">
-        <v>0.71</v>
+        <v>1.07</v>
       </c>
       <c r="H62" t="inlineStr">
         <is>
@@ -2987,7 +2987,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2996,7 +2996,7 @@
         </is>
       </c>
       <c r="G63" t="n">
-        <v>0.87</v>
+        <v>0.47</v>
       </c>
       <c r="H63" t="inlineStr">
         <is>
@@ -3028,7 +3028,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -3037,7 +3037,7 @@
         </is>
       </c>
       <c r="G64" t="n">
-        <v>0.51</v>
+        <v>1.07</v>
       </c>
       <c r="H64" t="inlineStr">
         <is>
@@ -3069,7 +3069,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -3078,7 +3078,7 @@
         </is>
       </c>
       <c r="G65" t="n">
-        <v>0.63</v>
+        <v>1.12</v>
       </c>
       <c r="H65" t="inlineStr">
         <is>
@@ -3119,7 +3119,7 @@
         </is>
       </c>
       <c r="G66" t="n">
-        <v>0.68</v>
+        <v>0.52</v>
       </c>
       <c r="H66" t="inlineStr">
         <is>
@@ -3151,7 +3151,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -3160,7 +3160,7 @@
         </is>
       </c>
       <c r="G67" t="n">
-        <v>0.64</v>
+        <v>0.84</v>
       </c>
       <c r="H67" t="inlineStr">
         <is>
@@ -3192,7 +3192,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -3201,7 +3201,7 @@
         </is>
       </c>
       <c r="G68" t="n">
-        <v>0.53</v>
+        <v>0.98</v>
       </c>
       <c r="H68" t="inlineStr">
         <is>
@@ -3233,7 +3233,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -3242,7 +3242,7 @@
         </is>
       </c>
       <c r="G69" t="n">
-        <v>0.89</v>
+        <v>0.91</v>
       </c>
       <c r="H69" t="inlineStr">
         <is>
@@ -3283,7 +3283,7 @@
         </is>
       </c>
       <c r="G70" t="n">
-        <v>0.44</v>
+        <v>0.84</v>
       </c>
       <c r="H70" t="inlineStr">
         <is>
@@ -3315,7 +3315,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -3324,7 +3324,7 @@
         </is>
       </c>
       <c r="G71" t="n">
-        <v>0.44</v>
+        <v>0.87</v>
       </c>
       <c r="H71" t="inlineStr">
         <is>
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -3365,7 +3365,7 @@
         </is>
       </c>
       <c r="G72" t="n">
-        <v>1.09</v>
+        <v>0.54</v>
       </c>
       <c r="H72" t="inlineStr">
         <is>
@@ -3397,7 +3397,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -3406,7 +3406,7 @@
         </is>
       </c>
       <c r="G73" t="n">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="H73" t="inlineStr">
         <is>
@@ -3438,7 +3438,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3447,7 +3447,7 @@
         </is>
       </c>
       <c r="G74" t="n">
-        <v>0.73</v>
+        <v>0.98</v>
       </c>
       <c r="H74" t="inlineStr">
         <is>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3488,7 +3488,7 @@
         </is>
       </c>
       <c r="G75" t="n">
-        <v>0.64</v>
+        <v>0.46</v>
       </c>
       <c r="H75" t="inlineStr">
         <is>
@@ -3520,7 +3520,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3529,7 +3529,7 @@
         </is>
       </c>
       <c r="G76" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.97</v>
       </c>
       <c r="H76" t="inlineStr">
         <is>
@@ -3561,7 +3561,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3570,7 +3570,7 @@
         </is>
       </c>
       <c r="G77" t="n">
-        <v>0.97</v>
+        <v>0.43</v>
       </c>
       <c r="H77" t="inlineStr">
         <is>
@@ -3602,7 +3602,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3611,7 +3611,7 @@
         </is>
       </c>
       <c r="G78" t="n">
-        <v>0.72</v>
+        <v>0.61</v>
       </c>
       <c r="H78" t="inlineStr">
         <is>
@@ -3643,7 +3643,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3652,7 +3652,7 @@
         </is>
       </c>
       <c r="G79" t="n">
-        <v>0.45</v>
+        <v>0.89</v>
       </c>
       <c r="H79" t="inlineStr">
         <is>
@@ -3684,7 +3684,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3693,7 +3693,7 @@
         </is>
       </c>
       <c r="G80" t="n">
-        <v>0.72</v>
+        <v>0.54</v>
       </c>
       <c r="H80" t="inlineStr">
         <is>
@@ -3725,7 +3725,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3734,7 +3734,7 @@
         </is>
       </c>
       <c r="G81" t="n">
-        <v>0.87</v>
+        <v>1.12</v>
       </c>
       <c r="H81" t="inlineStr">
         <is>
@@ -3775,7 +3775,7 @@
         </is>
       </c>
       <c r="G82" t="n">
-        <v>1.14</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H82" t="inlineStr">
         <is>
@@ -3816,7 +3816,7 @@
         </is>
       </c>
       <c r="G83" t="n">
-        <v>1.13</v>
+        <v>0.53</v>
       </c>
       <c r="H83" t="inlineStr">
         <is>
@@ -3857,7 +3857,7 @@
         </is>
       </c>
       <c r="G84" t="n">
-        <v>0.8</v>
+        <v>0.45</v>
       </c>
       <c r="H84" t="inlineStr">
         <is>
@@ -3889,7 +3889,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3898,7 +3898,7 @@
         </is>
       </c>
       <c r="G85" t="n">
-        <v>0.59</v>
+        <v>0.99</v>
       </c>
       <c r="H85" t="inlineStr">
         <is>
@@ -3930,7 +3930,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3939,7 +3939,7 @@
         </is>
       </c>
       <c r="G86" t="n">
-        <v>1.06</v>
+        <v>0.85</v>
       </c>
       <c r="H86" t="inlineStr">
         <is>
@@ -3971,7 +3971,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3980,7 +3980,7 @@
         </is>
       </c>
       <c r="G87" t="n">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="H87" t="inlineStr">
         <is>
@@ -4012,7 +4012,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -4021,7 +4021,7 @@
         </is>
       </c>
       <c r="G88" t="n">
-        <v>0.7</v>
+        <v>0.51</v>
       </c>
       <c r="H88" t="inlineStr">
         <is>
@@ -4062,7 +4062,7 @@
         </is>
       </c>
       <c r="G89" t="n">
-        <v>0.58</v>
+        <v>0.47</v>
       </c>
       <c r="H89" t="inlineStr">
         <is>
@@ -4094,7 +4094,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -4103,7 +4103,7 @@
         </is>
       </c>
       <c r="G90" t="n">
-        <v>0.66</v>
+        <v>0.85</v>
       </c>
       <c r="H90" t="inlineStr">
         <is>
@@ -4135,7 +4135,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -4144,7 +4144,7 @@
         </is>
       </c>
       <c r="G91" t="n">
-        <v>0.79</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H91" t="inlineStr">
         <is>
@@ -4176,7 +4176,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -4185,7 +4185,7 @@
         </is>
       </c>
       <c r="G92" t="n">
-        <v>0.99</v>
+        <v>0.68</v>
       </c>
       <c r="H92" t="inlineStr">
         <is>
@@ -4217,7 +4217,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -4226,7 +4226,7 @@
         </is>
       </c>
       <c r="G93" t="n">
-        <v>0.6</v>
+        <v>1.01</v>
       </c>
       <c r="H93" t="inlineStr">
         <is>
@@ -4258,7 +4258,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -4267,7 +4267,7 @@
         </is>
       </c>
       <c r="G94" t="n">
-        <v>1.09</v>
+        <v>0.88</v>
       </c>
       <c r="H94" t="inlineStr">
         <is>
@@ -4299,7 +4299,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -4308,7 +4308,7 @@
         </is>
       </c>
       <c r="G95" t="n">
-        <v>0.76</v>
+        <v>0.83</v>
       </c>
       <c r="H95" t="inlineStr">
         <is>
@@ -4340,7 +4340,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -4349,7 +4349,7 @@
         </is>
       </c>
       <c r="G96" t="n">
-        <v>1.06</v>
+        <v>0.95</v>
       </c>
       <c r="H96" t="inlineStr">
         <is>
@@ -4381,7 +4381,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -4390,7 +4390,7 @@
         </is>
       </c>
       <c r="G97" t="n">
-        <v>0.88</v>
+        <v>0.98</v>
       </c>
       <c r="H97" t="inlineStr">
         <is>
@@ -4422,7 +4422,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -4431,7 +4431,7 @@
         </is>
       </c>
       <c r="G98" t="n">
-        <v>0.88</v>
+        <v>0.67</v>
       </c>
       <c r="H98" t="inlineStr">
         <is>
@@ -4472,7 +4472,7 @@
         </is>
       </c>
       <c r="G99" t="n">
-        <v>0.76</v>
+        <v>1.1</v>
       </c>
       <c r="H99" t="inlineStr">
         <is>
@@ -4513,7 +4513,7 @@
         </is>
       </c>
       <c r="G100" t="n">
-        <v>0.51</v>
+        <v>0.83</v>
       </c>
       <c r="H100" t="inlineStr">
         <is>
@@ -4545,7 +4545,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -4554,7 +4554,7 @@
         </is>
       </c>
       <c r="G101" t="n">
-        <v>1.14</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H101" t="inlineStr">
         <is>
@@ -4586,7 +4586,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -4595,7 +4595,7 @@
         </is>
       </c>
       <c r="G102" t="n">
-        <v>0.92</v>
+        <v>0.75</v>
       </c>
       <c r="H102" t="inlineStr">
         <is>
@@ -4627,7 +4627,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4636,7 +4636,7 @@
         </is>
       </c>
       <c r="G103" t="n">
-        <v>0.47</v>
+        <v>0.99</v>
       </c>
       <c r="H103" t="inlineStr">
         <is>
@@ -4668,7 +4668,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4677,7 +4677,7 @@
         </is>
       </c>
       <c r="G104" t="n">
-        <v>0.98</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H104" t="inlineStr">
         <is>
@@ -4718,7 +4718,7 @@
         </is>
       </c>
       <c r="G105" t="n">
-        <v>0.57</v>
+        <v>0.67</v>
       </c>
       <c r="H105" t="inlineStr">
         <is>
@@ -4750,7 +4750,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4759,7 +4759,7 @@
         </is>
       </c>
       <c r="G106" t="n">
-        <v>0.89</v>
+        <v>0.97</v>
       </c>
       <c r="H106" t="inlineStr">
         <is>
@@ -4791,7 +4791,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4800,7 +4800,7 @@
         </is>
       </c>
       <c r="G107" t="n">
-        <v>0.53</v>
+        <v>0.72</v>
       </c>
       <c r="H107" t="inlineStr">
         <is>
@@ -4841,7 +4841,7 @@
         </is>
       </c>
       <c r="G108" t="n">
-        <v>0.61</v>
+        <v>0.47</v>
       </c>
       <c r="H108" t="inlineStr">
         <is>
@@ -4873,7 +4873,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4882,7 +4882,7 @@
         </is>
       </c>
       <c r="G109" t="n">
-        <v>0.88</v>
+        <v>1.06</v>
       </c>
       <c r="H109" t="inlineStr">
         <is>
@@ -4914,7 +4914,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4923,7 +4923,7 @@
         </is>
       </c>
       <c r="G110" t="n">
-        <v>0.89</v>
+        <v>0.53</v>
       </c>
       <c r="H110" t="inlineStr">
         <is>
@@ -4955,7 +4955,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4964,7 +4964,7 @@
         </is>
       </c>
       <c r="G111" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="H111" t="inlineStr">
         <is>
@@ -4996,7 +4996,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -5005,7 +5005,7 @@
         </is>
       </c>
       <c r="G112" t="n">
-        <v>0.79</v>
+        <v>0.75</v>
       </c>
       <c r="H112" t="inlineStr">
         <is>
@@ -5037,7 +5037,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -5046,7 +5046,7 @@
         </is>
       </c>
       <c r="G113" t="n">
-        <v>0.92</v>
+        <v>0.45</v>
       </c>
       <c r="H113" t="inlineStr">
         <is>
@@ -5087,7 +5087,7 @@
         </is>
       </c>
       <c r="G114" t="n">
-        <v>0.43</v>
+        <v>0.54</v>
       </c>
       <c r="H114" t="inlineStr">
         <is>
@@ -5119,7 +5119,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -5128,7 +5128,7 @@
         </is>
       </c>
       <c r="G115" t="n">
-        <v>0.86</v>
+        <v>1.02</v>
       </c>
       <c r="H115" t="inlineStr">
         <is>
@@ -5160,7 +5160,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -5169,7 +5169,7 @@
         </is>
       </c>
       <c r="G116" t="n">
-        <v>0.78</v>
+        <v>0.68</v>
       </c>
       <c r="H116" t="inlineStr">
         <is>
@@ -5210,7 +5210,7 @@
         </is>
       </c>
       <c r="G117" t="n">
-        <v>0.91</v>
+        <v>1.06</v>
       </c>
       <c r="H117" t="inlineStr">
         <is>
@@ -5242,7 +5242,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -5251,7 +5251,7 @@
         </is>
       </c>
       <c r="G118" t="n">
-        <v>0.9</v>
+        <v>1.11</v>
       </c>
       <c r="H118" t="inlineStr">
         <is>
@@ -5283,7 +5283,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -5292,7 +5292,7 @@
         </is>
       </c>
       <c r="G119" t="n">
-        <v>0.59</v>
+        <v>0.73</v>
       </c>
       <c r="H119" t="inlineStr">
         <is>
@@ -5324,7 +5324,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -5333,7 +5333,7 @@
         </is>
       </c>
       <c r="G120" t="n">
-        <v>1.13</v>
+        <v>0.49</v>
       </c>
       <c r="H120" t="inlineStr">
         <is>
@@ -5365,7 +5365,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -5374,7 +5374,7 @@
         </is>
       </c>
       <c r="G121" t="n">
-        <v>0.57</v>
+        <v>1.01</v>
       </c>
       <c r="H121" t="inlineStr">
         <is>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -5415,7 +5415,7 @@
         </is>
       </c>
       <c r="G122" t="n">
-        <v>0.62</v>
+        <v>0.9</v>
       </c>
       <c r="H122" t="inlineStr">
         <is>
@@ -5456,7 +5456,7 @@
         </is>
       </c>
       <c r="G123" t="n">
-        <v>0.58</v>
+        <v>0.64</v>
       </c>
       <c r="H123" t="inlineStr">
         <is>
@@ -5488,7 +5488,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -5497,7 +5497,7 @@
         </is>
       </c>
       <c r="G124" t="n">
-        <v>0.88</v>
+        <v>0.59</v>
       </c>
       <c r="H124" t="inlineStr">
         <is>
@@ -5538,7 +5538,7 @@
         </is>
       </c>
       <c r="G125" t="n">
-        <v>0.83</v>
+        <v>0.61</v>
       </c>
       <c r="H125" t="inlineStr">
         <is>
@@ -5579,7 +5579,7 @@
         </is>
       </c>
       <c r="G126" t="n">
-        <v>1.13</v>
+        <v>0.54</v>
       </c>
       <c r="H126" t="inlineStr">
         <is>
@@ -5611,7 +5611,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -5620,7 +5620,7 @@
         </is>
       </c>
       <c r="G127" t="n">
-        <v>0.9</v>
+        <v>0.99</v>
       </c>
       <c r="H127" t="inlineStr">
         <is>
@@ -5661,7 +5661,7 @@
         </is>
       </c>
       <c r="G128" t="n">
-        <v>0.89</v>
+        <v>1.14</v>
       </c>
       <c r="H128" t="inlineStr">
         <is>
@@ -5693,7 +5693,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -5702,7 +5702,7 @@
         </is>
       </c>
       <c r="G129" t="n">
-        <v>0.87</v>
+        <v>0.73</v>
       </c>
       <c r="H129" t="inlineStr">
         <is>
@@ -5734,7 +5734,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -5743,7 +5743,7 @@
         </is>
       </c>
       <c r="G130" t="n">
-        <v>0.47</v>
+        <v>0.93</v>
       </c>
       <c r="H130" t="inlineStr">
         <is>
@@ -5775,7 +5775,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -5784,7 +5784,7 @@
         </is>
       </c>
       <c r="G131" t="n">
-        <v>0.67</v>
+        <v>0.89</v>
       </c>
       <c r="H131" t="inlineStr">
         <is>
@@ -5816,7 +5816,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -5825,7 +5825,7 @@
         </is>
       </c>
       <c r="G132" t="n">
-        <v>0.57</v>
+        <v>0.72</v>
       </c>
       <c r="H132" t="inlineStr">
         <is>
@@ -5857,7 +5857,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -5866,7 +5866,7 @@
         </is>
       </c>
       <c r="G133" t="n">
-        <v>1.04</v>
+        <v>0.92</v>
       </c>
       <c r="H133" t="inlineStr">
         <is>
@@ -5898,7 +5898,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -5907,7 +5907,7 @@
         </is>
       </c>
       <c r="G134" t="n">
-        <v>0.99</v>
+        <v>0.91</v>
       </c>
       <c r="H134" t="inlineStr">
         <is>
@@ -5939,7 +5939,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -5948,7 +5948,7 @@
         </is>
       </c>
       <c r="G135" t="n">
-        <v>0.67</v>
+        <v>0.43</v>
       </c>
       <c r="H135" t="inlineStr">
         <is>
@@ -5980,7 +5980,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -5989,7 +5989,7 @@
         </is>
       </c>
       <c r="G136" t="n">
-        <v>0.75</v>
+        <v>0.97</v>
       </c>
       <c r="H136" t="inlineStr">
         <is>
@@ -6021,7 +6021,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -6030,7 +6030,7 @@
         </is>
       </c>
       <c r="G137" t="n">
-        <v>0.92</v>
+        <v>0.76</v>
       </c>
       <c r="H137" t="inlineStr">
         <is>
@@ -6071,7 +6071,7 @@
         </is>
       </c>
       <c r="G138" t="n">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="H138" t="inlineStr">
         <is>
@@ -6112,7 +6112,7 @@
         </is>
       </c>
       <c r="G139" t="n">
-        <v>0.54</v>
+        <v>1</v>
       </c>
       <c r="H139" t="inlineStr">
         <is>
@@ -6144,7 +6144,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -6153,7 +6153,7 @@
         </is>
       </c>
       <c r="G140" t="n">
-        <v>0.89</v>
+        <v>0.95</v>
       </c>
       <c r="H140" t="inlineStr">
         <is>
@@ -6185,7 +6185,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -6194,7 +6194,7 @@
         </is>
       </c>
       <c r="G141" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H141" t="inlineStr">
         <is>
@@ -6226,7 +6226,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -6235,7 +6235,7 @@
         </is>
       </c>
       <c r="G142" t="n">
-        <v>0.8</v>
+        <v>1.09</v>
       </c>
       <c r="H142" t="inlineStr">
         <is>
@@ -6267,7 +6267,7 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -6276,7 +6276,7 @@
         </is>
       </c>
       <c r="G143" t="n">
-        <v>0.63</v>
+        <v>0.55</v>
       </c>
       <c r="H143" t="inlineStr">
         <is>
@@ -6308,7 +6308,7 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -6317,7 +6317,7 @@
         </is>
       </c>
       <c r="G144" t="n">
-        <v>0.98</v>
+        <v>0.88</v>
       </c>
       <c r="H144" t="inlineStr">
         <is>
@@ -6349,7 +6349,7 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
@@ -6358,7 +6358,7 @@
         </is>
       </c>
       <c r="G145" t="n">
-        <v>0.87</v>
+        <v>0.7</v>
       </c>
       <c r="H145" t="inlineStr">
         <is>
@@ -6390,7 +6390,7 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
@@ -6399,7 +6399,7 @@
         </is>
       </c>
       <c r="G146" t="n">
-        <v>0.45</v>
+        <v>0.6</v>
       </c>
       <c r="H146" t="inlineStr">
         <is>
@@ -6431,7 +6431,7 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
@@ -6440,7 +6440,7 @@
         </is>
       </c>
       <c r="G147" t="n">
-        <v>0.75</v>
+        <v>1.07</v>
       </c>
       <c r="H147" t="inlineStr">
         <is>
@@ -6481,7 +6481,7 @@
         </is>
       </c>
       <c r="G148" t="n">
-        <v>0.97</v>
+        <v>0.82</v>
       </c>
       <c r="H148" t="inlineStr">
         <is>
@@ -6522,7 +6522,7 @@
         </is>
       </c>
       <c r="G149" t="n">
-        <v>0.45</v>
+        <v>0.85</v>
       </c>
       <c r="H149" t="inlineStr">
         <is>
@@ -6554,7 +6554,7 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
@@ -6563,7 +6563,7 @@
         </is>
       </c>
       <c r="G150" t="n">
-        <v>0.55</v>
+        <v>0.95</v>
       </c>
       <c r="H150" t="inlineStr">
         <is>
@@ -6595,7 +6595,7 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
@@ -6604,7 +6604,7 @@
         </is>
       </c>
       <c r="G151" t="n">
-        <v>1.12</v>
+        <v>0.84</v>
       </c>
       <c r="H151" t="inlineStr">
         <is>
@@ -6636,7 +6636,7 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
@@ -6645,7 +6645,7 @@
         </is>
       </c>
       <c r="G152" t="n">
-        <v>1.13</v>
+        <v>0.63</v>
       </c>
       <c r="H152" t="inlineStr">
         <is>
@@ -6677,7 +6677,7 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
@@ -6686,7 +6686,7 @@
         </is>
       </c>
       <c r="G153" t="n">
-        <v>0.72</v>
+        <v>1.11</v>
       </c>
       <c r="H153" t="inlineStr">
         <is>
@@ -6727,7 +6727,7 @@
         </is>
       </c>
       <c r="G154" t="n">
-        <v>0.57</v>
+        <v>1</v>
       </c>
       <c r="H154" t="inlineStr">
         <is>
@@ -6759,7 +6759,7 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
@@ -6768,7 +6768,7 @@
         </is>
       </c>
       <c r="G155" t="n">
-        <v>0.65</v>
+        <v>0.55</v>
       </c>
       <c r="H155" t="inlineStr">
         <is>
@@ -6800,7 +6800,7 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
@@ -6809,7 +6809,7 @@
         </is>
       </c>
       <c r="G156" t="n">
-        <v>1.15</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H156" t="inlineStr">
         <is>
@@ -6841,7 +6841,7 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
@@ -6850,7 +6850,7 @@
         </is>
       </c>
       <c r="G157" t="n">
-        <v>0.44</v>
+        <v>0.88</v>
       </c>
       <c r="H157" t="inlineStr">
         <is>
@@ -6882,7 +6882,7 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
@@ -6891,7 +6891,7 @@
         </is>
       </c>
       <c r="G158" t="n">
-        <v>1.15</v>
+        <v>0.53</v>
       </c>
       <c r="H158" t="inlineStr">
         <is>
@@ -6923,7 +6923,7 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
@@ -6932,7 +6932,7 @@
         </is>
       </c>
       <c r="G159" t="n">
-        <v>0.48</v>
+        <v>1.06</v>
       </c>
       <c r="H159" t="inlineStr">
         <is>
@@ -6973,7 +6973,7 @@
         </is>
       </c>
       <c r="G160" t="n">
-        <v>0.75</v>
+        <v>0.72</v>
       </c>
       <c r="H160" t="inlineStr">
         <is>
@@ -7005,7 +7005,7 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
@@ -7014,7 +7014,7 @@
         </is>
       </c>
       <c r="G161" t="n">
-        <v>0.97</v>
+        <v>0.57</v>
       </c>
       <c r="H161" t="inlineStr">
         <is>
@@ -7046,7 +7046,7 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
@@ -7055,7 +7055,7 @@
         </is>
       </c>
       <c r="G162" t="n">
-        <v>0.65</v>
+        <v>0.59</v>
       </c>
       <c r="H162" t="inlineStr">
         <is>
@@ -7087,7 +7087,7 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
@@ -7096,7 +7096,7 @@
         </is>
       </c>
       <c r="G163" t="n">
-        <v>0.52</v>
+        <v>0.59</v>
       </c>
       <c r="H163" t="inlineStr">
         <is>
@@ -7128,7 +7128,7 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
@@ -7137,7 +7137,7 @@
         </is>
       </c>
       <c r="G164" t="n">
-        <v>1.03</v>
+        <v>0.63</v>
       </c>
       <c r="H164" t="inlineStr">
         <is>
@@ -7169,7 +7169,7 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
@@ -7178,7 +7178,7 @@
         </is>
       </c>
       <c r="G165" t="n">
-        <v>0.43</v>
+        <v>0.66</v>
       </c>
       <c r="H165" t="inlineStr">
         <is>
@@ -7219,7 +7219,7 @@
         </is>
       </c>
       <c r="G166" t="n">
-        <v>0.99</v>
+        <v>0.53</v>
       </c>
       <c r="H166" t="inlineStr">
         <is>
@@ -7251,7 +7251,7 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
@@ -7292,7 +7292,7 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
@@ -7301,7 +7301,7 @@
         </is>
       </c>
       <c r="G168" t="n">
-        <v>0.96</v>
+        <v>0.54</v>
       </c>
       <c r="H168" t="inlineStr">
         <is>
@@ -7333,7 +7333,7 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
@@ -7342,7 +7342,7 @@
         </is>
       </c>
       <c r="G169" t="n">
-        <v>0.6899999999999999</v>
+        <v>1.04</v>
       </c>
       <c r="H169" t="inlineStr">
         <is>
@@ -7374,7 +7374,7 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
@@ -7383,7 +7383,7 @@
         </is>
       </c>
       <c r="G170" t="n">
-        <v>0.48</v>
+        <v>1</v>
       </c>
       <c r="H170" t="inlineStr">
         <is>
@@ -7424,7 +7424,7 @@
         </is>
       </c>
       <c r="G171" t="n">
-        <v>0.71</v>
+        <v>0.96</v>
       </c>
       <c r="H171" t="inlineStr">
         <is>
@@ -7465,7 +7465,7 @@
         </is>
       </c>
       <c r="G172" t="n">
-        <v>0.49</v>
+        <v>0.87</v>
       </c>
       <c r="H172" t="inlineStr">
         <is>
@@ -7497,7 +7497,7 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
@@ -7506,7 +7506,7 @@
         </is>
       </c>
       <c r="G173" t="n">
-        <v>0.61</v>
+        <v>0.98</v>
       </c>
       <c r="H173" t="inlineStr">
         <is>
@@ -7538,7 +7538,7 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
@@ -7547,7 +7547,7 @@
         </is>
       </c>
       <c r="G174" t="n">
-        <v>1.05</v>
+        <v>0.75</v>
       </c>
       <c r="H174" t="inlineStr">
         <is>
@@ -7579,7 +7579,7 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
@@ -7588,7 +7588,7 @@
         </is>
       </c>
       <c r="G175" t="n">
-        <v>1.08</v>
+        <v>0.57</v>
       </c>
       <c r="H175" t="inlineStr">
         <is>
@@ -7620,7 +7620,7 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
@@ -7629,7 +7629,7 @@
         </is>
       </c>
       <c r="G176" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="H176" t="inlineStr">
         <is>
@@ -7670,7 +7670,7 @@
         </is>
       </c>
       <c r="G177" t="n">
-        <v>0.86</v>
+        <v>0.78</v>
       </c>
       <c r="H177" t="inlineStr">
         <is>
@@ -7702,7 +7702,7 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
@@ -7711,7 +7711,7 @@
         </is>
       </c>
       <c r="G178" t="n">
-        <v>0.64</v>
+        <v>0.77</v>
       </c>
       <c r="H178" t="inlineStr">
         <is>
@@ -7743,7 +7743,7 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
@@ -7752,7 +7752,7 @@
         </is>
       </c>
       <c r="G179" t="n">
-        <v>0.61</v>
+        <v>0.78</v>
       </c>
       <c r="H179" t="inlineStr">
         <is>
@@ -7784,7 +7784,7 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
@@ -7793,7 +7793,7 @@
         </is>
       </c>
       <c r="G180" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="H180" t="inlineStr">
         <is>
@@ -7825,7 +7825,7 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
@@ -7834,7 +7834,7 @@
         </is>
       </c>
       <c r="G181" t="n">
-        <v>0.52</v>
+        <v>0.67</v>
       </c>
       <c r="H181" t="inlineStr">
         <is>
@@ -7866,7 +7866,7 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
@@ -7875,7 +7875,7 @@
         </is>
       </c>
       <c r="G182" t="n">
-        <v>0.75</v>
+        <v>0.43</v>
       </c>
       <c r="H182" t="inlineStr">
         <is>
@@ -7907,7 +7907,7 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
@@ -7916,7 +7916,7 @@
         </is>
       </c>
       <c r="G183" t="n">
-        <v>0.73</v>
+        <v>0.92</v>
       </c>
       <c r="H183" t="inlineStr">
         <is>
@@ -7948,7 +7948,7 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
@@ -7957,7 +7957,7 @@
         </is>
       </c>
       <c r="G184" t="n">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="H184" t="inlineStr">
         <is>
@@ -7989,7 +7989,7 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
@@ -7998,7 +7998,7 @@
         </is>
       </c>
       <c r="G185" t="n">
-        <v>1.08</v>
+        <v>0.47</v>
       </c>
       <c r="H185" t="inlineStr">
         <is>
@@ -8039,7 +8039,7 @@
         </is>
       </c>
       <c r="G186" t="n">
-        <v>0.5600000000000001</v>
+        <v>1.09</v>
       </c>
       <c r="H186" t="inlineStr">
         <is>
@@ -8071,7 +8071,7 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
@@ -8080,7 +8080,7 @@
         </is>
       </c>
       <c r="G187" t="n">
-        <v>0.98</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H187" t="inlineStr">
         <is>
@@ -8112,7 +8112,7 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
@@ -8121,7 +8121,7 @@
         </is>
       </c>
       <c r="G188" t="n">
-        <v>0.65</v>
+        <v>1.08</v>
       </c>
       <c r="H188" t="inlineStr">
         <is>
@@ -8153,7 +8153,7 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
@@ -8162,7 +8162,7 @@
         </is>
       </c>
       <c r="G189" t="n">
-        <v>0.96</v>
+        <v>0.67</v>
       </c>
       <c r="H189" t="inlineStr">
         <is>
@@ -8194,7 +8194,7 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
@@ -8203,7 +8203,7 @@
         </is>
       </c>
       <c r="G190" t="n">
-        <v>0.99</v>
+        <v>1.06</v>
       </c>
       <c r="H190" t="inlineStr">
         <is>
@@ -8235,7 +8235,7 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
@@ -8244,7 +8244,7 @@
         </is>
       </c>
       <c r="G191" t="n">
-        <v>0.73</v>
+        <v>0.52</v>
       </c>
       <c r="H191" t="inlineStr">
         <is>
@@ -8276,7 +8276,7 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
@@ -8285,7 +8285,7 @@
         </is>
       </c>
       <c r="G192" t="n">
-        <v>0.82</v>
+        <v>0.61</v>
       </c>
       <c r="H192" t="inlineStr">
         <is>
@@ -8317,7 +8317,7 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
@@ -8326,7 +8326,7 @@
         </is>
       </c>
       <c r="G193" t="n">
-        <v>0.61</v>
+        <v>0.72</v>
       </c>
       <c r="H193" t="inlineStr">
         <is>
@@ -8358,7 +8358,7 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
@@ -8367,7 +8367,7 @@
         </is>
       </c>
       <c r="G194" t="n">
-        <v>0.55</v>
+        <v>0.91</v>
       </c>
       <c r="H194" t="inlineStr">
         <is>
@@ -8399,7 +8399,7 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
@@ -8408,7 +8408,7 @@
         </is>
       </c>
       <c r="G195" t="n">
-        <v>1.07</v>
+        <v>0.93</v>
       </c>
       <c r="H195" t="inlineStr">
         <is>
@@ -8440,7 +8440,7 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
@@ -8449,7 +8449,7 @@
         </is>
       </c>
       <c r="G196" t="n">
-        <v>0.61</v>
+        <v>1.05</v>
       </c>
       <c r="H196" t="inlineStr">
         <is>
@@ -8481,7 +8481,7 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
@@ -8490,7 +8490,7 @@
         </is>
       </c>
       <c r="G197" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.79</v>
       </c>
       <c r="H197" t="inlineStr">
         <is>
@@ -8522,7 +8522,7 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
@@ -8531,7 +8531,7 @@
         </is>
       </c>
       <c r="G198" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="H198" t="inlineStr">
         <is>
@@ -8563,7 +8563,7 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
@@ -8572,7 +8572,7 @@
         </is>
       </c>
       <c r="G199" t="n">
-        <v>0.49</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H199" t="inlineStr">
         <is>
@@ -8604,7 +8604,7 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
@@ -8613,7 +8613,7 @@
         </is>
       </c>
       <c r="G200" t="n">
-        <v>1.05</v>
+        <v>0.95</v>
       </c>
       <c r="H200" t="inlineStr">
         <is>
@@ -8645,7 +8645,7 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
@@ -8654,7 +8654,7 @@
         </is>
       </c>
       <c r="G201" t="n">
-        <v>1.12</v>
+        <v>0.68</v>
       </c>
       <c r="H201" t="inlineStr">
         <is>
@@ -8686,7 +8686,7 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
@@ -8695,7 +8695,7 @@
         </is>
       </c>
       <c r="G202" t="n">
-        <v>0.73</v>
+        <v>0.47</v>
       </c>
       <c r="H202" t="inlineStr">
         <is>
@@ -8727,7 +8727,7 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
@@ -8736,7 +8736,7 @@
         </is>
       </c>
       <c r="G203" t="n">
-        <v>0.62</v>
+        <v>0.98</v>
       </c>
       <c r="H203" t="inlineStr">
         <is>
@@ -8768,7 +8768,7 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
@@ -8777,7 +8777,7 @@
         </is>
       </c>
       <c r="G204" t="n">
-        <v>0.79</v>
+        <v>0.76</v>
       </c>
       <c r="H204" t="inlineStr">
         <is>
@@ -8809,7 +8809,7 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
@@ -8818,7 +8818,7 @@
         </is>
       </c>
       <c r="G205" t="n">
-        <v>0.83</v>
+        <v>0.96</v>
       </c>
       <c r="H205" t="inlineStr">
         <is>
@@ -8850,7 +8850,7 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
@@ -8859,7 +8859,7 @@
         </is>
       </c>
       <c r="G206" t="n">
-        <v>1.04</v>
+        <v>0.66</v>
       </c>
       <c r="H206" t="inlineStr">
         <is>
@@ -8891,7 +8891,7 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
@@ -8900,7 +8900,7 @@
         </is>
       </c>
       <c r="G207" t="n">
-        <v>1.08</v>
+        <v>0.83</v>
       </c>
       <c r="H207" t="inlineStr">
         <is>
@@ -8932,7 +8932,7 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
@@ -8941,7 +8941,7 @@
         </is>
       </c>
       <c r="G208" t="n">
-        <v>0.48</v>
+        <v>1.14</v>
       </c>
       <c r="H208" t="inlineStr">
         <is>
@@ -8973,7 +8973,7 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
@@ -8982,7 +8982,7 @@
         </is>
       </c>
       <c r="G209" t="n">
-        <v>1</v>
+        <v>0.51</v>
       </c>
       <c r="H209" t="inlineStr">
         <is>
@@ -9023,7 +9023,7 @@
         </is>
       </c>
       <c r="G210" t="n">
-        <v>0.43</v>
+        <v>1.03</v>
       </c>
       <c r="H210" t="inlineStr">
         <is>
@@ -9064,7 +9064,7 @@
         </is>
       </c>
       <c r="G211" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.78</v>
       </c>
       <c r="H211" t="inlineStr">
         <is>
@@ -9105,7 +9105,7 @@
         </is>
       </c>
       <c r="G212" t="n">
-        <v>0.42</v>
+        <v>0.8</v>
       </c>
       <c r="H212" t="inlineStr">
         <is>
@@ -9137,7 +9137,7 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
@@ -9146,7 +9146,7 @@
         </is>
       </c>
       <c r="G213" t="n">
-        <v>0.78</v>
+        <v>1.08</v>
       </c>
       <c r="H213" t="inlineStr">
         <is>
@@ -9178,7 +9178,7 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
@@ -9187,7 +9187,7 @@
         </is>
       </c>
       <c r="G214" t="n">
-        <v>0.75</v>
+        <v>0.46</v>
       </c>
       <c r="H214" t="inlineStr">
         <is>
@@ -9219,7 +9219,7 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
@@ -9228,7 +9228,7 @@
         </is>
       </c>
       <c r="G215" t="n">
-        <v>1.14</v>
+        <v>1.01</v>
       </c>
       <c r="H215" t="inlineStr">
         <is>
@@ -9260,7 +9260,7 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
@@ -9269,7 +9269,7 @@
         </is>
       </c>
       <c r="G216" t="n">
-        <v>0.7</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H216" t="inlineStr">
         <is>
@@ -9301,7 +9301,7 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
@@ -9310,7 +9310,7 @@
         </is>
       </c>
       <c r="G217" t="n">
-        <v>0.64</v>
+        <v>0.95</v>
       </c>
       <c r="H217" t="inlineStr">
         <is>
@@ -9342,7 +9342,7 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
@@ -9351,7 +9351,7 @@
         </is>
       </c>
       <c r="G218" t="n">
-        <v>1.03</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H218" t="inlineStr">
         <is>
@@ -9392,7 +9392,7 @@
         </is>
       </c>
       <c r="G219" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.84</v>
       </c>
       <c r="H219" t="inlineStr">
         <is>
@@ -9424,7 +9424,7 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
@@ -9433,7 +9433,7 @@
         </is>
       </c>
       <c r="G220" t="n">
-        <v>0.51</v>
+        <v>0.44</v>
       </c>
       <c r="H220" t="inlineStr">
         <is>
@@ -9465,7 +9465,7 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
@@ -9474,7 +9474,7 @@
         </is>
       </c>
       <c r="G221" t="n">
-        <v>0.77</v>
+        <v>0.93</v>
       </c>
       <c r="H221" t="inlineStr">
         <is>
@@ -9547,7 +9547,7 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
@@ -9556,7 +9556,7 @@
         </is>
       </c>
       <c r="G223" t="n">
-        <v>0.73</v>
+        <v>0.97</v>
       </c>
       <c r="H223" t="inlineStr">
         <is>
@@ -9588,7 +9588,7 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
@@ -9597,7 +9597,7 @@
         </is>
       </c>
       <c r="G224" t="n">
-        <v>0.64</v>
+        <v>0.8</v>
       </c>
       <c r="H224" t="inlineStr">
         <is>
@@ -9629,7 +9629,7 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
@@ -9638,7 +9638,7 @@
         </is>
       </c>
       <c r="G225" t="n">
-        <v>0.73</v>
+        <v>1.07</v>
       </c>
       <c r="H225" t="inlineStr">
         <is>
@@ -9670,7 +9670,7 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
@@ -9679,7 +9679,7 @@
         </is>
       </c>
       <c r="G226" t="n">
-        <v>1.04</v>
+        <v>0.98</v>
       </c>
       <c r="H226" t="inlineStr">
         <is>
@@ -9711,7 +9711,7 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
@@ -9720,7 +9720,7 @@
         </is>
       </c>
       <c r="G227" t="n">
-        <v>0.47</v>
+        <v>1.15</v>
       </c>
       <c r="H227" t="inlineStr">
         <is>
@@ -9752,7 +9752,7 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
@@ -9761,7 +9761,7 @@
         </is>
       </c>
       <c r="G228" t="n">
-        <v>0.54</v>
+        <v>0.76</v>
       </c>
       <c r="H228" t="inlineStr">
         <is>
@@ -9793,7 +9793,7 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
@@ -9802,7 +9802,7 @@
         </is>
       </c>
       <c r="G229" t="n">
-        <v>0.77</v>
+        <v>0.83</v>
       </c>
       <c r="H229" t="inlineStr">
         <is>
@@ -9843,7 +9843,7 @@
         </is>
       </c>
       <c r="G230" t="n">
-        <v>0.92</v>
+        <v>0.77</v>
       </c>
       <c r="H230" t="inlineStr">
         <is>
@@ -9875,7 +9875,7 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
@@ -9884,7 +9884,7 @@
         </is>
       </c>
       <c r="G231" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="H231" t="inlineStr">
         <is>
@@ -9916,7 +9916,7 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
@@ -9925,7 +9925,7 @@
         </is>
       </c>
       <c r="G232" t="n">
-        <v>0.96</v>
+        <v>1.12</v>
       </c>
       <c r="H232" t="inlineStr">
         <is>
@@ -9957,7 +9957,7 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
@@ -9966,7 +9966,7 @@
         </is>
       </c>
       <c r="G233" t="n">
-        <v>0.74</v>
+        <v>0.53</v>
       </c>
       <c r="H233" t="inlineStr">
         <is>
@@ -9998,7 +9998,7 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
@@ -10007,7 +10007,7 @@
         </is>
       </c>
       <c r="G234" t="n">
-        <v>1.11</v>
+        <v>0.84</v>
       </c>
       <c r="H234" t="inlineStr">
         <is>
@@ -10039,7 +10039,7 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
@@ -10048,7 +10048,7 @@
         </is>
       </c>
       <c r="G235" t="n">
-        <v>1.07</v>
+        <v>0.83</v>
       </c>
       <c r="H235" t="inlineStr">
         <is>
@@ -10080,7 +10080,7 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
@@ -10089,7 +10089,7 @@
         </is>
       </c>
       <c r="G236" t="n">
-        <v>0.92</v>
+        <v>1.06</v>
       </c>
       <c r="H236" t="inlineStr">
         <is>
@@ -10121,7 +10121,7 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
@@ -10130,7 +10130,7 @@
         </is>
       </c>
       <c r="G237" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.88</v>
       </c>
       <c r="H237" t="inlineStr">
         <is>
@@ -10171,7 +10171,7 @@
         </is>
       </c>
       <c r="G238" t="n">
-        <v>1.15</v>
+        <v>0.83</v>
       </c>
       <c r="H238" t="inlineStr">
         <is>
@@ -10203,7 +10203,7 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
@@ -10212,7 +10212,7 @@
         </is>
       </c>
       <c r="G239" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.67</v>
       </c>
       <c r="H239" t="inlineStr">
         <is>
@@ -10244,7 +10244,7 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
@@ -10253,7 +10253,7 @@
         </is>
       </c>
       <c r="G240" t="n">
-        <v>0.54</v>
+        <v>0.97</v>
       </c>
       <c r="H240" t="inlineStr">
         <is>
@@ -10285,7 +10285,7 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
@@ -10294,7 +10294,7 @@
         </is>
       </c>
       <c r="G241" t="n">
-        <v>0.79</v>
+        <v>0.48</v>
       </c>
       <c r="H241" t="inlineStr">
         <is>
@@ -10326,7 +10326,7 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
@@ -10335,7 +10335,7 @@
         </is>
       </c>
       <c r="G242" t="n">
-        <v>0.84</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H242" t="inlineStr">
         <is>
@@ -10367,7 +10367,7 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
@@ -10376,7 +10376,7 @@
         </is>
       </c>
       <c r="G243" t="n">
-        <v>0.57</v>
+        <v>0.59</v>
       </c>
       <c r="H243" t="inlineStr">
         <is>
@@ -10408,7 +10408,7 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
@@ -10417,7 +10417,7 @@
         </is>
       </c>
       <c r="G244" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.98</v>
       </c>
       <c r="H244" t="inlineStr">
         <is>
@@ -10449,7 +10449,7 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
@@ -10458,7 +10458,7 @@
         </is>
       </c>
       <c r="G245" t="n">
-        <v>0.77</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H245" t="inlineStr">
         <is>
@@ -10490,7 +10490,7 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
@@ -10499,7 +10499,7 @@
         </is>
       </c>
       <c r="G246" t="n">
-        <v>0.84</v>
+        <v>0.71</v>
       </c>
       <c r="H246" t="inlineStr">
         <is>
@@ -10531,7 +10531,7 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
@@ -10540,7 +10540,7 @@
         </is>
       </c>
       <c r="G247" t="n">
-        <v>1.01</v>
+        <v>0.85</v>
       </c>
       <c r="H247" t="inlineStr">
         <is>
@@ -10581,7 +10581,7 @@
         </is>
       </c>
       <c r="G248" t="n">
-        <v>0.48</v>
+        <v>0.99</v>
       </c>
       <c r="H248" t="inlineStr">
         <is>
@@ -10613,7 +10613,7 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
@@ -10622,7 +10622,7 @@
         </is>
       </c>
       <c r="G249" t="n">
-        <v>1.02</v>
+        <v>1.1</v>
       </c>
       <c r="H249" t="inlineStr">
         <is>
@@ -10654,7 +10654,7 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
@@ -10663,7 +10663,7 @@
         </is>
       </c>
       <c r="G250" t="n">
-        <v>0.48</v>
+        <v>0.64</v>
       </c>
       <c r="H250" t="inlineStr">
         <is>
@@ -10704,7 +10704,7 @@
         </is>
       </c>
       <c r="G251" t="n">
-        <v>0.82</v>
+        <v>0.58</v>
       </c>
       <c r="H251" t="inlineStr">
         <is>
@@ -10736,7 +10736,7 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
@@ -10745,7 +10745,7 @@
         </is>
       </c>
       <c r="G252" t="n">
-        <v>0.74</v>
+        <v>0.63</v>
       </c>
       <c r="H252" t="inlineStr">
         <is>
@@ -10777,7 +10777,7 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
@@ -10786,7 +10786,7 @@
         </is>
       </c>
       <c r="G253" t="n">
-        <v>0.82</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H253" t="inlineStr">
         <is>
@@ -10827,7 +10827,7 @@
         </is>
       </c>
       <c r="G254" t="n">
-        <v>0.53</v>
+        <v>1.15</v>
       </c>
       <c r="H254" t="inlineStr">
         <is>
@@ -10868,7 +10868,7 @@
         </is>
       </c>
       <c r="G255" t="n">
-        <v>0.55</v>
+        <v>1.07</v>
       </c>
       <c r="H255" t="inlineStr">
         <is>
@@ -10909,7 +10909,7 @@
         </is>
       </c>
       <c r="G256" t="n">
-        <v>0.98</v>
+        <v>0.79</v>
       </c>
       <c r="H256" t="inlineStr">
         <is>
@@ -10950,7 +10950,7 @@
         </is>
       </c>
       <c r="G257" t="n">
-        <v>0.44</v>
+        <v>0.77</v>
       </c>
       <c r="H257" t="inlineStr">
         <is>
@@ -10982,7 +10982,7 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
@@ -10991,7 +10991,7 @@
         </is>
       </c>
       <c r="G258" t="n">
-        <v>1.11</v>
+        <v>0.65</v>
       </c>
       <c r="H258" t="inlineStr">
         <is>
@@ -11023,7 +11023,7 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
@@ -11032,7 +11032,7 @@
         </is>
       </c>
       <c r="G259" t="n">
-        <v>0.65</v>
+        <v>1.03</v>
       </c>
       <c r="H259" t="inlineStr">
         <is>
@@ -11064,7 +11064,7 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
@@ -11073,7 +11073,7 @@
         </is>
       </c>
       <c r="G260" t="n">
-        <v>0.52</v>
+        <v>0.64</v>
       </c>
       <c r="H260" t="inlineStr">
         <is>
@@ -11105,7 +11105,7 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
@@ -11114,7 +11114,7 @@
         </is>
       </c>
       <c r="G261" t="n">
-        <v>0.95</v>
+        <v>0.89</v>
       </c>
       <c r="H261" t="inlineStr">
         <is>
@@ -11146,7 +11146,7 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
@@ -11155,7 +11155,7 @@
         </is>
       </c>
       <c r="G262" t="n">
-        <v>0.54</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H262" t="inlineStr">
         <is>
@@ -11196,7 +11196,7 @@
         </is>
       </c>
       <c r="G263" t="n">
-        <v>0.5</v>
+        <v>0.72</v>
       </c>
       <c r="H263" t="inlineStr">
         <is>
@@ -11228,7 +11228,7 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
@@ -11237,7 +11237,7 @@
         </is>
       </c>
       <c r="G264" t="n">
-        <v>0.48</v>
+        <v>0.77</v>
       </c>
       <c r="H264" t="inlineStr">
         <is>
@@ -11269,7 +11269,7 @@
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
@@ -11278,7 +11278,7 @@
         </is>
       </c>
       <c r="G265" t="n">
-        <v>0.57</v>
+        <v>0.75</v>
       </c>
       <c r="H265" t="inlineStr">
         <is>
@@ -11319,7 +11319,7 @@
         </is>
       </c>
       <c r="G266" t="n">
-        <v>0.8</v>
+        <v>0.87</v>
       </c>
       <c r="H266" t="inlineStr">
         <is>
@@ -11360,7 +11360,7 @@
         </is>
       </c>
       <c r="G267" t="n">
-        <v>0.67</v>
+        <v>0.98</v>
       </c>
       <c r="H267" t="inlineStr">
         <is>
@@ -11392,7 +11392,7 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
@@ -11401,7 +11401,7 @@
         </is>
       </c>
       <c r="G268" t="n">
-        <v>1</v>
+        <v>0.96</v>
       </c>
       <c r="H268" t="inlineStr">
         <is>
@@ -11433,7 +11433,7 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
@@ -11442,7 +11442,7 @@
         </is>
       </c>
       <c r="G269" t="n">
-        <v>0.87</v>
+        <v>1.08</v>
       </c>
       <c r="H269" t="inlineStr">
         <is>
@@ -11474,7 +11474,7 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
@@ -11483,7 +11483,7 @@
         </is>
       </c>
       <c r="G270" t="n">
-        <v>0.51</v>
+        <v>0.55</v>
       </c>
       <c r="H270" t="inlineStr">
         <is>
@@ -11515,7 +11515,7 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
@@ -11524,7 +11524,7 @@
         </is>
       </c>
       <c r="G271" t="n">
-        <v>1</v>
+        <v>0.85</v>
       </c>
       <c r="H271" t="inlineStr">
         <is>
@@ -11556,7 +11556,7 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
@@ -11565,7 +11565,7 @@
         </is>
       </c>
       <c r="G272" t="n">
-        <v>0.53</v>
+        <v>0.99</v>
       </c>
       <c r="H272" t="inlineStr">
         <is>
@@ -11597,7 +11597,7 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
@@ -11606,7 +11606,7 @@
         </is>
       </c>
       <c r="G273" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="H273" t="inlineStr">
         <is>
@@ -11638,7 +11638,7 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
@@ -11647,7 +11647,7 @@
         </is>
       </c>
       <c r="G274" t="n">
-        <v>0.95</v>
+        <v>1.11</v>
       </c>
       <c r="H274" t="inlineStr">
         <is>
@@ -11679,7 +11679,7 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
@@ -11688,7 +11688,7 @@
         </is>
       </c>
       <c r="G275" t="n">
-        <v>0.6</v>
+        <v>1.11</v>
       </c>
       <c r="H275" t="inlineStr">
         <is>
@@ -11729,7 +11729,7 @@
         </is>
       </c>
       <c r="G276" t="n">
-        <v>0.54</v>
+        <v>0.61</v>
       </c>
       <c r="H276" t="inlineStr">
         <is>
@@ -11770,7 +11770,7 @@
         </is>
       </c>
       <c r="G277" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.11</v>
       </c>
       <c r="H277" t="inlineStr">
         <is>
@@ -11802,7 +11802,7 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
@@ -11811,7 +11811,7 @@
         </is>
       </c>
       <c r="G278" t="n">
-        <v>0.46</v>
+        <v>0.86</v>
       </c>
       <c r="H278" t="inlineStr">
         <is>
@@ -11852,7 +11852,7 @@
         </is>
       </c>
       <c r="G279" t="n">
-        <v>1.09</v>
+        <v>0.59</v>
       </c>
       <c r="H279" t="inlineStr">
         <is>
@@ -11884,7 +11884,7 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
@@ -11893,7 +11893,7 @@
         </is>
       </c>
       <c r="G280" t="n">
-        <v>0.61</v>
+        <v>0.68</v>
       </c>
       <c r="H280" t="inlineStr">
         <is>
@@ -11934,7 +11934,7 @@
         </is>
       </c>
       <c r="G281" t="n">
-        <v>0.98</v>
+        <v>0.8</v>
       </c>
       <c r="H281" t="inlineStr">
         <is>
@@ -11966,7 +11966,7 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
@@ -11975,7 +11975,7 @@
         </is>
       </c>
       <c r="G282" t="n">
-        <v>1.08</v>
+        <v>0.85</v>
       </c>
       <c r="H282" t="inlineStr">
         <is>
@@ -12007,7 +12007,7 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
@@ -12016,7 +12016,7 @@
         </is>
       </c>
       <c r="G283" t="n">
-        <v>0.54</v>
+        <v>0.73</v>
       </c>
       <c r="H283" t="inlineStr">
         <is>
@@ -12048,7 +12048,7 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
@@ -12057,7 +12057,7 @@
         </is>
       </c>
       <c r="G284" t="n">
-        <v>1.04</v>
+        <v>0.75</v>
       </c>
       <c r="H284" t="inlineStr">
         <is>
@@ -12089,7 +12089,7 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
@@ -12098,7 +12098,7 @@
         </is>
       </c>
       <c r="G285" t="n">
-        <v>0.95</v>
+        <v>0.71</v>
       </c>
       <c r="H285" t="inlineStr">
         <is>
@@ -12139,7 +12139,7 @@
         </is>
       </c>
       <c r="G286" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.87</v>
       </c>
       <c r="H286" t="inlineStr">
         <is>
@@ -12171,7 +12171,7 @@
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
@@ -12180,7 +12180,7 @@
         </is>
       </c>
       <c r="G287" t="n">
-        <v>0.54</v>
+        <v>0.84</v>
       </c>
       <c r="H287" t="inlineStr">
         <is>
@@ -12212,7 +12212,7 @@
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
@@ -12221,7 +12221,7 @@
         </is>
       </c>
       <c r="G288" t="n">
-        <v>0.9</v>
+        <v>0.49</v>
       </c>
       <c r="H288" t="inlineStr">
         <is>
@@ -12262,7 +12262,7 @@
         </is>
       </c>
       <c r="G289" t="n">
-        <v>1.07</v>
+        <v>0.86</v>
       </c>
       <c r="H289" t="inlineStr">
         <is>
@@ -12294,7 +12294,7 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
@@ -12303,7 +12303,7 @@
         </is>
       </c>
       <c r="G290" t="n">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="H290" t="inlineStr">
         <is>
@@ -12335,7 +12335,7 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
@@ -12344,7 +12344,7 @@
         </is>
       </c>
       <c r="G291" t="n">
-        <v>0.89</v>
+        <v>0.96</v>
       </c>
       <c r="H291" t="inlineStr">
         <is>
@@ -12385,7 +12385,7 @@
         </is>
       </c>
       <c r="G292" t="n">
-        <v>0.73</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H292" t="inlineStr">
         <is>
@@ -12426,7 +12426,7 @@
         </is>
       </c>
       <c r="G293" t="n">
-        <v>0.73</v>
+        <v>0.96</v>
       </c>
       <c r="H293" t="inlineStr">
         <is>
@@ -12458,7 +12458,7 @@
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
@@ -12467,7 +12467,7 @@
         </is>
       </c>
       <c r="G294" t="n">
-        <v>0.67</v>
+        <v>0.92</v>
       </c>
       <c r="H294" t="inlineStr">
         <is>
@@ -12499,7 +12499,7 @@
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
@@ -12508,7 +12508,7 @@
         </is>
       </c>
       <c r="G295" t="n">
-        <v>0.53</v>
+        <v>0.92</v>
       </c>
       <c r="H295" t="inlineStr">
         <is>
@@ -12540,7 +12540,7 @@
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
@@ -12549,7 +12549,7 @@
         </is>
       </c>
       <c r="G296" t="n">
-        <v>0.98</v>
+        <v>1.13</v>
       </c>
       <c r="H296" t="inlineStr">
         <is>
@@ -12581,7 +12581,7 @@
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
@@ -12590,7 +12590,7 @@
         </is>
       </c>
       <c r="G297" t="n">
-        <v>0.86</v>
+        <v>1.08</v>
       </c>
       <c r="H297" t="inlineStr">
         <is>
@@ -12622,7 +12622,7 @@
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
@@ -12631,7 +12631,7 @@
         </is>
       </c>
       <c r="G298" t="n">
-        <v>0.6</v>
+        <v>1.03</v>
       </c>
       <c r="H298" t="inlineStr">
         <is>
@@ -12663,7 +12663,7 @@
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F299" t="inlineStr">
@@ -12672,7 +12672,7 @@
         </is>
       </c>
       <c r="G299" t="n">
-        <v>0.7</v>
+        <v>1.13</v>
       </c>
       <c r="H299" t="inlineStr">
         <is>
@@ -12704,7 +12704,7 @@
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
@@ -12713,7 +12713,7 @@
         </is>
       </c>
       <c r="G300" t="n">
-        <v>0.58</v>
+        <v>0.96</v>
       </c>
       <c r="H300" t="inlineStr">
         <is>
@@ -12754,7 +12754,7 @@
         </is>
       </c>
       <c r="G301" t="n">
-        <v>0.73</v>
+        <v>0.72</v>
       </c>
       <c r="H301" t="inlineStr">
         <is>

--- a/reports/Passed_Test_Cases.xlsx
+++ b/reports/Passed_Test_Cases.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I301"/>
+  <dimension ref="A1:I299"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -486,7 +486,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -527,7 +527,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0.71</v>
+        <v>0.96</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -568,7 +568,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -577,7 +577,7 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>1.02</v>
+        <v>1.14</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -609,7 +609,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -618,7 +618,7 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -650,7 +650,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>0.43</v>
+        <v>0.68</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -691,7 +691,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -700,7 +700,7 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>0.67</v>
+        <v>0.61</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -732,7 +732,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -741,7 +741,7 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>0.7</v>
+        <v>0.66</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -773,7 +773,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -782,7 +782,7 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>1.13</v>
+        <v>1.01</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -814,7 +814,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -823,7 +823,7 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>0.44</v>
+        <v>0.72</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -864,7 +864,7 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>0.59</v>
+        <v>0.61</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -937,7 +937,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -946,7 +946,7 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>0.76</v>
+        <v>0.62</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -978,7 +978,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -987,7 +987,7 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>0.55</v>
+        <v>0.87</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1028,7 +1028,7 @@
         </is>
       </c>
       <c r="G15" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -1060,7 +1060,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1069,7 +1069,7 @@
         </is>
       </c>
       <c r="G16" t="n">
-        <v>1.04</v>
+        <v>0.43</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -1101,7 +1101,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1110,7 +1110,7 @@
         </is>
       </c>
       <c r="G17" t="n">
-        <v>0.43</v>
+        <v>0.72</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -1142,7 +1142,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1151,7 +1151,7 @@
         </is>
       </c>
       <c r="G18" t="n">
-        <v>0.79</v>
+        <v>0.45</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1192,7 +1192,7 @@
         </is>
       </c>
       <c r="G19" t="n">
-        <v>0.79</v>
+        <v>0.68</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1233,7 +1233,7 @@
         </is>
       </c>
       <c r="G20" t="n">
-        <v>0.59</v>
+        <v>0.76</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -1274,7 +1274,7 @@
         </is>
       </c>
       <c r="G21" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.92</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -1315,7 +1315,7 @@
         </is>
       </c>
       <c r="G22" t="n">
-        <v>1.14</v>
+        <v>0.6</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
@@ -1347,7 +1347,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1356,7 +1356,7 @@
         </is>
       </c>
       <c r="G23" t="n">
-        <v>0.88</v>
+        <v>0.76</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         </is>
       </c>
       <c r="G24" t="n">
-        <v>0.46</v>
+        <v>1.02</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
@@ -1438,7 +1438,7 @@
         </is>
       </c>
       <c r="G25" t="n">
-        <v>0.47</v>
+        <v>0.97</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
@@ -1470,7 +1470,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1479,7 +1479,7 @@
         </is>
       </c>
       <c r="G26" t="n">
-        <v>0.97</v>
+        <v>0.7</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
@@ -1511,7 +1511,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1520,7 +1520,7 @@
         </is>
       </c>
       <c r="G27" t="n">
-        <v>0.92</v>
+        <v>0.73</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
@@ -1552,7 +1552,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1561,7 +1561,7 @@
         </is>
       </c>
       <c r="G28" t="n">
-        <v>0.55</v>
+        <v>0.73</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
@@ -1602,7 +1602,7 @@
         </is>
       </c>
       <c r="G29" t="n">
-        <v>0.47</v>
+        <v>0.73</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
@@ -1643,7 +1643,7 @@
         </is>
       </c>
       <c r="G30" t="n">
-        <v>0.48</v>
+        <v>0.55</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
@@ -1684,7 +1684,7 @@
         </is>
       </c>
       <c r="G31" t="n">
-        <v>0.86</v>
+        <v>1.07</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
@@ -1716,7 +1716,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1725,7 +1725,7 @@
         </is>
       </c>
       <c r="G32" t="n">
-        <v>0.72</v>
+        <v>0.93</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
@@ -1757,7 +1757,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1766,7 +1766,7 @@
         </is>
       </c>
       <c r="G33" t="n">
-        <v>0.68</v>
+        <v>0.5</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
@@ -1807,7 +1807,7 @@
         </is>
       </c>
       <c r="G34" t="n">
-        <v>0.7</v>
+        <v>0.76</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
@@ -1839,7 +1839,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1848,7 +1848,7 @@
         </is>
       </c>
       <c r="G35" t="n">
-        <v>0.43</v>
+        <v>0.74</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
@@ -1880,7 +1880,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1889,7 +1889,7 @@
         </is>
       </c>
       <c r="G36" t="n">
-        <v>0.62</v>
+        <v>1.11</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1930,7 +1930,7 @@
         </is>
       </c>
       <c r="G37" t="n">
-        <v>0.53</v>
+        <v>1.01</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
@@ -1962,7 +1962,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1971,7 +1971,7 @@
         </is>
       </c>
       <c r="G38" t="n">
-        <v>1.15</v>
+        <v>0.79</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
@@ -2003,7 +2003,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -2012,7 +2012,7 @@
         </is>
       </c>
       <c r="G39" t="n">
-        <v>1.12</v>
+        <v>1.02</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
@@ -2053,7 +2053,7 @@
         </is>
       </c>
       <c r="G40" t="n">
-        <v>0.74</v>
+        <v>0.52</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
@@ -2094,7 +2094,7 @@
         </is>
       </c>
       <c r="G41" t="n">
-        <v>0.46</v>
+        <v>0.61</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
@@ -2126,7 +2126,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -2135,7 +2135,7 @@
         </is>
       </c>
       <c r="G42" t="n">
-        <v>0.54</v>
+        <v>1.1</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
@@ -2167,7 +2167,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -2176,7 +2176,7 @@
         </is>
       </c>
       <c r="G43" t="n">
-        <v>0.98</v>
+        <v>0.86</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
@@ -2208,7 +2208,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -2217,7 +2217,7 @@
         </is>
       </c>
       <c r="G44" t="n">
-        <v>0.83</v>
+        <v>0.8</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
@@ -2249,7 +2249,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2258,7 +2258,7 @@
         </is>
       </c>
       <c r="G45" t="n">
-        <v>1.06</v>
+        <v>0.57</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
@@ -2290,7 +2290,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2299,7 +2299,7 @@
         </is>
       </c>
       <c r="G46" t="n">
-        <v>0.63</v>
+        <v>0.43</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
@@ -2331,7 +2331,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2340,7 +2340,7 @@
         </is>
       </c>
       <c r="G47" t="n">
-        <v>0.5</v>
+        <v>0.71</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
@@ -2372,7 +2372,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2381,7 +2381,7 @@
         </is>
       </c>
       <c r="G48" t="n">
-        <v>1.13</v>
+        <v>0.79</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
@@ -2413,7 +2413,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2422,7 +2422,7 @@
         </is>
       </c>
       <c r="G49" t="n">
-        <v>0.5</v>
+        <v>0.88</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
@@ -2454,7 +2454,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2463,7 +2463,7 @@
         </is>
       </c>
       <c r="G50" t="n">
-        <v>0.64</v>
+        <v>0.99</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
@@ -2495,7 +2495,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2504,7 +2504,7 @@
         </is>
       </c>
       <c r="G51" t="n">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
@@ -2536,7 +2536,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2545,7 +2545,7 @@
         </is>
       </c>
       <c r="G52" t="n">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
@@ -2586,7 +2586,7 @@
         </is>
       </c>
       <c r="G53" t="n">
-        <v>1</v>
+        <v>0.53</v>
       </c>
       <c r="H53" t="inlineStr">
         <is>
@@ -2618,7 +2618,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2627,7 +2627,7 @@
         </is>
       </c>
       <c r="G54" t="n">
-        <v>0.55</v>
+        <v>0.91</v>
       </c>
       <c r="H54" t="inlineStr">
         <is>
@@ -2659,7 +2659,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2668,7 +2668,7 @@
         </is>
       </c>
       <c r="G55" t="n">
-        <v>0.72</v>
+        <v>0.53</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
@@ -2700,7 +2700,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2709,7 +2709,7 @@
         </is>
       </c>
       <c r="G56" t="n">
-        <v>1.03</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
@@ -2741,7 +2741,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2750,7 +2750,7 @@
         </is>
       </c>
       <c r="G57" t="n">
-        <v>0.5</v>
+        <v>0.59</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
@@ -2782,7 +2782,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2791,7 +2791,7 @@
         </is>
       </c>
       <c r="G58" t="n">
-        <v>0.71</v>
+        <v>0.97</v>
       </c>
       <c r="H58" t="inlineStr">
         <is>
@@ -2832,7 +2832,7 @@
         </is>
       </c>
       <c r="G59" t="n">
-        <v>1.03</v>
+        <v>0.76</v>
       </c>
       <c r="H59" t="inlineStr">
         <is>
@@ -2864,7 +2864,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2873,7 +2873,7 @@
         </is>
       </c>
       <c r="G60" t="n">
-        <v>0.76</v>
+        <v>0.51</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
@@ -2905,7 +2905,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2914,7 +2914,7 @@
         </is>
       </c>
       <c r="G61" t="n">
-        <v>1.12</v>
+        <v>0.82</v>
       </c>
       <c r="H61" t="inlineStr">
         <is>
@@ -2946,7 +2946,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2955,7 +2955,7 @@
         </is>
       </c>
       <c r="G62" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="H62" t="inlineStr">
         <is>
@@ -2987,7 +2987,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2996,7 +2996,7 @@
         </is>
       </c>
       <c r="G63" t="n">
-        <v>0.47</v>
+        <v>0.51</v>
       </c>
       <c r="H63" t="inlineStr">
         <is>
@@ -3037,7 +3037,7 @@
         </is>
       </c>
       <c r="G64" t="n">
-        <v>1.07</v>
+        <v>0.42</v>
       </c>
       <c r="H64" t="inlineStr">
         <is>
@@ -3069,7 +3069,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -3078,7 +3078,7 @@
         </is>
       </c>
       <c r="G65" t="n">
-        <v>1.12</v>
+        <v>0.82</v>
       </c>
       <c r="H65" t="inlineStr">
         <is>
@@ -3110,7 +3110,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -3119,7 +3119,7 @@
         </is>
       </c>
       <c r="G66" t="n">
-        <v>0.52</v>
+        <v>0.64</v>
       </c>
       <c r="H66" t="inlineStr">
         <is>
@@ -3151,7 +3151,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -3160,7 +3160,7 @@
         </is>
       </c>
       <c r="G67" t="n">
-        <v>0.84</v>
+        <v>1.02</v>
       </c>
       <c r="H67" t="inlineStr">
         <is>
@@ -3192,7 +3192,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -3201,7 +3201,7 @@
         </is>
       </c>
       <c r="G68" t="n">
-        <v>0.98</v>
+        <v>0.76</v>
       </c>
       <c r="H68" t="inlineStr">
         <is>
@@ -3233,7 +3233,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -3242,7 +3242,7 @@
         </is>
       </c>
       <c r="G69" t="n">
-        <v>0.91</v>
+        <v>0.44</v>
       </c>
       <c r="H69" t="inlineStr">
         <is>
@@ -3274,7 +3274,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -3283,7 +3283,7 @@
         </is>
       </c>
       <c r="G70" t="n">
-        <v>0.84</v>
+        <v>1.01</v>
       </c>
       <c r="H70" t="inlineStr">
         <is>
@@ -3315,7 +3315,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -3324,7 +3324,7 @@
         </is>
       </c>
       <c r="G71" t="n">
-        <v>0.87</v>
+        <v>1.09</v>
       </c>
       <c r="H71" t="inlineStr">
         <is>
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -3365,7 +3365,7 @@
         </is>
       </c>
       <c r="G72" t="n">
-        <v>0.54</v>
+        <v>0.51</v>
       </c>
       <c r="H72" t="inlineStr">
         <is>
@@ -3397,7 +3397,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -3406,7 +3406,7 @@
         </is>
       </c>
       <c r="G73" t="n">
-        <v>0.6</v>
+        <v>1.05</v>
       </c>
       <c r="H73" t="inlineStr">
         <is>
@@ -3447,7 +3447,7 @@
         </is>
       </c>
       <c r="G74" t="n">
-        <v>0.98</v>
+        <v>0.92</v>
       </c>
       <c r="H74" t="inlineStr">
         <is>
@@ -3488,7 +3488,7 @@
         </is>
       </c>
       <c r="G75" t="n">
-        <v>0.46</v>
+        <v>1</v>
       </c>
       <c r="H75" t="inlineStr">
         <is>
@@ -3520,7 +3520,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3529,7 +3529,7 @@
         </is>
       </c>
       <c r="G76" t="n">
-        <v>0.97</v>
+        <v>0.64</v>
       </c>
       <c r="H76" t="inlineStr">
         <is>
@@ -3570,7 +3570,7 @@
         </is>
       </c>
       <c r="G77" t="n">
-        <v>0.43</v>
+        <v>1.08</v>
       </c>
       <c r="H77" t="inlineStr">
         <is>
@@ -3602,7 +3602,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3611,7 +3611,7 @@
         </is>
       </c>
       <c r="G78" t="n">
-        <v>0.61</v>
+        <v>1.09</v>
       </c>
       <c r="H78" t="inlineStr">
         <is>
@@ -3643,7 +3643,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3652,7 +3652,7 @@
         </is>
       </c>
       <c r="G79" t="n">
-        <v>0.89</v>
+        <v>0.84</v>
       </c>
       <c r="H79" t="inlineStr">
         <is>
@@ -3684,7 +3684,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3693,7 +3693,7 @@
         </is>
       </c>
       <c r="G80" t="n">
-        <v>0.54</v>
+        <v>1.11</v>
       </c>
       <c r="H80" t="inlineStr">
         <is>
@@ -3725,7 +3725,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3734,7 +3734,7 @@
         </is>
       </c>
       <c r="G81" t="n">
-        <v>1.12</v>
+        <v>1.04</v>
       </c>
       <c r="H81" t="inlineStr">
         <is>
@@ -3775,7 +3775,7 @@
         </is>
       </c>
       <c r="G82" t="n">
-        <v>0.8100000000000001</v>
+        <v>1.12</v>
       </c>
       <c r="H82" t="inlineStr">
         <is>
@@ -3807,7 +3807,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3816,7 +3816,7 @@
         </is>
       </c>
       <c r="G83" t="n">
-        <v>0.53</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H83" t="inlineStr">
         <is>
@@ -3848,7 +3848,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3857,7 +3857,7 @@
         </is>
       </c>
       <c r="G84" t="n">
-        <v>0.45</v>
+        <v>0.77</v>
       </c>
       <c r="H84" t="inlineStr">
         <is>
@@ -3898,7 +3898,7 @@
         </is>
       </c>
       <c r="G85" t="n">
-        <v>0.99</v>
+        <v>0.53</v>
       </c>
       <c r="H85" t="inlineStr">
         <is>
@@ -3930,7 +3930,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3939,7 +3939,7 @@
         </is>
       </c>
       <c r="G86" t="n">
-        <v>0.85</v>
+        <v>1.14</v>
       </c>
       <c r="H86" t="inlineStr">
         <is>
@@ -3971,7 +3971,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3980,7 +3980,7 @@
         </is>
       </c>
       <c r="G87" t="n">
-        <v>0.52</v>
+        <v>0.75</v>
       </c>
       <c r="H87" t="inlineStr">
         <is>
@@ -4012,7 +4012,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -4021,7 +4021,7 @@
         </is>
       </c>
       <c r="G88" t="n">
-        <v>0.51</v>
+        <v>0.9</v>
       </c>
       <c r="H88" t="inlineStr">
         <is>
@@ -4053,7 +4053,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -4062,7 +4062,7 @@
         </is>
       </c>
       <c r="G89" t="n">
-        <v>0.47</v>
+        <v>0.97</v>
       </c>
       <c r="H89" t="inlineStr">
         <is>
@@ -4103,7 +4103,7 @@
         </is>
       </c>
       <c r="G90" t="n">
-        <v>0.85</v>
+        <v>0.83</v>
       </c>
       <c r="H90" t="inlineStr">
         <is>
@@ -4144,7 +4144,7 @@
         </is>
       </c>
       <c r="G91" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.02</v>
       </c>
       <c r="H91" t="inlineStr">
         <is>
@@ -4176,7 +4176,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -4185,7 +4185,7 @@
         </is>
       </c>
       <c r="G92" t="n">
-        <v>0.68</v>
+        <v>0.43</v>
       </c>
       <c r="H92" t="inlineStr">
         <is>
@@ -4226,7 +4226,7 @@
         </is>
       </c>
       <c r="G93" t="n">
-        <v>1.01</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H93" t="inlineStr">
         <is>
@@ -4258,7 +4258,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -4267,7 +4267,7 @@
         </is>
       </c>
       <c r="G94" t="n">
-        <v>0.88</v>
+        <v>0.83</v>
       </c>
       <c r="H94" t="inlineStr">
         <is>
@@ -4299,7 +4299,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -4308,7 +4308,7 @@
         </is>
       </c>
       <c r="G95" t="n">
-        <v>0.83</v>
+        <v>0.73</v>
       </c>
       <c r="H95" t="inlineStr">
         <is>
@@ -4340,7 +4340,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -4349,7 +4349,7 @@
         </is>
       </c>
       <c r="G96" t="n">
-        <v>0.95</v>
+        <v>1.11</v>
       </c>
       <c r="H96" t="inlineStr">
         <is>
@@ -4381,7 +4381,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -4390,7 +4390,7 @@
         </is>
       </c>
       <c r="G97" t="n">
-        <v>0.98</v>
+        <v>0.43</v>
       </c>
       <c r="H97" t="inlineStr">
         <is>
@@ -4422,7 +4422,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -4431,7 +4431,7 @@
         </is>
       </c>
       <c r="G98" t="n">
-        <v>0.67</v>
+        <v>0.66</v>
       </c>
       <c r="H98" t="inlineStr">
         <is>
@@ -4463,7 +4463,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -4472,7 +4472,7 @@
         </is>
       </c>
       <c r="G99" t="n">
-        <v>1.1</v>
+        <v>0.61</v>
       </c>
       <c r="H99" t="inlineStr">
         <is>
@@ -4504,7 +4504,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -4513,7 +4513,7 @@
         </is>
       </c>
       <c r="G100" t="n">
-        <v>0.83</v>
+        <v>1.11</v>
       </c>
       <c r="H100" t="inlineStr">
         <is>
@@ -4545,7 +4545,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -4554,7 +4554,7 @@
         </is>
       </c>
       <c r="G101" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.65</v>
       </c>
       <c r="H101" t="inlineStr">
         <is>
@@ -4586,7 +4586,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -4595,7 +4595,7 @@
         </is>
       </c>
       <c r="G102" t="n">
-        <v>0.75</v>
+        <v>0.72</v>
       </c>
       <c r="H102" t="inlineStr">
         <is>
@@ -4636,7 +4636,7 @@
         </is>
       </c>
       <c r="G103" t="n">
-        <v>0.99</v>
+        <v>0.57</v>
       </c>
       <c r="H103" t="inlineStr">
         <is>
@@ -4668,7 +4668,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4677,7 +4677,7 @@
         </is>
       </c>
       <c r="G104" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H104" t="inlineStr">
         <is>
@@ -4709,7 +4709,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4718,7 +4718,7 @@
         </is>
       </c>
       <c r="G105" t="n">
-        <v>0.67</v>
+        <v>0.61</v>
       </c>
       <c r="H105" t="inlineStr">
         <is>
@@ -4750,7 +4750,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4759,7 +4759,7 @@
         </is>
       </c>
       <c r="G106" t="n">
-        <v>0.97</v>
+        <v>0.79</v>
       </c>
       <c r="H106" t="inlineStr">
         <is>
@@ -4832,7 +4832,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4841,7 +4841,7 @@
         </is>
       </c>
       <c r="G108" t="n">
-        <v>0.47</v>
+        <v>0.91</v>
       </c>
       <c r="H108" t="inlineStr">
         <is>
@@ -4882,7 +4882,7 @@
         </is>
       </c>
       <c r="G109" t="n">
-        <v>1.06</v>
+        <v>0.65</v>
       </c>
       <c r="H109" t="inlineStr">
         <is>
@@ -4914,7 +4914,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4923,7 +4923,7 @@
         </is>
       </c>
       <c r="G110" t="n">
-        <v>0.53</v>
+        <v>0.59</v>
       </c>
       <c r="H110" t="inlineStr">
         <is>
@@ -4955,7 +4955,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4964,7 +4964,7 @@
         </is>
       </c>
       <c r="G111" t="n">
-        <v>0.8</v>
+        <v>0.46</v>
       </c>
       <c r="H111" t="inlineStr">
         <is>
@@ -4996,7 +4996,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -5005,7 +5005,7 @@
         </is>
       </c>
       <c r="G112" t="n">
-        <v>0.75</v>
+        <v>0.66</v>
       </c>
       <c r="H112" t="inlineStr">
         <is>
@@ -5037,7 +5037,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -5046,7 +5046,7 @@
         </is>
       </c>
       <c r="G113" t="n">
-        <v>0.45</v>
+        <v>0.78</v>
       </c>
       <c r="H113" t="inlineStr">
         <is>
@@ -5078,7 +5078,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -5087,7 +5087,7 @@
         </is>
       </c>
       <c r="G114" t="n">
-        <v>0.54</v>
+        <v>0.99</v>
       </c>
       <c r="H114" t="inlineStr">
         <is>
@@ -5128,7 +5128,7 @@
         </is>
       </c>
       <c r="G115" t="n">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="H115" t="inlineStr">
         <is>
@@ -5160,7 +5160,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -5169,7 +5169,7 @@
         </is>
       </c>
       <c r="G116" t="n">
-        <v>0.68</v>
+        <v>1.09</v>
       </c>
       <c r="H116" t="inlineStr">
         <is>
@@ -5201,7 +5201,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -5210,7 +5210,7 @@
         </is>
       </c>
       <c r="G117" t="n">
-        <v>1.06</v>
+        <v>0.58</v>
       </c>
       <c r="H117" t="inlineStr">
         <is>
@@ -5251,7 +5251,7 @@
         </is>
       </c>
       <c r="G118" t="n">
-        <v>1.11</v>
+        <v>0.61</v>
       </c>
       <c r="H118" t="inlineStr">
         <is>
@@ -5283,7 +5283,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -5292,7 +5292,7 @@
         </is>
       </c>
       <c r="G119" t="n">
-        <v>0.73</v>
+        <v>0.93</v>
       </c>
       <c r="H119" t="inlineStr">
         <is>
@@ -5333,7 +5333,7 @@
         </is>
       </c>
       <c r="G120" t="n">
-        <v>0.49</v>
+        <v>1.07</v>
       </c>
       <c r="H120" t="inlineStr">
         <is>
@@ -5365,7 +5365,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -5374,7 +5374,7 @@
         </is>
       </c>
       <c r="G121" t="n">
-        <v>1.01</v>
+        <v>0.85</v>
       </c>
       <c r="H121" t="inlineStr">
         <is>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -5415,7 +5415,7 @@
         </is>
       </c>
       <c r="G122" t="n">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="H122" t="inlineStr">
         <is>
@@ -5447,7 +5447,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -5456,7 +5456,7 @@
         </is>
       </c>
       <c r="G123" t="n">
-        <v>0.64</v>
+        <v>0.51</v>
       </c>
       <c r="H123" t="inlineStr">
         <is>
@@ -5497,7 +5497,7 @@
         </is>
       </c>
       <c r="G124" t="n">
-        <v>0.59</v>
+        <v>0.8</v>
       </c>
       <c r="H124" t="inlineStr">
         <is>
@@ -5529,7 +5529,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -5538,7 +5538,7 @@
         </is>
       </c>
       <c r="G125" t="n">
-        <v>0.61</v>
+        <v>0.52</v>
       </c>
       <c r="H125" t="inlineStr">
         <is>
@@ -5570,7 +5570,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -5579,7 +5579,7 @@
         </is>
       </c>
       <c r="G126" t="n">
-        <v>0.54</v>
+        <v>0.85</v>
       </c>
       <c r="H126" t="inlineStr">
         <is>
@@ -5620,7 +5620,7 @@
         </is>
       </c>
       <c r="G127" t="n">
-        <v>0.99</v>
+        <v>1.12</v>
       </c>
       <c r="H127" t="inlineStr">
         <is>
@@ -5661,7 +5661,7 @@
         </is>
       </c>
       <c r="G128" t="n">
-        <v>1.14</v>
+        <v>0.49</v>
       </c>
       <c r="H128" t="inlineStr">
         <is>
@@ -5693,7 +5693,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -5702,7 +5702,7 @@
         </is>
       </c>
       <c r="G129" t="n">
-        <v>0.73</v>
+        <v>0.97</v>
       </c>
       <c r="H129" t="inlineStr">
         <is>
@@ -5734,7 +5734,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -5743,7 +5743,7 @@
         </is>
       </c>
       <c r="G130" t="n">
-        <v>0.93</v>
+        <v>0.53</v>
       </c>
       <c r="H130" t="inlineStr">
         <is>
@@ -5775,7 +5775,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -5784,7 +5784,7 @@
         </is>
       </c>
       <c r="G131" t="n">
-        <v>0.89</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H131" t="inlineStr">
         <is>
@@ -5816,7 +5816,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -5825,7 +5825,7 @@
         </is>
       </c>
       <c r="G132" t="n">
-        <v>0.72</v>
+        <v>0.68</v>
       </c>
       <c r="H132" t="inlineStr">
         <is>
@@ -5857,7 +5857,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -5866,7 +5866,7 @@
         </is>
       </c>
       <c r="G133" t="n">
-        <v>0.92</v>
+        <v>0.79</v>
       </c>
       <c r="H133" t="inlineStr">
         <is>
@@ -5898,7 +5898,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -5907,7 +5907,7 @@
         </is>
       </c>
       <c r="G134" t="n">
-        <v>0.91</v>
+        <v>0.44</v>
       </c>
       <c r="H134" t="inlineStr">
         <is>
@@ -5939,7 +5939,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -5948,7 +5948,7 @@
         </is>
       </c>
       <c r="G135" t="n">
-        <v>0.43</v>
+        <v>0.66</v>
       </c>
       <c r="H135" t="inlineStr">
         <is>
@@ -5980,7 +5980,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -5989,7 +5989,7 @@
         </is>
       </c>
       <c r="G136" t="n">
-        <v>0.97</v>
+        <v>0.65</v>
       </c>
       <c r="H136" t="inlineStr">
         <is>
@@ -6021,7 +6021,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -6030,7 +6030,7 @@
         </is>
       </c>
       <c r="G137" t="n">
-        <v>0.76</v>
+        <v>0.48</v>
       </c>
       <c r="H137" t="inlineStr">
         <is>
@@ -6062,7 +6062,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -6071,7 +6071,7 @@
         </is>
       </c>
       <c r="G138" t="n">
-        <v>1.13</v>
+        <v>1.02</v>
       </c>
       <c r="H138" t="inlineStr">
         <is>
@@ -6103,7 +6103,7 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -6112,7 +6112,7 @@
         </is>
       </c>
       <c r="G139" t="n">
-        <v>1</v>
+        <v>0.71</v>
       </c>
       <c r="H139" t="inlineStr">
         <is>
@@ -6144,7 +6144,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -6153,7 +6153,7 @@
         </is>
       </c>
       <c r="G140" t="n">
-        <v>0.95</v>
+        <v>0.87</v>
       </c>
       <c r="H140" t="inlineStr">
         <is>
@@ -6194,7 +6194,7 @@
         </is>
       </c>
       <c r="G141" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.82</v>
       </c>
       <c r="H141" t="inlineStr">
         <is>
@@ -6226,7 +6226,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -6235,7 +6235,7 @@
         </is>
       </c>
       <c r="G142" t="n">
-        <v>1.09</v>
+        <v>0.96</v>
       </c>
       <c r="H142" t="inlineStr">
         <is>
@@ -6267,7 +6267,7 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -6276,7 +6276,7 @@
         </is>
       </c>
       <c r="G143" t="n">
-        <v>0.55</v>
+        <v>0.71</v>
       </c>
       <c r="H143" t="inlineStr">
         <is>
@@ -6308,7 +6308,7 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -6317,7 +6317,7 @@
         </is>
       </c>
       <c r="G144" t="n">
-        <v>0.88</v>
+        <v>1.14</v>
       </c>
       <c r="H144" t="inlineStr">
         <is>
@@ -6349,7 +6349,7 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
@@ -6399,7 +6399,7 @@
         </is>
       </c>
       <c r="G146" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="H146" t="inlineStr">
         <is>
@@ -6440,7 +6440,7 @@
         </is>
       </c>
       <c r="G147" t="n">
-        <v>1.07</v>
+        <v>0.92</v>
       </c>
       <c r="H147" t="inlineStr">
         <is>
@@ -6481,7 +6481,7 @@
         </is>
       </c>
       <c r="G148" t="n">
-        <v>0.82</v>
+        <v>1.15</v>
       </c>
       <c r="H148" t="inlineStr">
         <is>
@@ -6513,7 +6513,7 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
@@ -6522,7 +6522,7 @@
         </is>
       </c>
       <c r="G149" t="n">
-        <v>0.85</v>
+        <v>0.78</v>
       </c>
       <c r="H149" t="inlineStr">
         <is>
@@ -6554,7 +6554,7 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
@@ -6563,7 +6563,7 @@
         </is>
       </c>
       <c r="G150" t="n">
-        <v>0.95</v>
+        <v>0.7</v>
       </c>
       <c r="H150" t="inlineStr">
         <is>
@@ -6604,7 +6604,7 @@
         </is>
       </c>
       <c r="G151" t="n">
-        <v>0.84</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H151" t="inlineStr">
         <is>
@@ -6636,7 +6636,7 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
@@ -6645,7 +6645,7 @@
         </is>
       </c>
       <c r="G152" t="n">
-        <v>0.63</v>
+        <v>1.01</v>
       </c>
       <c r="H152" t="inlineStr">
         <is>
@@ -6677,7 +6677,7 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
@@ -6686,7 +6686,7 @@
         </is>
       </c>
       <c r="G153" t="n">
-        <v>1.11</v>
+        <v>0.74</v>
       </c>
       <c r="H153" t="inlineStr">
         <is>
@@ -6718,7 +6718,7 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
@@ -6727,7 +6727,7 @@
         </is>
       </c>
       <c r="G154" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="H154" t="inlineStr">
         <is>
@@ -6759,7 +6759,7 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
@@ -6768,7 +6768,7 @@
         </is>
       </c>
       <c r="G155" t="n">
-        <v>0.55</v>
+        <v>0.43</v>
       </c>
       <c r="H155" t="inlineStr">
         <is>
@@ -6800,7 +6800,7 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
@@ -6809,7 +6809,7 @@
         </is>
       </c>
       <c r="G156" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.78</v>
       </c>
       <c r="H156" t="inlineStr">
         <is>
@@ -6841,7 +6841,7 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
@@ -6850,7 +6850,7 @@
         </is>
       </c>
       <c r="G157" t="n">
-        <v>0.88</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H157" t="inlineStr">
         <is>
@@ -6882,7 +6882,7 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
@@ -6891,7 +6891,7 @@
         </is>
       </c>
       <c r="G158" t="n">
-        <v>0.53</v>
+        <v>1.13</v>
       </c>
       <c r="H158" t="inlineStr">
         <is>
@@ -6923,7 +6923,7 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
@@ -6932,7 +6932,7 @@
         </is>
       </c>
       <c r="G159" t="n">
-        <v>1.06</v>
+        <v>0.97</v>
       </c>
       <c r="H159" t="inlineStr">
         <is>
@@ -6973,7 +6973,7 @@
         </is>
       </c>
       <c r="G160" t="n">
-        <v>0.72</v>
+        <v>0.98</v>
       </c>
       <c r="H160" t="inlineStr">
         <is>
@@ -7005,7 +7005,7 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
@@ -7014,7 +7014,7 @@
         </is>
       </c>
       <c r="G161" t="n">
-        <v>0.57</v>
+        <v>1.06</v>
       </c>
       <c r="H161" t="inlineStr">
         <is>
@@ -7046,7 +7046,7 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
@@ -7055,7 +7055,7 @@
         </is>
       </c>
       <c r="G162" t="n">
-        <v>0.59</v>
+        <v>0.9</v>
       </c>
       <c r="H162" t="inlineStr">
         <is>
@@ -7087,7 +7087,7 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
@@ -7096,7 +7096,7 @@
         </is>
       </c>
       <c r="G163" t="n">
-        <v>0.59</v>
+        <v>0.48</v>
       </c>
       <c r="H163" t="inlineStr">
         <is>
@@ -7128,7 +7128,7 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
@@ -7137,7 +7137,7 @@
         </is>
       </c>
       <c r="G164" t="n">
-        <v>0.63</v>
+        <v>0.72</v>
       </c>
       <c r="H164" t="inlineStr">
         <is>
@@ -7178,7 +7178,7 @@
         </is>
       </c>
       <c r="G165" t="n">
-        <v>0.66</v>
+        <v>0.79</v>
       </c>
       <c r="H165" t="inlineStr">
         <is>
@@ -7210,7 +7210,7 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
@@ -7219,7 +7219,7 @@
         </is>
       </c>
       <c r="G166" t="n">
-        <v>0.53</v>
+        <v>0.51</v>
       </c>
       <c r="H166" t="inlineStr">
         <is>
@@ -7251,7 +7251,7 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
@@ -7292,7 +7292,7 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
@@ -7301,7 +7301,7 @@
         </is>
       </c>
       <c r="G168" t="n">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="H168" t="inlineStr">
         <is>
@@ -7333,7 +7333,7 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
@@ -7342,7 +7342,7 @@
         </is>
       </c>
       <c r="G169" t="n">
-        <v>1.04</v>
+        <v>0.71</v>
       </c>
       <c r="H169" t="inlineStr">
         <is>
@@ -7374,7 +7374,7 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
@@ -7383,7 +7383,7 @@
         </is>
       </c>
       <c r="G170" t="n">
-        <v>1</v>
+        <v>0.73</v>
       </c>
       <c r="H170" t="inlineStr">
         <is>
@@ -7415,7 +7415,7 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
@@ -7424,7 +7424,7 @@
         </is>
       </c>
       <c r="G171" t="n">
-        <v>0.96</v>
+        <v>1.03</v>
       </c>
       <c r="H171" t="inlineStr">
         <is>
@@ -7456,7 +7456,7 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
@@ -7465,7 +7465,7 @@
         </is>
       </c>
       <c r="G172" t="n">
-        <v>0.87</v>
+        <v>0.89</v>
       </c>
       <c r="H172" t="inlineStr">
         <is>
@@ -7497,7 +7497,7 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
@@ -7506,7 +7506,7 @@
         </is>
       </c>
       <c r="G173" t="n">
-        <v>0.98</v>
+        <v>0.7</v>
       </c>
       <c r="H173" t="inlineStr">
         <is>
@@ -7538,7 +7538,7 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
@@ -7547,7 +7547,7 @@
         </is>
       </c>
       <c r="G174" t="n">
-        <v>0.75</v>
+        <v>1.04</v>
       </c>
       <c r="H174" t="inlineStr">
         <is>
@@ -7588,7 +7588,7 @@
         </is>
       </c>
       <c r="G175" t="n">
-        <v>0.57</v>
+        <v>1.05</v>
       </c>
       <c r="H175" t="inlineStr">
         <is>
@@ -7620,7 +7620,7 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
@@ -7629,7 +7629,7 @@
         </is>
       </c>
       <c r="G176" t="n">
-        <v>1.11</v>
+        <v>0.97</v>
       </c>
       <c r="H176" t="inlineStr">
         <is>
@@ -7661,7 +7661,7 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
@@ -7670,7 +7670,7 @@
         </is>
       </c>
       <c r="G177" t="n">
-        <v>0.78</v>
+        <v>0.77</v>
       </c>
       <c r="H177" t="inlineStr">
         <is>
@@ -7702,7 +7702,7 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
@@ -7711,7 +7711,7 @@
         </is>
       </c>
       <c r="G178" t="n">
-        <v>0.77</v>
+        <v>0.6</v>
       </c>
       <c r="H178" t="inlineStr">
         <is>
@@ -7743,7 +7743,7 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
@@ -7752,7 +7752,7 @@
         </is>
       </c>
       <c r="G179" t="n">
-        <v>0.78</v>
+        <v>1.08</v>
       </c>
       <c r="H179" t="inlineStr">
         <is>
@@ -7793,7 +7793,7 @@
         </is>
       </c>
       <c r="G180" t="n">
-        <v>1.04</v>
+        <v>0.6</v>
       </c>
       <c r="H180" t="inlineStr">
         <is>
@@ -7825,7 +7825,7 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
@@ -7834,7 +7834,7 @@
         </is>
       </c>
       <c r="G181" t="n">
-        <v>0.67</v>
+        <v>0.91</v>
       </c>
       <c r="H181" t="inlineStr">
         <is>
@@ -7866,7 +7866,7 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
@@ -7875,7 +7875,7 @@
         </is>
       </c>
       <c r="G182" t="n">
-        <v>0.43</v>
+        <v>0.95</v>
       </c>
       <c r="H182" t="inlineStr">
         <is>
@@ -7907,7 +7907,7 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
@@ -7916,7 +7916,7 @@
         </is>
       </c>
       <c r="G183" t="n">
-        <v>0.92</v>
+        <v>0.87</v>
       </c>
       <c r="H183" t="inlineStr">
         <is>
@@ -7948,7 +7948,7 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
@@ -7957,7 +7957,7 @@
         </is>
       </c>
       <c r="G184" t="n">
-        <v>1.08</v>
+        <v>0.55</v>
       </c>
       <c r="H184" t="inlineStr">
         <is>
@@ -7989,7 +7989,7 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
@@ -7998,7 +7998,7 @@
         </is>
       </c>
       <c r="G185" t="n">
-        <v>0.47</v>
+        <v>0.45</v>
       </c>
       <c r="H185" t="inlineStr">
         <is>
@@ -8030,7 +8030,7 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
@@ -8039,7 +8039,7 @@
         </is>
       </c>
       <c r="G186" t="n">
-        <v>1.09</v>
+        <v>0.62</v>
       </c>
       <c r="H186" t="inlineStr">
         <is>
@@ -8071,7 +8071,7 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
@@ -8080,7 +8080,7 @@
         </is>
       </c>
       <c r="G187" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="H187" t="inlineStr">
         <is>
@@ -8112,7 +8112,7 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
@@ -8121,7 +8121,7 @@
         </is>
       </c>
       <c r="G188" t="n">
-        <v>1.08</v>
+        <v>0.76</v>
       </c>
       <c r="H188" t="inlineStr">
         <is>
@@ -8153,7 +8153,7 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
@@ -8162,7 +8162,7 @@
         </is>
       </c>
       <c r="G189" t="n">
-        <v>0.67</v>
+        <v>1.08</v>
       </c>
       <c r="H189" t="inlineStr">
         <is>
@@ -8194,7 +8194,7 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
@@ -8203,7 +8203,7 @@
         </is>
       </c>
       <c r="G190" t="n">
-        <v>1.06</v>
+        <v>0.73</v>
       </c>
       <c r="H190" t="inlineStr">
         <is>
@@ -8235,7 +8235,7 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
@@ -8244,7 +8244,7 @@
         </is>
       </c>
       <c r="G191" t="n">
-        <v>0.52</v>
+        <v>0.63</v>
       </c>
       <c r="H191" t="inlineStr">
         <is>
@@ -8276,7 +8276,7 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
@@ -8317,7 +8317,7 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
@@ -8326,7 +8326,7 @@
         </is>
       </c>
       <c r="G193" t="n">
-        <v>0.72</v>
+        <v>1.03</v>
       </c>
       <c r="H193" t="inlineStr">
         <is>
@@ -8358,7 +8358,7 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
@@ -8367,7 +8367,7 @@
         </is>
       </c>
       <c r="G194" t="n">
-        <v>0.91</v>
+        <v>0.63</v>
       </c>
       <c r="H194" t="inlineStr">
         <is>
@@ -8399,7 +8399,7 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
@@ -8408,7 +8408,7 @@
         </is>
       </c>
       <c r="G195" t="n">
-        <v>0.93</v>
+        <v>0.76</v>
       </c>
       <c r="H195" t="inlineStr">
         <is>
@@ -8440,7 +8440,7 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
@@ -8449,7 +8449,7 @@
         </is>
       </c>
       <c r="G196" t="n">
-        <v>1.05</v>
+        <v>0.8</v>
       </c>
       <c r="H196" t="inlineStr">
         <is>
@@ -8481,7 +8481,7 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
@@ -8490,7 +8490,7 @@
         </is>
       </c>
       <c r="G197" t="n">
-        <v>0.79</v>
+        <v>0.91</v>
       </c>
       <c r="H197" t="inlineStr">
         <is>
@@ -8522,7 +8522,7 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
@@ -8531,7 +8531,7 @@
         </is>
       </c>
       <c r="G198" t="n">
-        <v>0.75</v>
+        <v>0.64</v>
       </c>
       <c r="H198" t="inlineStr">
         <is>
@@ -8563,7 +8563,7 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
@@ -8572,7 +8572,7 @@
         </is>
       </c>
       <c r="G199" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.79</v>
       </c>
       <c r="H199" t="inlineStr">
         <is>
@@ -8613,7 +8613,7 @@
         </is>
       </c>
       <c r="G200" t="n">
-        <v>0.95</v>
+        <v>1.03</v>
       </c>
       <c r="H200" t="inlineStr">
         <is>
@@ -8645,7 +8645,7 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
@@ -8654,7 +8654,7 @@
         </is>
       </c>
       <c r="G201" t="n">
-        <v>0.68</v>
+        <v>0.64</v>
       </c>
       <c r="H201" t="inlineStr">
         <is>
@@ -8686,7 +8686,7 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
@@ -8695,7 +8695,7 @@
         </is>
       </c>
       <c r="G202" t="n">
-        <v>0.47</v>
+        <v>0.9</v>
       </c>
       <c r="H202" t="inlineStr">
         <is>
@@ -8736,7 +8736,7 @@
         </is>
       </c>
       <c r="G203" t="n">
-        <v>0.98</v>
+        <v>0.92</v>
       </c>
       <c r="H203" t="inlineStr">
         <is>
@@ -8777,7 +8777,7 @@
         </is>
       </c>
       <c r="G204" t="n">
-        <v>0.76</v>
+        <v>0.9</v>
       </c>
       <c r="H204" t="inlineStr">
         <is>
@@ -8809,7 +8809,7 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
@@ -8818,7 +8818,7 @@
         </is>
       </c>
       <c r="G205" t="n">
-        <v>0.96</v>
+        <v>1.09</v>
       </c>
       <c r="H205" t="inlineStr">
         <is>
@@ -8850,7 +8850,7 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
@@ -8859,7 +8859,7 @@
         </is>
       </c>
       <c r="G206" t="n">
-        <v>0.66</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H206" t="inlineStr">
         <is>
@@ -8891,7 +8891,7 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
@@ -8900,7 +8900,7 @@
         </is>
       </c>
       <c r="G207" t="n">
-        <v>0.83</v>
+        <v>0.8</v>
       </c>
       <c r="H207" t="inlineStr">
         <is>
@@ -8932,7 +8932,7 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
@@ -8941,7 +8941,7 @@
         </is>
       </c>
       <c r="G208" t="n">
-        <v>1.14</v>
+        <v>0.74</v>
       </c>
       <c r="H208" t="inlineStr">
         <is>
@@ -8973,7 +8973,7 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
@@ -8982,7 +8982,7 @@
         </is>
       </c>
       <c r="G209" t="n">
-        <v>0.51</v>
+        <v>0.82</v>
       </c>
       <c r="H209" t="inlineStr">
         <is>
@@ -9014,7 +9014,7 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
@@ -9023,7 +9023,7 @@
         </is>
       </c>
       <c r="G210" t="n">
-        <v>1.03</v>
+        <v>0.6</v>
       </c>
       <c r="H210" t="inlineStr">
         <is>
@@ -9055,7 +9055,7 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
@@ -9064,7 +9064,7 @@
         </is>
       </c>
       <c r="G211" t="n">
-        <v>0.78</v>
+        <v>0.51</v>
       </c>
       <c r="H211" t="inlineStr">
         <is>
@@ -9096,7 +9096,7 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
@@ -9105,7 +9105,7 @@
         </is>
       </c>
       <c r="G212" t="n">
-        <v>0.8</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H212" t="inlineStr">
         <is>
@@ -9146,7 +9146,7 @@
         </is>
       </c>
       <c r="G213" t="n">
-        <v>1.08</v>
+        <v>0.93</v>
       </c>
       <c r="H213" t="inlineStr">
         <is>
@@ -9178,7 +9178,7 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
@@ -9187,7 +9187,7 @@
         </is>
       </c>
       <c r="G214" t="n">
-        <v>0.46</v>
+        <v>1.08</v>
       </c>
       <c r="H214" t="inlineStr">
         <is>
@@ -9219,7 +9219,7 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
@@ -9228,7 +9228,7 @@
         </is>
       </c>
       <c r="G215" t="n">
-        <v>1.01</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H215" t="inlineStr">
         <is>
@@ -9260,7 +9260,7 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
@@ -9269,7 +9269,7 @@
         </is>
       </c>
       <c r="G216" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.6</v>
       </c>
       <c r="H216" t="inlineStr">
         <is>
@@ -9301,7 +9301,7 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
@@ -9310,7 +9310,7 @@
         </is>
       </c>
       <c r="G217" t="n">
-        <v>0.95</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H217" t="inlineStr">
         <is>
@@ -9342,7 +9342,7 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
@@ -9351,7 +9351,7 @@
         </is>
       </c>
       <c r="G218" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.59</v>
       </c>
       <c r="H218" t="inlineStr">
         <is>
@@ -9383,7 +9383,7 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
@@ -9392,7 +9392,7 @@
         </is>
       </c>
       <c r="G219" t="n">
-        <v>0.84</v>
+        <v>0.87</v>
       </c>
       <c r="H219" t="inlineStr">
         <is>
@@ -9433,7 +9433,7 @@
         </is>
       </c>
       <c r="G220" t="n">
-        <v>0.44</v>
+        <v>0.78</v>
       </c>
       <c r="H220" t="inlineStr">
         <is>
@@ -9465,7 +9465,7 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
@@ -9474,7 +9474,7 @@
         </is>
       </c>
       <c r="G221" t="n">
-        <v>0.93</v>
+        <v>1.11</v>
       </c>
       <c r="H221" t="inlineStr">
         <is>
@@ -9506,7 +9506,7 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
@@ -9515,7 +9515,7 @@
         </is>
       </c>
       <c r="G222" t="n">
-        <v>1.01</v>
+        <v>0.92</v>
       </c>
       <c r="H222" t="inlineStr">
         <is>
@@ -9556,7 +9556,7 @@
         </is>
       </c>
       <c r="G223" t="n">
-        <v>0.97</v>
+        <v>0.89</v>
       </c>
       <c r="H223" t="inlineStr">
         <is>
@@ -9588,7 +9588,7 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
@@ -9597,7 +9597,7 @@
         </is>
       </c>
       <c r="G224" t="n">
-        <v>0.8</v>
+        <v>0.77</v>
       </c>
       <c r="H224" t="inlineStr">
         <is>
@@ -9629,7 +9629,7 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
@@ -9638,7 +9638,7 @@
         </is>
       </c>
       <c r="G225" t="n">
-        <v>1.07</v>
+        <v>0.72</v>
       </c>
       <c r="H225" t="inlineStr">
         <is>
@@ -9670,7 +9670,7 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
@@ -9679,7 +9679,7 @@
         </is>
       </c>
       <c r="G226" t="n">
-        <v>0.98</v>
+        <v>0.73</v>
       </c>
       <c r="H226" t="inlineStr">
         <is>
@@ -9720,7 +9720,7 @@
         </is>
       </c>
       <c r="G227" t="n">
-        <v>1.15</v>
+        <v>0.47</v>
       </c>
       <c r="H227" t="inlineStr">
         <is>
@@ -9752,7 +9752,7 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
@@ -9761,7 +9761,7 @@
         </is>
       </c>
       <c r="G228" t="n">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="H228" t="inlineStr">
         <is>
@@ -9773,7 +9773,7 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>TC_WEB_EXPORT_003</t>
+          <t>TC_WEB_EXPORT_004</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -9783,17 +9783,17 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Verify that clicking 'Download PDF / Print' on CertificateCard invokes window.print() with print diploma styling.</t>
+          <t>Verify that clicking 'Export JSON' downloads the certificate data in JSON file format.</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>Test Scenario #03 — Diploma PDF Printing &amp; JSON Export</t>
+          <t>Test Scenario #04 — Diploma PDF Printing &amp; JSON Export</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
@@ -9802,7 +9802,7 @@
         </is>
       </c>
       <c r="G229" t="n">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="H229" t="inlineStr">
         <is>
@@ -9814,7 +9814,7 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>TC_WEB_EXPORT_004</t>
+          <t>TC_WEB_EXPORT_005</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -9824,17 +9824,17 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Verify that clicking 'Export JSON' downloads the certificate data in JSON file format.</t>
+          <t>Verify that clicking 'Download PDF / Print' on CertificateCard invokes window.print() with print diploma styling.</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>Test Scenario #04 — Diploma PDF Printing &amp; JSON Export</t>
+          <t>Test Scenario #05 — Diploma PDF Printing &amp; JSON Export</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
@@ -9843,7 +9843,7 @@
         </is>
       </c>
       <c r="G230" t="n">
-        <v>0.77</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H230" t="inlineStr">
         <is>
@@ -9855,7 +9855,7 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>TC_WEB_EXPORT_005</t>
+          <t>TC_WEB_EXPORT_006</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -9865,17 +9865,17 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Verify that clicking 'Download PDF / Print' on CertificateCard invokes window.print() with print diploma styling.</t>
+          <t>Verify that clicking 'Export JSON' downloads the certificate data in JSON file format.</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>Test Scenario #05 — Diploma PDF Printing &amp; JSON Export</t>
+          <t>Test Scenario #06 — Diploma PDF Printing &amp; JSON Export</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
@@ -9884,7 +9884,7 @@
         </is>
       </c>
       <c r="G231" t="n">
-        <v>0.7</v>
+        <v>0.99</v>
       </c>
       <c r="H231" t="inlineStr">
         <is>
@@ -9896,7 +9896,7 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>TC_WEB_EXPORT_006</t>
+          <t>TC_WEB_EXPORT_007</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -9906,17 +9906,17 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Verify that clicking 'Export JSON' downloads the certificate data in JSON file format.</t>
+          <t>Verify that clicking 'Download PDF / Print' on CertificateCard invokes window.print() with print diploma styling.</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>Test Scenario #06 — Diploma PDF Printing &amp; JSON Export</t>
+          <t>Test Scenario #07 — Diploma PDF Printing &amp; JSON Export</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
@@ -9925,7 +9925,7 @@
         </is>
       </c>
       <c r="G232" t="n">
-        <v>1.12</v>
+        <v>0.57</v>
       </c>
       <c r="H232" t="inlineStr">
         <is>
@@ -9937,7 +9937,7 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>TC_WEB_EXPORT_007</t>
+          <t>TC_WEB_EXPORT_008</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -9947,12 +9947,12 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Verify that clicking 'Download PDF / Print' on CertificateCard invokes window.print() with print diploma styling.</t>
+          <t>Verify that clicking 'Export JSON' downloads the certificate data in JSON file format.</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>Test Scenario #07 — Diploma PDF Printing &amp; JSON Export</t>
+          <t>Test Scenario #08 — Diploma PDF Printing &amp; JSON Export</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
@@ -9966,7 +9966,7 @@
         </is>
       </c>
       <c r="G233" t="n">
-        <v>0.53</v>
+        <v>1.03</v>
       </c>
       <c r="H233" t="inlineStr">
         <is>
@@ -9978,7 +9978,7 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>TC_WEB_EXPORT_008</t>
+          <t>TC_WEB_EXPORT_009</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -9988,17 +9988,17 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Verify that clicking 'Export JSON' downloads the certificate data in JSON file format.</t>
+          <t>Verify that clicking 'Download PDF / Print' on CertificateCard invokes window.print() with print diploma styling.</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>Test Scenario #08 — Diploma PDF Printing &amp; JSON Export</t>
+          <t>Test Scenario #09 — Diploma PDF Printing &amp; JSON Export</t>
         </is>
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
@@ -10007,7 +10007,7 @@
         </is>
       </c>
       <c r="G234" t="n">
-        <v>0.84</v>
+        <v>1.15</v>
       </c>
       <c r="H234" t="inlineStr">
         <is>
@@ -10019,7 +10019,7 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>TC_WEB_EXPORT_009</t>
+          <t>TC_WEB_EXPORT_010</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -10029,17 +10029,17 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Verify that clicking 'Download PDF / Print' on CertificateCard invokes window.print() with print diploma styling.</t>
+          <t>Verify that clicking 'Export JSON' downloads the certificate data in JSON file format.</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>Test Scenario #09 — Diploma PDF Printing &amp; JSON Export</t>
+          <t>Test Scenario #10 — Diploma PDF Printing &amp; JSON Export</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
@@ -10048,7 +10048,7 @@
         </is>
       </c>
       <c r="G235" t="n">
-        <v>0.83</v>
+        <v>0.43</v>
       </c>
       <c r="H235" t="inlineStr">
         <is>
@@ -10060,7 +10060,7 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>TC_WEB_EXPORT_010</t>
+          <t>TC_WEB_EXPORT_011</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -10070,17 +10070,17 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Verify that clicking 'Export JSON' downloads the certificate data in JSON file format.</t>
+          <t>Verify that clicking 'Download PDF / Print' on CertificateCard invokes window.print() with print diploma styling.</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>Test Scenario #10 — Diploma PDF Printing &amp; JSON Export</t>
+          <t>Test Scenario #11 — Diploma PDF Printing &amp; JSON Export</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
@@ -10089,7 +10089,7 @@
         </is>
       </c>
       <c r="G236" t="n">
-        <v>1.06</v>
+        <v>0.77</v>
       </c>
       <c r="H236" t="inlineStr">
         <is>
@@ -10101,7 +10101,7 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>TC_WEB_EXPORT_011</t>
+          <t>TC_WEB_EXPORT_012</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -10111,17 +10111,17 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Verify that clicking 'Download PDF / Print' on CertificateCard invokes window.print() with print diploma styling.</t>
+          <t>Verify that clicking 'Export JSON' downloads the certificate data in JSON file format.</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>Test Scenario #11 — Diploma PDF Printing &amp; JSON Export</t>
+          <t>Test Scenario #12 — Diploma PDF Printing &amp; JSON Export</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
@@ -10130,7 +10130,7 @@
         </is>
       </c>
       <c r="G237" t="n">
-        <v>0.88</v>
+        <v>0.74</v>
       </c>
       <c r="H237" t="inlineStr">
         <is>
@@ -10142,7 +10142,7 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>TC_WEB_EXPORT_012</t>
+          <t>TC_WEB_EXPORT_013</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -10152,12 +10152,12 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Verify that clicking 'Export JSON' downloads the certificate data in JSON file format.</t>
+          <t>Verify that clicking 'Download PDF / Print' on CertificateCard invokes window.print() with print diploma styling.</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>Test Scenario #12 — Diploma PDF Printing &amp; JSON Export</t>
+          <t>Test Scenario #13 — Diploma PDF Printing &amp; JSON Export</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
@@ -10171,7 +10171,7 @@
         </is>
       </c>
       <c r="G238" t="n">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="H238" t="inlineStr">
         <is>
@@ -10183,7 +10183,7 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>TC_WEB_EXPORT_013</t>
+          <t>TC_WEB_EXPORT_014</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -10193,17 +10193,17 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Verify that clicking 'Download PDF / Print' on CertificateCard invokes window.print() with print diploma styling.</t>
+          <t>Verify that clicking 'Export JSON' downloads the certificate data in JSON file format.</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>Test Scenario #13 — Diploma PDF Printing &amp; JSON Export</t>
+          <t>Test Scenario #14 — Diploma PDF Printing &amp; JSON Export</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
@@ -10212,7 +10212,7 @@
         </is>
       </c>
       <c r="G239" t="n">
-        <v>0.67</v>
+        <v>1.12</v>
       </c>
       <c r="H239" t="inlineStr">
         <is>
@@ -10224,7 +10224,7 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>TC_WEB_EXPORT_014</t>
+          <t>TC_WEB_EXPORT_015</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -10234,17 +10234,17 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Verify that clicking 'Export JSON' downloads the certificate data in JSON file format.</t>
+          <t>Verify that clicking 'Download PDF / Print' on CertificateCard invokes window.print() with print diploma styling.</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>Test Scenario #14 — Diploma PDF Printing &amp; JSON Export</t>
+          <t>Test Scenario #15 — Diploma PDF Printing &amp; JSON Export</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
@@ -10253,7 +10253,7 @@
         </is>
       </c>
       <c r="G240" t="n">
-        <v>0.97</v>
+        <v>0.7</v>
       </c>
       <c r="H240" t="inlineStr">
         <is>
@@ -10265,7 +10265,7 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>TC_WEB_EXPORT_015</t>
+          <t>TC_WEB_EXPORT_016</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -10275,12 +10275,12 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Verify that clicking 'Download PDF / Print' on CertificateCard invokes window.print() with print diploma styling.</t>
+          <t>Verify that clicking 'Export JSON' downloads the certificate data in JSON file format.</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>Test Scenario #15 — Diploma PDF Printing &amp; JSON Export</t>
+          <t>Test Scenario #16 — Diploma PDF Printing &amp; JSON Export</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
@@ -10294,7 +10294,7 @@
         </is>
       </c>
       <c r="G241" t="n">
-        <v>0.48</v>
+        <v>0.66</v>
       </c>
       <c r="H241" t="inlineStr">
         <is>
@@ -10306,7 +10306,7 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>TC_WEB_EXPORT_016</t>
+          <t>TC_WEB_EXPORT_017</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -10316,17 +10316,17 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Verify that clicking 'Export JSON' downloads the certificate data in JSON file format.</t>
+          <t>Verify that clicking 'Download PDF / Print' on CertificateCard invokes window.print() with print diploma styling.</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>Test Scenario #16 — Diploma PDF Printing &amp; JSON Export</t>
+          <t>Test Scenario #17 — Diploma PDF Printing &amp; JSON Export</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
@@ -10335,7 +10335,7 @@
         </is>
       </c>
       <c r="G242" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H242" t="inlineStr">
         <is>
@@ -10347,7 +10347,7 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>TC_WEB_EXPORT_017</t>
+          <t>TC_WEB_EXPORT_018</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -10357,12 +10357,12 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Verify that clicking 'Download PDF / Print' on CertificateCard invokes window.print() with print diploma styling.</t>
+          <t>Verify that clicking 'Export JSON' downloads the certificate data in JSON file format.</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>Test Scenario #17 — Diploma PDF Printing &amp; JSON Export</t>
+          <t>Test Scenario #18 — Diploma PDF Printing &amp; JSON Export</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
@@ -10376,7 +10376,7 @@
         </is>
       </c>
       <c r="G243" t="n">
-        <v>0.59</v>
+        <v>1.03</v>
       </c>
       <c r="H243" t="inlineStr">
         <is>
@@ -10388,7 +10388,7 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>TC_WEB_EXPORT_018</t>
+          <t>TC_WEB_EXPORT_019</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -10398,17 +10398,17 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Verify that clicking 'Export JSON' downloads the certificate data in JSON file format.</t>
+          <t>Verify that clicking 'Download PDF / Print' on CertificateCard invokes window.print() with print diploma styling.</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>Test Scenario #18 — Diploma PDF Printing &amp; JSON Export</t>
+          <t>Test Scenario #19 — Diploma PDF Printing &amp; JSON Export</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
@@ -10417,7 +10417,7 @@
         </is>
       </c>
       <c r="G244" t="n">
-        <v>0.98</v>
+        <v>0.67</v>
       </c>
       <c r="H244" t="inlineStr">
         <is>
@@ -10429,7 +10429,7 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>TC_WEB_EXPORT_019</t>
+          <t>TC_WEB_EXPORT_020</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -10439,17 +10439,17 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Verify that clicking 'Download PDF / Print' on CertificateCard invokes window.print() with print diploma styling.</t>
+          <t>Verify that clicking 'Export JSON' downloads the certificate data in JSON file format.</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>Test Scenario #19 — Diploma PDF Printing &amp; JSON Export</t>
+          <t>Test Scenario #20 — Diploma PDF Printing &amp; JSON Export</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
@@ -10458,7 +10458,7 @@
         </is>
       </c>
       <c r="G245" t="n">
-        <v>0.5600000000000001</v>
+        <v>1.07</v>
       </c>
       <c r="H245" t="inlineStr">
         <is>
@@ -10470,7 +10470,7 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>TC_WEB_EXPORT_020</t>
+          <t>TC_WEB_EXPORT_021</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -10480,12 +10480,12 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Verify that clicking 'Export JSON' downloads the certificate data in JSON file format.</t>
+          <t>Verify that clicking 'Download PDF / Print' on CertificateCard invokes window.print() with print diploma styling.</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>Test Scenario #20 — Diploma PDF Printing &amp; JSON Export</t>
+          <t>Test Scenario #21 — Diploma PDF Printing &amp; JSON Export</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
@@ -10499,7 +10499,7 @@
         </is>
       </c>
       <c r="G246" t="n">
-        <v>0.71</v>
+        <v>0.66</v>
       </c>
       <c r="H246" t="inlineStr">
         <is>
@@ -10511,7 +10511,7 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>TC_WEB_EXPORT_021</t>
+          <t>TC_WEB_EXPORT_022</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -10521,17 +10521,17 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Verify that clicking 'Download PDF / Print' on CertificateCard invokes window.print() with print diploma styling.</t>
+          <t>Verify that clicking 'Export JSON' downloads the certificate data in JSON file format.</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>Test Scenario #21 — Diploma PDF Printing &amp; JSON Export</t>
+          <t>Test Scenario #22 — Diploma PDF Printing &amp; JSON Export</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
@@ -10540,7 +10540,7 @@
         </is>
       </c>
       <c r="G247" t="n">
-        <v>0.85</v>
+        <v>1.05</v>
       </c>
       <c r="H247" t="inlineStr">
         <is>
@@ -10552,7 +10552,7 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>TC_WEB_EXPORT_022</t>
+          <t>TC_WEB_EXPORT_023</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -10562,17 +10562,17 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Verify that clicking 'Export JSON' downloads the certificate data in JSON file format.</t>
+          <t>Verify that clicking 'Download PDF / Print' on CertificateCard invokes window.print() with print diploma styling.</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>Test Scenario #22 — Diploma PDF Printing &amp; JSON Export</t>
+          <t>Test Scenario #23 — Diploma PDF Printing &amp; JSON Export</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
@@ -10581,7 +10581,7 @@
         </is>
       </c>
       <c r="G248" t="n">
-        <v>0.99</v>
+        <v>1.14</v>
       </c>
       <c r="H248" t="inlineStr">
         <is>
@@ -10593,7 +10593,7 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>TC_WEB_EXPORT_023</t>
+          <t>TC_WEB_EXPORT_024</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -10603,17 +10603,17 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Verify that clicking 'Download PDF / Print' on CertificateCard invokes window.print() with print diploma styling.</t>
+          <t>Verify that clicking 'Export JSON' downloads the certificate data in JSON file format.</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>Test Scenario #23 — Diploma PDF Printing &amp; JSON Export</t>
+          <t>Test Scenario #24 — Diploma PDF Printing &amp; JSON Export</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
@@ -10622,7 +10622,7 @@
         </is>
       </c>
       <c r="G249" t="n">
-        <v>1.1</v>
+        <v>0.91</v>
       </c>
       <c r="H249" t="inlineStr">
         <is>
@@ -10634,7 +10634,7 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>TC_WEB_EXPORT_024</t>
+          <t>TC_WEB_EXPORT_025</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -10644,17 +10644,17 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Verify that clicking 'Export JSON' downloads the certificate data in JSON file format.</t>
+          <t>Verify that clicking 'Download PDF / Print' on CertificateCard invokes window.print() with print diploma styling.</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>Test Scenario #24 — Diploma PDF Printing &amp; JSON Export</t>
+          <t>Test Scenario #25 — Diploma PDF Printing &amp; JSON Export</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
@@ -10663,7 +10663,7 @@
         </is>
       </c>
       <c r="G250" t="n">
-        <v>0.64</v>
+        <v>1.06</v>
       </c>
       <c r="H250" t="inlineStr">
         <is>
@@ -10675,27 +10675,27 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>TC_WEB_EXPORT_025</t>
+          <t>TC_WEB_SEC_001</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Diploma PDF Printing &amp; JSON Export</t>
+          <t>Security &amp; Input Validation</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Verify that clicking 'Download PDF / Print' on CertificateCard invokes window.print() with print diploma styling.</t>
+          <t>Verify that input fields sanitize HTML tags and script injections to prevent Cross-Site Scripting (XSS).</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>Test Scenario #25 — Diploma PDF Printing &amp; JSON Export</t>
+          <t>Test Scenario #01 — Security &amp; Input Validation</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
@@ -10704,7 +10704,7 @@
         </is>
       </c>
       <c r="G251" t="n">
-        <v>0.58</v>
+        <v>0.5</v>
       </c>
       <c r="H251" t="inlineStr">
         <is>
@@ -10716,7 +10716,7 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>TC_WEB_SEC_001</t>
+          <t>TC_WEB_SEC_002</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -10726,17 +10726,17 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Verify that input fields sanitize HTML tags and script injections to prevent Cross-Site Scripting (XSS).</t>
+          <t>Verify that JWT token stored in localStorage is encrypted and validated before granting privileged access.</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>Test Scenario #01 — Security &amp; Input Validation</t>
+          <t>Test Scenario #02 — Security &amp; Input Validation</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
@@ -10745,7 +10745,7 @@
         </is>
       </c>
       <c r="G252" t="n">
-        <v>0.63</v>
+        <v>0.99</v>
       </c>
       <c r="H252" t="inlineStr">
         <is>
@@ -10757,7 +10757,7 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>TC_WEB_SEC_002</t>
+          <t>TC_WEB_SEC_003</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -10767,17 +10767,17 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Verify that JWT token stored in localStorage is encrypted and validated before granting privileged access.</t>
+          <t>Verify that input fields sanitize HTML tags and script injections to prevent Cross-Site Scripting (XSS).</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>Test Scenario #02 — Security &amp; Input Validation</t>
+          <t>Test Scenario #03 — Security &amp; Input Validation</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
@@ -10786,7 +10786,7 @@
         </is>
       </c>
       <c r="G253" t="n">
-        <v>0.8100000000000001</v>
+        <v>1.05</v>
       </c>
       <c r="H253" t="inlineStr">
         <is>
@@ -10798,7 +10798,7 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>TC_WEB_SEC_003</t>
+          <t>TC_WEB_SEC_004</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -10808,12 +10808,12 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Verify that input fields sanitize HTML tags and script injections to prevent Cross-Site Scripting (XSS).</t>
+          <t>Verify that JWT token stored in localStorage is encrypted and validated before granting privileged access.</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>Test Scenario #03 — Security &amp; Input Validation</t>
+          <t>Test Scenario #04 — Security &amp; Input Validation</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
@@ -10827,7 +10827,7 @@
         </is>
       </c>
       <c r="G254" t="n">
-        <v>1.15</v>
+        <v>0.61</v>
       </c>
       <c r="H254" t="inlineStr">
         <is>
@@ -10839,7 +10839,7 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>TC_WEB_SEC_004</t>
+          <t>TC_WEB_SEC_006</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -10854,12 +10854,12 @@
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>Test Scenario #04 — Security &amp; Input Validation</t>
+          <t>Test Scenario #06 — Security &amp; Input Validation</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
@@ -10868,7 +10868,7 @@
         </is>
       </c>
       <c r="G255" t="n">
-        <v>1.07</v>
+        <v>0.87</v>
       </c>
       <c r="H255" t="inlineStr">
         <is>
@@ -10880,7 +10880,7 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>TC_WEB_SEC_005</t>
+          <t>TC_WEB_SEC_007</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -10895,12 +10895,12 @@
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>Test Scenario #05 — Security &amp; Input Validation</t>
+          <t>Test Scenario #07 — Security &amp; Input Validation</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
@@ -10909,7 +10909,7 @@
         </is>
       </c>
       <c r="G256" t="n">
-        <v>0.79</v>
+        <v>1</v>
       </c>
       <c r="H256" t="inlineStr">
         <is>
@@ -10921,7 +10921,7 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>TC_WEB_SEC_006</t>
+          <t>TC_WEB_SEC_008</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -10936,12 +10936,12 @@
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>Test Scenario #06 — Security &amp; Input Validation</t>
+          <t>Test Scenario #08 — Security &amp; Input Validation</t>
         </is>
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
@@ -10950,7 +10950,7 @@
         </is>
       </c>
       <c r="G257" t="n">
-        <v>0.77</v>
+        <v>0.73</v>
       </c>
       <c r="H257" t="inlineStr">
         <is>
@@ -10962,7 +10962,7 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>TC_WEB_SEC_007</t>
+          <t>TC_WEB_SEC_009</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -10977,12 +10977,12 @@
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>Test Scenario #07 — Security &amp; Input Validation</t>
+          <t>Test Scenario #09 — Security &amp; Input Validation</t>
         </is>
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
@@ -10991,7 +10991,7 @@
         </is>
       </c>
       <c r="G258" t="n">
-        <v>0.65</v>
+        <v>0.45</v>
       </c>
       <c r="H258" t="inlineStr">
         <is>
@@ -11003,7 +11003,7 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>TC_WEB_SEC_008</t>
+          <t>TC_WEB_SEC_010</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -11018,12 +11018,12 @@
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>Test Scenario #08 — Security &amp; Input Validation</t>
+          <t>Test Scenario #10 — Security &amp; Input Validation</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
@@ -11032,7 +11032,7 @@
         </is>
       </c>
       <c r="G259" t="n">
-        <v>1.03</v>
+        <v>0.5</v>
       </c>
       <c r="H259" t="inlineStr">
         <is>
@@ -11044,7 +11044,7 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>TC_WEB_SEC_009</t>
+          <t>TC_WEB_SEC_011</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -11059,12 +11059,12 @@
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>Test Scenario #09 — Security &amp; Input Validation</t>
+          <t>Test Scenario #11 — Security &amp; Input Validation</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
@@ -11073,7 +11073,7 @@
         </is>
       </c>
       <c r="G260" t="n">
-        <v>0.64</v>
+        <v>0.95</v>
       </c>
       <c r="H260" t="inlineStr">
         <is>
@@ -11085,7 +11085,7 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>TC_WEB_SEC_010</t>
+          <t>TC_WEB_SEC_012</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -11100,12 +11100,12 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>Test Scenario #10 — Security &amp; Input Validation</t>
+          <t>Test Scenario #12 — Security &amp; Input Validation</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
@@ -11114,7 +11114,7 @@
         </is>
       </c>
       <c r="G261" t="n">
-        <v>0.89</v>
+        <v>0.49</v>
       </c>
       <c r="H261" t="inlineStr">
         <is>
@@ -11126,7 +11126,7 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>TC_WEB_SEC_011</t>
+          <t>TC_WEB_SEC_013</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -11141,7 +11141,7 @@
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>Test Scenario #11 — Security &amp; Input Validation</t>
+          <t>Test Scenario #13 — Security &amp; Input Validation</t>
         </is>
       </c>
       <c r="E262" t="inlineStr">
@@ -11155,7 +11155,7 @@
         </is>
       </c>
       <c r="G262" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.6</v>
       </c>
       <c r="H262" t="inlineStr">
         <is>
@@ -11167,7 +11167,7 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>TC_WEB_SEC_012</t>
+          <t>TC_WEB_SEC_014</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -11182,12 +11182,12 @@
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>Test Scenario #12 — Security &amp; Input Validation</t>
+          <t>Test Scenario #14 — Security &amp; Input Validation</t>
         </is>
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
@@ -11196,7 +11196,7 @@
         </is>
       </c>
       <c r="G263" t="n">
-        <v>0.72</v>
+        <v>0.9</v>
       </c>
       <c r="H263" t="inlineStr">
         <is>
@@ -11208,7 +11208,7 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>TC_WEB_SEC_013</t>
+          <t>TC_WEB_SEC_015</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -11223,12 +11223,12 @@
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>Test Scenario #13 — Security &amp; Input Validation</t>
+          <t>Test Scenario #15 — Security &amp; Input Validation</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
@@ -11237,7 +11237,7 @@
         </is>
       </c>
       <c r="G264" t="n">
-        <v>0.77</v>
+        <v>0.55</v>
       </c>
       <c r="H264" t="inlineStr">
         <is>
@@ -11249,7 +11249,7 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>TC_WEB_SEC_014</t>
+          <t>TC_WEB_SEC_016</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -11264,12 +11264,12 @@
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>Test Scenario #14 — Security &amp; Input Validation</t>
+          <t>Test Scenario #16 — Security &amp; Input Validation</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
@@ -11278,7 +11278,7 @@
         </is>
       </c>
       <c r="G265" t="n">
-        <v>0.75</v>
+        <v>0.63</v>
       </c>
       <c r="H265" t="inlineStr">
         <is>
@@ -11290,7 +11290,7 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>TC_WEB_SEC_015</t>
+          <t>TC_WEB_SEC_017</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -11305,12 +11305,12 @@
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>Test Scenario #15 — Security &amp; Input Validation</t>
+          <t>Test Scenario #17 — Security &amp; Input Validation</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
@@ -11319,7 +11319,7 @@
         </is>
       </c>
       <c r="G266" t="n">
-        <v>0.87</v>
+        <v>0.58</v>
       </c>
       <c r="H266" t="inlineStr">
         <is>
@@ -11331,7 +11331,7 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>TC_WEB_SEC_016</t>
+          <t>TC_WEB_SEC_018</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -11346,7 +11346,7 @@
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>Test Scenario #16 — Security &amp; Input Validation</t>
+          <t>Test Scenario #18 — Security &amp; Input Validation</t>
         </is>
       </c>
       <c r="E267" t="inlineStr">
@@ -11360,7 +11360,7 @@
         </is>
       </c>
       <c r="G267" t="n">
-        <v>0.98</v>
+        <v>0.76</v>
       </c>
       <c r="H267" t="inlineStr">
         <is>
@@ -11372,7 +11372,7 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>TC_WEB_SEC_017</t>
+          <t>TC_WEB_SEC_019</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
@@ -11387,12 +11387,12 @@
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>Test Scenario #17 — Security &amp; Input Validation</t>
+          <t>Test Scenario #19 — Security &amp; Input Validation</t>
         </is>
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
@@ -11401,7 +11401,7 @@
         </is>
       </c>
       <c r="G268" t="n">
-        <v>0.96</v>
+        <v>0.57</v>
       </c>
       <c r="H268" t="inlineStr">
         <is>
@@ -11413,7 +11413,7 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>TC_WEB_SEC_018</t>
+          <t>TC_WEB_SEC_020</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
@@ -11428,12 +11428,12 @@
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>Test Scenario #18 — Security &amp; Input Validation</t>
+          <t>Test Scenario #20 — Security &amp; Input Validation</t>
         </is>
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
@@ -11442,7 +11442,7 @@
         </is>
       </c>
       <c r="G269" t="n">
-        <v>1.08</v>
+        <v>0.96</v>
       </c>
       <c r="H269" t="inlineStr">
         <is>
@@ -11454,7 +11454,7 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>TC_WEB_SEC_019</t>
+          <t>TC_WEB_SEC_021</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
@@ -11469,12 +11469,12 @@
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>Test Scenario #19 — Security &amp; Input Validation</t>
+          <t>Test Scenario #21 — Security &amp; Input Validation</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
@@ -11483,7 +11483,7 @@
         </is>
       </c>
       <c r="G270" t="n">
-        <v>0.55</v>
+        <v>0.46</v>
       </c>
       <c r="H270" t="inlineStr">
         <is>
@@ -11495,7 +11495,7 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>TC_WEB_SEC_020</t>
+          <t>TC_WEB_SEC_022</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
@@ -11510,12 +11510,12 @@
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>Test Scenario #20 — Security &amp; Input Validation</t>
+          <t>Test Scenario #22 — Security &amp; Input Validation</t>
         </is>
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
@@ -11524,7 +11524,7 @@
         </is>
       </c>
       <c r="G271" t="n">
-        <v>0.85</v>
+        <v>1.01</v>
       </c>
       <c r="H271" t="inlineStr">
         <is>
@@ -11536,7 +11536,7 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>TC_WEB_SEC_021</t>
+          <t>TC_WEB_SEC_023</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
@@ -11551,12 +11551,12 @@
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>Test Scenario #21 — Security &amp; Input Validation</t>
+          <t>Test Scenario #23 — Security &amp; Input Validation</t>
         </is>
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
@@ -11565,7 +11565,7 @@
         </is>
       </c>
       <c r="G272" t="n">
-        <v>0.99</v>
+        <v>1.13</v>
       </c>
       <c r="H272" t="inlineStr">
         <is>
@@ -11577,7 +11577,7 @@
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>TC_WEB_SEC_022</t>
+          <t>TC_WEB_SEC_024</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
@@ -11592,7 +11592,7 @@
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>Test Scenario #22 — Security &amp; Input Validation</t>
+          <t>Test Scenario #24 — Security &amp; Input Validation</t>
         </is>
       </c>
       <c r="E273" t="inlineStr">
@@ -11606,7 +11606,7 @@
         </is>
       </c>
       <c r="G273" t="n">
-        <v>0.7</v>
+        <v>0.91</v>
       </c>
       <c r="H273" t="inlineStr">
         <is>
@@ -11618,7 +11618,7 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>TC_WEB_SEC_023</t>
+          <t>TC_WEB_SEC_025</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
@@ -11633,12 +11633,12 @@
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>Test Scenario #23 — Security &amp; Input Validation</t>
+          <t>Test Scenario #25 — Security &amp; Input Validation</t>
         </is>
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
@@ -11647,7 +11647,7 @@
         </is>
       </c>
       <c r="G274" t="n">
-        <v>1.11</v>
+        <v>0.92</v>
       </c>
       <c r="H274" t="inlineStr">
         <is>
@@ -11659,27 +11659,27 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>TC_WEB_SEC_024</t>
+          <t>TC_WEB_PERF_001</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>Security &amp; Input Validation</t>
+          <t>Performance Smoke &amp; Error Handling</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Verify that JWT token stored in localStorage is encrypted and validated before granting privileged access.</t>
+          <t>Verify that all static pages (https://kaushikreddym5014sse-art.github.io/App-PDD/, /login/, /dashboard/, /issuer/, /verify/, /profile/) load within 200ms threshold.</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>Test Scenario #24 — Security &amp; Input Validation</t>
+          <t>Test Scenario #01 — Performance Smoke &amp; Error Handling</t>
         </is>
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
@@ -11688,7 +11688,7 @@
         </is>
       </c>
       <c r="G275" t="n">
-        <v>1.11</v>
+        <v>0.73</v>
       </c>
       <c r="H275" t="inlineStr">
         <is>
@@ -11700,27 +11700,27 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>TC_WEB_SEC_025</t>
+          <t>TC_WEB_PERF_002</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>Security &amp; Input Validation</t>
+          <t>Performance Smoke &amp; Error Handling</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Verify that input fields sanitize HTML tags and script injections to prevent Cross-Site Scripting (XSS).</t>
+          <t>Verify that network disconnects trigger graceful offline local storage fallback without throwing unhandled JS exceptions.</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>Test Scenario #25 — Security &amp; Input Validation</t>
+          <t>Test Scenario #02 — Performance Smoke &amp; Error Handling</t>
         </is>
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
@@ -11729,7 +11729,7 @@
         </is>
       </c>
       <c r="G276" t="n">
-        <v>0.61</v>
+        <v>0.67</v>
       </c>
       <c r="H276" t="inlineStr">
         <is>
@@ -11741,7 +11741,7 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>TC_WEB_PERF_001</t>
+          <t>TC_WEB_PERF_003</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
@@ -11756,7 +11756,7 @@
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>Test Scenario #01 — Performance Smoke &amp; Error Handling</t>
+          <t>Test Scenario #03 — Performance Smoke &amp; Error Handling</t>
         </is>
       </c>
       <c r="E277" t="inlineStr">
@@ -11770,7 +11770,7 @@
         </is>
       </c>
       <c r="G277" t="n">
-        <v>1.11</v>
+        <v>0.58</v>
       </c>
       <c r="H277" t="inlineStr">
         <is>
@@ -11782,7 +11782,7 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>TC_WEB_PERF_002</t>
+          <t>TC_WEB_PERF_004</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
@@ -11797,7 +11797,7 @@
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>Test Scenario #02 — Performance Smoke &amp; Error Handling</t>
+          <t>Test Scenario #04 — Performance Smoke &amp; Error Handling</t>
         </is>
       </c>
       <c r="E278" t="inlineStr">
@@ -11811,7 +11811,7 @@
         </is>
       </c>
       <c r="G278" t="n">
-        <v>0.86</v>
+        <v>1.07</v>
       </c>
       <c r="H278" t="inlineStr">
         <is>
@@ -11823,7 +11823,7 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>TC_WEB_PERF_003</t>
+          <t>TC_WEB_PERF_005</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
@@ -11838,12 +11838,12 @@
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>Test Scenario #03 — Performance Smoke &amp; Error Handling</t>
+          <t>Test Scenario #05 — Performance Smoke &amp; Error Handling</t>
         </is>
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
@@ -11852,7 +11852,7 @@
         </is>
       </c>
       <c r="G279" t="n">
-        <v>0.59</v>
+        <v>0.78</v>
       </c>
       <c r="H279" t="inlineStr">
         <is>
@@ -11864,7 +11864,7 @@
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>TC_WEB_PERF_004</t>
+          <t>TC_WEB_PERF_006</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
@@ -11879,12 +11879,12 @@
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>Test Scenario #04 — Performance Smoke &amp; Error Handling</t>
+          <t>Test Scenario #06 — Performance Smoke &amp; Error Handling</t>
         </is>
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
@@ -11893,7 +11893,7 @@
         </is>
       </c>
       <c r="G280" t="n">
-        <v>0.68</v>
+        <v>0.72</v>
       </c>
       <c r="H280" t="inlineStr">
         <is>
@@ -11905,7 +11905,7 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>TC_WEB_PERF_005</t>
+          <t>TC_WEB_PERF_007</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
@@ -11920,12 +11920,12 @@
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>Test Scenario #05 — Performance Smoke &amp; Error Handling</t>
+          <t>Test Scenario #07 — Performance Smoke &amp; Error Handling</t>
         </is>
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
@@ -11934,7 +11934,7 @@
         </is>
       </c>
       <c r="G281" t="n">
-        <v>0.8</v>
+        <v>0.99</v>
       </c>
       <c r="H281" t="inlineStr">
         <is>
@@ -11946,7 +11946,7 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>TC_WEB_PERF_006</t>
+          <t>TC_WEB_PERF_008</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
@@ -11961,7 +11961,7 @@
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>Test Scenario #06 — Performance Smoke &amp; Error Handling</t>
+          <t>Test Scenario #08 — Performance Smoke &amp; Error Handling</t>
         </is>
       </c>
       <c r="E282" t="inlineStr">
@@ -11975,7 +11975,7 @@
         </is>
       </c>
       <c r="G282" t="n">
-        <v>0.85</v>
+        <v>0.65</v>
       </c>
       <c r="H282" t="inlineStr">
         <is>
@@ -11987,7 +11987,7 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>TC_WEB_PERF_007</t>
+          <t>TC_WEB_PERF_009</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
@@ -12002,12 +12002,12 @@
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>Test Scenario #07 — Performance Smoke &amp; Error Handling</t>
+          <t>Test Scenario #09 — Performance Smoke &amp; Error Handling</t>
         </is>
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
@@ -12016,7 +12016,7 @@
         </is>
       </c>
       <c r="G283" t="n">
-        <v>0.73</v>
+        <v>0.52</v>
       </c>
       <c r="H283" t="inlineStr">
         <is>
@@ -12028,7 +12028,7 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>TC_WEB_PERF_008</t>
+          <t>TC_WEB_PERF_010</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
@@ -12043,12 +12043,12 @@
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>Test Scenario #08 — Performance Smoke &amp; Error Handling</t>
+          <t>Test Scenario #10 — Performance Smoke &amp; Error Handling</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
@@ -12057,7 +12057,7 @@
         </is>
       </c>
       <c r="G284" t="n">
-        <v>0.75</v>
+        <v>0.47</v>
       </c>
       <c r="H284" t="inlineStr">
         <is>
@@ -12069,7 +12069,7 @@
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>TC_WEB_PERF_009</t>
+          <t>TC_WEB_PERF_011</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
@@ -12084,7 +12084,7 @@
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>Test Scenario #09 — Performance Smoke &amp; Error Handling</t>
+          <t>Test Scenario #11 — Performance Smoke &amp; Error Handling</t>
         </is>
       </c>
       <c r="E285" t="inlineStr">
@@ -12098,7 +12098,7 @@
         </is>
       </c>
       <c r="G285" t="n">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="H285" t="inlineStr">
         <is>
@@ -12110,7 +12110,7 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>TC_WEB_PERF_010</t>
+          <t>TC_WEB_PERF_012</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
@@ -12125,12 +12125,12 @@
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>Test Scenario #10 — Performance Smoke &amp; Error Handling</t>
+          <t>Test Scenario #12 — Performance Smoke &amp; Error Handling</t>
         </is>
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
@@ -12139,7 +12139,7 @@
         </is>
       </c>
       <c r="G286" t="n">
-        <v>0.87</v>
+        <v>0.67</v>
       </c>
       <c r="H286" t="inlineStr">
         <is>
@@ -12151,7 +12151,7 @@
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>TC_WEB_PERF_011</t>
+          <t>TC_WEB_PERF_013</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
@@ -12166,7 +12166,7 @@
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>Test Scenario #11 — Performance Smoke &amp; Error Handling</t>
+          <t>Test Scenario #13 — Performance Smoke &amp; Error Handling</t>
         </is>
       </c>
       <c r="E287" t="inlineStr">
@@ -12180,7 +12180,7 @@
         </is>
       </c>
       <c r="G287" t="n">
-        <v>0.84</v>
+        <v>0.79</v>
       </c>
       <c r="H287" t="inlineStr">
         <is>
@@ -12192,7 +12192,7 @@
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>TC_WEB_PERF_012</t>
+          <t>TC_WEB_PERF_014</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
@@ -12207,7 +12207,7 @@
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>Test Scenario #12 — Performance Smoke &amp; Error Handling</t>
+          <t>Test Scenario #14 — Performance Smoke &amp; Error Handling</t>
         </is>
       </c>
       <c r="E288" t="inlineStr">
@@ -12221,7 +12221,7 @@
         </is>
       </c>
       <c r="G288" t="n">
-        <v>0.49</v>
+        <v>0.54</v>
       </c>
       <c r="H288" t="inlineStr">
         <is>
@@ -12233,7 +12233,7 @@
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>TC_WEB_PERF_013</t>
+          <t>TC_WEB_PERF_015</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
@@ -12248,12 +12248,12 @@
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>Test Scenario #13 — Performance Smoke &amp; Error Handling</t>
+          <t>Test Scenario #15 — Performance Smoke &amp; Error Handling</t>
         </is>
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
@@ -12262,7 +12262,7 @@
         </is>
       </c>
       <c r="G289" t="n">
-        <v>0.86</v>
+        <v>1.12</v>
       </c>
       <c r="H289" t="inlineStr">
         <is>
@@ -12274,7 +12274,7 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>TC_WEB_PERF_014</t>
+          <t>TC_WEB_PERF_016</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
@@ -12289,7 +12289,7 @@
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>Test Scenario #14 — Performance Smoke &amp; Error Handling</t>
+          <t>Test Scenario #16 — Performance Smoke &amp; Error Handling</t>
         </is>
       </c>
       <c r="E290" t="inlineStr">
@@ -12303,7 +12303,7 @@
         </is>
       </c>
       <c r="G290" t="n">
-        <v>1.09</v>
+        <v>0.95</v>
       </c>
       <c r="H290" t="inlineStr">
         <is>
@@ -12315,7 +12315,7 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>TC_WEB_PERF_015</t>
+          <t>TC_WEB_PERF_017</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
@@ -12330,12 +12330,12 @@
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>Test Scenario #15 — Performance Smoke &amp; Error Handling</t>
+          <t>Test Scenario #17 — Performance Smoke &amp; Error Handling</t>
         </is>
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
@@ -12344,7 +12344,7 @@
         </is>
       </c>
       <c r="G291" t="n">
-        <v>0.96</v>
+        <v>0.48</v>
       </c>
       <c r="H291" t="inlineStr">
         <is>
@@ -12356,7 +12356,7 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>TC_WEB_PERF_016</t>
+          <t>TC_WEB_PERF_018</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
@@ -12371,7 +12371,7 @@
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>Test Scenario #16 — Performance Smoke &amp; Error Handling</t>
+          <t>Test Scenario #18 — Performance Smoke &amp; Error Handling</t>
         </is>
       </c>
       <c r="E292" t="inlineStr">
@@ -12385,7 +12385,7 @@
         </is>
       </c>
       <c r="G292" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.98</v>
       </c>
       <c r="H292" t="inlineStr">
         <is>
@@ -12397,7 +12397,7 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>TC_WEB_PERF_017</t>
+          <t>TC_WEB_PERF_019</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
@@ -12412,12 +12412,12 @@
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>Test Scenario #17 — Performance Smoke &amp; Error Handling</t>
+          <t>Test Scenario #19 — Performance Smoke &amp; Error Handling</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
@@ -12426,7 +12426,7 @@
         </is>
       </c>
       <c r="G293" t="n">
-        <v>0.96</v>
+        <v>0.48</v>
       </c>
       <c r="H293" t="inlineStr">
         <is>
@@ -12438,7 +12438,7 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>TC_WEB_PERF_018</t>
+          <t>TC_WEB_PERF_020</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
@@ -12453,7 +12453,7 @@
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>Test Scenario #18 — Performance Smoke &amp; Error Handling</t>
+          <t>Test Scenario #20 — Performance Smoke &amp; Error Handling</t>
         </is>
       </c>
       <c r="E294" t="inlineStr">
@@ -12467,7 +12467,7 @@
         </is>
       </c>
       <c r="G294" t="n">
-        <v>0.92</v>
+        <v>0.44</v>
       </c>
       <c r="H294" t="inlineStr">
         <is>
@@ -12479,7 +12479,7 @@
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>TC_WEB_PERF_019</t>
+          <t>TC_WEB_PERF_021</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
@@ -12494,7 +12494,7 @@
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>Test Scenario #19 — Performance Smoke &amp; Error Handling</t>
+          <t>Test Scenario #21 — Performance Smoke &amp; Error Handling</t>
         </is>
       </c>
       <c r="E295" t="inlineStr">
@@ -12508,7 +12508,7 @@
         </is>
       </c>
       <c r="G295" t="n">
-        <v>0.92</v>
+        <v>0.62</v>
       </c>
       <c r="H295" t="inlineStr">
         <is>
@@ -12520,7 +12520,7 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>TC_WEB_PERF_020</t>
+          <t>TC_WEB_PERF_022</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
@@ -12535,12 +12535,12 @@
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>Test Scenario #20 — Performance Smoke &amp; Error Handling</t>
+          <t>Test Scenario #22 — Performance Smoke &amp; Error Handling</t>
         </is>
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
@@ -12549,7 +12549,7 @@
         </is>
       </c>
       <c r="G296" t="n">
-        <v>1.13</v>
+        <v>0.45</v>
       </c>
       <c r="H296" t="inlineStr">
         <is>
@@ -12561,7 +12561,7 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>TC_WEB_PERF_021</t>
+          <t>TC_WEB_PERF_023</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
@@ -12576,12 +12576,12 @@
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>Test Scenario #21 — Performance Smoke &amp; Error Handling</t>
+          <t>Test Scenario #23 — Performance Smoke &amp; Error Handling</t>
         </is>
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
@@ -12590,7 +12590,7 @@
         </is>
       </c>
       <c r="G297" t="n">
-        <v>1.08</v>
+        <v>0.7</v>
       </c>
       <c r="H297" t="inlineStr">
         <is>
@@ -12602,7 +12602,7 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>TC_WEB_PERF_022</t>
+          <t>TC_WEB_PERF_024</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
@@ -12617,12 +12617,12 @@
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>Test Scenario #22 — Performance Smoke &amp; Error Handling</t>
+          <t>Test Scenario #24 — Performance Smoke &amp; Error Handling</t>
         </is>
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
@@ -12631,7 +12631,7 @@
         </is>
       </c>
       <c r="G298" t="n">
-        <v>1.03</v>
+        <v>0.59</v>
       </c>
       <c r="H298" t="inlineStr">
         <is>
@@ -12643,7 +12643,7 @@
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>TC_WEB_PERF_023</t>
+          <t>TC_WEB_PERF_025</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
@@ -12658,7 +12658,7 @@
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>Test Scenario #23 — Performance Smoke &amp; Error Handling</t>
+          <t>Test Scenario #25 — Performance Smoke &amp; Error Handling</t>
         </is>
       </c>
       <c r="E299" t="inlineStr">
@@ -12672,7 +12672,7 @@
         </is>
       </c>
       <c r="G299" t="n">
-        <v>1.13</v>
+        <v>0.68</v>
       </c>
       <c r="H299" t="inlineStr">
         <is>
@@ -12680,88 +12680,6 @@
         </is>
       </c>
       <c r="I299" t="inlineStr"/>
-    </row>
-    <row r="300">
-      <c r="A300" t="inlineStr">
-        <is>
-          <t>TC_WEB_PERF_024</t>
-        </is>
-      </c>
-      <c r="B300" t="inlineStr">
-        <is>
-          <t>Performance Smoke &amp; Error Handling</t>
-        </is>
-      </c>
-      <c r="C300" t="inlineStr">
-        <is>
-          <t>Verify that network disconnects trigger graceful offline local storage fallback without throwing unhandled JS exceptions.</t>
-        </is>
-      </c>
-      <c r="D300" t="inlineStr">
-        <is>
-          <t>Test Scenario #24 — Performance Smoke &amp; Error Handling</t>
-        </is>
-      </c>
-      <c r="E300" t="inlineStr">
-        <is>
-          <t>P2 - Medium</t>
-        </is>
-      </c>
-      <c r="F300" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G300" t="n">
-        <v>0.96</v>
-      </c>
-      <c r="H300" t="inlineStr">
-        <is>
-          <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
-        </is>
-      </c>
-      <c r="I300" t="inlineStr"/>
-    </row>
-    <row r="301">
-      <c r="A301" t="inlineStr">
-        <is>
-          <t>TC_WEB_PERF_025</t>
-        </is>
-      </c>
-      <c r="B301" t="inlineStr">
-        <is>
-          <t>Performance Smoke &amp; Error Handling</t>
-        </is>
-      </c>
-      <c r="C301" t="inlineStr">
-        <is>
-          <t>Verify that all static pages (https://kaushikreddym5014sse-art.github.io/App-PDD/, /login/, /dashboard/, /issuer/, /verify/, /profile/) load within 200ms threshold.</t>
-        </is>
-      </c>
-      <c r="D301" t="inlineStr">
-        <is>
-          <t>Test Scenario #25 — Performance Smoke &amp; Error Handling</t>
-        </is>
-      </c>
-      <c r="E301" t="inlineStr">
-        <is>
-          <t>P2 - Medium</t>
-        </is>
-      </c>
-      <c r="F301" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G301" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="H301" t="inlineStr">
-        <is>
-          <t>https://kaushikreddym5014sse-art.github.io/App-PDD/</t>
-        </is>
-      </c>
-      <c r="I301" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
